--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable" displayName="AveragesTable" ref="A1:EC19" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_France_Lig" displayName="AveragesTable_France_Lig" ref="A1:EC19" headerRowCount="1">
   <autoFilter ref="A1:EC19"/>
   <tableColumns count="133">
     <tableColumn id="1" name="team_name"/>

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -5232,13 +5232,13 @@
         <v>4.91</v>
       </c>
       <c r="BZ11" t="n">
-        <v>5.59</v>
+        <v>5.86</v>
       </c>
       <c r="CA11" t="n">
         <v>3.89</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.07</v>
+        <v>4.12</v>
       </c>
       <c r="CC11" t="n">
         <v>4.85</v>
@@ -5310,7 +5310,7 @@
         <v>1.9</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DA11" t="n">
         <v>1.91</v>
@@ -5322,7 +5322,7 @@
         <v>1.9</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="DE11" t="n">
         <v>0.25</v>
@@ -5407,94 +5407,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
         <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F12" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H12" t="n">
+        <v>66.14</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="M12" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="N12" t="n">
         <v>1</v>
       </c>
-      <c r="G12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H12" t="n">
-        <v>77.17</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="K12" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="M12" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.83</v>
-      </c>
       <c r="O12" t="n">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>12.17</v>
+        <v>11.71</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.67</v>
+        <v>12.29</v>
       </c>
       <c r="R12" t="n">
-        <v>7.33</v>
+        <v>6.43</v>
       </c>
       <c r="S12" t="n">
-        <v>0.83</v>
+        <v>1.43</v>
       </c>
       <c r="T12" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="U12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>46.33</v>
+        <v>47.29</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>12</v>
+        <v>12.43</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.17</v>
+        <v>7.29</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.83</v>
+        <v>5.14</v>
       </c>
       <c r="AC12" t="n">
-        <v>14.83</v>
+        <v>14</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5578,70 +5578,70 @@
         <v>2.67</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="BH12" t="n">
-        <v>11.08</v>
+        <v>11.31</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="BL12" t="n">
         <v>1.08</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.83</v>
+        <v>4.46</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6</v>
+        <v>5.69</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT12" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BU12" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BV12" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="BX12" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.13</v>
+        <v>4.09</v>
       </c>
       <c r="CC12" t="n">
         <v>3.58</v>
@@ -5653,31 +5653,31 @@
         <v>1.31</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CK12" t="n">
         <v>1.46</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CO12" t="n">
         <v>1.22</v>
@@ -5701,10 +5701,10 @@
         <v>1.54</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CX12" t="n">
         <v>1.54</v>
@@ -5713,10 +5713,10 @@
         <v>1.84</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="DA12" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DB12" t="n">
         <v>1.3</v>
@@ -5731,76 +5731,76 @@
         <v>0.16</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.34</v>
+        <v>2.23</v>
       </c>
       <c r="DH12" t="n">
-        <v>78.58</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="DI12" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.58</v>
+        <v>4.85</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="DM12" t="n">
-        <v>36.92</v>
+        <v>34.08</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.5</v>
+        <v>1.92</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.92</v>
+        <v>12.61</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.67</v>
+        <v>12.47</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.75</v>
+        <v>7.23</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>45.75</v>
+        <v>46.31</v>
       </c>
       <c r="DW12" t="n">
         <v>0.08</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.08</v>
+        <v>11.39</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.17</v>
+        <v>7.23</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.92</v>
+        <v>4.15</v>
       </c>
       <c r="EA12" t="n">
-        <v>15.75</v>
+        <v>15.23</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="13">
@@ -6213,13 +6213,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
         <v>0.17</v>
@@ -6306,49 +6306,49 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.83</v>
+        <v>3.43</v>
       </c>
       <c r="AI14" t="n">
-        <v>113</v>
+        <v>96.86</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.83</v>
+        <v>5.86</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AN14" t="n">
-        <v>49.17</v>
+        <v>42.14</v>
       </c>
       <c r="AO14" t="n">
         <v>2</v>
       </c>
       <c r="AP14" t="n">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11.17</v>
+        <v>11</v>
       </c>
       <c r="AR14" t="n">
-        <v>11.5</v>
+        <v>11.14</v>
       </c>
       <c r="AS14" t="n">
-        <v>7</v>
+        <v>7.14</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.17</v>
+        <v>1.71</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6360,82 +6360,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>59.33</v>
+        <v>57.57</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BA14" t="n">
-        <v>14.83</v>
+        <v>14.57</v>
       </c>
       <c r="BB14" t="n">
-        <v>10.33</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.5</v>
+        <v>5.43</v>
       </c>
       <c r="BD14" t="n">
-        <v>15.83</v>
+        <v>13.86</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.58</v>
+        <v>9</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="BN14" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.33</v>
+        <v>4</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT14" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BU14" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BV14" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BW14" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BX14" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BY14" t="n">
         <v>1.82</v>
@@ -6444,43 +6444,43 @@
         <v>1.82</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.38</v>
+        <v>4.31</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="CC14" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CE14" t="n">
         <v>1.29</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CH14" t="n">
         <v>1.53</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CN14" t="n">
         <v>1.72</v>
@@ -6489,10 +6489,10 @@
         <v>1.2</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="CR14" t="n">
         <v>1.36</v>
@@ -6507,22 +6507,22 @@
         <v>1.53</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DB14" t="n">
         <v>1.28</v>
@@ -6531,82 +6531,82 @@
         <v>1.71</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="DE14" t="n">
         <v>0.08</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="DH14" t="n">
-        <v>115.34</v>
+        <v>106.46</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.33</v>
+        <v>5.38</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="DM14" t="n">
-        <v>52.58</v>
+        <v>48.54</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.08</v>
+        <v>2.31</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.5</v>
+        <v>12.31</v>
       </c>
       <c r="DQ14" t="n">
-        <v>9.83</v>
+        <v>9.77</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.75</v>
+        <v>5.92</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>59.83</v>
+        <v>58.84</v>
       </c>
       <c r="DW14" t="n">
         <v>0.16</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.33</v>
+        <v>14.23</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.75</v>
+        <v>8.23</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.58</v>
+        <v>6</v>
       </c>
       <c r="EA14" t="n">
-        <v>15.08</v>
+        <v>14.08</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="15">
@@ -7660,7 +7660,7 @@
         <v>2.52</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.63</v>
+        <v>2.77</v>
       </c>
       <c r="CE17" t="n">
         <v>1.34</v>
@@ -7714,31 +7714,31 @@
         <v>1.48</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DB17" t="n">
         <v>1.28</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="DE17" t="n">
         <v>0.17</v>

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
         <v>0.17</v>
@@ -1472,136 +1472,136 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AI2" t="n">
-        <v>62.17</v>
+        <v>63</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>37.29</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BL2" t="n">
         <v>1</v>
       </c>
-      <c r="AL2" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>23.83</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>10.17</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>35.83</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>14.67</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>9.42</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1.08</v>
-      </c>
       <c r="BM2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.67</v>
+        <v>5.69</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BT2" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BU2" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV2" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BY2" t="n">
         <v>3.45</v>
@@ -1610,25 +1610,25 @@
         <v>3.69</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.56</v>
+        <v>4.5</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.93</v>
+        <v>4.84</v>
       </c>
       <c r="CC2" t="n">
-        <v>10.82</v>
+        <v>10.08</v>
       </c>
       <c r="CD2" t="n">
-        <v>11.45</v>
+        <v>10.61</v>
       </c>
       <c r="CE2" t="n">
         <v>1.37</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CH2" t="n">
         <v>1.45</v>
@@ -1637,7 +1637,7 @@
         <v>1.8</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CK2" t="n">
         <v>1.65</v>
@@ -1646,100 +1646,100 @@
         <v>2.14</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CO2" t="n">
         <v>1.3</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="CR2" t="n">
         <v>1.44</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DB2" t="n">
         <v>1.36</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.09</v>
+        <v>3.14</v>
       </c>
       <c r="DE2" t="n">
         <v>0.08</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="DH2" t="n">
-        <v>69.75</v>
+        <v>69.61</v>
       </c>
       <c r="DI2" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="DK2" t="n">
-        <v>4</v>
+        <v>3.77</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM2" t="n">
-        <v>29.33</v>
+        <v>28.69</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.5</v>
+        <v>11.77</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.75</v>
+        <v>11.08</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.75</v>
+        <v>9.16</v>
       </c>
       <c r="DS2" t="n">
         <v>0.08</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>39.08</v>
+        <v>39.62</v>
       </c>
       <c r="DW2" t="n">
         <v>0.08</v>
       </c>
       <c r="DX2" t="n">
-        <v>8.92</v>
+        <v>8.69</v>
       </c>
       <c r="DY2" t="n">
-        <v>5.83</v>
+        <v>5.69</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="EA2" t="n">
-        <v>15.84</v>
+        <v>15.77</v>
       </c>
       <c r="EB2" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
@@ -1794,49 +1794,49 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>93.5</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>5.29</v>
       </c>
       <c r="L3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="M3" t="n">
-        <v>40</v>
+        <v>39.86</v>
       </c>
       <c r="N3" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="O3" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="P3" t="n">
-        <v>14.17</v>
+        <v>13.57</v>
       </c>
       <c r="Q3" t="n">
-        <v>16.5</v>
+        <v>15.57</v>
       </c>
       <c r="R3" t="n">
-        <v>5.5</v>
+        <v>5.71</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="T3" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>45.67</v>
+        <v>43.43</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.5</v>
+        <v>10.71</v>
       </c>
       <c r="AA3" t="n">
-        <v>8</v>
+        <v>7.86</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="AC3" t="n">
-        <v>19.33</v>
+        <v>19.29</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
         <v>0.17</v>
@@ -1953,49 +1953,49 @@
         <v>2.17</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="BH3" t="n">
-        <v>9</v>
+        <v>9.69</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.08</v>
+        <v>5.69</v>
       </c>
       <c r="BR3" t="n">
-        <v>100</v>
+        <v>92.31</v>
       </c>
       <c r="BS3" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BT3" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BU3" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
@@ -2004,19 +2004,19 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.77</v>
+        <v>3.81</v>
       </c>
       <c r="CA3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="CB3" t="n">
         <v>3.94</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>3.97</v>
       </c>
       <c r="CC3" t="n">
         <v>5.28</v>
@@ -2031,13 +2031,13 @@
         <v>2.69</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CH3" t="n">
         <v>1.45</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.81</v>
@@ -2046,10 +2046,10 @@
         <v>1.55</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CN3" t="n">
         <v>1.83</v>
@@ -2058,22 +2058,22 @@
         <v>1.27</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="CR3" t="n">
         <v>1.41</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CT3" t="n">
         <v>3</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV3" t="n">
         <v>2.06</v>
@@ -2085,13 +2085,13 @@
         <v>1.61</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.3</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="DB3" t="n">
         <v>1.33</v>
@@ -2100,49 +2100,49 @@
         <v>1.96</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="DE3" t="n">
         <v>0.08</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="DH3" t="n">
-        <v>91.16</v>
+        <v>89.62</v>
       </c>
       <c r="DI3" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.66</v>
+        <v>4.85</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM3" t="n">
-        <v>38.42</v>
+        <v>38.46</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.84</v>
+        <v>13.54</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.92</v>
+        <v>14.54</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.34</v>
+        <v>6.38</v>
       </c>
       <c r="DS3" t="n">
         <v>0.08</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>45.42</v>
+        <v>44.23</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.5</v>
+        <v>10.61</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.16</v>
+        <v>7.15</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.33</v>
+        <v>3.46</v>
       </c>
       <c r="EA3" t="n">
         <v>19.16</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
         <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="G4" t="n">
-        <v>3.17</v>
+        <v>2.86</v>
       </c>
       <c r="H4" t="n">
-        <v>92.83</v>
+        <v>100.14</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="K4" t="n">
         <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="M4" t="n">
-        <v>40.17</v>
+        <v>41.29</v>
       </c>
       <c r="N4" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="O4" t="n">
-        <v>2.83</v>
+        <v>3.14</v>
       </c>
       <c r="P4" t="n">
-        <v>13.17</v>
+        <v>12.86</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>9.43</v>
       </c>
       <c r="R4" t="n">
-        <v>7.67</v>
+        <v>7</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="T4" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="U4" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="V4" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>42.67</v>
+        <v>44.57</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>15</v>
+        <v>15.71</v>
       </c>
       <c r="AA4" t="n">
-        <v>10.33</v>
+        <v>10.71</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.67</v>
+        <v>5</v>
       </c>
       <c r="AC4" t="n">
-        <v>17.67</v>
+        <v>17.43</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,70 +2356,70 @@
         <v>1.83</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.17</v>
+        <v>10</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BK4" t="n">
         <v>1</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.25</v>
+        <v>5.08</v>
       </c>
       <c r="BR4" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS4" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT4" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BU4" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BV4" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BW4" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BX4" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.35</v>
+        <v>3.12</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.83</v>
+        <v>3.55</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="CC4" t="n">
         <v>3.62</v>
@@ -2431,16 +2431,16 @@
         <v>1.35</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.73</v>
@@ -2449,37 +2449,37 @@
         <v>1.64</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CM4" t="n">
         <v>2.17</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CO4" t="n">
         <v>1.27</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="CU4" t="n">
         <v>1.48</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CW4" t="n">
         <v>1.77</v>
@@ -2491,7 +2491,7 @@
         <v>2.1</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DA4" t="n">
         <v>1.74</v>
@@ -2500,85 +2500,85 @@
         <v>1.33</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="DH4" t="n">
-        <v>89.58</v>
+        <v>93.77</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.58</v>
+        <v>4.69</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="DM4" t="n">
-        <v>39.08</v>
+        <v>39.77</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.5</v>
+        <v>12.38</v>
       </c>
       <c r="DQ4" t="n">
-        <v>10.75</v>
+        <v>10.39</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.58</v>
+        <v>7.23</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>43.67</v>
+        <v>44.62</v>
       </c>
       <c r="DW4" t="n">
         <v>0.08</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.84</v>
+        <v>12.46</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.25</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.58</v>
+        <v>3.85</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.42</v>
+        <v>18.23</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2681,49 +2681,49 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AI5" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>36.14</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AP5" t="n">
         <v>2</v>
       </c>
-      <c r="AL5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AQ5" t="n">
-        <v>14</v>
+        <v>13.14</v>
       </c>
       <c r="AR5" t="n">
-        <v>13.17</v>
+        <v>12.71</v>
       </c>
       <c r="AS5" t="n">
-        <v>8</v>
+        <v>8.57</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>42.17</v>
+        <v>41.14</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.17</v>
+        <v>9.57</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.33</v>
+        <v>6.57</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="BD5" t="n">
-        <v>14.5</v>
+        <v>14.14</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.58</v>
+        <v>8.69</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="BO5" t="n">
         <v>1</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.58</v>
+        <v>3.69</v>
       </c>
       <c r="BQ5" t="n">
         <v>5</v>
       </c>
       <c r="BR5" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS5" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BT5" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BU5" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV5" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX5" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BY5" t="n">
         <v>2.8</v>
@@ -2819,55 +2819,55 @@
         <v>3</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.87</v>
+        <v>4.23</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.94</v>
+        <v>4.2</v>
       </c>
       <c r="CC5" t="n">
-        <v>5.72</v>
+        <v>6.9</v>
       </c>
       <c r="CD5" t="n">
-        <v>6.72</v>
+        <v>7.67</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.96</v>
+        <v>3.06</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="CR5" t="n">
         <v>1.42</v>
@@ -2882,73 +2882,73 @@
         <v>1.44</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DB5" t="n">
         <v>1.34</v>
       </c>
       <c r="DC5" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.26</v>
+        <v>3.19</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="DH5" t="n">
-        <v>89.34</v>
+        <v>88.08</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM5" t="n">
-        <v>45.58</v>
+        <v>44.69</v>
       </c>
       <c r="DN5" t="n">
         <v>1.08</v>
       </c>
       <c r="DO5" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="DP5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="DQ5" t="n">
-        <v>13.08</v>
+        <v>12.84</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.08</v>
+        <v>7.46</v>
       </c>
       <c r="DS5" t="n">
         <v>0.08</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>47.08</v>
+        <v>46.15</v>
       </c>
       <c r="DW5" t="n">
         <v>0.08</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.5</v>
+        <v>11.54</v>
       </c>
       <c r="DY5" t="n">
         <v>8</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.66</v>
+        <v>18.15</v>
       </c>
       <c r="EB5" t="n">
         <v>1.3</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="G6" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="H6" t="n">
-        <v>83.83</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="K6" t="n">
-        <v>8.83</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="M6" t="n">
-        <v>44.67</v>
+        <v>45.43</v>
       </c>
       <c r="N6" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="O6" t="n">
-        <v>3.17</v>
+        <v>2.86</v>
       </c>
       <c r="P6" t="n">
-        <v>11.33</v>
+        <v>11.57</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.17</v>
+        <v>11.43</v>
       </c>
       <c r="R6" t="n">
-        <v>4.83</v>
+        <v>4.86</v>
       </c>
       <c r="S6" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="T6" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="V6" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>48.83</v>
+        <v>49.71</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="Z6" t="n">
-        <v>15.17</v>
+        <v>14.86</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.33</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.83</v>
+        <v>5.71</v>
       </c>
       <c r="AC6" t="n">
-        <v>16.33</v>
+        <v>17</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AF6" t="n">
         <v>0.17</v>
@@ -3162,70 +3162,70 @@
         <v>2.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="BH6" t="n">
-        <v>11.25</v>
+        <v>10.69</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BL6" t="n">
         <v>1</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.33</v>
+        <v>4.08</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.42</v>
+        <v>5.23</v>
       </c>
       <c r="BR6" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS6" t="n">
-        <v>83.33</v>
+        <v>76.92</v>
       </c>
       <c r="BT6" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BU6" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV6" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="CC6" t="n">
         <v>3.16</v>
@@ -3240,22 +3240,22 @@
         <v>2.44</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="CH6" t="n">
         <v>1.53</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.64</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CM6" t="n">
         <v>2.23</v>
@@ -3264,7 +3264,7 @@
         <v>1.78</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="CP6" t="n">
         <v>1.72</v>
@@ -3285,22 +3285,22 @@
         <v>1.59</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DB6" t="n">
         <v>1.25</v>
@@ -3309,76 +3309,76 @@
         <v>1.7</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DH6" t="n">
-        <v>80.08</v>
+        <v>79.08</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.92</v>
+        <v>5.69</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DM6" t="n">
-        <v>39.75</v>
+        <v>40.54</v>
       </c>
       <c r="DN6" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.34</v>
+        <v>2.23</v>
       </c>
       <c r="DP6" t="n">
         <v>13</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.42</v>
+        <v>12.46</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.08</v>
+        <v>6.92</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>45.66</v>
+        <v>46.38</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.17</v>
+        <v>13.16</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.08</v>
+        <v>8.07</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.08</v>
+        <v>5.07</v>
       </c>
       <c r="EA6" t="n">
-        <v>15.08</v>
+        <v>15.54</v>
       </c>
       <c r="EB6" t="n">
         <v>1.48</v>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="G7" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="H7" t="n">
-        <v>105.5</v>
+        <v>106.86</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M7" t="n">
+        <v>56</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="P7" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="R7" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>54.29</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.83</v>
       </c>
-      <c r="K7" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M7" t="n">
-        <v>56.33</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P7" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>13.33</v>
-      </c>
-      <c r="R7" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>54.67</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>11.83</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>15.33</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AE7" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AF7" t="n">
         <v>0.17</v>
@@ -3565,34 +3565,34 @@
         <v>2.83</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.17</v>
+        <v>3.38</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.67</v>
+        <v>10.85</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.17</v>
+        <v>3.38</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="BM7" t="n">
         <v>1</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="BO7" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.75</v>
+        <v>5.92</v>
       </c>
       <c r="BQ7" t="n">
         <v>4.92</v>
@@ -3601,28 +3601,28 @@
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT7" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BU7" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BV7" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BW7" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BX7" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="CA7" t="n">
         <v>3.84</v>
@@ -3643,7 +3643,7 @@
         <v>2.53</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CH7" t="n">
         <v>1.47</v>
@@ -3652,13 +3652,13 @@
         <v>2.08</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CK7" t="n">
         <v>1.54</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CM7" t="n">
         <v>2.3</v>
@@ -3667,13 +3667,13 @@
         <v>1.83</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CR7" t="n">
         <v>1.36</v>
@@ -3688,7 +3688,7 @@
         <v>1.51</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CW7" t="n">
         <v>1.73</v>
@@ -3700,7 +3700,7 @@
         <v>1.98</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="DA7" t="n">
         <v>1.84</v>
@@ -3712,82 +3712,82 @@
         <v>1.77</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="DE7" t="n">
         <v>0.08</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="DH7" t="n">
-        <v>110</v>
+        <v>110.39</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.92</v>
+        <v>7.08</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="DM7" t="n">
-        <v>59.58</v>
+        <v>59.15</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="DP7" t="n">
-        <v>13.25</v>
+        <v>12.92</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.83</v>
+        <v>12.62</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.58</v>
+        <v>6.15</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.08</v>
+        <v>0.23</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.08</v>
+        <v>0.23</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>57.67</v>
+        <v>57.23</v>
       </c>
       <c r="DW7" t="n">
         <v>0.08</v>
       </c>
       <c r="DX7" t="n">
-        <v>16.34</v>
+        <v>16.39</v>
       </c>
       <c r="DY7" t="n">
-        <v>11.25</v>
+        <v>10.92</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.08</v>
+        <v>5.46</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.33</v>
+        <v>17.54</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
         <v>0.17</v>
@@ -3890,136 +3890,136 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AI8" t="n">
-        <v>94.83</v>
+        <v>95.70999999999999</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.83</v>
+        <v>3.43</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AN8" t="n">
-        <v>41.17</v>
+        <v>39.86</v>
       </c>
       <c r="AO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>44.86</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="BE8" t="n">
         <v>1.17</v>
       </c>
-      <c r="AP8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>15.83</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>45</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.24</v>
-      </c>
       <c r="BF8" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.25</v>
+        <v>7.77</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BN8" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.33</v>
+        <v>3.15</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BT8" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BU8" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BV8" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW8" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY8" t="n">
         <v>4.37</v>
@@ -4028,28 +4028,28 @@
         <v>4.3</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.49</v>
+        <v>4.2</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.82</v>
+        <v>4.48</v>
       </c>
       <c r="CE8" t="n">
         <v>1.34</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="CG8" t="n">
         <v>3.09</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CI8" t="n">
         <v>2</v>
@@ -4058,25 +4058,25 @@
         <v>1.76</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CO8" t="n">
         <v>1.26</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="CR8" t="n">
         <v>1.42</v>
@@ -4091,22 +4091,22 @@
         <v>1.48</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DB8" t="n">
         <v>1.35</v>
@@ -4115,49 +4115,49 @@
         <v>1.96</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="DE8" t="n">
         <v>0.08</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="DH8" t="n">
-        <v>87.16</v>
+        <v>88.23</v>
       </c>
       <c r="DI8" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.5</v>
+        <v>3.31</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DM8" t="n">
-        <v>43.92</v>
+        <v>43</v>
       </c>
       <c r="DN8" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DO8" t="n">
         <v>1.08</v>
       </c>
       <c r="DP8" t="n">
-        <v>10.25</v>
+        <v>10.77</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.66</v>
+        <v>14.85</v>
       </c>
       <c r="DR8" t="n">
-        <v>6</v>
+        <v>6.46</v>
       </c>
       <c r="DS8" t="n">
         <v>0.08</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>44.25</v>
+        <v>44.23</v>
       </c>
       <c r="DW8" t="n">
         <v>0.08</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.92</v>
+        <v>11.54</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.08</v>
+        <v>7.92</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.83</v>
+        <v>3.61</v>
       </c>
       <c r="EA8" t="n">
         <v>16</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4290,139 +4290,139 @@
         <v>1.33</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AG9" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AI9" t="n">
-        <v>78.83</v>
+        <v>75.14</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.67</v>
+        <v>4.29</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AN9" t="n">
-        <v>29.67</v>
+        <v>28.43</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AR9" t="n">
-        <v>11.83</v>
+        <v>11.71</v>
       </c>
       <c r="AS9" t="n">
-        <v>10</v>
+        <v>10.29</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>50.5</v>
+        <v>49.57</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.83</v>
+        <v>9.43</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.5</v>
+        <v>6.14</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="BD9" t="n">
-        <v>14.67</v>
+        <v>15.43</v>
       </c>
       <c r="BE9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BO9" t="n">
         <v>1.08</v>
       </c>
-      <c r="BF9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>1</v>
-      </c>
       <c r="BP9" t="n">
-        <v>4.83</v>
+        <v>4.85</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.92</v>
+        <v>4.77</v>
       </c>
       <c r="BR9" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS9" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT9" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BU9" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BV9" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BW9" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BX9" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BY9" t="n">
         <v>4.01</v>
@@ -4431,46 +4431,46 @@
         <v>4.06</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.12</v>
+        <v>4.07</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.41</v>
+        <v>4.36</v>
       </c>
       <c r="CC9" t="n">
-        <v>6.2</v>
+        <v>5.98</v>
       </c>
       <c r="CD9" t="n">
-        <v>7.32</v>
+        <v>6.89</v>
       </c>
       <c r="CE9" t="n">
         <v>1.31</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CH9" t="n">
         <v>1.51</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CO9" t="n">
         <v>1.21</v>
@@ -4479,121 +4479,121 @@
         <v>1.8</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="CU9" t="n">
         <v>1.53</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CW9" t="n">
         <v>1.78</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DC9" t="n">
         <v>1.74</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DE9" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="DH9" t="n">
-        <v>76.75</v>
+        <v>74.92</v>
       </c>
       <c r="DI9" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.25</v>
+        <v>4.08</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DM9" t="n">
-        <v>32.84</v>
+        <v>31.92</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.42</v>
+        <v>11.15</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.08</v>
+        <v>12</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.08</v>
+        <v>9.31</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>48.5</v>
+        <v>48.15</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.83</v>
+        <v>8.69</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.92</v>
+        <v>5.77</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="EA9" t="n">
-        <v>16</v>
+        <v>16.31</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
         <v>0.29</v>
@@ -4693,139 +4693,139 @@
         <v>1.57</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AI10" t="n">
-        <v>112.8</v>
+        <v>111.83</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AK10" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AN10" t="n">
-        <v>48.6</v>
+        <v>51</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.8</v>
+        <v>2.33</v>
       </c>
       <c r="AQ10" t="n">
-        <v>15</v>
+        <v>14.67</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.2</v>
+        <v>9.83</v>
       </c>
       <c r="AS10" t="n">
-        <v>7</v>
+        <v>6.33</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="BA10" t="n">
-        <v>10.8</v>
+        <v>11.17</v>
       </c>
       <c r="BB10" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.8</v>
+        <v>3.67</v>
       </c>
       <c r="BD10" t="n">
-        <v>21.8</v>
+        <v>21.83</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.8</v>
+        <v>3.33</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.17</v>
+        <v>9.23</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="BM10" t="n">
         <v>1</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT10" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BU10" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BV10" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BW10" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BX10" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BY10" t="n">
         <v>1.59</v>
@@ -4834,16 +4834,16 @@
         <v>1.71</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.49</v>
+        <v>4.42</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.49</v>
+        <v>4.43</v>
       </c>
       <c r="CC10" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="CD10" t="n">
-        <v>1.82</v>
+        <v>1.99</v>
       </c>
       <c r="CE10" t="n">
         <v>1.26</v>
@@ -4852,34 +4852,34 @@
         <v>2.28</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.61</v>
+        <v>3.64</v>
       </c>
       <c r="CH10" t="n">
         <v>1.6</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CM10" t="n">
         <v>2.25</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CO10" t="n">
         <v>1.16</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CQ10" t="n">
         <v>2.37</v>
@@ -4897,19 +4897,19 @@
         <v>1.66</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="CX10" t="n">
         <v>1.58</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="DA10" t="n">
         <v>1.84</v>
@@ -4922,79 +4922,79 @@
         <v>2.39</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="DH10" t="n">
-        <v>110.92</v>
+        <v>110.61</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.33</v>
+        <v>4.46</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DM10" t="n">
-        <v>49.42</v>
+        <v>50.46</v>
       </c>
       <c r="DN10" t="n">
         <v>1</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.17</v>
+        <v>13.16</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.84</v>
+        <v>11.15</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.83</v>
+        <v>6.53</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>55.42</v>
+        <v>55</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.92</v>
+        <v>12.93</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.75</v>
+        <v>8.85</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.17</v>
+        <v>4.08</v>
       </c>
       <c r="EA10" t="n">
-        <v>21.25</v>
+        <v>21.31</v>
       </c>
       <c r="EB10" t="n">
         <v>1.47</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="11">
@@ -5004,58 +5004,58 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F11" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="G11" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>77.83</v>
+        <v>83.14</v>
       </c>
       <c r="I11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J11" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="K11" t="n">
-        <v>3.83</v>
+        <v>3.43</v>
       </c>
       <c r="L11" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="M11" t="n">
-        <v>31.5</v>
+        <v>34.57</v>
       </c>
       <c r="N11" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="O11" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="P11" t="n">
-        <v>10.67</v>
+        <v>11.57</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.33</v>
+        <v>13</v>
       </c>
       <c r="R11" t="n">
-        <v>10.17</v>
+        <v>9.57</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
@@ -5070,28 +5070,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>11.17</v>
+        <v>10.86</v>
       </c>
       <c r="AA11" t="n">
         <v>8</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.17</v>
+        <v>2.86</v>
       </c>
       <c r="AC11" t="n">
-        <v>19.33</v>
+        <v>19.57</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
         <v>0.33</v>
@@ -5175,70 +5175,70 @@
         <v>1.83</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.42</v>
+        <v>9.77</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BO11" t="n">
         <v>1.08</v>
       </c>
       <c r="BP11" t="n">
-        <v>6.08</v>
+        <v>5.69</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.33</v>
+        <v>4.08</v>
       </c>
       <c r="BR11" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS11" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BT11" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BU11" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV11" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX11" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.91</v>
+        <v>4.62</v>
       </c>
       <c r="BZ11" t="n">
-        <v>5.86</v>
+        <v>5.23</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.89</v>
+        <v>3.84</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.12</v>
+        <v>4.02</v>
       </c>
       <c r="CC11" t="n">
         <v>4.85</v>
@@ -5250,7 +5250,7 @@
         <v>1.35</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="CG11" t="n">
         <v>2.99</v>
@@ -5259,19 +5259,19 @@
         <v>1.43</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CL11" t="n">
         <v>1.94</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CN11" t="n">
         <v>1.88</v>
@@ -5283,7 +5283,7 @@
         <v>1.92</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="CR11" t="n">
         <v>1.38</v>
@@ -5298,10 +5298,10 @@
         <v>1.47</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CX11" t="n">
         <v>1.55</v>
@@ -5310,61 +5310,61 @@
         <v>1.9</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="DA11" t="n">
         <v>1.91</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF11" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="DH11" t="n">
-        <v>75.75</v>
+        <v>78.77</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="DM11" t="n">
-        <v>27.83</v>
+        <v>29.77</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DO11" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.42</v>
+        <v>11.85</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.92</v>
+        <v>13.23</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.58</v>
+        <v>9.31</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5376,28 +5376,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>42.84</v>
+        <v>43.85</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.34</v>
+        <v>10.23</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.75</v>
+        <v>7.77</v>
       </c>
       <c r="DZ11" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.92</v>
+        <v>19.08</v>
       </c>
       <c r="EB11" t="n">
         <v>1.04</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="12">
@@ -5810,13 +5810,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5900,52 +5900,52 @@
         <v>1.67</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG13" t="n">
         <v>2</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.17</v>
+        <v>3.71</v>
       </c>
       <c r="AI13" t="n">
-        <v>80.33</v>
+        <v>84.14</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="AL13" t="n">
-        <v>6</v>
+        <v>6.71</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN13" t="n">
-        <v>44</v>
+        <v>45.29</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15</v>
+        <v>14.43</v>
       </c>
       <c r="AR13" t="n">
-        <v>16.17</v>
+        <v>15.29</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.83</v>
+        <v>8</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5957,82 +5957,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>51.67</v>
+        <v>54.29</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BA13" t="n">
-        <v>10.67</v>
+        <v>11.43</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.83</v>
+        <v>7.14</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.83</v>
+        <v>4.29</v>
       </c>
       <c r="BD13" t="n">
-        <v>14.5</v>
+        <v>15.71</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="BH13" t="n">
-        <v>11.08</v>
+        <v>11.62</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL13" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.5</v>
+        <v>4.54</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.58</v>
+        <v>7.08</v>
       </c>
       <c r="BR13" t="n">
-        <v>91.67</v>
+        <v>84.62</v>
       </c>
       <c r="BS13" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BT13" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BU13" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV13" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BW13" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BY13" t="n">
         <v>2.31</v>
@@ -6041,40 +6041,40 @@
         <v>2.65</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CK13" t="n">
         <v>1.52</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CM13" t="n">
         <v>2.38</v>
@@ -6083,94 +6083,94 @@
         <v>1.9</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.97</v>
+        <v>3.01</v>
       </c>
       <c r="DE13" t="n">
         <v>0.08</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.25</v>
+        <v>3.53</v>
       </c>
       <c r="DH13" t="n">
-        <v>85.08</v>
+        <v>86.77</v>
       </c>
       <c r="DI13" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="DK13" t="n">
-        <v>6.08</v>
+        <v>6.46</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM13" t="n">
-        <v>42.5</v>
+        <v>43.31</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.42</v>
+        <v>14.15</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.67</v>
+        <v>14.31</v>
       </c>
       <c r="DR13" t="n">
-        <v>7</v>
+        <v>6.69</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6182,28 +6182,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>52.75</v>
+        <v>54.08</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.75</v>
+        <v>12.08</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.58</v>
+        <v>7.69</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.16</v>
+        <v>4.39</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.34</v>
+        <v>16.85</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -6616,94 +6616,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>4.83</v>
       </c>
       <c r="H15" t="n">
-        <v>152.4</v>
+        <v>148.17</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="K15" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="M15" t="n">
-        <v>86.8</v>
+        <v>81.67</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="O15" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="P15" t="n">
-        <v>10.2</v>
+        <v>10.17</v>
       </c>
       <c r="Q15" t="n">
-        <v>9</v>
+        <v>8.83</v>
       </c>
       <c r="R15" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>73.2</v>
+        <v>71.83</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.8</v>
+        <v>21.67</v>
       </c>
       <c r="AA15" t="n">
-        <v>12.8</v>
+        <v>14</v>
       </c>
       <c r="AB15" t="n">
-        <v>7</v>
+        <v>7.67</v>
       </c>
       <c r="AC15" t="n">
-        <v>20.8</v>
+        <v>20.33</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AF15" t="n">
         <v>0.29</v>
@@ -6790,31 +6790,31 @@
         <v>2.92</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.17</v>
+        <v>9.23</v>
       </c>
       <c r="BI15" t="n">
         <v>2.92</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.25</v>
+        <v>4.31</v>
       </c>
       <c r="BQ15" t="n">
         <v>4.92</v>
@@ -6823,34 +6823,34 @@
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT15" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BU15" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV15" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BW15" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BX15" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BY15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BZ15" t="n">
         <v>1.23</v>
       </c>
-      <c r="BZ15" t="n">
-        <v>1.24</v>
-      </c>
       <c r="CA15" t="n">
-        <v>5.96</v>
+        <v>6.17</v>
       </c>
       <c r="CB15" t="n">
-        <v>6.61</v>
+        <v>6.66</v>
       </c>
       <c r="CC15" t="n">
         <v>1.48</v>
@@ -6862,31 +6862,31 @@
         <v>1.21</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.96</v>
+        <v>3.98</v>
       </c>
       <c r="CH15" t="n">
         <v>1.73</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CK15" t="n">
         <v>1.52</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CO15" t="n">
         <v>1.12</v>
@@ -6910,104 +6910,104 @@
         <v>1.76</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY15" t="n">
         <v>1.88</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DB15" t="inlineStr"/>
       <c r="DC15" t="n">
         <v>1.52</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="DG15" t="n">
         <v>3.92</v>
       </c>
       <c r="DH15" t="n">
-        <v>141.58</v>
+        <v>140.46</v>
       </c>
       <c r="DI15" t="n">
         <v>-0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="DK15" t="n">
-        <v>6.5</v>
+        <v>6.46</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DM15" t="n">
-        <v>77</v>
+        <v>75.39</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="DP15" t="n">
-        <v>9.83</v>
+        <v>9.85</v>
       </c>
       <c r="DQ15" t="n">
-        <v>9</v>
+        <v>8.92</v>
       </c>
       <c r="DR15" t="n">
-        <v>4.08</v>
+        <v>4.38</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>72.33</v>
+        <v>71.77</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>16.75</v>
+        <v>17.85</v>
       </c>
       <c r="DY15" t="n">
-        <v>10.33</v>
+        <v>11.08</v>
       </c>
       <c r="DZ15" t="n">
-        <v>6.42</v>
+        <v>6.77</v>
       </c>
       <c r="EA15" t="n">
         <v>18</v>
       </c>
       <c r="EB15" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="16">
@@ -7017,13 +7017,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7110,136 +7110,136 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AH16" t="n">
         <v>2</v>
       </c>
       <c r="AI16" t="n">
-        <v>85</v>
+        <v>82.14</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.33</v>
+        <v>3.43</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="AN16" t="n">
-        <v>32.67</v>
+        <v>32.57</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.67</v>
+        <v>10.86</v>
       </c>
       <c r="AR16" t="n">
-        <v>11.33</v>
+        <v>11</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.83</v>
+        <v>9</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>53.17</v>
+        <v>52.43</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA16" t="n">
-        <v>10.5</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.83</v>
+        <v>6.29</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.67</v>
+        <v>3.57</v>
       </c>
       <c r="BD16" t="n">
-        <v>17.83</v>
+        <v>18.43</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.83</v>
+        <v>10.08</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BL16" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.92</v>
+        <v>4.23</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.33</v>
+        <v>4.38</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT16" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BU16" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BV16" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BW16" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BX16" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BY16" t="n">
         <v>2</v>
@@ -7248,19 +7248,19 @@
         <v>2.11</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.81</v>
+        <v>3.83</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.51</v>
+        <v>4.58</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CF16" t="n">
         <v>2.51</v>
@@ -7269,22 +7269,22 @@
         <v>3.26</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CL16" t="n">
         <v>2.1</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CN16" t="n">
         <v>1.76</v>
@@ -7296,7 +7296,7 @@
         <v>1.75</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CR16" t="n">
         <v>1.35</v>
@@ -7311,22 +7311,22 @@
         <v>1.53</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CW16" t="n">
         <v>1.68</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DB16" t="n">
         <v>1.27</v>
@@ -7341,13 +7341,13 @@
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DH16" t="n">
-        <v>92.16</v>
+        <v>90.06999999999999</v>
       </c>
       <c r="DI16" t="n">
         <v>0.16</v>
@@ -7356,58 +7356,58 @@
         <v>2.16</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.92</v>
+        <v>4.85</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.25</v>
+        <v>0.39</v>
       </c>
       <c r="DM16" t="n">
-        <v>43.67</v>
+        <v>42.77</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO16" t="n">
         <v>1.92</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.25</v>
+        <v>11.31</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.42</v>
+        <v>11.23</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.66</v>
+        <v>7.38</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>55.17</v>
+        <v>54.62</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.34</v>
+        <v>12.77</v>
       </c>
       <c r="DY16" t="n">
-        <v>9.25</v>
+        <v>8.77</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.83</v>
+        <v>17.23</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="EC16" t="n">
         <v>1.92</v>
@@ -7420,94 +7420,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
         <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F17" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="G17" t="n">
         <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>101.5</v>
+        <v>102.57</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="K17" t="n">
-        <v>5.5</v>
+        <v>5.29</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="M17" t="n">
-        <v>53.33</v>
+        <v>54.57</v>
       </c>
       <c r="N17" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="O17" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="P17" t="n">
-        <v>13.17</v>
+        <v>11.71</v>
       </c>
       <c r="Q17" t="n">
-        <v>13.17</v>
+        <v>13</v>
       </c>
       <c r="R17" t="n">
-        <v>7.83</v>
+        <v>7.29</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>49</v>
+        <v>49.14</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z17" t="n">
-        <v>16.67</v>
+        <v>16.71</v>
       </c>
       <c r="AA17" t="n">
-        <v>11.33</v>
+        <v>10.86</v>
       </c>
       <c r="AB17" t="n">
-        <v>5.33</v>
+        <v>5.86</v>
       </c>
       <c r="AC17" t="n">
-        <v>17.83</v>
+        <v>17.71</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
         <v>0.17</v>
@@ -7591,115 +7591,115 @@
         <v>1.67</v>
       </c>
       <c r="BG17" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="BH17" t="n">
         <v>10.08</v>
       </c>
       <c r="BI17" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.67</v>
+        <v>4.62</v>
       </c>
       <c r="BR17" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS17" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT17" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BU17" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BV17" t="n">
-        <v>8.33</v>
+        <v>15.38</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BY17" t="n">
         <v>2.51</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="CC17" t="n">
         <v>2.52</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.77</v>
+        <v>2.63</v>
       </c>
       <c r="CE17" t="n">
         <v>1.34</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CK17" t="n">
         <v>1.62</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CN17" t="n">
         <v>1.74</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="CR17" t="n">
         <v>1.36</v>
@@ -7714,106 +7714,106 @@
         <v>1.48</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="CW17" t="n">
         <v>1.68</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DB17" t="n">
         <v>1.28</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="DH17" t="n">
-        <v>96.58</v>
+        <v>97.54000000000001</v>
       </c>
       <c r="DI17" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.58</v>
+        <v>5.47</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DM17" t="n">
-        <v>44.58</v>
+        <v>45.92</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.42</v>
+        <v>11.69</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.5</v>
+        <v>12.46</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.58</v>
+        <v>8.23</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>51.08</v>
+        <v>51</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.08</v>
+        <v>13.38</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.5</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.58</v>
+        <v>4.92</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.33</v>
+        <v>18.23</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="EC17" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="18">
@@ -7823,13 +7823,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7916,136 +7916,136 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AH18" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AI18" t="n">
-        <v>98.67</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AK18" t="n">
-        <v>3</v>
+        <v>3.29</v>
       </c>
       <c r="AL18" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN18" t="n">
-        <v>41.83</v>
+        <v>41.57</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AP18" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12.33</v>
+        <v>12.43</v>
       </c>
       <c r="AR18" t="n">
-        <v>13.5</v>
+        <v>13.43</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.83</v>
+        <v>7.14</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>49.67</v>
+        <v>49</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BA18" t="n">
-        <v>11.33</v>
+        <v>10.71</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.5</v>
+        <v>7.29</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.83</v>
+        <v>3.43</v>
       </c>
       <c r="BD18" t="n">
-        <v>16.83</v>
+        <v>17.57</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.33</v>
+        <v>3.15</v>
       </c>
       <c r="BH18" t="n">
-        <v>7.75</v>
+        <v>7.46</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.33</v>
+        <v>3.15</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN18" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BP18" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.75</v>
+        <v>4.62</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BT18" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BU18" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BV18" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BW18" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX18" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BY18" t="n">
         <v>2.21</v>
@@ -8054,61 +8054,61 @@
         <v>2.19</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="CC18" t="n">
-        <v>4.19</v>
+        <v>4.09</v>
       </c>
       <c r="CD18" t="n">
-        <v>4.39</v>
+        <v>4.25</v>
       </c>
       <c r="CE18" t="n">
         <v>1.32</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="CH18" t="n">
         <v>1.49</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CL18" t="n">
         <v>2.17</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CO18" t="n">
         <v>1.22</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CR18" t="n">
         <v>1.37</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CT18" t="n">
         <v>3.17</v>
@@ -8117,10 +8117,10 @@
         <v>1.52</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CX18" t="n">
         <v>1.65</v>
@@ -8138,85 +8138,85 @@
         <v>1.3</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="DH18" t="n">
-        <v>98.75</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.42</v>
+        <v>3.23</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DM18" t="n">
-        <v>40.75</v>
+        <v>40.69</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="DO18" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DP18" t="n">
-        <v>11.5</v>
+        <v>11.62</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.92</v>
+        <v>13.85</v>
       </c>
       <c r="DR18" t="n">
-        <v>7</v>
+        <v>7.15</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>50.67</v>
+        <v>50.23</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.83</v>
+        <v>11.46</v>
       </c>
       <c r="DY18" t="n">
-        <v>7</v>
+        <v>6.93</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.83</v>
+        <v>4.54</v>
       </c>
       <c r="EA18" t="n">
-        <v>15.08</v>
+        <v>15.61</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="19">
@@ -8226,94 +8226,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F19" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="G19" t="n">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="H19" t="n">
-        <v>90</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="K19" t="n">
-        <v>4.83</v>
+        <v>5.71</v>
       </c>
       <c r="L19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="M19" t="n">
-        <v>51.17</v>
+        <v>52.86</v>
       </c>
       <c r="N19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="O19" t="n">
-        <v>2.33</v>
+        <v>2.86</v>
       </c>
       <c r="P19" t="n">
-        <v>12.33</v>
+        <v>12.71</v>
       </c>
       <c r="Q19" t="n">
-        <v>11</v>
+        <v>11.57</v>
       </c>
       <c r="R19" t="n">
-        <v>5.33</v>
+        <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="T19" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>42.33</v>
+        <v>44</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>14.83</v>
+        <v>16.29</v>
       </c>
       <c r="AA19" t="n">
-        <v>10</v>
+        <v>11.29</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.83</v>
+        <v>5</v>
       </c>
       <c r="AC19" t="n">
-        <v>17.33</v>
+        <v>17.71</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8397,64 +8397,64 @@
         <v>3.83</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.25</v>
+        <v>10.38</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BL19" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="BO19" t="n">
         <v>1</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.67</v>
+        <v>4.77</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.58</v>
+        <v>5.62</v>
       </c>
       <c r="BR19" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS19" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BT19" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BU19" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV19" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW19" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX19" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.92</v>
+        <v>2.75</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="CA19" t="n">
         <v>3.69</v>
@@ -8472,154 +8472,154 @@
         <v>1.36</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CJ19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="CN19" t="n">
         <v>1.78</v>
-      </c>
-      <c r="CK19" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="CL19" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="CM19" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="CN19" t="n">
-        <v>1.79</v>
       </c>
       <c r="CO19" t="n">
         <v>1.28</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="CR19" t="n">
         <v>1.41</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="CT19" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CV19" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CW19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CX19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CY19" t="n">
         <v>2.05</v>
       </c>
-      <c r="CW19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="CX19" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="CY19" t="n">
-        <v>2.03</v>
-      </c>
       <c r="CZ19" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DB19" t="n">
         <v>1.33</v>
       </c>
       <c r="DC19" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="DE19" t="n">
         <v>0.16</v>
       </c>
       <c r="DF19" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="DH19" t="n">
-        <v>91.34</v>
+        <v>94.69</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.75</v>
+        <v>5.23</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DM19" t="n">
-        <v>46.5</v>
+        <v>47.77</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.58</v>
+        <v>2.85</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.16</v>
+        <v>14.23</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.16</v>
+        <v>11.46</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.33</v>
+        <v>6.08</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>42.83</v>
+        <v>43.69</v>
       </c>
       <c r="DW19" t="n">
         <v>0.08</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.58</v>
+        <v>13.54</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.83</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.75</v>
+        <v>17</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
         <v>7</v>
@@ -4212,82 +4212,82 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="H9" t="n">
-        <v>74.67</v>
+        <v>76.14</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.17</v>
+        <v>-0.29</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="K9" t="n">
-        <v>3.83</v>
+        <v>4.14</v>
       </c>
       <c r="L9" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="M9" t="n">
-        <v>36</v>
+        <v>37.57</v>
       </c>
       <c r="N9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="O9" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="P9" t="n">
-        <v>12.83</v>
+        <v>12.29</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.33</v>
+        <v>11.71</v>
       </c>
       <c r="R9" t="n">
-        <v>8.17</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="U9" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="V9" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>46.5</v>
+        <v>47.14</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.83</v>
+        <v>9</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.33</v>
+        <v>6.14</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="AC9" t="n">
-        <v>17.33</v>
+        <v>17.57</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AF9" t="n">
         <v>0.14</v>
@@ -4371,70 +4371,70 @@
         <v>1.57</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.38</v>
+        <v>3.21</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.619999999999999</v>
+        <v>9.57</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.38</v>
+        <v>3.21</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BN9" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.85</v>
+        <v>4.86</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.77</v>
+        <v>4.71</v>
       </c>
       <c r="BR9" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS9" t="n">
-        <v>84.62</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BU9" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BV9" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BW9" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BX9" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BY9" t="n">
         <v>4.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>4.06</v>
+        <v>4.02</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.07</v>
+        <v>4.05</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.36</v>
+        <v>4.33</v>
       </c>
       <c r="CC9" t="n">
         <v>5.98</v>
@@ -4455,19 +4455,19 @@
         <v>1.51</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CK9" t="n">
         <v>1.59</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CN9" t="n">
         <v>1.78</v>
@@ -4476,10 +4476,10 @@
         <v>1.21</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CR9" t="n">
         <v>1.37</v>
@@ -4494,10 +4494,10 @@
         <v>1.53</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CX9" t="n">
         <v>1.59</v>
@@ -4506,94 +4506,94 @@
         <v>1.98</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="DB9" t="n">
         <v>1.28</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="DH9" t="n">
-        <v>74.92</v>
+        <v>75.64</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.08</v>
+        <v>-0.14</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.08</v>
+        <v>4.22</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM9" t="n">
-        <v>31.92</v>
+        <v>33</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.15</v>
+        <v>11</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12</v>
+        <v>11.71</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.31</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>48.15</v>
+        <v>48.36</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.69</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.77</v>
+        <v>6.14</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.93</v>
+        <v>3.08</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.31</v>
+        <v>16.5</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.99</v>
+        <v>1.04</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="10">
@@ -7420,13 +7420,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
         <v>0.14</v>
@@ -7510,139 +7510,139 @@
         <v>2</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG17" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AH17" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>90.86</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
         <v>2</v>
       </c>
-      <c r="AI17" t="n">
-        <v>91.67</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>2.33</v>
-      </c>
       <c r="AL17" t="n">
-        <v>5.67</v>
+        <v>5.29</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AN17" t="n">
-        <v>35.83</v>
+        <v>36</v>
       </c>
       <c r="AO17" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.67</v>
+        <v>11.14</v>
       </c>
       <c r="AR17" t="n">
-        <v>11.83</v>
+        <v>11.43</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.33</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>53.17</v>
+        <v>52.57</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BA17" t="n">
-        <v>9.5</v>
+        <v>9.43</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.67</v>
+        <v>5.86</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.83</v>
+        <v>3.57</v>
       </c>
       <c r="BD17" t="n">
-        <v>18.83</v>
+        <v>19</v>
       </c>
       <c r="BE17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BO17" t="n">
         <v>1.14</v>
       </c>
-      <c r="BF17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>1.15</v>
-      </c>
       <c r="BP17" t="n">
-        <v>4</v>
+        <v>4.07</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.62</v>
+        <v>4.57</v>
       </c>
       <c r="BR17" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS17" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT17" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU17" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BV17" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY17" t="n">
         <v>2.51</v>
@@ -7651,55 +7651,55 @@
         <v>2.65</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.49</v>
+        <v>3.51</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.58</v>
+        <v>3.61</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.52</v>
+        <v>2.43</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CH17" t="n">
         <v>1.47</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CK17" t="n">
         <v>1.62</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="CR17" t="n">
         <v>1.36</v>
@@ -7714,10 +7714,10 @@
         <v>1.48</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CX17" t="n">
         <v>1.61</v>
@@ -7729,91 +7729,91 @@
         <v>2.3</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DB17" t="n">
         <v>1.28</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="DH17" t="n">
-        <v>97.54000000000001</v>
+        <v>96.72</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.47</v>
+        <v>5.29</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DM17" t="n">
-        <v>45.92</v>
+        <v>45.28</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="DO17" t="n">
         <v>2.08</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.69</v>
+        <v>11.42</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.46</v>
+        <v>12.22</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.23</v>
+        <v>8.07</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>51</v>
+        <v>50.86</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.38</v>
+        <v>13.07</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.460000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.92</v>
+        <v>4.72</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.23</v>
+        <v>18.36</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="18">

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -1379,61 +1379,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F2" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="G2" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="H2" t="n">
-        <v>77.33</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="K2" t="n">
-        <v>4.83</v>
+        <v>4.43</v>
       </c>
       <c r="L2" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="M2" t="n">
-        <v>34.83</v>
+        <v>32.86</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="O2" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="P2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.33</v>
+        <v>11.29</v>
       </c>
       <c r="R2" t="n">
-        <v>9</v>
+        <v>9.43</v>
       </c>
       <c r="S2" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="T2" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>42.33</v>
+        <v>42.71</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>10.17</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.33</v>
+        <v>5.71</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="AC2" t="n">
-        <v>17</v>
+        <v>17.43</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>1.29</v>
       </c>
       <c r="BG2" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.619999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="BL2" t="n">
         <v>1</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.69</v>
+        <v>5.64</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT2" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BU2" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV2" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.45</v>
+        <v>3.61</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.69</v>
+        <v>3.93</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.84</v>
+        <v>4.77</v>
       </c>
       <c r="CC2" t="n">
         <v>10.08</v>
@@ -1634,13 +1634,13 @@
         <v>1.45</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CL2" t="n">
         <v>2.14</v>
@@ -1655,10 +1655,10 @@
         <v>1.3</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="CR2" t="n">
         <v>1.44</v>
@@ -1673,10 +1673,10 @@
         <v>1.48</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CX2" t="n">
         <v>1.68</v>
@@ -1685,7 +1685,7 @@
         <v>2.1</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DA2" t="n">
         <v>1.75</v>
@@ -1694,85 +1694,85 @@
         <v>1.36</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="DH2" t="n">
-        <v>69.61</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.77</v>
+        <v>3.64</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM2" t="n">
-        <v>28.69</v>
+        <v>28.14</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.77</v>
+        <v>11.43</v>
       </c>
       <c r="DQ2" t="n">
         <v>11.08</v>
       </c>
       <c r="DR2" t="n">
-        <v>9.16</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>39.62</v>
+        <v>40</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX2" t="n">
-        <v>8.69</v>
+        <v>8.57</v>
       </c>
       <c r="DY2" t="n">
-        <v>5.69</v>
+        <v>5.42</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="EA2" t="n">
-        <v>15.77</v>
+        <v>16.07</v>
       </c>
       <c r="EB2" t="n">
         <v>0.97</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,130 +1872,130 @@
         <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AI3" t="n">
-        <v>88.83</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.33</v>
+        <v>4.14</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN3" t="n">
-        <v>36.83</v>
+        <v>37.14</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.33</v>
+        <v>13</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.17</v>
+        <v>7.57</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>45.17</v>
+        <v>45.14</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.5</v>
+        <v>10.57</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.33</v>
+        <v>6.57</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BD3" t="n">
-        <v>19</v>
+        <v>19.29</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="BG3" t="n">
         <v>2</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.69</v>
+        <v>9.5</v>
       </c>
       <c r="BI3" t="n">
         <v>2</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="BP3" t="n">
-        <v>4</v>
+        <v>3.79</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.69</v>
+        <v>5.71</v>
       </c>
       <c r="BR3" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS3" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BT3" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BU3" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BY3" t="n">
         <v>3.41</v>
@@ -2013,25 +2013,25 @@
         <v>3.81</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="CC3" t="n">
-        <v>5.28</v>
+        <v>5.11</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.55</v>
+        <v>5.38</v>
       </c>
       <c r="CE3" t="n">
         <v>1.36</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="CH3" t="n">
         <v>1.45</v>
@@ -2040,37 +2040,37 @@
         <v>2</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CO3" t="n">
         <v>1.27</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CQ3" t="n">
         <v>3.17</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CT3" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CU3" t="n">
         <v>1.47</v>
@@ -2079,103 +2079,103 @@
         <v>2.06</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CX3" t="n">
         <v>1.61</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="DB3" t="n">
         <v>1.33</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="DG3" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="DH3" t="n">
-        <v>89.62</v>
+        <v>89.93000000000001</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.85</v>
+        <v>4.71</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM3" t="n">
-        <v>38.46</v>
+        <v>38.5</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.54</v>
+        <v>13.78</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.54</v>
+        <v>14.28</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.38</v>
+        <v>6.64</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>44.23</v>
+        <v>44.28</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.61</v>
+        <v>10.64</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.15</v>
+        <v>7.22</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.16</v>
+        <v>19.29</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
         <v>0.43</v>
@@ -2278,136 +2278,136 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AI4" t="n">
-        <v>86.33</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.17</v>
+        <v>2.71</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AN4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11.83</v>
+        <v>12.14</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.5</v>
+        <v>11.43</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.5</v>
+        <v>7.14</v>
       </c>
       <c r="AT4" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AU4" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>44.67</v>
+        <v>44.43</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.67</v>
+        <v>8.43</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.17</v>
+        <v>5.71</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="BD4" t="n">
-        <v>19.17</v>
+        <v>19.29</v>
       </c>
       <c r="BE4" t="n">
         <v>1</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="BH4" t="n">
-        <v>10</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BK4" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.31</v>
+        <v>0.43</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.08</v>
+        <v>4.86</v>
       </c>
       <c r="BR4" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU4" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BV4" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BW4" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BX4" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
         <v>3.12</v>
@@ -2416,25 +2416,25 @@
         <v>3.55</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.56</v>
+        <v>3.67</v>
       </c>
       <c r="CE4" t="n">
         <v>1.35</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CH4" t="n">
         <v>1.46</v>
@@ -2446,43 +2446,43 @@
         <v>1.73</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CL4" t="n">
         <v>2.1</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CN4" t="n">
         <v>1.73</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CQ4" t="n">
         <v>3.05</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CX4" t="n">
         <v>1.67</v>
@@ -2497,88 +2497,88 @@
         <v>1.74</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.16</v>
+        <v>3.13</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF4" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="DH4" t="n">
-        <v>93.77</v>
+        <v>94.22</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.69</v>
+        <v>4.35</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM4" t="n">
-        <v>39.77</v>
+        <v>39.14</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.38</v>
+        <v>12.5</v>
       </c>
       <c r="DQ4" t="n">
-        <v>10.39</v>
+        <v>10.43</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.23</v>
+        <v>7.07</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.62</v>
+        <v>44.5</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.46</v>
+        <v>12.07</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.609999999999999</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.23</v>
+        <v>18.36</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="5">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
         <v>7</v>
@@ -2600,34 +2600,34 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="G5" t="n">
-        <v>2.67</v>
+        <v>2.86</v>
       </c>
       <c r="H5" t="n">
-        <v>98.67</v>
+        <v>98.43000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="K5" t="n">
-        <v>4.83</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="M5" t="n">
-        <v>54.67</v>
+        <v>55.14</v>
       </c>
       <c r="N5" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="O5" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="P5" t="n">
         <v>15</v>
@@ -2636,46 +2636,46 @@
         <v>13</v>
       </c>
       <c r="R5" t="n">
-        <v>6.17</v>
+        <v>5.57</v>
       </c>
       <c r="S5" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="U5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>52</v>
+        <v>50.71</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>13.83</v>
+        <v>13.86</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.67</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.17</v>
+        <v>4.57</v>
       </c>
       <c r="AC5" t="n">
-        <v>22.83</v>
+        <v>21.57</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>1.57</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.69</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.69</v>
+        <v>3.64</v>
       </c>
       <c r="BQ5" t="n">
         <v>5</v>
       </c>
       <c r="BR5" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BT5" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BU5" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV5" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX5" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3</v>
+        <v>3.23</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.23</v>
+        <v>4.19</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.2</v>
+        <v>4.17</v>
       </c>
       <c r="CC5" t="n">
         <v>6.9</v>
@@ -2831,19 +2831,19 @@
         <v>7.67</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CH5" t="n">
         <v>1.45</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.84</v>
@@ -2852,7 +2852,7 @@
         <v>1.67</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CM5" t="n">
         <v>2.17</v>
@@ -2867,16 +2867,16 @@
         <v>1.88</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="CU5" t="n">
         <v>1.44</v>
@@ -2894,7 +2894,7 @@
         <v>2.04</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DA5" t="n">
         <v>1.78</v>
@@ -2912,76 +2912,76 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="DH5" t="n">
-        <v>88.08</v>
+        <v>88.72</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.15</v>
+        <v>4.28</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DM5" t="n">
-        <v>44.69</v>
+        <v>45.64</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DP5" t="n">
-        <v>14</v>
+        <v>14.07</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.84</v>
+        <v>12.86</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.46</v>
+        <v>7.07</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>46.15</v>
+        <v>45.92</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.54</v>
+        <v>11.72</v>
       </c>
       <c r="DY5" t="n">
-        <v>8</v>
+        <v>7.93</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.54</v>
+        <v>3.78</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.15</v>
+        <v>17.86</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
         <v>0.14</v>
@@ -3081,139 +3081,139 @@
         <v>1.86</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="AI6" t="n">
-        <v>76.33</v>
+        <v>83.43000000000001</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AK6" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AL6" t="n">
-        <v>3</v>
+        <v>3.71</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AN6" t="n">
-        <v>34.83</v>
+        <v>37.86</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="AQ6" t="n">
-        <v>14.67</v>
+        <v>14.14</v>
       </c>
       <c r="AR6" t="n">
-        <v>13.67</v>
+        <v>12.71</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.33</v>
+        <v>8.57</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>42.5</v>
+        <v>44.29</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BA6" t="n">
-        <v>11.17</v>
+        <v>12</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.83</v>
+        <v>7.43</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.33</v>
+        <v>4.57</v>
       </c>
       <c r="BD6" t="n">
-        <v>13.83</v>
+        <v>14.71</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.69</v>
+        <v>10.64</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BL6" t="n">
         <v>1</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.08</v>
+        <v>4.14</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.23</v>
+        <v>5.21</v>
       </c>
       <c r="BR6" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS6" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU6" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV6" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BY6" t="n">
         <v>2.15</v>
@@ -3222,43 +3222,43 @@
         <v>2.14</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.16</v>
+        <v>2.95</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="CH6" t="n">
         <v>1.53</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.64</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CN6" t="n">
         <v>1.78</v>
@@ -3270,7 +3270,7 @@
         <v>1.72</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="CR6" t="n">
         <v>1.34</v>
@@ -3285,106 +3285,106 @@
         <v>1.59</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="DB6" t="n">
         <v>1.25</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="DH6" t="n">
-        <v>79.08</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.69</v>
+        <v>5.86</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="DM6" t="n">
-        <v>40.54</v>
+        <v>41.64</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="DP6" t="n">
-        <v>13</v>
+        <v>12.86</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.46</v>
+        <v>12.07</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.92</v>
+        <v>6.72</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.38</v>
+        <v>47</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.16</v>
+        <v>13.43</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.07</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.07</v>
+        <v>5.14</v>
       </c>
       <c r="EA6" t="n">
-        <v>15.54</v>
+        <v>15.86</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" t="n">
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3484,52 +3484,52 @@
         <v>1.71</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AI7" t="n">
-        <v>114.5</v>
+        <v>111.71</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.17</v>
+        <v>3.43</v>
       </c>
       <c r="AL7" t="n">
-        <v>7.67</v>
+        <v>6.86</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AN7" t="n">
-        <v>62.83</v>
+        <v>60.43</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.17</v>
+        <v>3.71</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13.5</v>
+        <v>13.43</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.33</v>
+        <v>12.71</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.33</v>
+        <v>7.29</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AU7" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>60.67</v>
+        <v>60.14</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="BA7" t="n">
-        <v>16.17</v>
+        <v>15</v>
       </c>
       <c r="BB7" t="n">
-        <v>10.67</v>
+        <v>10</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BD7" t="n">
-        <v>19.33</v>
+        <v>18.57</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.38</v>
+        <v>3.21</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.85</v>
+        <v>10.64</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.38</v>
+        <v>3.21</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="BM7" t="n">
         <v>1</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.92</v>
+        <v>5.71</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.92</v>
+        <v>4.93</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT7" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BU7" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV7" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BW7" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BX7" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BY7" t="n">
         <v>2.22</v>
@@ -3625,25 +3625,25 @@
         <v>2.21</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.41</v>
+        <v>2.32</v>
       </c>
       <c r="CD7" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="CE7" t="n">
         <v>1.33</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CH7" t="n">
         <v>1.47</v>
@@ -3652,55 +3652,55 @@
         <v>2.08</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CL7" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CO7" t="n">
         <v>1.23</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CQ7" t="n">
         <v>2.9</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="DA7" t="n">
         <v>1.84</v>
@@ -3709,85 +3709,85 @@
         <v>1.28</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.07</v>
+        <v>2.92</v>
       </c>
       <c r="DH7" t="n">
-        <v>110.39</v>
+        <v>109.28</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.38</v>
+        <v>2.57</v>
       </c>
       <c r="DK7" t="n">
-        <v>7.08</v>
+        <v>6.72</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DM7" t="n">
-        <v>59.15</v>
+        <v>58.22</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="DO7" t="n">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.92</v>
+        <v>12.93</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.62</v>
+        <v>12.78</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.15</v>
+        <v>6.21</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>57.23</v>
+        <v>57.22</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DX7" t="n">
-        <v>16.39</v>
+        <v>15.78</v>
       </c>
       <c r="DY7" t="n">
-        <v>10.92</v>
+        <v>10.57</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.46</v>
+        <v>5.21</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.54</v>
+        <v>17.28</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="8">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="G8" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="H8" t="n">
-        <v>79.5</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="K8" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="M8" t="n">
-        <v>46.67</v>
+        <v>45.71</v>
       </c>
       <c r="N8" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="O8" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="P8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.5</v>
+        <v>13.14</v>
       </c>
       <c r="R8" t="n">
-        <v>5.83</v>
+        <v>5.57</v>
       </c>
       <c r="S8" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="U8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>43.5</v>
+        <v>43.43</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.33</v>
+        <v>13.14</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.67</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.67</v>
+        <v>5</v>
       </c>
       <c r="AC8" t="n">
-        <v>15.33</v>
+        <v>14.57</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3968,70 +3968,70 @@
         <v>2.29</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="BH8" t="n">
-        <v>7.77</v>
+        <v>7.93</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BN8" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BT8" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BU8" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BV8" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW8" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BX8" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY8" t="n">
-        <v>4.37</v>
+        <v>4.06</v>
       </c>
       <c r="BZ8" t="n">
-        <v>4.3</v>
+        <v>4.04</v>
       </c>
       <c r="CA8" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="CB8" t="n">
         <v>3.85</v>
-      </c>
-      <c r="CB8" t="n">
-        <v>3.88</v>
       </c>
       <c r="CC8" t="n">
         <v>4.2</v>
@@ -4049,22 +4049,22 @@
         <v>3.09</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CI8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CN8" t="n">
         <v>1.69</v>
@@ -4076,7 +4076,7 @@
         <v>1.9</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="CR8" t="n">
         <v>1.42</v>
@@ -4091,10 +4091,10 @@
         <v>1.48</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CX8" t="n">
         <v>1.72</v>
@@ -4109,88 +4109,88 @@
         <v>1.69</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DD8" t="n">
         <v>3.12</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DH8" t="n">
-        <v>88.23</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DM8" t="n">
-        <v>43</v>
+        <v>42.78</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DP8" t="n">
-        <v>10.77</v>
+        <v>10.5</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.85</v>
+        <v>14.57</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.46</v>
+        <v>6.29</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>44.23</v>
+        <v>44.14</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.54</v>
+        <v>12</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.92</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.61</v>
+        <v>3.86</v>
       </c>
       <c r="EA8" t="n">
-        <v>16</v>
+        <v>15.57</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="9">
@@ -4266,7 +4266,7 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>47.14</v>
+        <v>47.29</v>
       </c>
       <c r="Y9" t="n">
         <v>0.14</v>
@@ -4572,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>48.36</v>
+        <v>48.43</v>
       </c>
       <c r="DW9" t="n">
         <v>0.22</v>
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
         <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F10" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="G10" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="H10" t="n">
-        <v>109.57</v>
+        <v>108.38</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="K10" t="n">
-        <v>4.43</v>
+        <v>4.38</v>
       </c>
       <c r="L10" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="M10" t="n">
-        <v>50</v>
+        <v>48.38</v>
       </c>
       <c r="N10" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="O10" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="P10" t="n">
-        <v>11.86</v>
+        <v>11.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.29</v>
+        <v>12.38</v>
       </c>
       <c r="R10" t="n">
-        <v>6.71</v>
+        <v>7.38</v>
       </c>
       <c r="S10" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="V10" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>55</v>
+        <v>53.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.43</v>
+        <v>13.88</v>
       </c>
       <c r="AA10" t="n">
-        <v>10</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>20.86</v>
+        <v>20</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AF10" t="n">
         <v>0.17</v>
@@ -4774,64 +4774,64 @@
         <v>3.33</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.85</v>
+        <v>3.64</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.23</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.85</v>
+        <v>3.64</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BM10" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="BP10" t="n">
         <v>4</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT10" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU10" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BV10" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BW10" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BX10" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.59</v>
+        <v>2.04</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.71</v>
+        <v>2.07</v>
       </c>
       <c r="CA10" t="n">
         <v>4.42</v>
@@ -4846,22 +4846,22 @@
         <v>1.99</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.64</v>
+        <v>3.67</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="CK10" t="n">
         <v>1.57</v>
@@ -4870,37 +4870,37 @@
         <v>2</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="CR10" t="n">
         <v>1.35</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="CT10" t="n">
         <v>3.26</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CX10" t="n">
         <v>1.58</v>
@@ -4912,89 +4912,89 @@
         <v>2.33</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="DB10" t="inlineStr"/>
       <c r="DC10" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="DH10" t="n">
-        <v>110.61</v>
+        <v>109.86</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.77</v>
+        <v>2.93</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="DM10" t="n">
-        <v>50.46</v>
+        <v>49.5</v>
       </c>
       <c r="DN10" t="n">
         <v>1</v>
       </c>
       <c r="DO10" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.16</v>
+        <v>12.93</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.15</v>
+        <v>11.29</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.53</v>
+        <v>6.93</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>55</v>
+        <v>54.14</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.93</v>
+        <v>12.72</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.85</v>
+        <v>8.57</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.08</v>
+        <v>4.14</v>
       </c>
       <c r="EA10" t="n">
-        <v>21.31</v>
+        <v>20.78</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="11">
@@ -5004,13 +5004,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
         <v>0.14</v>
@@ -5094,139 +5094,139 @@
         <v>1.57</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AI11" t="n">
-        <v>73.67</v>
+        <v>70</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.67</v>
+        <v>3.14</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AN11" t="n">
-        <v>24.17</v>
+        <v>22.86</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12.17</v>
+        <v>11.71</v>
       </c>
       <c r="AR11" t="n">
-        <v>13.5</v>
+        <v>13.57</v>
       </c>
       <c r="AS11" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>41.43</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BA11" t="n">
         <v>9</v>
       </c>
-      <c r="AT11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>43.67</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>9.5</v>
-      </c>
       <c r="BB11" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="BC11" t="n">
         <v>2</v>
       </c>
       <c r="BD11" t="n">
-        <v>18.5</v>
+        <v>19.14</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.77</v>
+        <v>9.57</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.69</v>
+        <v>5.43</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.08</v>
+        <v>4.14</v>
       </c>
       <c r="BR11" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS11" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT11" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BU11" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV11" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX11" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BY11" t="n">
         <v>4.62</v>
@@ -5235,61 +5235,61 @@
         <v>5.23</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.84</v>
+        <v>3.91</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.02</v>
+        <v>4.08</v>
       </c>
       <c r="CC11" t="n">
-        <v>4.85</v>
+        <v>5.23</v>
       </c>
       <c r="CD11" t="n">
-        <v>5.27</v>
+        <v>5.64</v>
       </c>
       <c r="CE11" t="n">
         <v>1.35</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="CH11" t="n">
         <v>1.43</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.84</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CN11" t="n">
         <v>1.88</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="CR11" t="n">
         <v>1.38</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="CT11" t="n">
         <v>3.1</v>
@@ -5298,73 +5298,73 @@
         <v>1.47</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CY11" t="n">
         <v>1.9</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DB11" t="n">
         <v>1.31</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF11" t="n">
         <v>0.92</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="DH11" t="n">
-        <v>78.77</v>
+        <v>76.56999999999999</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.54</v>
+        <v>3.28</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="DM11" t="n">
-        <v>29.77</v>
+        <v>28.72</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.85</v>
+        <v>11.64</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.23</v>
+        <v>13.28</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.31</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5376,28 +5376,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>43.85</v>
+        <v>42.72</v>
       </c>
       <c r="DW11" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.23</v>
+        <v>9.93</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.77</v>
+        <v>7.5</v>
       </c>
       <c r="DZ11" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.08</v>
+        <v>19.36</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="12">
@@ -5407,13 +5407,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
         <v>0.29</v>
@@ -5500,136 +5500,136 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AI12" t="n">
-        <v>80</v>
+        <v>85.86</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.33</v>
+        <v>4.71</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN12" t="n">
-        <v>34.33</v>
+        <v>36.14</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.67</v>
+        <v>1.14</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.67</v>
+        <v>13.29</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.67</v>
+        <v>11.86</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.17</v>
+        <v>8</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>45.17</v>
+        <v>46.86</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.17</v>
+        <v>10</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.17</v>
+        <v>7.14</v>
       </c>
       <c r="BC12" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="BD12" t="n">
-        <v>16.67</v>
+        <v>16.43</v>
       </c>
       <c r="BE12" t="n">
         <v>1.1</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="BH12" t="n">
-        <v>11.31</v>
+        <v>11.21</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.69</v>
+        <v>5.71</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU12" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BV12" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW12" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX12" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY12" t="n">
         <v>2.34</v>
@@ -5638,16 +5638,16 @@
         <v>2.54</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.77</v>
+        <v>3.74</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.09</v>
+        <v>4.05</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.58</v>
+        <v>3.48</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.45</v>
+        <v>5.1</v>
       </c>
       <c r="CE12" t="n">
         <v>1.31</v>
@@ -5656,7 +5656,7 @@
         <v>2.49</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="CH12" t="n">
         <v>1.51</v>
@@ -5668,25 +5668,25 @@
         <v>1.66</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CO12" t="n">
         <v>1.22</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CR12" t="n">
         <v>1.36</v>
@@ -5701,106 +5701,106 @@
         <v>1.54</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CW12" t="n">
         <v>1.69</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="DB12" t="n">
         <v>1.3</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="DH12" t="n">
-        <v>72.54000000000001</v>
+        <v>76</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DM12" t="n">
-        <v>34.08</v>
+        <v>35</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.61</v>
+        <v>12.5</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.47</v>
+        <v>12.08</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.23</v>
+        <v>7.21</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>46.31</v>
+        <v>47.08</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.39</v>
+        <v>11.22</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.23</v>
+        <v>7.21</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="EA12" t="n">
-        <v>15.23</v>
+        <v>15.22</v>
       </c>
       <c r="EB12" t="n">
         <v>1.14</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="13">
@@ -5810,10 +5810,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
         <v>7</v>
@@ -5822,49 +5822,49 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="G13" t="n">
-        <v>3.33</v>
+        <v>3.57</v>
       </c>
       <c r="H13" t="n">
-        <v>89.83</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="K13" t="n">
-        <v>6.17</v>
+        <v>6.29</v>
       </c>
       <c r="L13" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="M13" t="n">
-        <v>41</v>
+        <v>45.43</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="O13" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="P13" t="n">
-        <v>13.83</v>
+        <v>13.86</v>
       </c>
       <c r="Q13" t="n">
-        <v>13.17</v>
+        <v>12.57</v>
       </c>
       <c r="R13" t="n">
-        <v>5.17</v>
+        <v>5.14</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="T13" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5876,28 +5876,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>53.83</v>
+        <v>56.43</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.83</v>
+        <v>13.86</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.33</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AC13" t="n">
-        <v>18.17</v>
+        <v>16.57</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AF13" t="n">
         <v>0.14</v>
@@ -5981,70 +5981,70 @@
         <v>2.29</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="BH13" t="n">
-        <v>11.62</v>
+        <v>11.29</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.54</v>
+        <v>4.36</v>
       </c>
       <c r="BQ13" t="n">
-        <v>7.08</v>
+        <v>6.93</v>
       </c>
       <c r="BR13" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BT13" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BU13" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV13" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW13" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX13" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.64</v>
+        <v>3.72</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.77</v>
+        <v>3.85</v>
       </c>
       <c r="CC13" t="n">
         <v>2.62</v>
@@ -6056,37 +6056,37 @@
         <v>1.31</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CH13" t="n">
         <v>1.5</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CK13" t="n">
         <v>1.52</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CQ13" t="n">
         <v>2.76</v>
@@ -6095,7 +6095,7 @@
         <v>1.36</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CT13" t="n">
         <v>3.21</v>
@@ -6104,22 +6104,22 @@
         <v>1.5</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DB13" t="n">
         <v>1.3</v>
@@ -6128,49 +6128,49 @@
         <v>1.83</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.53</v>
+        <v>3.64</v>
       </c>
       <c r="DH13" t="n">
-        <v>86.77</v>
+        <v>89.28</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="DK13" t="n">
-        <v>6.46</v>
+        <v>6.5</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DM13" t="n">
-        <v>43.31</v>
+        <v>45.36</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.15</v>
+        <v>14.14</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.31</v>
+        <v>13.93</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.69</v>
+        <v>6.57</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6182,28 +6182,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>54.08</v>
+        <v>55.36</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.08</v>
+        <v>12.64</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.69</v>
+        <v>8</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.39</v>
+        <v>4.65</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.85</v>
+        <v>16.14</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="EC13" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="14">
@@ -6213,94 +6213,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
         <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="G14" t="n">
-        <v>2.67</v>
+        <v>3.29</v>
       </c>
       <c r="H14" t="n">
-        <v>117.67</v>
+        <v>121</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="K14" t="n">
-        <v>4.83</v>
+        <v>5.43</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="M14" t="n">
-        <v>56</v>
+        <v>59.86</v>
       </c>
       <c r="N14" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="O14" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="P14" t="n">
-        <v>13.83</v>
+        <v>12.86</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.17</v>
+        <v>8.43</v>
       </c>
       <c r="R14" t="n">
-        <v>4.5</v>
+        <v>4.29</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="T14" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="U14" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="V14" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>60.33</v>
+        <v>62.71</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>13.83</v>
+        <v>14.71</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.17</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AB14" t="n">
-        <v>6.67</v>
+        <v>6.43</v>
       </c>
       <c r="AC14" t="n">
-        <v>14.33</v>
+        <v>13.57</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6384,70 +6384,70 @@
         <v>2.43</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="BH14" t="n">
-        <v>9</v>
+        <v>9.07</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BP14" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5</v>
+        <v>5.21</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT14" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU14" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BV14" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW14" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BX14" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.44</v>
+        <v>4.41</v>
       </c>
       <c r="CC14" t="n">
         <v>1.96</v>
@@ -6456,16 +6456,16 @@
         <v>2.1</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI14" t="n">
         <v>2.06</v>
@@ -6477,7 +6477,7 @@
         <v>1.65</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CM14" t="n">
         <v>2.12</v>
@@ -6489,10 +6489,10 @@
         <v>1.2</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="CR14" t="n">
         <v>1.36</v>
@@ -6525,88 +6525,88 @@
         <v>1.76</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DD14" t="n">
         <v>2.75</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF14" t="n">
         <v>1.07</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.08</v>
+        <v>3.36</v>
       </c>
       <c r="DH14" t="n">
-        <v>106.46</v>
+        <v>108.93</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.38</v>
+        <v>5.64</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DM14" t="n">
-        <v>48.54</v>
+        <v>51</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.31</v>
+        <v>11.93</v>
       </c>
       <c r="DQ14" t="n">
-        <v>9.77</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.92</v>
+        <v>5.71</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>58.84</v>
+        <v>60.14</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.23</v>
+        <v>14.64</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.23</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="DZ14" t="n">
-        <v>6</v>
+        <v>5.93</v>
       </c>
       <c r="EA14" t="n">
-        <v>14.08</v>
+        <v>13.72</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="15">
@@ -6616,13 +6616,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
         <v>0.17</v>
@@ -6706,139 +6706,139 @@
         <v>1.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG15" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>66</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>69.88</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK15" t="n">
         <v>0.71</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>133.86</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>70</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>9.57</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>71.70999999999999</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>14.57</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>8.57</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>16</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>9.23</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>0.77</v>
       </c>
       <c r="BL15" t="n">
         <v>1</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.92</v>
+        <v>4.86</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT15" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BU15" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV15" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW15" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BX15" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BY15" t="n">
         <v>1.22</v>
@@ -6847,22 +6847,22 @@
         <v>1.23</v>
       </c>
       <c r="CA15" t="n">
-        <v>6.17</v>
+        <v>6.03</v>
       </c>
       <c r="CB15" t="n">
-        <v>6.66</v>
+        <v>6.5</v>
       </c>
       <c r="CC15" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="CD15" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CE15" t="n">
         <v>1.21</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CG15" t="n">
         <v>3.98</v>
@@ -6871,37 +6871,37 @@
         <v>1.73</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="CK15" t="n">
         <v>1.52</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CM15" t="n">
         <v>2.37</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CO15" t="n">
         <v>1.12</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CR15" t="n">
         <v>1.34</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CT15" t="n">
         <v>3.34</v>
@@ -6910,104 +6910,104 @@
         <v>1.76</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="CW15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CY15" t="n">
         <v>1.89</v>
       </c>
-      <c r="CX15" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="CY15" t="n">
-        <v>1.88</v>
-      </c>
       <c r="CZ15" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="DB15" t="inlineStr"/>
       <c r="DC15" t="n">
         <v>1.52</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF15" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="DH15" t="n">
-        <v>140.46</v>
+        <v>137.5</v>
       </c>
       <c r="DI15" t="n">
         <v>-0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="DK15" t="n">
-        <v>6.46</v>
+        <v>6.29</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="DM15" t="n">
-        <v>75.39</v>
+        <v>72.72</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="DP15" t="n">
-        <v>9.85</v>
+        <v>10.07</v>
       </c>
       <c r="DQ15" t="n">
-        <v>8.92</v>
+        <v>9</v>
       </c>
       <c r="DR15" t="n">
-        <v>4.38</v>
+        <v>4.57</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>71.77</v>
+        <v>70.72</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>17.85</v>
+        <v>17.79</v>
       </c>
       <c r="DY15" t="n">
-        <v>11.08</v>
+        <v>11.21</v>
       </c>
       <c r="DZ15" t="n">
-        <v>6.77</v>
+        <v>6.57</v>
       </c>
       <c r="EA15" t="n">
         <v>18</v>
       </c>
       <c r="EB15" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="16">
@@ -7017,10 +7017,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -7029,82 +7029,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="G16" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="H16" t="n">
-        <v>99.33</v>
+        <v>99.14</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="K16" t="n">
-        <v>6.5</v>
+        <v>6.14</v>
       </c>
       <c r="L16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="M16" t="n">
-        <v>54.67</v>
+        <v>50.71</v>
       </c>
       <c r="N16" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="O16" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="P16" t="n">
-        <v>11.83</v>
+        <v>11.71</v>
       </c>
       <c r="Q16" t="n">
-        <v>11.5</v>
+        <v>12.14</v>
       </c>
       <c r="R16" t="n">
-        <v>5.5</v>
+        <v>5.71</v>
       </c>
       <c r="S16" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="T16" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="U16" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="V16" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>57.17</v>
+        <v>56.86</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z16" t="n">
-        <v>16.17</v>
+        <v>15.43</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.67</v>
+        <v>11.29</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.5</v>
+        <v>4.14</v>
       </c>
       <c r="AC16" t="n">
-        <v>15.83</v>
+        <v>16.29</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7188,70 +7188,70 @@
         <v>1.57</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.46</v>
+        <v>3.36</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.08</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.46</v>
+        <v>3.36</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BL16" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.23</v>
+        <v>4</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.38</v>
+        <v>4.5</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT16" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BU16" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BV16" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BW16" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BX16" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY16" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.83</v>
+        <v>3.81</v>
       </c>
       <c r="CC16" t="n">
         <v>4.58</v>
@@ -7260,31 +7260,31 @@
         <v>4.3</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CN16" t="n">
         <v>1.76</v>
@@ -7293,31 +7293,31 @@
         <v>1.23</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="CR16" t="n">
         <v>1.35</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CY16" t="n">
         <v>2.08</v>
@@ -7326,91 +7326,91 @@
         <v>2.21</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>90.64</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>41.64</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>54.64</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>17.36</v>
+      </c>
+      <c r="EB16" t="n">
         <v>1.38</v>
       </c>
-      <c r="DG16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="DH16" t="n">
-        <v>90.06999999999999</v>
-      </c>
-      <c r="DI16" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="DJ16" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="DK16" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="DL16" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="DM16" t="n">
-        <v>42.77</v>
-      </c>
-      <c r="DN16" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="DO16" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="DP16" t="n">
-        <v>11.31</v>
-      </c>
-      <c r="DQ16" t="n">
-        <v>11.23</v>
-      </c>
-      <c r="DR16" t="n">
-        <v>7.38</v>
-      </c>
-      <c r="DS16" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="DT16" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="DU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV16" t="n">
-        <v>54.62</v>
-      </c>
-      <c r="DW16" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="DX16" t="n">
-        <v>12.77</v>
-      </c>
-      <c r="DY16" t="n">
-        <v>8.77</v>
-      </c>
-      <c r="DZ16" t="n">
-        <v>4</v>
-      </c>
-      <c r="EA16" t="n">
-        <v>17.23</v>
-      </c>
-      <c r="EB16" t="n">
-        <v>1.4</v>
-      </c>
       <c r="EC16" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="17">
@@ -7567,7 +7567,7 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>52.57</v>
+        <v>52.43</v>
       </c>
       <c r="AZ17" t="n">
         <v>0.29</v>
@@ -7792,7 +7792,7 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50.86</v>
+        <v>50.78</v>
       </c>
       <c r="DW17" t="n">
         <v>0.22</v>
@@ -7823,10 +7823,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
         <v>7</v>
@@ -7835,82 +7835,82 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="G18" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="H18" t="n">
-        <v>98.83</v>
+        <v>99</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M18" t="n">
+        <v>39.71</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P18" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="T18" t="n">
         <v>2</v>
       </c>
-      <c r="K18" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="M18" t="n">
-        <v>39.67</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1</v>
-      </c>
-      <c r="P18" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>14.33</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7.17</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.17</v>
-      </c>
       <c r="U18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>51.67</v>
+        <v>52.43</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z18" t="n">
-        <v>12.33</v>
+        <v>12.57</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.5</v>
+        <v>6.71</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.83</v>
+        <v>5.86</v>
       </c>
       <c r="AC18" t="n">
-        <v>13.33</v>
+        <v>14.43</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7994,67 +7994,67 @@
         <v>2.43</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="BH18" t="n">
-        <v>7.46</v>
+        <v>7.29</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="BN18" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BP18" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.62</v>
+        <v>4.43</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT18" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU18" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BV18" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BW18" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX18" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.83</v>
+        <v>3.81</v>
       </c>
       <c r="CB18" t="n">
         <v>3.9</v>
@@ -8069,31 +8069,31 @@
         <v>1.32</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CH18" t="n">
         <v>1.49</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CJ18" t="n">
         <v>1.7</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CO18" t="n">
         <v>1.22</v>
@@ -8102,16 +8102,16 @@
         <v>1.73</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="CU18" t="n">
         <v>1.52</v>
@@ -8135,88 +8135,88 @@
         <v>1.76</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="DC18" t="n">
         <v>1.79</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="DH18" t="n">
-        <v>96.45999999999999</v>
+        <v>96.72</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.23</v>
+        <v>3.36</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="DM18" t="n">
-        <v>40.69</v>
+        <v>40.64</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="DO18" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DP18" t="n">
-        <v>11.62</v>
+        <v>11.64</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.85</v>
+        <v>13.86</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.15</v>
+        <v>7.14</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>50.23</v>
+        <v>50.72</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.46</v>
+        <v>11.64</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.93</v>
+        <v>7</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.54</v>
+        <v>4.65</v>
       </c>
       <c r="EA18" t="n">
-        <v>15.61</v>
+        <v>16</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -8226,13 +8226,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
         <v>0.29</v>
@@ -8319,136 +8319,136 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.67</v>
+        <v>3.29</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AI19" t="n">
-        <v>92.67</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>4.17</v>
+        <v>3.71</v>
       </c>
       <c r="AL19" t="n">
-        <v>4.67</v>
+        <v>4.14</v>
       </c>
       <c r="AM19" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>38.86</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>40.43</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BJ19" t="n">
         <v>0.5</v>
       </c>
-      <c r="AN19" t="n">
-        <v>41.83</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="AT19" t="n">
+      <c r="BK19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL19" t="n">
         <v>1</v>
       </c>
-      <c r="AU19" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>43.33</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>16.17</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>10.38</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>0.92</v>
-      </c>
       <c r="BM19" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="BO19" t="n">
         <v>1</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.77</v>
+        <v>4.57</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.62</v>
+        <v>5.79</v>
       </c>
       <c r="BR19" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS19" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT19" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BU19" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BV19" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW19" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX19" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BY19" t="n">
         <v>2.75</v>
@@ -8457,31 +8457,31 @@
         <v>2.8</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.69</v>
+        <v>3.72</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.4</v>
+        <v>3.63</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.46</v>
+        <v>3.72</v>
       </c>
       <c r="CE19" t="n">
         <v>1.36</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.8</v>
@@ -8490,22 +8490,22 @@
         <v>1.6</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CO19" t="n">
         <v>1.28</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CR19" t="n">
         <v>1.41</v>
@@ -8520,10 +8520,10 @@
         <v>1.43</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CX19" t="n">
         <v>1.62</v>
@@ -8532,7 +8532,7 @@
         <v>2.05</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DA19" t="n">
         <v>1.78</v>
@@ -8541,85 +8541,85 @@
         <v>1.33</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF19" t="n">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="DH19" t="n">
-        <v>94.69</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.23</v>
+        <v>4.92</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DM19" t="n">
-        <v>47.77</v>
+        <v>45.86</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.23</v>
+        <v>13.92</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.46</v>
+        <v>11.14</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.08</v>
+        <v>6.5</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>43.69</v>
+        <v>42.22</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX19" t="n">
-        <v>13.54</v>
+        <v>13</v>
       </c>
       <c r="DY19" t="n">
-        <v>9.619999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.92</v>
+        <v>3.93</v>
       </c>
       <c r="EA19" t="n">
-        <v>17</v>
+        <v>16.64</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="F4" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="G4" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="H4" t="n">
-        <v>100.14</v>
+        <v>100</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="L4" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="M4" t="n">
-        <v>41.29</v>
+        <v>39.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="O4" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="P4" t="n">
-        <v>12.86</v>
+        <v>13.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.43</v>
+        <v>10.12</v>
       </c>
       <c r="R4" t="n">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="S4" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="T4" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="U4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>44.57</v>
+        <v>44.12</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="Z4" t="n">
-        <v>15.71</v>
+        <v>15.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>10.71</v>
+        <v>10.38</v>
       </c>
       <c r="AB4" t="n">
-        <v>5</v>
+        <v>4.88</v>
       </c>
       <c r="AC4" t="n">
-        <v>17.43</v>
+        <v>17.62</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,70 +2356,70 @@
         <v>2</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.07</v>
+        <v>2.93</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.640000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.07</v>
+        <v>2.93</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.86</v>
+        <v>4.8</v>
       </c>
       <c r="BR4" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS4" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BT4" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BU4" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV4" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BW4" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="CC4" t="n">
         <v>3.7</v>
@@ -2428,157 +2428,157 @@
         <v>3.67</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CN4" t="n">
         <v>1.73</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="CR4" t="n">
         <v>1.38</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="CT4" t="n">
         <v>3.12</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DB4" t="n">
         <v>1.32</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="DH4" t="n">
-        <v>94.22</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM4" t="n">
-        <v>39.14</v>
+        <v>38.33</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.5</v>
+        <v>12.8</v>
       </c>
       <c r="DQ4" t="n">
-        <v>10.43</v>
+        <v>10.73</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.07</v>
+        <v>7.47</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.5</v>
+        <v>44.26</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DX4" t="n">
         <v>12.07</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.210000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.36</v>
+        <v>18.4</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="5">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="F7" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="G7" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="H7" t="n">
-        <v>106.86</v>
+        <v>106.5</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="K7" t="n">
-        <v>6.57</v>
+        <v>6</v>
       </c>
       <c r="L7" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="M7" t="n">
-        <v>56</v>
+        <v>53.12</v>
       </c>
       <c r="N7" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="O7" t="n">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>12.43</v>
+        <v>12</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.86</v>
+        <v>12.62</v>
       </c>
       <c r="R7" t="n">
-        <v>5.14</v>
+        <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="T7" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="V7" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>54.29</v>
+        <v>52.75</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>16.57</v>
+        <v>15.12</v>
       </c>
       <c r="AA7" t="n">
-        <v>11.14</v>
+        <v>10.12</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.43</v>
+        <v>5</v>
       </c>
       <c r="AC7" t="n">
-        <v>16</v>
+        <v>16.12</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AF7" t="n">
         <v>0.14</v>
@@ -3565,70 +3565,70 @@
         <v>2.86</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.21</v>
+        <v>3.07</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.64</v>
+        <v>10.4</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.21</v>
+        <v>3.07</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="BM7" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="BO7" t="n">
         <v>1</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.71</v>
+        <v>5.53</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.93</v>
+        <v>4.87</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT7" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BU7" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV7" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BW7" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BX7" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.04</v>
+        <v>4.01</v>
       </c>
       <c r="CC7" t="n">
         <v>2.32</v>
@@ -3649,22 +3649,22 @@
         <v>1.47</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CO7" t="n">
         <v>1.23</v>
@@ -3673,37 +3673,37 @@
         <v>1.79</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="CU7" t="n">
         <v>1.5</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CX7" t="n">
         <v>1.61</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="DB7" t="n">
         <v>1.28</v>
@@ -3715,79 +3715,79 @@
         <v>2.9</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="DH7" t="n">
-        <v>109.28</v>
+        <v>108.93</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.72</v>
+        <v>6.4</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="DM7" t="n">
-        <v>58.22</v>
+        <v>56.53</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.93</v>
+        <v>12.67</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.78</v>
+        <v>12.66</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.21</v>
+        <v>6.07</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>57.22</v>
+        <v>56.2</v>
       </c>
       <c r="DW7" t="n">
         <v>0.14</v>
       </c>
       <c r="DX7" t="n">
-        <v>15.78</v>
+        <v>15.06</v>
       </c>
       <c r="DY7" t="n">
-        <v>10.57</v>
+        <v>10.06</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.21</v>
+        <v>5</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.28</v>
+        <v>17.26</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="8">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
         <v>0.25</v>
@@ -4693,139 +4693,139 @@
         <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AI10" t="n">
-        <v>111.83</v>
+        <v>111.57</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.5</v>
+        <v>4.29</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN10" t="n">
-        <v>51</v>
+        <v>49.71</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.67</v>
+        <v>14.71</v>
       </c>
       <c r="AR10" t="n">
-        <v>9.83</v>
+        <v>10.86</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.33</v>
+        <v>6.86</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>55</v>
+        <v>55.57</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BA10" t="n">
-        <v>11.17</v>
+        <v>11</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.5</v>
+        <v>7.57</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.67</v>
+        <v>3.43</v>
       </c>
       <c r="BD10" t="n">
-        <v>21.83</v>
+        <v>21.14</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.33</v>
+        <v>3.43</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.64</v>
+        <v>3.47</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.140000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.64</v>
+        <v>3.47</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BP10" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT10" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BU10" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BV10" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BW10" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX10" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY10" t="n">
         <v>2.04</v>
@@ -4834,16 +4834,16 @@
         <v>2.07</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.42</v>
+        <v>4.37</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.43</v>
+        <v>4.39</v>
       </c>
       <c r="CC10" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="CD10" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CE10" t="n">
         <v>1.25</v>
@@ -4858,7 +4858,7 @@
         <v>1.62</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.58</v>
@@ -4879,7 +4879,7 @@
         <v>1.15</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CQ10" t="n">
         <v>2.34</v>
@@ -4897,7 +4897,7 @@
         <v>1.68</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CW10" t="n">
         <v>1.62</v>
@@ -4912,89 +4912,89 @@
         <v>2.33</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DB10" t="inlineStr"/>
       <c r="DC10" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="DH10" t="n">
-        <v>109.86</v>
+        <v>109.87</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.43</v>
+        <v>4.34</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM10" t="n">
-        <v>49.5</v>
+        <v>49</v>
       </c>
       <c r="DN10" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.93</v>
+        <v>13.06</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.29</v>
+        <v>11.67</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.93</v>
+        <v>7.14</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>54.14</v>
+        <v>54.47</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.72</v>
+        <v>12.54</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.57</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.78</v>
+        <v>20.53</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="11">
@@ -6213,13 +6213,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
         <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
         <v>0.14</v>
@@ -6306,49 +6306,49 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="AI14" t="n">
-        <v>96.86</v>
+        <v>100.12</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AK14" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.86</v>
+        <v>5.75</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AN14" t="n">
-        <v>42.14</v>
+        <v>44.12</v>
       </c>
       <c r="AO14" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AQ14" t="n">
         <v>11</v>
       </c>
       <c r="AR14" t="n">
-        <v>11.14</v>
+        <v>10.88</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.14</v>
+        <v>6.38</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6360,82 +6360,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>57.57</v>
+        <v>57.62</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA14" t="n">
-        <v>14.57</v>
+        <v>13.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>9.140000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.43</v>
+        <v>5</v>
       </c>
       <c r="BD14" t="n">
-        <v>13.86</v>
+        <v>15.88</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.07</v>
+        <v>8.93</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.21</v>
+        <v>5.13</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT14" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BU14" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BV14" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW14" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BX14" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY14" t="n">
         <v>1.79</v>
@@ -6444,16 +6444,16 @@
         <v>1.8</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.29</v>
+        <v>4.24</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.41</v>
+        <v>4.35</v>
       </c>
       <c r="CC14" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="CE14" t="n">
         <v>1.3</v>
@@ -6462,22 +6462,22 @@
         <v>2.4</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CH14" t="n">
         <v>1.52</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CK14" t="n">
         <v>1.65</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CM14" t="n">
         <v>2.12</v>
@@ -6489,28 +6489,28 @@
         <v>1.2</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CS14" t="n">
         <v>2.56</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="CU14" t="n">
         <v>1.53</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CX14" t="n">
         <v>1.65</v>
@@ -6531,82 +6531,82 @@
         <v>1.72</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="DE14" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="DH14" t="n">
-        <v>108.93</v>
+        <v>109.86</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.64</v>
+        <v>5.6</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DM14" t="n">
-        <v>51</v>
+        <v>51.47</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DP14" t="n">
-        <v>11.93</v>
+        <v>11.87</v>
       </c>
       <c r="DQ14" t="n">
-        <v>9.779999999999999</v>
+        <v>9.74</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.71</v>
+        <v>5.4</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>60.14</v>
+        <v>60</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.64</v>
+        <v>14.06</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.720000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.93</v>
+        <v>5.67</v>
       </c>
       <c r="EA14" t="n">
-        <v>13.72</v>
+        <v>14.8</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="15">

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
         <v>0.14</v>
@@ -1472,136 +1472,136 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AI2" t="n">
-        <v>63</v>
+        <v>68.12</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN2" t="n">
-        <v>23.43</v>
+        <v>26.38</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.859999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.86</v>
+        <v>10.88</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.289999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>37.29</v>
+        <v>38.88</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.43</v>
+        <v>7.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.14</v>
+        <v>5</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>14.71</v>
+        <v>13.88</v>
       </c>
       <c r="BE2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BO2" t="n">
         <v>0.8</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>9.640000000000001</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0.79</v>
       </c>
       <c r="BP2" t="n">
         <v>4</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.64</v>
+        <v>5.33</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BT2" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BU2" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV2" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BY2" t="n">
         <v>3.61</v>
@@ -1610,22 +1610,22 @@
         <v>3.93</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.45</v>
+        <v>4.39</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.77</v>
+        <v>4.71</v>
       </c>
       <c r="CC2" t="n">
-        <v>10.08</v>
+        <v>9.33</v>
       </c>
       <c r="CD2" t="n">
-        <v>10.61</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="CE2" t="n">
         <v>1.37</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CG2" t="n">
         <v>3.03</v>
@@ -1634,31 +1634,31 @@
         <v>1.45</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="CR2" t="n">
         <v>1.44</v>
@@ -1673,106 +1673,106 @@
         <v>1.48</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CW2" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="DA2" t="n">
         <v>1.75</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="DE2" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.22</v>
+        <v>2.07</v>
       </c>
       <c r="DH2" t="n">
-        <v>69.34999999999999</v>
+        <v>71.66</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.64</v>
+        <v>3.46</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM2" t="n">
-        <v>28.14</v>
+        <v>29.4</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.43</v>
+        <v>11.27</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.08</v>
+        <v>11.07</v>
       </c>
       <c r="DR2" t="n">
-        <v>9.359999999999999</v>
+        <v>9.26</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>40</v>
+        <v>40.67</v>
       </c>
       <c r="DW2" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX2" t="n">
-        <v>8.57</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DY2" t="n">
-        <v>5.42</v>
+        <v>5.33</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.07</v>
+        <v>15.54</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
@@ -1794,79 +1794,79 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="G3" t="n">
         <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>90.29000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="K3" t="n">
-        <v>5.29</v>
+        <v>5.25</v>
       </c>
       <c r="L3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M3" t="n">
-        <v>39.86</v>
+        <v>40.75</v>
       </c>
       <c r="N3" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>13.57</v>
+        <v>13.12</v>
       </c>
       <c r="Q3" t="n">
-        <v>15.57</v>
+        <v>15</v>
       </c>
       <c r="R3" t="n">
-        <v>5.71</v>
+        <v>5.75</v>
       </c>
       <c r="S3" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="T3" t="n">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>43.43</v>
+        <v>42.88</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.71</v>
+        <v>11.12</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.86</v>
+        <v>7.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.86</v>
+        <v>3.38</v>
       </c>
       <c r="AC3" t="n">
-        <v>19.29</v>
+        <v>18.38</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -1953,49 +1953,49 @@
         <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BN3" t="n">
         <v>1.07</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.79</v>
+        <v>3.73</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.71</v>
+        <v>5.67</v>
       </c>
       <c r="BR3" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS3" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BT3" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BU3" t="n">
-        <v>14.29</v>
+        <v>20</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
@@ -2004,19 +2004,19 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.41</v>
+        <v>3.21</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.81</v>
+        <v>3.59</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
       <c r="CC3" t="n">
         <v>5.11</v>
@@ -2025,16 +2025,16 @@
         <v>5.38</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI3" t="n">
         <v>2</v>
@@ -2043,13 +2043,13 @@
         <v>1.8</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CN3" t="n">
         <v>1.82</v>
@@ -2061,7 +2061,7 @@
         <v>1.92</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="CR3" t="n">
         <v>1.4</v>
@@ -2079,13 +2079,13 @@
         <v>2.06</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CX3" t="n">
         <v>1.61</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.29</v>
@@ -2100,79 +2100,79 @@
         <v>1.97</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="DE3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="DH3" t="n">
-        <v>89.93000000000001</v>
+        <v>89.53</v>
       </c>
       <c r="DI3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.71</v>
+        <v>4.73</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM3" t="n">
-        <v>38.5</v>
+        <v>39.07</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.78</v>
+        <v>13.53</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.28</v>
+        <v>14.07</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.64</v>
+        <v>6.6</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>44.28</v>
+        <v>43.93</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.64</v>
+        <v>10.86</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.22</v>
+        <v>7.2</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.43</v>
+        <v>3.67</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.29</v>
+        <v>18.8</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="EC3" t="n">
         <v>2</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>44.12</v>
+        <v>44</v>
       </c>
       <c r="Y4" t="n">
         <v>0.12</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.26</v>
+        <v>44.2</v>
       </c>
       <c r="DW4" t="n">
         <v>0.13</v>
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>7</v>
@@ -2600,82 +2600,82 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="G5" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H5" t="n">
-        <v>98.43000000000001</v>
+        <v>95.88</v>
       </c>
       <c r="I5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J5" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="L5" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="M5" t="n">
-        <v>55.14</v>
+        <v>54.38</v>
       </c>
       <c r="N5" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="P5" t="n">
-        <v>15</v>
+        <v>14.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>13</v>
+        <v>12.88</v>
       </c>
       <c r="R5" t="n">
-        <v>5.57</v>
+        <v>5.75</v>
       </c>
       <c r="S5" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="U5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>50.71</v>
+        <v>50</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>13.86</v>
+        <v>13.75</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.289999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.57</v>
+        <v>4.25</v>
       </c>
       <c r="AC5" t="n">
-        <v>21.57</v>
+        <v>21.62</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>1.57</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.640000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.64</v>
+        <v>3.73</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5</v>
+        <v>4.93</v>
       </c>
       <c r="BR5" t="n">
-        <v>85.70999999999999</v>
+        <v>80</v>
       </c>
       <c r="BS5" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BT5" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BU5" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV5" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.23</v>
+        <v>3.19</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.19</v>
+        <v>4.12</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.17</v>
+        <v>4.11</v>
       </c>
       <c r="CC5" t="n">
         <v>6.9</v>
@@ -2834,19 +2834,19 @@
         <v>1.35</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CK5" t="n">
         <v>1.67</v>
@@ -2864,28 +2864,28 @@
         <v>1.26</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="CR5" t="n">
         <v>1.41</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CX5" t="n">
         <v>1.63</v>
@@ -2903,85 +2903,85 @@
         <v>1.34</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="DH5" t="n">
-        <v>88.72</v>
+        <v>88</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.28</v>
+        <v>4.47</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.28</v>
+        <v>0.4</v>
       </c>
       <c r="DM5" t="n">
-        <v>45.64</v>
+        <v>45.87</v>
       </c>
       <c r="DN5" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="DP5" t="n">
-        <v>14.07</v>
+        <v>13.8</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.86</v>
+        <v>12.8</v>
       </c>
       <c r="DR5" t="n">
         <v>7.07</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>45.92</v>
+        <v>45.87</v>
       </c>
       <c r="DW5" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.72</v>
+        <v>11.8</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.93</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.78</v>
+        <v>3.67</v>
       </c>
       <c r="EA5" t="n">
-        <v>17.86</v>
+        <v>18.13</v>
       </c>
       <c r="EB5" t="n">
         <v>1.34</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
         <v>0.14</v>
@@ -3081,139 +3081,139 @@
         <v>1.86</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.86</v>
+        <v>2.38</v>
       </c>
       <c r="AI6" t="n">
-        <v>83.43000000000001</v>
+        <v>86</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.71</v>
+        <v>4.75</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AN6" t="n">
-        <v>37.86</v>
+        <v>41.25</v>
       </c>
       <c r="AO6" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.86</v>
+        <v>2.38</v>
       </c>
       <c r="AQ6" t="n">
-        <v>14.14</v>
+        <v>14</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.71</v>
+        <v>12.12</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.57</v>
+        <v>8</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>44.29</v>
+        <v>47</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.43</v>
+        <v>8.25</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.57</v>
+        <v>4.75</v>
       </c>
       <c r="BD6" t="n">
-        <v>14.71</v>
+        <v>16</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.64</v>
+        <v>10.8</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BL6" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.14</v>
+        <v>4.33</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.21</v>
+        <v>5.27</v>
       </c>
       <c r="BR6" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS6" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT6" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BU6" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV6" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BY6" t="n">
         <v>2.15</v>
@@ -3228,16 +3228,16 @@
         <v>3.94</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.95</v>
+        <v>2.79</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.05</v>
+        <v>2.89</v>
       </c>
       <c r="CE6" t="n">
         <v>1.31</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CG6" t="n">
         <v>3.3</v>
@@ -3246,25 +3246,25 @@
         <v>1.53</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CK6" t="n">
         <v>1.57</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="CN6" t="n">
         <v>1.78</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CP6" t="n">
         <v>1.72</v>
@@ -3276,31 +3276,31 @@
         <v>1.34</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY6" t="n">
         <v>1.99</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DB6" t="n">
         <v>1.25</v>
@@ -3309,82 +3309,82 @@
         <v>1.71</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.28</v>
+        <v>2.53</v>
       </c>
       <c r="DH6" t="n">
-        <v>82.43000000000001</v>
+        <v>83.87</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.86</v>
+        <v>6.27</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="DM6" t="n">
-        <v>41.64</v>
+        <v>43.2</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.86</v>
+        <v>12.87</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.07</v>
+        <v>11.8</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.72</v>
+        <v>6.53</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>47</v>
+        <v>48.26</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.43</v>
+        <v>13.87</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.279999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.14</v>
+        <v>5.2</v>
       </c>
       <c r="EA6" t="n">
-        <v>15.86</v>
+        <v>16.47</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="7">
@@ -3622,13 +3622,13 @@
         <v>2.24</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CA7" t="n">
         <v>3.81</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="CC7" t="n">
         <v>2.32</v>
@@ -3688,7 +3688,7 @@
         <v>1.5</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CW7" t="n">
         <v>1.73</v>
@@ -3703,7 +3703,7 @@
         <v>2.29</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DB7" t="n">
         <v>1.28</v>
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F8" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="G8" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="H8" t="n">
-        <v>82.43000000000001</v>
+        <v>80.12</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="K8" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.14</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>45.71</v>
+        <v>43.62</v>
       </c>
       <c r="N8" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="O8" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="P8" t="n">
-        <v>10</v>
+        <v>10.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.14</v>
+        <v>14.12</v>
       </c>
       <c r="R8" t="n">
-        <v>5.57</v>
+        <v>5.88</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="T8" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="U8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>43.43</v>
+        <v>43</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>13.14</v>
+        <v>13.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.140000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AB8" t="n">
-        <v>5</v>
+        <v>5.12</v>
       </c>
       <c r="AC8" t="n">
-        <v>14.57</v>
+        <v>14.5</v>
       </c>
       <c r="AD8" t="n">
         <v>1.51</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3968,70 +3968,70 @@
         <v>2.29</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.29</v>
+        <v>3.13</v>
       </c>
       <c r="BH8" t="n">
         <v>7.93</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.29</v>
+        <v>3.13</v>
       </c>
       <c r="BJ8" t="n">
         <v>0.93</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BN8" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>92.86</v>
+        <v>86.67</v>
       </c>
       <c r="BT8" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BU8" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BV8" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW8" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX8" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BY8" t="n">
-        <v>4.06</v>
+        <v>3.96</v>
       </c>
       <c r="BZ8" t="n">
-        <v>4.04</v>
+        <v>4.02</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="CC8" t="n">
         <v>4.2</v>
@@ -4043,16 +4043,16 @@
         <v>1.34</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.09</v>
+        <v>3.06</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.75</v>
@@ -4061,10 +4061,10 @@
         <v>1.66</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CN8" t="n">
         <v>1.69</v>
@@ -4073,37 +4073,37 @@
         <v>1.26</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="CR8" t="n">
         <v>1.42</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CW8" t="n">
         <v>1.81</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DA8" t="n">
         <v>1.69</v>
@@ -4112,85 +4112,85 @@
         <v>1.34</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="DG8" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DH8" t="n">
-        <v>89.06999999999999</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="DI8" t="n">
         <v>0.14</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DM8" t="n">
-        <v>42.78</v>
+        <v>41.87</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="DO8" t="n">
         <v>1</v>
       </c>
       <c r="DP8" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.57</v>
+        <v>15</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.29</v>
+        <v>6.4</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>44.14</v>
+        <v>43.87</v>
       </c>
       <c r="DW8" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX8" t="n">
-        <v>12</v>
+        <v>12.13</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.140000000000001</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="EA8" t="n">
-        <v>15.57</v>
+        <v>15.47</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4290,139 +4290,139 @@
         <v>1.14</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AI9" t="n">
-        <v>75.14</v>
+        <v>75.75</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.29</v>
+        <v>4.12</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AN9" t="n">
-        <v>28.43</v>
+        <v>29.12</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9.710000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR9" t="n">
-        <v>11.71</v>
+        <v>11.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>10.29</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>49.57</v>
+        <v>51</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.43</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.14</v>
+        <v>5.62</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="BD9" t="n">
-        <v>15.43</v>
+        <v>16.12</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.57</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BN9" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.86</v>
+        <v>4.73</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.71</v>
+        <v>4.73</v>
       </c>
       <c r="BR9" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS9" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT9" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BU9" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BV9" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BW9" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX9" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BY9" t="n">
         <v>4.01</v>
@@ -4431,31 +4431,31 @@
         <v>4.02</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.05</v>
+        <v>4.02</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.33</v>
+        <v>4.27</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.98</v>
+        <v>5.7</v>
       </c>
       <c r="CD9" t="n">
-        <v>6.89</v>
+        <v>6.51</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.74</v>
@@ -4464,22 +4464,22 @@
         <v>1.59</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="CR9" t="n">
         <v>1.37</v>
@@ -4494,7 +4494,7 @@
         <v>1.53</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CW9" t="n">
         <v>1.76</v>
@@ -4506,94 +4506,94 @@
         <v>1.98</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="DH9" t="n">
-        <v>75.64</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="DI9" t="n">
         <v>-0.14</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.22</v>
+        <v>4.13</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="DM9" t="n">
-        <v>33</v>
+        <v>33.06</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DO9" t="n">
         <v>1.86</v>
       </c>
       <c r="DP9" t="n">
-        <v>11</v>
+        <v>11.07</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.71</v>
+        <v>11.6</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.220000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>48.43</v>
+        <v>49.27</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.220000000000001</v>
+        <v>8.94</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.14</v>
+        <v>5.86</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.5</v>
+        <v>16.8</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="10">
@@ -4750,7 +4750,7 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>55.57</v>
+        <v>55.71</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.29</v>
@@ -4973,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>54.47</v>
+        <v>54.53</v>
       </c>
       <c r="DW10" t="n">
         <v>0.27</v>
@@ -5004,58 +5004,58 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
         <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F11" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="H11" t="n">
-        <v>83.14</v>
+        <v>83.5</v>
       </c>
       <c r="I11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J11" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="K11" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="L11" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="M11" t="n">
-        <v>34.57</v>
+        <v>33.88</v>
       </c>
       <c r="N11" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="O11" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="P11" t="n">
-        <v>11.57</v>
+        <v>11.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>13</v>
+        <v>12.88</v>
       </c>
       <c r="R11" t="n">
-        <v>9.57</v>
+        <v>9.75</v>
       </c>
       <c r="S11" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
@@ -5070,28 +5070,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>44</v>
+        <v>42.75</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.86</v>
+        <v>10.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="AC11" t="n">
-        <v>19.57</v>
+        <v>19.38</v>
       </c>
       <c r="AD11" t="n">
         <v>1.14</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AF11" t="n">
         <v>0.29</v>
@@ -5175,70 +5175,70 @@
         <v>1.86</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.57</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="BO11" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.43</v>
+        <v>5.53</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.14</v>
+        <v>4.27</v>
       </c>
       <c r="BR11" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS11" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT11" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BU11" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV11" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX11" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.62</v>
+        <v>4.6</v>
       </c>
       <c r="BZ11" t="n">
-        <v>5.23</v>
+        <v>5.22</v>
       </c>
       <c r="CA11" t="n">
         <v>3.91</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="CC11" t="n">
         <v>5.23</v>
@@ -5250,25 +5250,25 @@
         <v>1.35</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.84</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CM11" t="n">
         <v>2.42</v>
@@ -5280,25 +5280,25 @@
         <v>1.26</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="CR11" t="n">
         <v>1.38</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CW11" t="n">
         <v>1.87</v>
@@ -5310,61 +5310,61 @@
         <v>1.9</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="DA11" t="n">
         <v>1.92</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="DH11" t="n">
-        <v>76.56999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.28</v>
+        <v>3.13</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DM11" t="n">
-        <v>28.72</v>
+        <v>28.74</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.64</v>
+        <v>11.4</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.28</v>
+        <v>13.2</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.359999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>42.72</v>
+        <v>42.13</v>
       </c>
       <c r="DW11" t="n">
         <v>0.07000000000000001</v>
@@ -5385,19 +5385,19 @@
         <v>9.93</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="DZ11" t="n">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.36</v>
+        <v>19.27</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="12">
@@ -5407,94 +5407,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
         <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F12" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="H12" t="n">
-        <v>66.14</v>
+        <v>71</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>5.29</v>
+        <v>5.12</v>
       </c>
       <c r="L12" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="M12" t="n">
-        <v>33.86</v>
+        <v>33.62</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="O12" t="n">
         <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>11.71</v>
+        <v>11.62</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.29</v>
+        <v>11.88</v>
       </c>
       <c r="R12" t="n">
-        <v>6.43</v>
+        <v>6.12</v>
       </c>
       <c r="S12" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="T12" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="U12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>47.29</v>
+        <v>47.62</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.43</v>
+        <v>12.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.29</v>
+        <v>7.75</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.14</v>
+        <v>4.88</v>
       </c>
       <c r="AC12" t="n">
-        <v>14</v>
+        <v>14.88</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5578,70 +5578,70 @@
         <v>2.57</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.21</v>
+        <v>3.07</v>
       </c>
       <c r="BH12" t="n">
-        <v>11.21</v>
+        <v>10.8</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.21</v>
+        <v>3.07</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.43</v>
+        <v>4.4</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.71</v>
+        <v>5.4</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BT12" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BU12" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BV12" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW12" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX12" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.05</v>
+        <v>4.03</v>
       </c>
       <c r="CC12" t="n">
         <v>3.48</v>
@@ -5653,16 +5653,16 @@
         <v>1.31</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CH12" t="n">
         <v>1.51</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.66</v>
@@ -5671,7 +5671,7 @@
         <v>1.47</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CM12" t="n">
         <v>2.45</v>
@@ -5686,7 +5686,7 @@
         <v>1.75</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CR12" t="n">
         <v>1.36</v>
@@ -5701,16 +5701,16 @@
         <v>1.54</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CX12" t="n">
         <v>1.55</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.41</v>
@@ -5719,88 +5719,88 @@
         <v>1.96</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="DH12" t="n">
-        <v>76</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="DI12" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="DK12" t="n">
-        <v>5</v>
+        <v>4.93</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DM12" t="n">
-        <v>35</v>
+        <v>34.8</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.08</v>
+        <v>11.87</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.21</v>
+        <v>7</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.08</v>
+        <v>47.27</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.22</v>
+        <v>11.4</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.21</v>
+        <v>7.47</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="EA12" t="n">
-        <v>15.22</v>
+        <v>15.6</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="13">
@@ -5810,13 +5810,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5900,52 +5900,52 @@
         <v>1.57</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG13" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.71</v>
+        <v>3.75</v>
       </c>
       <c r="AI13" t="n">
-        <v>84.14</v>
+        <v>87.38</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AL13" t="n">
-        <v>6.71</v>
+        <v>6.75</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN13" t="n">
-        <v>45.29</v>
+        <v>44.88</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="AP13" t="n">
         <v>3</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14.43</v>
+        <v>15.25</v>
       </c>
       <c r="AR13" t="n">
-        <v>15.29</v>
+        <v>14.88</v>
       </c>
       <c r="AS13" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5957,82 +5957,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>54.29</v>
+        <v>55</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>11.43</v>
+        <v>11</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.14</v>
+        <v>6.62</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.29</v>
+        <v>4.38</v>
       </c>
       <c r="BD13" t="n">
-        <v>15.71</v>
+        <v>16.88</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.57</v>
+        <v>2.47</v>
       </c>
       <c r="BH13" t="n">
-        <v>11.29</v>
+        <v>11.07</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.57</v>
+        <v>2.47</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BO13" t="n">
         <v>1.07</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.36</v>
+        <v>4.33</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.93</v>
+        <v>6.73</v>
       </c>
       <c r="BR13" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS13" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BT13" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU13" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV13" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW13" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX13" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BY13" t="n">
         <v>2.18</v>
@@ -6041,34 +6041,34 @@
         <v>2.47</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="CH13" t="n">
         <v>1.5</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CK13" t="n">
         <v>1.52</v>
@@ -6077,100 +6077,100 @@
         <v>1.94</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="CW13" t="n">
         <v>1.75</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DD13" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.64</v>
+        <v>3.67</v>
       </c>
       <c r="DH13" t="n">
-        <v>89.28</v>
+        <v>90.67</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="DK13" t="n">
-        <v>6.5</v>
+        <v>6.54</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DM13" t="n">
-        <v>45.36</v>
+        <v>45.14</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="DO13" t="n">
         <v>2.86</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.14</v>
+        <v>14.6</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.93</v>
+        <v>13.8</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.57</v>
+        <v>6.4</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6182,28 +6182,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>55.36</v>
+        <v>55.67</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.64</v>
+        <v>12.33</v>
       </c>
       <c r="DY13" t="n">
-        <v>8</v>
+        <v>7.67</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.65</v>
+        <v>4.67</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.14</v>
+        <v>16.74</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="14">
@@ -6616,94 +6616,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
         <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F15" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="G15" t="n">
-        <v>4.83</v>
+        <v>5.14</v>
       </c>
       <c r="H15" t="n">
-        <v>148.17</v>
+        <v>144.14</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="K15" t="n">
-        <v>7</v>
+        <v>7.14</v>
       </c>
       <c r="L15" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="M15" t="n">
-        <v>81.67</v>
+        <v>79.14</v>
       </c>
       <c r="N15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="O15" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>10.17</v>
+        <v>10</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.83</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>4.33</v>
+        <v>4.43</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="U15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>71.83</v>
+        <v>71</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.67</v>
+        <v>21.43</v>
       </c>
       <c r="AA15" t="n">
-        <v>14</v>
+        <v>13.57</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.67</v>
+        <v>7.86</v>
       </c>
       <c r="AC15" t="n">
-        <v>20.33</v>
+        <v>19</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AF15" t="n">
         <v>0.25</v>
@@ -6787,70 +6787,70 @@
         <v>1.12</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.79</v>
+        <v>2.93</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.140000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.79</v>
+        <v>2.93</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL15" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.29</v>
+        <v>4.4</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.86</v>
+        <v>5.07</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT15" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BU15" t="n">
-        <v>21.43</v>
+        <v>26.67</v>
       </c>
       <c r="BV15" t="n">
-        <v>21.43</v>
+        <v>26.67</v>
       </c>
       <c r="BW15" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX15" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CA15" t="n">
-        <v>6.03</v>
+        <v>6.05</v>
       </c>
       <c r="CB15" t="n">
-        <v>6.5</v>
+        <v>6.49</v>
       </c>
       <c r="CC15" t="n">
         <v>1.5</v>
@@ -6859,22 +6859,22 @@
         <v>1.56</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.98</v>
+        <v>4.06</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CK15" t="n">
         <v>1.52</v>
@@ -6889,125 +6889,125 @@
         <v>1.84</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CR15" t="n">
         <v>1.34</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CT15" t="n">
         <v>3.34</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CX15" t="n">
         <v>1.57</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.37</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DB15" t="inlineStr"/>
       <c r="DC15" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.85</v>
+        <v>4.06</v>
       </c>
       <c r="DH15" t="n">
-        <v>137.5</v>
+        <v>136.33</v>
       </c>
       <c r="DI15" t="n">
         <v>-0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="DK15" t="n">
-        <v>6.29</v>
+        <v>6.4</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM15" t="n">
-        <v>72.72</v>
+        <v>72.13</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.07</v>
+        <v>10</v>
       </c>
       <c r="DQ15" t="n">
-        <v>9</v>
+        <v>8.73</v>
       </c>
       <c r="DR15" t="n">
-        <v>4.57</v>
+        <v>4.6</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>70.72</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>17.79</v>
+        <v>17.94</v>
       </c>
       <c r="DY15" t="n">
-        <v>11.21</v>
+        <v>11.2</v>
       </c>
       <c r="DZ15" t="n">
-        <v>6.57</v>
+        <v>6.73</v>
       </c>
       <c r="EA15" t="n">
-        <v>18</v>
+        <v>17.53</v>
       </c>
       <c r="EB15" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="16">
@@ -7017,13 +7017,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
         <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7110,136 +7110,136 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AH16" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AI16" t="n">
-        <v>82.14</v>
+        <v>82</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.43</v>
+        <v>3.25</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AN16" t="n">
-        <v>32.57</v>
+        <v>31.75</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.86</v>
+        <v>11.12</v>
       </c>
       <c r="AR16" t="n">
-        <v>11</v>
+        <v>10.88</v>
       </c>
       <c r="AS16" t="n">
-        <v>9</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AT16" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>52.43</v>
+        <v>52.75</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.859999999999999</v>
+        <v>10.25</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.29</v>
+        <v>6.88</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.57</v>
+        <v>3.38</v>
       </c>
       <c r="BD16" t="n">
-        <v>18.43</v>
+        <v>18.25</v>
       </c>
       <c r="BE16" t="n">
         <v>1.12</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.36</v>
+        <v>3.13</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.859999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.36</v>
+        <v>3.13</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BL16" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="BP16" t="n">
-        <v>4</v>
+        <v>4.07</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="BR16" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="BS16" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BT16" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU16" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV16" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BW16" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BX16" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY16" t="n">
         <v>1.96</v>
@@ -7248,28 +7248,28 @@
         <v>2.08</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.77</v>
+        <v>3.73</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.81</v>
+        <v>3.78</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.58</v>
+        <v>4.34</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.3</v>
+        <v>4.09</v>
       </c>
       <c r="CE16" t="n">
         <v>1.31</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI16" t="n">
         <v>2.14</v>
@@ -7278,49 +7278,49 @@
         <v>1.68</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CL16" t="n">
         <v>2.13</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CX16" t="n">
         <v>1.66</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.21</v>
@@ -7329,85 +7329,85 @@
         <v>1.75</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="DH16" t="n">
-        <v>90.64</v>
+        <v>90</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ16" t="n">
         <v>2.14</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.78</v>
+        <v>4.6</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DM16" t="n">
-        <v>41.64</v>
+        <v>40.6</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.28</v>
+        <v>11.4</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.57</v>
+        <v>11.47</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.36</v>
+        <v>7.67</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>54.64</v>
+        <v>54.67</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.64</v>
+        <v>12.67</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.789999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.86</v>
+        <v>3.73</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.36</v>
+        <v>17.34</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="EC16" t="n">
         <v>1.93</v>
@@ -7420,13 +7420,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
         <v>0.14</v>
@@ -7510,139 +7510,139 @@
         <v>2</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.86</v>
+        <v>1.12</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AI17" t="n">
-        <v>90.86</v>
+        <v>87.62</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>35.12</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="AT17" t="n">
         <v>2</v>
       </c>
-      <c r="AL17" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>11.14</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>11.43</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>8.859999999999999</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AU17" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>52.43</v>
+        <v>50.12</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="BA17" t="n">
-        <v>9.43</v>
+        <v>9</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.86</v>
+        <v>5.62</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.57</v>
+        <v>3.38</v>
       </c>
       <c r="BD17" t="n">
-        <v>19</v>
+        <v>18.12</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="BH17" t="n">
-        <v>10</v>
+        <v>10.27</v>
       </c>
       <c r="BI17" t="n">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.43</v>
+        <v>0.53</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.07</v>
+        <v>4.2</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.57</v>
+        <v>4.8</v>
       </c>
       <c r="BR17" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS17" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT17" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BU17" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BV17" t="n">
-        <v>14.29</v>
+        <v>20</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BY17" t="n">
         <v>2.51</v>
@@ -7651,31 +7651,31 @@
         <v>2.65</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.51</v>
+        <v>3.7</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.61</v>
+        <v>3.79</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.43</v>
+        <v>3.26</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.53</v>
+        <v>3.33</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.59</v>
+        <v>2.54</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.13</v>
+        <v>3.26</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.63</v>
@@ -7684,34 +7684,34 @@
         <v>1.62</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.93</v>
+        <v>2.86</v>
       </c>
       <c r="CR17" t="n">
         <v>1.36</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="CT17" t="n">
         <v>3.19</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="CV17" t="n">
         <v>2.33</v>
@@ -7720,7 +7720,7 @@
         <v>1.67</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CY17" t="n">
         <v>1.98</v>
@@ -7735,85 +7735,85 @@
         <v>1.28</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.06</v>
+        <v>2.97</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="DH17" t="n">
-        <v>96.72</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.29</v>
+        <v>5.34</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DM17" t="n">
-        <v>45.28</v>
+        <v>44.2</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.08</v>
+        <v>2.27</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.42</v>
+        <v>11</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.22</v>
+        <v>12</v>
       </c>
       <c r="DR17" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="DS17" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DT17" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV17" t="n">
+        <v>49.66</v>
+      </c>
+      <c r="DW17" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="DX17" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="DY17" t="n">
         <v>8.07</v>
       </c>
-      <c r="DS17" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DT17" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV17" t="n">
-        <v>50.78</v>
-      </c>
-      <c r="DW17" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DX17" t="n">
-        <v>13.07</v>
-      </c>
-      <c r="DY17" t="n">
-        <v>8.359999999999999</v>
-      </c>
       <c r="DZ17" t="n">
-        <v>4.72</v>
+        <v>4.54</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.36</v>
+        <v>17.93</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="18">
@@ -7823,13 +7823,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
         <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7916,136 +7916,136 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AI18" t="n">
-        <v>94.43000000000001</v>
+        <v>98.12</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN18" t="n">
-        <v>41.57</v>
+        <v>41.62</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12.43</v>
+        <v>12.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>13.43</v>
+        <v>14.38</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.14</v>
+        <v>6.88</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>49</v>
+        <v>51.88</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BA18" t="n">
-        <v>10.71</v>
+        <v>9.75</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.29</v>
+        <v>6.75</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.43</v>
+        <v>3</v>
       </c>
       <c r="BD18" t="n">
-        <v>17.57</v>
+        <v>17</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="BH18" t="n">
-        <v>7.29</v>
+        <v>7</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BN18" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BP18" t="n">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT18" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BU18" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV18" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BW18" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX18" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY18" t="n">
         <v>2.15</v>
@@ -8054,25 +8054,25 @@
         <v>2.14</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.81</v>
+        <v>3.76</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="CC18" t="n">
-        <v>4.09</v>
+        <v>3.92</v>
       </c>
       <c r="CD18" t="n">
-        <v>4.25</v>
+        <v>4.07</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CH18" t="n">
         <v>1.49</v>
@@ -8084,13 +8084,13 @@
         <v>1.7</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CN18" t="n">
         <v>1.76</v>
@@ -8099,25 +8099,25 @@
         <v>1.22</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CW18" t="n">
         <v>1.71</v>
@@ -8138,85 +8138,85 @@
         <v>1.29</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DH18" t="n">
-        <v>96.72</v>
+        <v>98.53</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.36</v>
+        <v>3.26</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM18" t="n">
-        <v>40.64</v>
+        <v>40.73</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DP18" t="n">
-        <v>11.64</v>
+        <v>11.73</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.86</v>
+        <v>14.34</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.14</v>
+        <v>7</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>50.72</v>
+        <v>52.14</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.64</v>
+        <v>11.07</v>
       </c>
       <c r="DY18" t="n">
-        <v>7</v>
+        <v>6.73</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.65</v>
+        <v>4.33</v>
       </c>
       <c r="EA18" t="n">
-        <v>16</v>
+        <v>15.8</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="EC18" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="19">
@@ -8226,94 +8226,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F19" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="G19" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="H19" t="n">
-        <v>96.43000000000001</v>
+        <v>92.88</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="K19" t="n">
-        <v>5.71</v>
+        <v>5.12</v>
       </c>
       <c r="L19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M19" t="n">
-        <v>52.86</v>
+        <v>48.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0.14</v>
+        <v>0.38</v>
       </c>
       <c r="O19" t="n">
-        <v>2.86</v>
+        <v>2.5</v>
       </c>
       <c r="P19" t="n">
-        <v>12.71</v>
+        <v>13.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.57</v>
+        <v>11.75</v>
       </c>
       <c r="R19" t="n">
-        <v>5</v>
+        <v>5.38</v>
       </c>
       <c r="S19" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="T19" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="U19" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="V19" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>16.29</v>
+        <v>15</v>
       </c>
       <c r="AA19" t="n">
-        <v>11.29</v>
+        <v>10.25</v>
       </c>
       <c r="AB19" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AC19" t="n">
-        <v>17.71</v>
+        <v>17.38</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8397,70 +8397,70 @@
         <v>3.43</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.79</v>
+        <v>2.67</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.36</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.79</v>
+        <v>2.67</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL19" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="BO19" t="n">
         <v>1</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.57</v>
+        <v>4.27</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.79</v>
+        <v>5.6</v>
       </c>
       <c r="BR19" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS19" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BT19" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BU19" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV19" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW19" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX19" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="CC19" t="n">
         <v>3.63</v>
@@ -8472,10 +8472,10 @@
         <v>1.36</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CG19" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CH19" t="n">
         <v>1.43</v>
@@ -8487,13 +8487,13 @@
         <v>1.8</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CL19" t="n">
         <v>2.07</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CN19" t="n">
         <v>1.77</v>
@@ -8511,7 +8511,7 @@
         <v>1.41</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CT19" t="n">
         <v>2.97</v>
@@ -8541,85 +8541,85 @@
         <v>1.33</v>
       </c>
       <c r="DC19" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF19" t="n">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="DH19" t="n">
-        <v>90.93000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.92</v>
+        <v>4.66</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DM19" t="n">
-        <v>45.86</v>
+        <v>44</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.22</v>
+        <v>0.34</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.92</v>
+        <v>14.4</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.14</v>
+        <v>11.26</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>42.22</v>
+        <v>41.27</v>
       </c>
       <c r="DW19" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX19" t="n">
-        <v>13</v>
+        <v>12.53</v>
       </c>
       <c r="DY19" t="n">
-        <v>9.08</v>
+        <v>8.67</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.93</v>
+        <v>3.87</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.64</v>
+        <v>16.54</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -2654,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>50</v>
+        <v>49.88</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>45.87</v>
+        <v>45.8</v>
       </c>
       <c r="DW5" t="n">
         <v>0.07000000000000001</v>
@@ -4025,7 +4025,7 @@
         <v>3.96</v>
       </c>
       <c r="BZ8" t="n">
-        <v>4.02</v>
+        <v>4.01</v>
       </c>
       <c r="CA8" t="n">
         <v>3.78</v>
@@ -4082,10 +4082,10 @@
         <v>1.42</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CU8" t="n">
         <v>1.47</v>
@@ -4112,7 +4112,7 @@
         <v>1.34</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DD8" t="n">
         <v>3.16</v>
@@ -5479,10 +5479,10 @@
         <v>0.12</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.62</v>
+        <v>12.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.75</v>
+        <v>7.62</v>
       </c>
       <c r="AB12" t="n">
         <v>4.88</v>
@@ -5491,7 +5491,7 @@
         <v>14.88</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE12" t="n">
         <v>1.75</v>
@@ -5785,10 +5785,10 @@
         <v>0.13</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.4</v>
+        <v>11.33</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.47</v>
+        <v>7.4</v>
       </c>
       <c r="DZ12" t="n">
         <v>3.94</v>
@@ -5963,19 +5963,19 @@
         <v>0.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>11</v>
+        <v>10.88</v>
       </c>
       <c r="BB13" t="n">
         <v>6.62</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.38</v>
+        <v>4.25</v>
       </c>
       <c r="BD13" t="n">
         <v>16.88</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BF13" t="n">
         <v>2.12</v>
@@ -6044,7 +6044,7 @@
         <v>3.68</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="CC13" t="n">
         <v>2.53</v>
@@ -6098,7 +6098,7 @@
         <v>2.71</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CU13" t="n">
         <v>1.49</v>
@@ -6107,7 +6107,7 @@
         <v>2.19</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CX13" t="n">
         <v>1.58</v>
@@ -6125,7 +6125,7 @@
         <v>1.31</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DD13" t="n">
         <v>3.05</v>
@@ -6188,19 +6188,19 @@
         <v>0.33</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.33</v>
+        <v>12.27</v>
       </c>
       <c r="DY13" t="n">
         <v>7.67</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.67</v>
+        <v>4.6</v>
       </c>
       <c r="EA13" t="n">
         <v>16.74</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="EC13" t="n">
         <v>1.86</v>
@@ -7164,7 +7164,7 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>52.75</v>
+        <v>52.88</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.12</v>
@@ -7389,7 +7389,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>54.67</v>
+        <v>54.74</v>
       </c>
       <c r="DW16" t="n">
         <v>0.13</v>

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F2" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="G2" t="n">
-        <v>2.14</v>
+        <v>2.62</v>
       </c>
       <c r="H2" t="n">
-        <v>75.70999999999999</v>
+        <v>76.25</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="K2" t="n">
-        <v>4.43</v>
+        <v>4.62</v>
       </c>
       <c r="L2" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="M2" t="n">
-        <v>32.86</v>
+        <v>34.25</v>
       </c>
       <c r="N2" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="O2" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.29</v>
+        <v>11.38</v>
       </c>
       <c r="R2" t="n">
-        <v>9.43</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="T2" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>42.71</v>
+        <v>44.12</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.710000000000001</v>
+        <v>11</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.71</v>
+        <v>6.38</v>
       </c>
       <c r="AB2" t="n">
-        <v>4</v>
+        <v>4.62</v>
       </c>
       <c r="AC2" t="n">
-        <v>17.43</v>
+        <v>18.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>1.25</v>
       </c>
       <c r="BG2" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.33</v>
+        <v>9.31</v>
       </c>
       <c r="BI2" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BP2" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.33</v>
+        <v>5.44</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BU2" t="n">
-        <v>13.33</v>
+        <v>18.75</v>
       </c>
       <c r="BV2" t="n">
-        <v>6.67</v>
+        <v>12.5</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.61</v>
+        <v>3.42</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.93</v>
+        <v>3.71</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.39</v>
+        <v>4.31</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.71</v>
+        <v>4.61</v>
       </c>
       <c r="CC2" t="n">
         <v>9.33</v>
@@ -1622,16 +1622,16 @@
         <v>9.859999999999999</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI2" t="n">
         <v>1.83</v>
@@ -1643,7 +1643,7 @@
         <v>1.65</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="CM2" t="n">
         <v>2.13</v>
@@ -1652,31 +1652,31 @@
         <v>1.69</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.32</v>
+        <v>3.39</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CX2" t="n">
         <v>1.67</v>
@@ -1691,88 +1691,88 @@
         <v>1.75</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="DD2" t="n">
         <v>3.13</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.07</v>
+        <v>2.31</v>
       </c>
       <c r="DH2" t="n">
-        <v>71.66</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="DI2" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.46</v>
+        <v>3.62</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DM2" t="n">
-        <v>29.4</v>
+        <v>30.32</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.27</v>
+        <v>11.62</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.07</v>
+        <v>11.13</v>
       </c>
       <c r="DR2" t="n">
-        <v>9.26</v>
+        <v>8.75</v>
       </c>
       <c r="DS2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="DW2" t="n">
         <v>0.06</v>
       </c>
-      <c r="DT2" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>40.67</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>0.07000000000000001</v>
-      </c>
       <c r="DX2" t="n">
-        <v>8.529999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="DY2" t="n">
-        <v>5.33</v>
+        <v>5.69</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.2</v>
+        <v>3.56</v>
       </c>
       <c r="EA2" t="n">
-        <v>15.54</v>
+        <v>16.07</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.99</v>
+        <v>1.06</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.88</v>
+        <v>2.22</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>4.22</v>
       </c>
       <c r="H3" t="n">
-        <v>89.5</v>
+        <v>88.44</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>5.25</v>
+        <v>5.78</v>
       </c>
       <c r="L3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="M3" t="n">
-        <v>40.75</v>
+        <v>43.89</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="P3" t="n">
-        <v>13.12</v>
+        <v>14</v>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>14.33</v>
       </c>
       <c r="R3" t="n">
-        <v>5.75</v>
+        <v>5.33</v>
       </c>
       <c r="S3" t="n">
-        <v>0.88</v>
+        <v>1.22</v>
       </c>
       <c r="T3" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="V3" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>42.88</v>
+        <v>43.11</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.12</v>
+        <v>11.89</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.38</v>
+        <v>3.89</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.38</v>
+        <v>17.89</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="AF3" t="n">
         <v>0.14</v>
@@ -1953,70 +1953,70 @@
         <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.13</v>
+        <v>2.44</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.4</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.13</v>
+        <v>2.44</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.07</v>
+        <v>1.38</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.73</v>
+        <v>3.88</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.67</v>
+        <v>5.75</v>
       </c>
       <c r="BR3" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS3" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BT3" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BU3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="BX3" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.21</v>
+        <v>3.31</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.59</v>
+        <v>3.69</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.84</v>
+        <v>3.81</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.89</v>
+        <v>3.86</v>
       </c>
       <c r="CC3" t="n">
         <v>5.11</v>
@@ -2028,10 +2028,10 @@
         <v>1.37</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="CH3" t="n">
         <v>1.44</v>
@@ -2040,55 +2040,55 @@
         <v>2</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CN3" t="n">
         <v>1.82</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DA3" t="n">
         <v>1.8</v>
@@ -2097,85 +2097,85 @@
         <v>1.33</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="DG3" t="n">
-        <v>3</v>
+        <v>3.19</v>
       </c>
       <c r="DH3" t="n">
-        <v>89.53</v>
+        <v>88.93000000000001</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.4</v>
+        <v>2.69</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.73</v>
+        <v>5.06</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DM3" t="n">
-        <v>39.07</v>
+        <v>40.94</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.53</v>
+        <v>14</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.07</v>
+        <v>13.75</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.6</v>
+        <v>6.31</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.93</v>
+        <v>44</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.27</v>
+        <v>0.38</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.86</v>
+        <v>11.31</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.2</v>
+        <v>7.37</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.67</v>
+        <v>3.94</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.8</v>
+        <v>18.5</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="EC3" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>0.38</v>
@@ -2278,136 +2278,136 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
-        <v>88.29000000000001</v>
+        <v>91.25</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.71</v>
+        <v>3.25</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AN4" t="n">
-        <v>37</v>
+        <v>38.75</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.43</v>
+        <v>0.88</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.14</v>
+        <v>13.38</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.43</v>
+        <v>12</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.14</v>
+        <v>6.62</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>44.43</v>
+        <v>43.75</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.43</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.71</v>
+        <v>5.88</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.71</v>
+        <v>3.25</v>
       </c>
       <c r="BD4" t="n">
-        <v>19.29</v>
+        <v>19.75</v>
       </c>
       <c r="BE4" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="BF4" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.33</v>
+        <v>9.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.8</v>
+        <v>4.88</v>
       </c>
       <c r="BR4" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS4" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT4" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BU4" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BV4" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BW4" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX4" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
         <v>3.14</v>
@@ -2419,19 +2419,19 @@
         <v>3.66</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.67</v>
+        <v>3.73</v>
       </c>
       <c r="CE4" t="n">
         <v>1.34</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CG4" t="n">
         <v>3.15</v>
@@ -2449,22 +2449,22 @@
         <v>1.64</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CO4" t="n">
         <v>1.25</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CR4" t="n">
         <v>1.38</v>
@@ -2488,10 +2488,10 @@
         <v>1.66</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DA4" t="n">
         <v>1.75</v>
@@ -2503,82 +2503,82 @@
         <v>1.89</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="DH4" t="n">
-        <v>94.54000000000001</v>
+        <v>95.62</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.2</v>
+        <v>4.38</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.2</v>
+        <v>0.38</v>
       </c>
       <c r="DM4" t="n">
-        <v>38.33</v>
+        <v>39.12</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.8</v>
+        <v>13.38</v>
       </c>
       <c r="DQ4" t="n">
-        <v>10.73</v>
+        <v>11.06</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.47</v>
+        <v>7.18</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.2</v>
+        <v>43.88</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.07</v>
+        <v>12.18</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.87</v>
+        <v>4.06</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.4</v>
+        <v>18.69</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2681,49 +2681,49 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.86</v>
+        <v>1.12</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AI5" t="n">
-        <v>79</v>
+        <v>77.12</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.57</v>
+        <v>3.62</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>36.14</v>
+        <v>36.75</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AP5" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13.14</v>
+        <v>13.75</v>
       </c>
       <c r="AR5" t="n">
-        <v>12.71</v>
+        <v>12.75</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.57</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>41.14</v>
+        <v>41.38</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.57</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.57</v>
+        <v>6.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="BD5" t="n">
-        <v>14.14</v>
+        <v>14.62</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.67</v>
+        <v>8.69</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.73</v>
+        <v>3.69</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.93</v>
+        <v>5</v>
       </c>
       <c r="BR5" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BS5" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BT5" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV5" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX5" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BY5" t="n">
         <v>2.96</v>
@@ -2819,22 +2819,22 @@
         <v>3.19</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="CB5" t="n">
         <v>4.11</v>
       </c>
       <c r="CC5" t="n">
-        <v>6.9</v>
+        <v>6.77</v>
       </c>
       <c r="CD5" t="n">
-        <v>7.67</v>
+        <v>7.41</v>
       </c>
       <c r="CE5" t="n">
         <v>1.35</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CG5" t="n">
         <v>3.03</v>
@@ -2843,22 +2843,22 @@
         <v>1.44</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CO5" t="n">
         <v>1.26</v>
@@ -2867,7 +2867,7 @@
         <v>1.89</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CR5" t="n">
         <v>1.41</v>
@@ -2912,43 +2912,43 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.73</v>
+        <v>0.87</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="DH5" t="n">
-        <v>88</v>
+        <v>86.5</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.47</v>
+        <v>4.44</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM5" t="n">
-        <v>45.87</v>
+        <v>45.56</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="DP5" t="n">
-        <v>13.8</v>
+        <v>14.07</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.8</v>
+        <v>12.82</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.07</v>
+        <v>7.32</v>
       </c>
       <c r="DS5" t="n">
         <v>0.06</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>45.8</v>
+        <v>45.63</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.8</v>
+        <v>11.68</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.130000000000001</v>
+        <v>8</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.13</v>
+        <v>18.12</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F6" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="G6" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="H6" t="n">
-        <v>81.43000000000001</v>
+        <v>82.75</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="K6" t="n">
-        <v>8</v>
+        <v>7.25</v>
       </c>
       <c r="L6" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M6" t="n">
-        <v>45.43</v>
+        <v>43.62</v>
       </c>
       <c r="N6" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="O6" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="P6" t="n">
-        <v>11.57</v>
+        <v>12.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.43</v>
+        <v>11.62</v>
       </c>
       <c r="R6" t="n">
-        <v>4.86</v>
+        <v>5</v>
       </c>
       <c r="S6" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="T6" t="n">
         <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V6" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>49.71</v>
+        <v>49.25</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.86</v>
+        <v>14.88</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.140000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.71</v>
+        <v>5.62</v>
       </c>
       <c r="AC6" t="n">
-        <v>17</v>
+        <v>17.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AF6" t="n">
         <v>0.12</v>
@@ -3162,70 +3162,70 @@
         <v>2</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.8</v>
+        <v>10.56</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.33</v>
+        <v>4.19</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.27</v>
+        <v>5.25</v>
       </c>
       <c r="BR6" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS6" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT6" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BV6" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.94</v>
+        <v>3.99</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="CC6" t="n">
         <v>2.79</v>
@@ -3234,16 +3234,16 @@
         <v>2.89</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CI6" t="n">
         <v>2.19</v>
@@ -3252,25 +3252,25 @@
         <v>1.65</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="CR6" t="n">
         <v>1.34</v>
@@ -3294,13 +3294,13 @@
         <v>1.58</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.34</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="DB6" t="n">
         <v>1.25</v>
@@ -3312,79 +3312,79 @@
         <v>2.74</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="DH6" t="n">
-        <v>83.87</v>
+        <v>84.38</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.27</v>
+        <v>2.13</v>
       </c>
       <c r="DK6" t="n">
-        <v>6.27</v>
+        <v>6</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM6" t="n">
-        <v>43.2</v>
+        <v>42.44</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.87</v>
+        <v>13.12</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.8</v>
+        <v>11.87</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.53</v>
+        <v>6.5</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>48.26</v>
+        <v>48.12</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.87</v>
+        <v>13.94</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.67</v>
+        <v>8.75</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.2</v>
+        <v>5.18</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.47</v>
+        <v>16.88</v>
       </c>
       <c r="EB6" t="n">
         <v>1.55</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
         <v>0.12</v>
@@ -3484,52 +3484,52 @@
         <v>1.62</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="AI7" t="n">
-        <v>111.71</v>
+        <v>110.62</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.43</v>
+        <v>3.75</v>
       </c>
       <c r="AL7" t="n">
-        <v>6.86</v>
+        <v>6.38</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="AN7" t="n">
-        <v>60.43</v>
+        <v>58.12</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13.43</v>
+        <v>13</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.71</v>
+        <v>13.75</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.29</v>
+        <v>7.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>60.14</v>
+        <v>59.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.29</v>
+        <v>0.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC7" t="n">
         <v>5</v>
       </c>
       <c r="BD7" t="n">
-        <v>18.57</v>
+        <v>18.25</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.07</v>
+        <v>3.31</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.4</v>
+        <v>10.56</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.07</v>
+        <v>3.31</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.07</v>
+        <v>2.31</v>
       </c>
       <c r="BO7" t="n">
         <v>1</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.53</v>
+        <v>5.56</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.87</v>
+        <v>5</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT7" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BU7" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BV7" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BW7" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BX7" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BY7" t="n">
         <v>2.24</v>
@@ -3625,169 +3625,169 @@
         <v>2.24</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.81</v>
+        <v>3.78</v>
       </c>
       <c r="CB7" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="CD7" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CI7" t="n">
         <v>2.1</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CK7" t="n">
         <v>1.56</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CN7" t="n">
         <v>1.81</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.67</v>
+        <v>2.72</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CY7" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="DH7" t="n">
-        <v>108.93</v>
+        <v>108.56</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.4</v>
+        <v>6.19</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM7" t="n">
-        <v>56.53</v>
+        <v>55.62</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.67</v>
+        <v>12.5</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.66</v>
+        <v>13.18</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.07</v>
+        <v>6.25</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>56.2</v>
+        <v>56.12</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="DX7" t="n">
-        <v>15.06</v>
+        <v>14.56</v>
       </c>
       <c r="DY7" t="n">
-        <v>10.06</v>
+        <v>9.56</v>
       </c>
       <c r="DZ7" t="n">
         <v>5</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.26</v>
+        <v>17.19</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
         <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
         <v>0.12</v>
@@ -3890,136 +3890,136 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AI8" t="n">
-        <v>95.70999999999999</v>
+        <v>91.75</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AN8" t="n">
-        <v>39.86</v>
+        <v>37.62</v>
       </c>
       <c r="AO8" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR8" t="n">
-        <v>16</v>
+        <v>14.75</v>
       </c>
       <c r="AS8" t="n">
-        <v>7</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AT8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>43.88</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BF8" t="n">
         <v>2</v>
       </c>
-      <c r="AU8" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>44.86</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>10.86</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>16.57</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>2.29</v>
-      </c>
       <c r="BG8" t="n">
-        <v>3.13</v>
+        <v>2.94</v>
       </c>
       <c r="BH8" t="n">
-        <v>7.93</v>
+        <v>8.31</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.13</v>
+        <v>2.94</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.27</v>
+        <v>3.62</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.13</v>
+        <v>4.19</v>
       </c>
       <c r="BR8" t="n">
-        <v>100</v>
+        <v>93.75</v>
       </c>
       <c r="BS8" t="n">
-        <v>86.67</v>
+        <v>81.25</v>
       </c>
       <c r="BT8" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BU8" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BV8" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX8" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
         <v>3.96</v>
@@ -4028,22 +4028,22 @@
         <v>4.01</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.2</v>
+        <v>4.26</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.48</v>
+        <v>4.49</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CG8" t="n">
         <v>3.06</v>
@@ -4052,40 +4052,40 @@
         <v>1.45</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.75</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CO8" t="n">
         <v>1.26</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="CU8" t="n">
         <v>1.47</v>
@@ -4097,22 +4097,22 @@
         <v>1.81</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="DB8" t="n">
         <v>1.34</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DD8" t="n">
         <v>3.16</v>
@@ -4121,43 +4121,43 @@
         <v>0.06</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="DH8" t="n">
-        <v>87.40000000000001</v>
+        <v>85.94</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DM8" t="n">
-        <v>41.87</v>
+        <v>40.62</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="DO8" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="DP8" t="n">
-        <v>10.6</v>
+        <v>10.12</v>
       </c>
       <c r="DQ8" t="n">
-        <v>15</v>
+        <v>14.43</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="DS8" t="n">
         <v>0.06</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>43.87</v>
+        <v>43.44</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.13</v>
+        <v>11.93</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.130000000000001</v>
+        <v>8.06</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4</v>
+        <v>3.87</v>
       </c>
       <c r="EA8" t="n">
-        <v>15.47</v>
+        <v>15</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="9">
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
@@ -4212,82 +4212,82 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="G9" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="H9" t="n">
-        <v>76.14</v>
+        <v>76.25</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.29</v>
+        <v>-0.25</v>
       </c>
       <c r="J9" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="K9" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="L9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="M9" t="n">
-        <v>37.57</v>
+        <v>37.62</v>
       </c>
       <c r="N9" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="P9" t="n">
-        <v>12.29</v>
+        <v>12</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.71</v>
+        <v>11.5</v>
       </c>
       <c r="R9" t="n">
-        <v>8.140000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="U9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>47.29</v>
+        <v>46.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z9" t="n">
         <v>9</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.14</v>
+        <v>5.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.86</v>
+        <v>3.12</v>
       </c>
       <c r="AC9" t="n">
-        <v>17.57</v>
+        <v>16.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AF9" t="n">
         <v>0.12</v>
@@ -4371,70 +4371,70 @@
         <v>1.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.27</v>
+        <v>3.38</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.470000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.27</v>
+        <v>3.38</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BN9" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.73</v>
+        <v>4.56</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.73</v>
+        <v>4.81</v>
       </c>
       <c r="BR9" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS9" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT9" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BV9" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BW9" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX9" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
-        <v>4.01</v>
+        <v>4.63</v>
       </c>
       <c r="BZ9" t="n">
-        <v>4.02</v>
+        <v>4.84</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.02</v>
+        <v>4.14</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.27</v>
+        <v>4.43</v>
       </c>
       <c r="CC9" t="n">
         <v>5.7</v>
@@ -4443,28 +4443,28 @@
         <v>6.51</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CK9" t="n">
         <v>1.59</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CM9" t="n">
         <v>2.23</v>
@@ -4473,127 +4473,127 @@
         <v>1.79</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="CR9" t="n">
         <v>1.37</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CX9" t="n">
         <v>1.59</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="DB9" t="n">
         <v>1.29</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="DE9" t="n">
         <v>0.06</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="DH9" t="n">
-        <v>75.93000000000001</v>
+        <v>76</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.13</v>
+        <v>4.12</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM9" t="n">
-        <v>33.06</v>
+        <v>33.37</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.07</v>
+        <v>11</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.07</v>
+        <v>9</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>49.27</v>
+        <v>48.75</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX9" t="n">
         <v>8.94</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.86</v>
+        <v>5.75</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.07</v>
+        <v>3.18</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.8</v>
+        <v>16.19</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
         <v>0.25</v>
@@ -4693,139 +4693,139 @@
         <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AI10" t="n">
-        <v>111.57</v>
+        <v>108.75</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.29</v>
+        <v>4.62</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN10" t="n">
-        <v>49.71</v>
+        <v>51.62</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AP10" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.71</v>
+        <v>14.25</v>
       </c>
       <c r="AR10" t="n">
-        <v>10.86</v>
+        <v>10.88</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.86</v>
+        <v>7</v>
       </c>
       <c r="AT10" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>55.71</v>
+        <v>54</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA10" t="n">
-        <v>11</v>
+        <v>11.88</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.57</v>
+        <v>8</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.43</v>
+        <v>3.88</v>
       </c>
       <c r="BD10" t="n">
-        <v>21.14</v>
+        <v>20.25</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.47</v>
+        <v>3.31</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.869999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.47</v>
+        <v>3.31</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.53</v>
+        <v>3.62</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BT10" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BU10" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BV10" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BW10" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX10" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BY10" t="n">
         <v>2.04</v>
@@ -4834,16 +4834,16 @@
         <v>2.07</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.37</v>
+        <v>4.33</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.39</v>
+        <v>4.36</v>
       </c>
       <c r="CC10" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="CD10" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="CE10" t="n">
         <v>1.25</v>
@@ -4852,25 +4852,25 @@
         <v>2.26</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="CH10" t="n">
         <v>1.62</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CK10" t="n">
         <v>1.57</v>
       </c>
       <c r="CL10" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CN10" t="n">
         <v>1.78</v>
@@ -4897,104 +4897,104 @@
         <v>1.68</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="DB10" t="inlineStr"/>
       <c r="DC10" t="n">
         <v>1.56</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="DH10" t="n">
-        <v>109.87</v>
+        <v>108.56</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.34</v>
+        <v>4.5</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DM10" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.06</v>
+        <v>12.93</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.67</v>
+        <v>11.63</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.14</v>
+        <v>7.19</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>54.53</v>
+        <v>53.75</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.54</v>
+        <v>12.88</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.539999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4</v>
+        <v>4.19</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.53</v>
+        <v>20.12</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="11">
@@ -5004,13 +5004,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
         <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
         <v>0.12</v>
@@ -5094,52 +5094,52 @@
         <v>1.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AI11" t="n">
-        <v>70</v>
+        <v>71.5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AN11" t="n">
-        <v>22.86</v>
+        <v>25.25</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AP11" t="n">
         <v>2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>11.71</v>
+        <v>11.88</v>
       </c>
       <c r="AR11" t="n">
-        <v>13.57</v>
+        <v>14</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.140000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5151,82 +5151,82 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>41.43</v>
+        <v>42</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA11" t="n">
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="BB11" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="BD11" t="n">
-        <v>19.14</v>
+        <v>19.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.53</v>
+        <v>5.31</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.27</v>
+        <v>4.44</v>
       </c>
       <c r="BR11" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS11" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT11" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BU11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BV11" t="n">
-        <v>6.67</v>
+        <v>12.5</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX11" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
         <v>4.6</v>
@@ -5235,136 +5235,136 @@
         <v>5.22</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.91</v>
+        <v>3.86</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.07</v>
+        <v>4.02</v>
       </c>
       <c r="CC11" t="n">
-        <v>5.23</v>
+        <v>4.98</v>
       </c>
       <c r="CD11" t="n">
-        <v>5.64</v>
+        <v>5.42</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI11" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="CP11" t="n">
         <v>1.93</v>
       </c>
-      <c r="CJ11" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="CK11" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="CL11" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="CM11" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="CN11" t="n">
+      <c r="CQ11" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CW11" t="n">
         <v>1.88</v>
       </c>
-      <c r="CO11" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="CP11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="CQ11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="CR11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="CS11" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="CT11" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="CU11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="CV11" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="CW11" t="n">
-        <v>1.87</v>
-      </c>
       <c r="CX11" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="DD11" t="n">
         <v>3.14</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="DH11" t="n">
-        <v>77.2</v>
+        <v>77.5</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM11" t="n">
-        <v>28.74</v>
+        <v>29.56</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.2</v>
+        <v>13.44</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.470000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5376,28 +5376,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>42.13</v>
+        <v>42.38</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX11" t="n">
-        <v>9.93</v>
+        <v>9.75</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.4</v>
+        <v>7.12</v>
       </c>
       <c r="DZ11" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.27</v>
+        <v>19.44</v>
       </c>
       <c r="EB11" t="n">
         <v>1.02</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="12">
@@ -5407,13 +5407,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
         <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
         <v>0.25</v>
@@ -5500,136 +5500,136 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>85.86</v>
+        <v>87.75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.71</v>
+        <v>4.75</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN12" t="n">
-        <v>36.14</v>
+        <v>37.12</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.29</v>
+        <v>13.25</v>
       </c>
       <c r="AR12" t="n">
-        <v>11.86</v>
+        <v>12.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>8</v>
+        <v>7.62</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>46.86</v>
+        <v>47.75</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA12" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.14</v>
+        <v>6.75</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="BD12" t="n">
-        <v>16.43</v>
+        <v>17.38</v>
       </c>
       <c r="BE12" t="n">
         <v>1.1</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.8</v>
+        <v>10.56</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BL12" t="n">
         <v>1</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.4</v>
+        <v>5.38</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT12" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BU12" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BV12" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX12" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BY12" t="n">
         <v>2.29</v>
@@ -5638,28 +5638,28 @@
         <v>2.44</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.73</v>
+        <v>3.8</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.03</v>
+        <v>4.07</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.48</v>
+        <v>3.79</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.1</v>
+        <v>5.15</v>
       </c>
       <c r="CE12" t="n">
         <v>1.31</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CI12" t="n">
         <v>2.18</v>
@@ -5680,13 +5680,13 @@
         <v>1.91</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="CR12" t="n">
         <v>1.36</v>
@@ -5704,19 +5704,19 @@
         <v>2.3</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CX12" t="n">
         <v>1.55</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.41</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DB12" t="n">
         <v>1.29</v>
@@ -5728,79 +5728,79 @@
         <v>2.86</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="DH12" t="n">
-        <v>77.93000000000001</v>
+        <v>79.38</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.93</v>
+        <v>4.94</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM12" t="n">
-        <v>34.8</v>
+        <v>35.37</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.4</v>
+        <v>12.43</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.87</v>
+        <v>12.19</v>
       </c>
       <c r="DR12" t="n">
-        <v>7</v>
+        <v>6.87</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.27</v>
+        <v>47.68</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.33</v>
+        <v>11.12</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.4</v>
+        <v>7.18</v>
       </c>
       <c r="DZ12" t="n">
         <v>3.94</v>
       </c>
       <c r="EA12" t="n">
-        <v>15.6</v>
+        <v>16.13</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="13">
@@ -5810,10 +5810,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
         <v>8</v>
@@ -5822,49 +5822,49 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="G13" t="n">
-        <v>3.57</v>
+        <v>3.5</v>
       </c>
       <c r="H13" t="n">
-        <v>94.43000000000001</v>
+        <v>93</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="K13" t="n">
-        <v>6.29</v>
+        <v>6.12</v>
       </c>
       <c r="L13" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="M13" t="n">
-        <v>45.43</v>
+        <v>48.25</v>
       </c>
       <c r="N13" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="P13" t="n">
-        <v>13.86</v>
+        <v>13.88</v>
       </c>
       <c r="Q13" t="n">
-        <v>12.57</v>
+        <v>13.25</v>
       </c>
       <c r="R13" t="n">
-        <v>5.14</v>
+        <v>5.88</v>
       </c>
       <c r="S13" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="T13" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5876,28 +5876,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>56.43</v>
+        <v>56.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.86</v>
+        <v>14.38</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.859999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>5</v>
+        <v>4.88</v>
       </c>
       <c r="AC13" t="n">
-        <v>16.57</v>
+        <v>17.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AF13" t="n">
         <v>0.12</v>
@@ -5981,70 +5981,70 @@
         <v>2.12</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="BH13" t="n">
-        <v>11.07</v>
+        <v>10.94</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL13" t="n">
         <v>1</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.73</v>
+        <v>6.69</v>
       </c>
       <c r="BR13" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS13" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BT13" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BU13" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV13" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW13" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX13" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.47</v>
+        <v>2.37</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="CC13" t="n">
         <v>2.53</v>
@@ -6056,25 +6056,25 @@
         <v>1.32</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CK13" t="n">
         <v>1.52</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CM13" t="n">
         <v>2.38</v>
@@ -6086,10 +6086,10 @@
         <v>1.23</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="CR13" t="n">
         <v>1.37</v>
@@ -6104,7 +6104,7 @@
         <v>1.49</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CW13" t="n">
         <v>1.76</v>
@@ -6113,7 +6113,7 @@
         <v>1.58</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.36</v>
@@ -6122,7 +6122,7 @@
         <v>1.88</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DC13" t="n">
         <v>1.85</v>
@@ -6134,43 +6134,43 @@
         <v>0.06</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.67</v>
+        <v>3.62</v>
       </c>
       <c r="DH13" t="n">
-        <v>90.67</v>
+        <v>90.19</v>
       </c>
       <c r="DI13" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DK13" t="n">
-        <v>6.54</v>
+        <v>6.44</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="DM13" t="n">
-        <v>45.14</v>
+        <v>46.56</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.6</v>
+        <v>14.57</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.8</v>
+        <v>14.07</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.4</v>
+        <v>6.69</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6182,28 +6182,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>55.67</v>
+        <v>55.75</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.27</v>
+        <v>12.63</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.67</v>
+        <v>8.06</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.6</v>
+        <v>4.56</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.74</v>
+        <v>17.19</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="14">
@@ -6213,94 +6213,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F14" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="G14" t="n">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>121</v>
+        <v>119.25</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="K14" t="n">
-        <v>5.43</v>
+        <v>5.12</v>
       </c>
       <c r="L14" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="M14" t="n">
-        <v>59.86</v>
+        <v>56.62</v>
       </c>
       <c r="N14" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="O14" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="P14" t="n">
-        <v>12.86</v>
+        <v>12.62</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.43</v>
+        <v>8.75</v>
       </c>
       <c r="R14" t="n">
-        <v>4.29</v>
+        <v>4.88</v>
       </c>
       <c r="S14" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="V14" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>62.71</v>
+        <v>62.12</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>14.71</v>
+        <v>15.12</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.289999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>6.43</v>
+        <v>6.62</v>
       </c>
       <c r="AC14" t="n">
-        <v>13.57</v>
+        <v>14.38</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6384,70 +6384,70 @@
         <v>2.25</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.33</v>
+        <v>3.19</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.93</v>
+        <v>9</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.33</v>
+        <v>3.19</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.13</v>
+        <v>5.12</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BT14" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BU14" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BV14" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW14" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BX14" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.24</v>
+        <v>4.21</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.35</v>
+        <v>4.32</v>
       </c>
       <c r="CC14" t="n">
         <v>2.05</v>
@@ -6459,25 +6459,25 @@
         <v>1.3</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CK14" t="n">
         <v>1.65</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CM14" t="n">
         <v>2.12</v>
@@ -6489,10 +6489,10 @@
         <v>1.2</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CR14" t="n">
         <v>1.35</v>
@@ -6507,106 +6507,106 @@
         <v>1.53</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CX14" t="n">
         <v>1.65</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.22</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DB14" t="n">
         <v>1.27</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF14" t="n">
         <v>1</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.34</v>
+        <v>3.19</v>
       </c>
       <c r="DH14" t="n">
-        <v>109.86</v>
+        <v>109.68</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.6</v>
+        <v>5.44</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DM14" t="n">
-        <v>51.47</v>
+        <v>50.37</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="DP14" t="n">
-        <v>11.87</v>
+        <v>11.81</v>
       </c>
       <c r="DQ14" t="n">
-        <v>9.74</v>
+        <v>9.82</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.4</v>
+        <v>5.63</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>60</v>
+        <v>59.87</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.06</v>
+        <v>14.31</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.67</v>
+        <v>5.81</v>
       </c>
       <c r="EA14" t="n">
-        <v>14.8</v>
+        <v>15.13</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="15">
@@ -6616,13 +6616,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15" t="n">
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
         <v>0.14</v>
@@ -6706,139 +6706,139 @@
         <v>1.29</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="AI15" t="n">
-        <v>129.5</v>
+        <v>129</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.75</v>
+        <v>5.56</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN15" t="n">
-        <v>66</v>
+        <v>63.22</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="AQ15" t="n">
         <v>10</v>
       </c>
       <c r="AR15" t="n">
-        <v>9.119999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.75</v>
+        <v>4.44</v>
       </c>
       <c r="AT15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>68.67</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>14.78</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BL15" t="n">
         <v>1.12</v>
       </c>
-      <c r="AU15" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>69.88</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>14.88</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>16.25</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>9.470000000000001</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1.13</v>
-      </c>
       <c r="BM15" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.07</v>
+        <v>5.12</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT15" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BU15" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BV15" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BW15" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX15" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BY15" t="n">
         <v>1.21</v>
@@ -6847,43 +6847,43 @@
         <v>1.24</v>
       </c>
       <c r="CA15" t="n">
-        <v>6.05</v>
+        <v>6.04</v>
       </c>
       <c r="CB15" t="n">
-        <v>6.49</v>
+        <v>6.51</v>
       </c>
       <c r="CC15" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="CD15" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="CE15" t="n">
         <v>1.2</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CG15" t="n">
-        <v>4.06</v>
+        <v>4.09</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CL15" t="n">
         <v>1.92</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CN15" t="n">
         <v>1.84</v>
@@ -6895,119 +6895,119 @@
         <v>1.44</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CR15" t="n">
         <v>1.34</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CT15" t="n">
         <v>3.34</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DA15" t="n">
         <v>1.92</v>
       </c>
       <c r="DB15" t="inlineStr"/>
       <c r="DC15" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DG15" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="DH15" t="n">
-        <v>136.33</v>
+        <v>135.62</v>
       </c>
       <c r="DI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DK15" t="n">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DM15" t="n">
-        <v>72.13</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="DP15" t="n">
         <v>10</v>
       </c>
       <c r="DQ15" t="n">
-        <v>8.73</v>
+        <v>8.81</v>
       </c>
       <c r="DR15" t="n">
-        <v>4.6</v>
+        <v>4.44</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>70.40000000000001</v>
+        <v>69.69</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>17.94</v>
+        <v>17.69</v>
       </c>
       <c r="DY15" t="n">
-        <v>11.2</v>
+        <v>10.81</v>
       </c>
       <c r="DZ15" t="n">
-        <v>6.73</v>
+        <v>6.88</v>
       </c>
       <c r="EA15" t="n">
-        <v>17.53</v>
+        <v>17.31</v>
       </c>
       <c r="EB15" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="16">
@@ -7017,10 +7017,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -7029,82 +7029,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="G16" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="H16" t="n">
-        <v>99.14</v>
+        <v>98.25</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="K16" t="n">
-        <v>6.14</v>
+        <v>6.25</v>
       </c>
       <c r="L16" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="M16" t="n">
-        <v>50.71</v>
+        <v>51.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="O16" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="P16" t="n">
-        <v>11.71</v>
+        <v>11.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>12.14</v>
+        <v>12.38</v>
       </c>
       <c r="R16" t="n">
-        <v>5.71</v>
+        <v>5.62</v>
       </c>
       <c r="S16" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="T16" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="U16" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V16" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>56.86</v>
+        <v>57.88</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z16" t="n">
-        <v>15.43</v>
+        <v>14.62</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.29</v>
+        <v>10.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.14</v>
+        <v>3.88</v>
       </c>
       <c r="AC16" t="n">
-        <v>16.29</v>
+        <v>15.88</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7188,70 +7188,70 @@
         <v>1.62</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL16" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.07</v>
+        <v>4.31</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.47</v>
+        <v>4.38</v>
       </c>
       <c r="BR16" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS16" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT16" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU16" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV16" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BW16" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BX16" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="CC16" t="n">
         <v>4.34</v>
@@ -7260,22 +7260,22 @@
         <v>4.09</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CK16" t="n">
         <v>1.6</v>
@@ -7287,34 +7287,34 @@
         <v>2.18</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CO16" t="n">
         <v>1.24</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CX16" t="n">
         <v>1.66</v>
@@ -7323,94 +7323,94 @@
         <v>2.09</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="DH16" t="n">
-        <v>90</v>
+        <v>90.12</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="DM16" t="n">
-        <v>40.6</v>
+        <v>41.62</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.4</v>
+        <v>11.43</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.47</v>
+        <v>11.63</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.67</v>
+        <v>7.5</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>54.74</v>
+        <v>55.38</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.67</v>
+        <v>12.43</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.94</v>
+        <v>8.82</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.73</v>
+        <v>3.63</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.34</v>
+        <v>17.07</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -7420,91 +7420,91 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
         <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F17" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="G17" t="n">
         <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>102.57</v>
+        <v>100.5</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="K17" t="n">
-        <v>5.29</v>
+        <v>5.25</v>
       </c>
       <c r="L17" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M17" t="n">
-        <v>54.57</v>
+        <v>51.25</v>
       </c>
       <c r="N17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="O17" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="P17" t="n">
-        <v>11.71</v>
+        <v>12.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>13</v>
+        <v>14.12</v>
       </c>
       <c r="R17" t="n">
-        <v>7.29</v>
+        <v>7</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="U17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>49.14</v>
+        <v>50.62</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z17" t="n">
-        <v>16.71</v>
+        <v>15.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>10.86</v>
+        <v>10</v>
       </c>
       <c r="AB17" t="n">
-        <v>5.86</v>
+        <v>5.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>17.71</v>
+        <v>18.38</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -7591,64 +7591,64 @@
         <v>1.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.13</v>
+        <v>3.19</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.27</v>
+        <v>10.38</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.13</v>
+        <v>3.19</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.53</v>
+        <v>0.62</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.2</v>
+        <v>4.31</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.8</v>
+        <v>4.88</v>
       </c>
       <c r="BR17" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS17" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT17" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BU17" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BV17" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.51</v>
+        <v>2.43</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="CA17" t="n">
         <v>3.7</v>
@@ -7666,16 +7666,16 @@
         <v>1.32</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CH17" t="n">
         <v>1.5</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.63</v>
@@ -7684,7 +7684,7 @@
         <v>1.62</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CM17" t="n">
         <v>2.22</v>
@@ -7714,7 +7714,7 @@
         <v>1.52</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CW17" t="n">
         <v>1.67</v>
@@ -7741,79 +7741,79 @@
         <v>2.97</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="DH17" t="n">
-        <v>94.59999999999999</v>
+        <v>94.06</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.34</v>
+        <v>5.32</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM17" t="n">
-        <v>44.2</v>
+        <v>43.18</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="DP17" t="n">
-        <v>11</v>
+        <v>11.32</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12</v>
+        <v>12.62</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.34</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>49.66</v>
+        <v>50.37</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.6</v>
+        <v>12.38</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.07</v>
+        <v>7.81</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.54</v>
+        <v>4.56</v>
       </c>
       <c r="EA17" t="n">
-        <v>17.93</v>
+        <v>18.25</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="18">
@@ -7823,10 +7823,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
         <v>8</v>
@@ -7835,82 +7835,82 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>99</v>
+        <v>104.25</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>4.88</v>
       </c>
       <c r="L18" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="M18" t="n">
-        <v>39.71</v>
+        <v>42.88</v>
       </c>
       <c r="N18" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="O18" t="n">
-        <v>1.29</v>
+        <v>1.88</v>
       </c>
       <c r="P18" t="n">
-        <v>10.86</v>
+        <v>10.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>14.29</v>
+        <v>12.88</v>
       </c>
       <c r="R18" t="n">
-        <v>7.14</v>
+        <v>7.38</v>
       </c>
       <c r="S18" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="U18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>52.43</v>
+        <v>53.75</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z18" t="n">
-        <v>12.57</v>
+        <v>12.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.71</v>
+        <v>7.12</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.86</v>
+        <v>5.38</v>
       </c>
       <c r="AC18" t="n">
-        <v>14.43</v>
+        <v>14.5</v>
       </c>
       <c r="AD18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.57</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7994,70 +7994,70 @@
         <v>2.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="BH18" t="n">
-        <v>7</v>
+        <v>7.44</v>
       </c>
       <c r="BI18" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN18" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BP18" t="n">
-        <v>2.67</v>
+        <v>3.06</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.33</v>
+        <v>4.38</v>
       </c>
       <c r="BR18" t="n">
-        <v>100</v>
+        <v>93.75</v>
       </c>
       <c r="BS18" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BT18" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BU18" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV18" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BW18" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX18" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="CC18" t="n">
         <v>3.92</v>
@@ -8069,40 +8069,40 @@
         <v>1.33</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CJ18" t="n">
         <v>1.7</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CO18" t="n">
         <v>1.22</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CR18" t="n">
         <v>1.37</v>
@@ -8111,28 +8111,28 @@
         <v>2.65</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CU18" t="n">
         <v>1.51</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="DB18" t="n">
         <v>1.29</v>
@@ -8141,82 +8141,82 @@
         <v>1.81</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.27</v>
+        <v>2.44</v>
       </c>
       <c r="DH18" t="n">
-        <v>98.53</v>
+        <v>101.18</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.26</v>
+        <v>3.75</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DM18" t="n">
-        <v>40.73</v>
+        <v>42.25</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO18" t="n">
-        <v>1</v>
+        <v>1.32</v>
       </c>
       <c r="DP18" t="n">
-        <v>11.73</v>
+        <v>11.38</v>
       </c>
       <c r="DQ18" t="n">
-        <v>14.34</v>
+        <v>13.63</v>
       </c>
       <c r="DR18" t="n">
-        <v>7</v>
+        <v>7.13</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>52.14</v>
+        <v>52.82</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.07</v>
+        <v>11.12</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.73</v>
+        <v>6.94</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.33</v>
+        <v>4.19</v>
       </c>
       <c r="EA18" t="n">
-        <v>15.8</v>
+        <v>15.75</v>
       </c>
       <c r="EB18" t="n">
         <v>1.31</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -8226,13 +8226,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" t="n">
         <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
         <v>0.25</v>
@@ -8319,136 +8319,136 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.29</v>
+        <v>2.88</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>85.43000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>3.71</v>
+        <v>3.38</v>
       </c>
       <c r="AL19" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="AN19" t="n">
-        <v>38.86</v>
+        <v>37.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="AQ19" t="n">
-        <v>15.14</v>
+        <v>15</v>
       </c>
       <c r="AR19" t="n">
-        <v>10.71</v>
+        <v>10.75</v>
       </c>
       <c r="AS19" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AU19" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>40.43</v>
+        <v>39.75</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA19" t="n">
-        <v>9.710000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.86</v>
+        <v>6.38</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="BD19" t="n">
-        <v>15.57</v>
+        <v>15.12</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.869999999999999</v>
+        <v>9.94</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.47</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="BO19" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.27</v>
+        <v>4.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.6</v>
+        <v>5.44</v>
       </c>
       <c r="BR19" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS19" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BT19" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BU19" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV19" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW19" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX19" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BY19" t="n">
         <v>2.71</v>
@@ -8457,28 +8457,28 @@
         <v>2.78</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.63</v>
+        <v>3.55</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.72</v>
+        <v>3.61</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CI19" t="n">
         <v>1.96</v>
@@ -8493,31 +8493,31 @@
         <v>2.07</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CO19" t="n">
         <v>1.28</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CV19" t="n">
         <v>2.04</v>
@@ -8526,100 +8526,100 @@
         <v>1.86</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DB19" t="n">
         <v>1.33</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF19" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="DH19" t="n">
-        <v>89.40000000000001</v>
+        <v>88.19</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.66</v>
+        <v>4.62</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.26</v>
+        <v>0.37</v>
       </c>
       <c r="DM19" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.4</v>
+        <v>14.38</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.26</v>
+        <v>11.25</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.6</v>
+        <v>6.44</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>41.27</v>
+        <v>40.88</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.53</v>
+        <v>12.19</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.67</v>
+        <v>8.32</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.54</v>
+        <v>16.25</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -3547,10 +3547,10 @@
         <v>0.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>14</v>
+        <v>14.12</v>
       </c>
       <c r="BB7" t="n">
-        <v>9</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BC7" t="n">
         <v>5</v>
@@ -3559,7 +3559,7 @@
         <v>18.25</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="BF7" t="n">
         <v>2.75</v>
@@ -3772,10 +3772,10 @@
         <v>0.25</v>
       </c>
       <c r="DX7" t="n">
-        <v>14.56</v>
+        <v>14.62</v>
       </c>
       <c r="DY7" t="n">
-        <v>9.56</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DZ7" t="n">
         <v>5</v>
@@ -3784,7 +3784,7 @@
         <v>17.19</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="EC7" t="n">
         <v>2.18</v>
@@ -4837,13 +4837,13 @@
         <v>4.33</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="CC10" t="n">
         <v>2.05</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CE10" t="n">
         <v>1.25</v>
@@ -4897,10 +4897,10 @@
         <v>1.68</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CX10" t="n">
         <v>1.59</v>
@@ -4916,10 +4916,10 @@
       </c>
       <c r="DB10" t="inlineStr"/>
       <c r="DC10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="DE10" t="n">
         <v>0.18</v>
@@ -6246,7 +6246,7 @@
         <v>0.5</v>
       </c>
       <c r="M14" t="n">
-        <v>56.62</v>
+        <v>56.75</v>
       </c>
       <c r="N14" t="n">
         <v>0.5</v>
@@ -6441,13 +6441,13 @@
         <v>1.81</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CA14" t="n">
         <v>4.21</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.32</v>
+        <v>4.3</v>
       </c>
       <c r="CC14" t="n">
         <v>2.05</v>
@@ -6507,10 +6507,10 @@
         <v>1.53</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CX14" t="n">
         <v>1.65</v>
@@ -6528,10 +6528,10 @@
         <v>1.27</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="DE14" t="n">
         <v>0.06</v>
@@ -6558,7 +6558,7 @@
         <v>0.44</v>
       </c>
       <c r="DM14" t="n">
-        <v>50.37</v>
+        <v>50.44</v>
       </c>
       <c r="DN14" t="n">
         <v>1.19</v>

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>0.12</v>
@@ -3081,139 +3081,139 @@
         <v>1.62</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AI6" t="n">
-        <v>86</v>
+        <v>88.56</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.75</v>
+        <v>5.11</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AN6" t="n">
-        <v>41.25</v>
+        <v>42.67</v>
       </c>
       <c r="AO6" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>16.22</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BL6" t="n">
         <v>0.88</v>
       </c>
-      <c r="AP6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>12.12</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>47</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>13</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>16</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>10.56</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0.9399999999999999</v>
-      </c>
       <c r="BM6" t="n">
-        <v>0.25</v>
+        <v>0.41</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.19</v>
+        <v>4.41</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.25</v>
+        <v>5.06</v>
       </c>
       <c r="BR6" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS6" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU6" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BV6" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BY6" t="n">
         <v>2.06</v>
@@ -3222,10 +3222,10 @@
         <v>2.07</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.99</v>
+        <v>3.93</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.98</v>
+        <v>3.94</v>
       </c>
       <c r="CC6" t="n">
         <v>2.79</v>
@@ -3234,124 +3234,124 @@
         <v>2.89</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CK6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="CU6" t="n">
         <v>1.56</v>
       </c>
-      <c r="CL6" t="n">
+      <c r="CV6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CY6" t="n">
         <v>1.98</v>
       </c>
-      <c r="CM6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="CN6" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="CO6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="CP6" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="CQ6" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="CS6" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="CT6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="CU6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CV6" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="CW6" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="CX6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CY6" t="n">
-        <v>1.97</v>
-      </c>
       <c r="CZ6" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="DH6" t="n">
-        <v>84.38</v>
+        <v>85.83</v>
       </c>
       <c r="DI6" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="DK6" t="n">
-        <v>6</v>
+        <v>6.12</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="DM6" t="n">
-        <v>42.44</v>
+        <v>43.12</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.12</v>
+        <v>13.29</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.87</v>
+        <v>12.12</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.5</v>
+        <v>6.29</v>
       </c>
       <c r="DS6" t="n">
         <v>0.18</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>48.12</v>
+        <v>49.29</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.94</v>
+        <v>14.06</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.75</v>
+        <v>8.76</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.18</v>
+        <v>5.29</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.88</v>
+        <v>16.94</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F7" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="H7" t="n">
-        <v>106.5</v>
+        <v>104.44</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>5.78</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M7" t="n">
-        <v>53.12</v>
+        <v>51.44</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>3.11</v>
       </c>
       <c r="P7" t="n">
-        <v>12</v>
+        <v>11.11</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.62</v>
+        <v>12.78</v>
       </c>
       <c r="R7" t="n">
-        <v>5</v>
+        <v>5.33</v>
       </c>
       <c r="S7" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="U7" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V7" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>52.75</v>
+        <v>51.22</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="Z7" t="n">
-        <v>15.12</v>
+        <v>14.89</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.12</v>
+        <v>10.11</v>
       </c>
       <c r="AB7" t="n">
-        <v>5</v>
+        <v>4.78</v>
       </c>
       <c r="AC7" t="n">
-        <v>16.12</v>
+        <v>16.44</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AF7" t="n">
         <v>0.25</v>
@@ -3565,64 +3565,64 @@
         <v>2.75</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.31</v>
+        <v>3.24</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.56</v>
+        <v>10.59</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.31</v>
+        <v>3.24</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="BO7" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.56</v>
+        <v>5.53</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5</v>
+        <v>5.06</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT7" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BU7" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV7" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BW7" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BX7" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="CA7" t="n">
         <v>3.78</v>
@@ -3640,13 +3640,13 @@
         <v>1.34</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CG7" t="n">
         <v>3.1</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CI7" t="n">
         <v>2.1</v>
@@ -3658,7 +3658,7 @@
         <v>1.56</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CM7" t="n">
         <v>2.26</v>
@@ -3670,10 +3670,10 @@
         <v>1.24</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CR7" t="n">
         <v>1.37</v>
@@ -3694,13 +3694,13 @@
         <v>1.75</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="DA7" t="n">
         <v>1.82</v>
@@ -3709,85 +3709,85 @@
         <v>1.29</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="DE7" t="n">
         <v>0.18</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="DH7" t="n">
-        <v>108.56</v>
+        <v>107.35</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.19</v>
+        <v>6.06</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="DM7" t="n">
-        <v>55.62</v>
+        <v>54.58</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.18</v>
+        <v>13.24</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.25</v>
+        <v>6.35</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>56.12</v>
+        <v>55.12</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="DX7" t="n">
-        <v>14.62</v>
+        <v>14.53</v>
       </c>
       <c r="DY7" t="n">
-        <v>9.619999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5</v>
+        <v>4.88</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.19</v>
+        <v>17.29</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="8">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F10" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="G10" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="H10" t="n">
-        <v>108.38</v>
+        <v>106.33</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="J10" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="K10" t="n">
-        <v>4.38</v>
+        <v>4.67</v>
       </c>
       <c r="L10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M10" t="n">
-        <v>48.38</v>
+        <v>47.89</v>
       </c>
       <c r="N10" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="O10" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="P10" t="n">
-        <v>11.62</v>
+        <v>11.89</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.38</v>
+        <v>12.33</v>
       </c>
       <c r="R10" t="n">
-        <v>7.38</v>
+        <v>7</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="U10" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V10" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>53.5</v>
+        <v>52.44</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.88</v>
+        <v>13</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.380000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.5</v>
+        <v>4.22</v>
       </c>
       <c r="AC10" t="n">
-        <v>20</v>
+        <v>19.78</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AF10" t="n">
         <v>0.12</v>
@@ -4774,70 +4774,70 @@
         <v>3.12</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="BH10" t="n">
         <v>8.94</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="BN10" t="n">
         <v>2.06</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU10" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BV10" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BW10" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX10" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.34</v>
+        <v>4.31</v>
       </c>
       <c r="CC10" t="n">
         <v>2.05</v>
@@ -4852,7 +4852,7 @@
         <v>2.26</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="CH10" t="n">
         <v>1.62</v>
@@ -4864,16 +4864,16 @@
         <v>1.57</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CO10" t="n">
         <v>1.15</v>
@@ -4882,7 +4882,7 @@
         <v>1.56</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CR10" t="n">
         <v>1.35</v>
@@ -4900,7 +4900,7 @@
         <v>2.46</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CX10" t="n">
         <v>1.59</v>
@@ -4919,82 +4919,82 @@
         <v>1.57</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="DH10" t="n">
-        <v>108.56</v>
+        <v>107.47</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DM10" t="n">
-        <v>50</v>
+        <v>49.65</v>
       </c>
       <c r="DN10" t="n">
         <v>1</v>
       </c>
       <c r="DO10" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.93</v>
+        <v>13</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.63</v>
+        <v>11.65</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.19</v>
+        <v>7</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>53.75</v>
+        <v>53.17</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.88</v>
+        <v>12.47</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.69</v>
+        <v>8.41</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.19</v>
+        <v>4.06</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.12</v>
+        <v>20</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="11">
@@ -5407,94 +5407,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="G12" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="H12" t="n">
-        <v>71</v>
+        <v>72.33</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="K12" t="n">
-        <v>5.12</v>
+        <v>5.11</v>
       </c>
       <c r="L12" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="M12" t="n">
-        <v>33.62</v>
+        <v>33.33</v>
       </c>
       <c r="N12" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="P12" t="n">
-        <v>11.62</v>
+        <v>11.67</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.88</v>
+        <v>11.89</v>
       </c>
       <c r="R12" t="n">
-        <v>6.12</v>
+        <v>5.89</v>
       </c>
       <c r="S12" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T12" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="U12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>47.62</v>
+        <v>47.33</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.5</v>
+        <v>13.22</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.62</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.88</v>
+        <v>5</v>
       </c>
       <c r="AC12" t="n">
-        <v>14.88</v>
+        <v>14.33</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5578,70 +5578,70 @@
         <v>2.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.56</v>
+        <v>10.65</v>
       </c>
       <c r="BI12" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BL12" t="n">
         <v>1</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.25</v>
+        <v>4.41</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.38</v>
+        <v>5.35</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT12" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU12" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BV12" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX12" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.07</v>
+        <v>4.05</v>
       </c>
       <c r="CC12" t="n">
         <v>3.79</v>
@@ -5653,13 +5653,13 @@
         <v>1.31</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI12" t="n">
         <v>2.18</v>
@@ -5668,16 +5668,16 @@
         <v>1.66</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL12" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="CN12" t="n">
         <v>1.89</v>
-      </c>
-      <c r="CM12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="CN12" t="n">
-        <v>1.91</v>
       </c>
       <c r="CO12" t="n">
         <v>1.21</v>
@@ -5686,13 +5686,13 @@
         <v>1.74</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CR12" t="n">
         <v>1.36</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CT12" t="n">
         <v>3.21</v>
@@ -5701,58 +5701,58 @@
         <v>1.54</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="DB12" t="n">
         <v>1.29</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="DE12" t="n">
         <v>0.12</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="DH12" t="n">
-        <v>79.38</v>
+        <v>79.59</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="DK12" t="n">
         <v>4.94</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM12" t="n">
-        <v>35.37</v>
+        <v>35.11</v>
       </c>
       <c r="DN12" t="n">
         <v>1.06</v>
@@ -5761,46 +5761,46 @@
         <v>2.06</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.43</v>
+        <v>12.41</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.19</v>
+        <v>12.18</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.87</v>
+        <v>6.7</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.68</v>
+        <v>47.53</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.12</v>
+        <v>11.59</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.18</v>
+        <v>7.53</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.94</v>
+        <v>4.06</v>
       </c>
       <c r="EA12" t="n">
-        <v>16.13</v>
+        <v>15.77</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="13">
@@ -5810,13 +5810,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5900,52 +5900,52 @@
         <v>1.62</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.75</v>
+        <v>3.44</v>
       </c>
       <c r="AI13" t="n">
-        <v>87.38</v>
+        <v>87.78</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK13" t="n">
         <v>3</v>
       </c>
       <c r="AL13" t="n">
-        <v>6.75</v>
+        <v>6.22</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN13" t="n">
-        <v>44.88</v>
+        <v>43.78</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AP13" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15.25</v>
+        <v>14.89</v>
       </c>
       <c r="AR13" t="n">
-        <v>14.88</v>
+        <v>14.78</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AU13" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5957,82 +5957,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>55</v>
+        <v>55.11</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BA13" t="n">
-        <v>10.88</v>
+        <v>11.11</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.62</v>
+        <v>6.33</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.25</v>
+        <v>4.78</v>
       </c>
       <c r="BD13" t="n">
-        <v>16.88</v>
+        <v>17.67</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.94</v>
+        <v>10.82</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL13" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.38</v>
+        <v>0.47</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BO13" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.25</v>
+        <v>4.29</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.69</v>
+        <v>6.53</v>
       </c>
       <c r="BR13" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BT13" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BU13" t="n">
-        <v>25</v>
+        <v>29.41</v>
       </c>
       <c r="BV13" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW13" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX13" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BY13" t="n">
         <v>2.1</v>
@@ -6047,16 +6047,16 @@
         <v>3.84</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.53</v>
+        <v>2.61</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.64</v>
+        <v>2.71</v>
       </c>
       <c r="CE13" t="n">
         <v>1.32</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="CG13" t="n">
         <v>3.2</v>
@@ -6065,7 +6065,7 @@
         <v>1.49</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.69</v>
@@ -6074,22 +6074,22 @@
         <v>1.52</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CO13" t="n">
         <v>1.23</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CR13" t="n">
         <v>1.37</v>
@@ -6104,10 +6104,10 @@
         <v>1.49</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CX13" t="n">
         <v>1.58</v>
@@ -6119,58 +6119,58 @@
         <v>2.36</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DB13" t="n">
         <v>1.3</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="DE13" t="n">
         <v>0.06</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.62</v>
+        <v>3.47</v>
       </c>
       <c r="DH13" t="n">
-        <v>90.19</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="DI13" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="DK13" t="n">
-        <v>6.44</v>
+        <v>6.17</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="DM13" t="n">
-        <v>46.56</v>
+        <v>45.88</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.57</v>
+        <v>14.41</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.07</v>
+        <v>14.06</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.69</v>
+        <v>6.47</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6182,28 +6182,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>55.75</v>
+        <v>55.76</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.63</v>
+        <v>12.65</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.06</v>
+        <v>7.82</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.56</v>
+        <v>4.83</v>
       </c>
       <c r="EA13" t="n">
-        <v>17.19</v>
+        <v>17.59</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="14">
@@ -7420,13 +7420,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
         <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
         <v>0.12</v>
@@ -7510,139 +7510,139 @@
         <v>2</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AI17" t="n">
-        <v>87.62</v>
+        <v>89.89</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.38</v>
+        <v>5.56</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="AN17" t="n">
-        <v>35.12</v>
+        <v>39.67</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="AQ17" t="n">
-        <v>10.38</v>
+        <v>10.78</v>
       </c>
       <c r="AR17" t="n">
-        <v>11.12</v>
+        <v>10.33</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.25</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="AT17" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>50.12</v>
+        <v>51.33</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BA17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.62</v>
+        <v>6.56</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="BD17" t="n">
-        <v>18.12</v>
+        <v>17.67</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.19</v>
+        <v>3.12</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.38</v>
+        <v>10.41</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.19</v>
+        <v>3.12</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.38</v>
+        <v>0.47</v>
       </c>
       <c r="BN17" t="n">
         <v>1.88</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.31</v>
+        <v>4.35</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.88</v>
+        <v>4.94</v>
       </c>
       <c r="BR17" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS17" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT17" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU17" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BV17" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BY17" t="n">
         <v>2.43</v>
@@ -7651,16 +7651,16 @@
         <v>2.55</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.79</v>
+        <v>3.81</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.26</v>
+        <v>3.41</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.33</v>
+        <v>3.52</v>
       </c>
       <c r="CE17" t="n">
         <v>1.32</v>
@@ -7669,7 +7669,7 @@
         <v>2.53</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CH17" t="n">
         <v>1.5</v>
@@ -7681,13 +7681,13 @@
         <v>1.63</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CN17" t="n">
         <v>1.76</v>
@@ -7696,10 +7696,10 @@
         <v>1.23</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CR17" t="n">
         <v>1.36</v>
@@ -7726,10 +7726,10 @@
         <v>1.98</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DB17" t="n">
         <v>1.28</v>
@@ -7738,82 +7738,82 @@
         <v>1.81</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="DH17" t="n">
-        <v>94.06</v>
+        <v>94.88</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.32</v>
+        <v>5.41</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.38</v>
+        <v>0.53</v>
       </c>
       <c r="DM17" t="n">
-        <v>43.18</v>
+        <v>45.12</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.32</v>
+        <v>11.47</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.62</v>
+        <v>12.11</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.119999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50.37</v>
+        <v>51</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.38</v>
+        <v>12.71</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.81</v>
+        <v>8.18</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.56</v>
+        <v>4.53</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.25</v>
+        <v>18</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="18">
@@ -7823,13 +7823,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
         <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7916,136 +7916,136 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AI18" t="n">
-        <v>98.12</v>
+        <v>96.78</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.62</v>
+        <v>3.11</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AN18" t="n">
-        <v>41.62</v>
+        <v>42.22</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.75</v>
+        <v>1.22</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12.5</v>
+        <v>12.44</v>
       </c>
       <c r="AR18" t="n">
-        <v>14.38</v>
+        <v>14</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.88</v>
+        <v>7.11</v>
       </c>
       <c r="AT18" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>51.88</v>
+        <v>52.22</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.75</v>
+        <v>9.56</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.75</v>
+        <v>6.33</v>
       </c>
       <c r="BC18" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="BD18" t="n">
-        <v>17</v>
+        <v>16.89</v>
       </c>
       <c r="BE18" t="n">
         <v>1.14</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="BH18" t="n">
-        <v>7.44</v>
+        <v>7.71</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BN18" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.06</v>
+        <v>3.29</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.38</v>
+        <v>4.41</v>
       </c>
       <c r="BR18" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS18" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU18" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV18" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BW18" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX18" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BY18" t="n">
         <v>2.1</v>
@@ -8054,16 +8054,16 @@
         <v>2.1</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="CB18" t="n">
         <v>3.85</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.92</v>
+        <v>3.76</v>
       </c>
       <c r="CD18" t="n">
-        <v>4.07</v>
+        <v>3.88</v>
       </c>
       <c r="CE18" t="n">
         <v>1.33</v>
@@ -8072,13 +8072,13 @@
         <v>2.55</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="CH18" t="n">
         <v>1.48</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CJ18" t="n">
         <v>1.7</v>
@@ -8087,10 +8087,10 @@
         <v>1.67</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CN18" t="n">
         <v>1.74</v>
@@ -8099,28 +8099,28 @@
         <v>1.22</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CR18" t="n">
         <v>1.37</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CU18" t="n">
         <v>1.51</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CX18" t="n">
         <v>1.67</v>
@@ -8141,79 +8141,79 @@
         <v>1.81</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="DH18" t="n">
-        <v>101.18</v>
+        <v>100.3</v>
       </c>
       <c r="DI18" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.75</v>
+        <v>3.94</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="DM18" t="n">
-        <v>42.25</v>
+        <v>42.53</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="DP18" t="n">
-        <v>11.38</v>
+        <v>11.41</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.63</v>
+        <v>13.47</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.13</v>
+        <v>7.24</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>52.82</v>
+        <v>52.94</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.12</v>
+        <v>10.94</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.94</v>
+        <v>6.7</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.19</v>
+        <v>4.24</v>
       </c>
       <c r="EA18" t="n">
-        <v>15.75</v>
+        <v>15.77</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="EC18" t="n">
         <v>2</v>
@@ -8226,94 +8226,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
         <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F19" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="G19" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="H19" t="n">
-        <v>92.88</v>
+        <v>89.89</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="K19" t="n">
-        <v>5.12</v>
+        <v>4.78</v>
       </c>
       <c r="L19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="M19" t="n">
-        <v>48.5</v>
+        <v>46.44</v>
       </c>
       <c r="N19" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="O19" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="P19" t="n">
-        <v>13.75</v>
+        <v>14</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.75</v>
+        <v>12.22</v>
       </c>
       <c r="R19" t="n">
-        <v>5.38</v>
+        <v>6.11</v>
       </c>
       <c r="S19" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="T19" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="U19" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V19" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>42</v>
+        <v>40.89</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="Z19" t="n">
-        <v>15</v>
+        <v>14.22</v>
       </c>
       <c r="AA19" t="n">
-        <v>10.25</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.75</v>
+        <v>4.44</v>
       </c>
       <c r="AC19" t="n">
-        <v>17.38</v>
+        <v>17.11</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8397,70 +8397,70 @@
         <v>3.12</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="BH19" t="n">
         <v>9.94</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BL19" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="BM19" t="n">
         <v>0.88</v>
       </c>
-      <c r="BM19" t="n">
-        <v>0.75</v>
-      </c>
       <c r="BN19" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.5</v>
+        <v>4.71</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.44</v>
+        <v>5.24</v>
       </c>
       <c r="BR19" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS19" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BU19" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV19" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW19" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX19" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.65</v>
+        <v>3.61</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="CC19" t="n">
         <v>3.55</v>
@@ -8472,10 +8472,10 @@
         <v>1.37</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="CH19" t="n">
         <v>1.42</v>
@@ -8484,19 +8484,19 @@
         <v>1.96</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CK19" t="n">
         <v>1.62</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CO19" t="n">
         <v>1.28</v>
@@ -8505,16 +8505,16 @@
         <v>1.94</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="CR19" t="n">
         <v>1.42</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CU19" t="n">
         <v>1.42</v>
@@ -8526,22 +8526,22 @@
         <v>1.86</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DB19" t="n">
         <v>1.33</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DD19" t="n">
         <v>3.38</v>
@@ -8553,73 +8553,73 @@
         <v>2</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DH19" t="n">
-        <v>88.19</v>
+        <v>86.88</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.62</v>
+        <v>4.47</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM19" t="n">
-        <v>43</v>
+        <v>42.23</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.38</v>
+        <v>14.47</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.25</v>
+        <v>11.53</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.44</v>
+        <v>6.76</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>40.88</v>
+        <v>40.35</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.19</v>
+        <v>11.94</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.32</v>
+        <v>8.18</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.88</v>
+        <v>3.76</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.25</v>
+        <v>16.17</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
         <v>0.12</v>
@@ -1472,136 +1472,136 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AH2" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="AI2" t="n">
-        <v>68.12</v>
+        <v>72</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AN2" t="n">
-        <v>26.38</v>
+        <v>28.44</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.75</v>
+        <v>9.56</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.88</v>
+        <v>11.33</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.119999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>38.88</v>
+        <v>40.11</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.5</v>
+        <v>7.67</v>
       </c>
       <c r="BB2" t="n">
-        <v>5</v>
+        <v>5.11</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="BD2" t="n">
-        <v>13.88</v>
+        <v>15</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.31</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BL2" t="n">
         <v>1.06</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.88</v>
+        <v>4.06</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.44</v>
+        <v>5.41</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>25</v>
+        <v>29.41</v>
       </c>
       <c r="BU2" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV2" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BY2" t="n">
         <v>3.42</v>
@@ -1610,28 +1610,28 @@
         <v>3.71</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.31</v>
+        <v>4.25</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.61</v>
+        <v>4.54</v>
       </c>
       <c r="CC2" t="n">
-        <v>9.33</v>
+        <v>8.68</v>
       </c>
       <c r="CD2" t="n">
-        <v>9.859999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI2" t="n">
         <v>1.83</v>
@@ -1640,61 +1640,61 @@
         <v>1.93</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.39</v>
+        <v>3.44</v>
       </c>
       <c r="CR2" t="n">
         <v>1.45</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CV2" t="n">
         <v>1.89</v>
       </c>
       <c r="CW2" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DB2" t="n">
         <v>1.36</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DD2" t="n">
         <v>3.13</v>
@@ -1706,73 +1706,73 @@
         <v>0.88</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="DH2" t="n">
-        <v>72.18000000000001</v>
+        <v>74</v>
       </c>
       <c r="DI2" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.62</v>
+        <v>3.76</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="DM2" t="n">
-        <v>30.32</v>
+        <v>31.17</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.62</v>
+        <v>11.41</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.13</v>
+        <v>11.35</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.75</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>41.5</v>
+        <v>42</v>
       </c>
       <c r="DW2" t="n">
         <v>0.06</v>
       </c>
       <c r="DX2" t="n">
-        <v>9.25</v>
+        <v>9.24</v>
       </c>
       <c r="DY2" t="n">
-        <v>5.69</v>
+        <v>5.71</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.07</v>
+        <v>16.53</v>
       </c>
       <c r="EB2" t="n">
         <v>1.06</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,139 +1872,139 @@
         <v>2.22</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="AI3" t="n">
-        <v>89.56999999999999</v>
+        <v>91.88</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.14</v>
+        <v>4.38</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN3" t="n">
-        <v>37.14</v>
+        <v>37.25</v>
       </c>
       <c r="AO3" t="n">
         <v>1</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14</v>
+        <v>13.38</v>
       </c>
       <c r="AR3" t="n">
-        <v>13</v>
+        <v>13.38</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.57</v>
+        <v>8</v>
       </c>
       <c r="AT3" t="n">
         <v>2</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>45.14</v>
+        <v>45.75</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.57</v>
+        <v>10.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.57</v>
+        <v>6.88</v>
       </c>
       <c r="BC3" t="n">
-        <v>4</v>
+        <v>3.62</v>
       </c>
       <c r="BD3" t="n">
-        <v>19.29</v>
+        <v>18.88</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BF3" t="n">
         <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.619999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL3" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BO3" t="n">
         <v>1.06</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.75</v>
+        <v>5.88</v>
       </c>
       <c r="BR3" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS3" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT3" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BU3" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV3" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX3" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BY3" t="n">
         <v>3.31</v>
@@ -2013,28 +2013,28 @@
         <v>3.69</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.81</v>
+        <v>3.78</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="CC3" t="n">
-        <v>5.11</v>
+        <v>4.95</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.38</v>
+        <v>5.26</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="CG3" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI3" t="n">
         <v>2</v>
@@ -2043,40 +2043,40 @@
         <v>1.81</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CL3" t="n">
         <v>2.06</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CO3" t="n">
         <v>1.28</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CR3" t="n">
         <v>1.41</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="CT3" t="n">
         <v>2.99</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CW3" t="n">
         <v>1.85</v>
@@ -2085,13 +2085,13 @@
         <v>1.62</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.28</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="DB3" t="n">
         <v>1.33</v>
@@ -2100,79 +2100,79 @@
         <v>1.99</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="DE3" t="n">
         <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="DH3" t="n">
-        <v>88.93000000000001</v>
+        <v>90.06</v>
       </c>
       <c r="DI3" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.06</v>
+        <v>5.12</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DM3" t="n">
-        <v>40.94</v>
+        <v>40.77</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DO3" t="n">
         <v>1.88</v>
       </c>
       <c r="DP3" t="n">
-        <v>14</v>
+        <v>13.71</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.75</v>
+        <v>13.88</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.31</v>
+        <v>6.59</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>44</v>
+        <v>44.35</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DX3" t="n">
-        <v>11.31</v>
+        <v>11.24</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.37</v>
+        <v>7.47</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.94</v>
+        <v>3.76</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.5</v>
+        <v>18.36</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="EC3" t="n">
         <v>2.12</v>
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="F4" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="G4" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="H4" t="n">
-        <v>100</v>
+        <v>100.33</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="K4" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M4" t="n">
-        <v>39.5</v>
+        <v>40.44</v>
       </c>
       <c r="N4" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="P4" t="n">
-        <v>13.38</v>
+        <v>13.67</v>
       </c>
       <c r="Q4" t="n">
-        <v>10.12</v>
+        <v>10</v>
       </c>
       <c r="R4" t="n">
-        <v>7.75</v>
+        <v>7.89</v>
       </c>
       <c r="S4" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="U4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>44</v>
+        <v>44.67</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z4" t="n">
-        <v>15.25</v>
+        <v>14.78</v>
       </c>
       <c r="AA4" t="n">
-        <v>10.38</v>
+        <v>10</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.88</v>
+        <v>4.78</v>
       </c>
       <c r="AC4" t="n">
-        <v>17.62</v>
+        <v>17.67</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,70 +2356,70 @@
         <v>2.12</v>
       </c>
       <c r="BG4" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.5</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BL4" t="n">
         <v>1.06</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.88</v>
+        <v>5.06</v>
       </c>
       <c r="BR4" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT4" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BU4" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV4" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW4" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.56</v>
+        <v>3.38</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="CC4" t="n">
         <v>3.75</v>
@@ -2428,61 +2428,61 @@
         <v>3.73</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="CH4" t="n">
         <v>1.47</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.71</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="CU4" t="n">
         <v>1.5</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CX4" t="n">
         <v>1.66</v>
@@ -2500,85 +2500,85 @@
         <v>1.32</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="DH4" t="n">
-        <v>95.62</v>
+        <v>96.06</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.38</v>
+        <v>4.53</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DM4" t="n">
-        <v>39.12</v>
+        <v>39.64</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.38</v>
+        <v>13.53</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.06</v>
+        <v>10.94</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.18</v>
+        <v>7.29</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>43.88</v>
+        <v>44.24</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.18</v>
+        <v>12.12</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.130000000000001</v>
+        <v>8.06</v>
       </c>
       <c r="DZ4" t="n">
         <v>4.06</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.69</v>
+        <v>18.65</v>
       </c>
       <c r="EB4" t="n">
         <v>1.34</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="5">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
         <v>8</v>
@@ -2600,82 +2600,82 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="G5" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="H5" t="n">
-        <v>95.88</v>
+        <v>98</v>
       </c>
       <c r="I5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J5" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="K5" t="n">
-        <v>5.25</v>
+        <v>5.33</v>
       </c>
       <c r="L5" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="M5" t="n">
-        <v>54.38</v>
+        <v>52.89</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="O5" t="n">
-        <v>2.38</v>
+        <v>2.67</v>
       </c>
       <c r="P5" t="n">
-        <v>14.38</v>
+        <v>14.44</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.88</v>
+        <v>12.33</v>
       </c>
       <c r="R5" t="n">
-        <v>5.75</v>
+        <v>5.67</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="U5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>49.88</v>
+        <v>49.89</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>13.75</v>
+        <v>13.44</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.25</v>
+        <v>4.44</v>
       </c>
       <c r="AC5" t="n">
-        <v>21.62</v>
+        <v>21.89</v>
       </c>
       <c r="AD5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.56</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.62</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>1.88</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.69</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BL5" t="n">
         <v>1.06</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.69</v>
+        <v>3.88</v>
       </c>
       <c r="BQ5" t="n">
         <v>5</v>
       </c>
       <c r="BR5" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BT5" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BU5" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV5" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX5" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.96</v>
+        <v>2.85</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.19</v>
+        <v>3.07</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.11</v>
+        <v>4.06</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.11</v>
+        <v>4.06</v>
       </c>
       <c r="CC5" t="n">
         <v>6.77</v>
@@ -2831,13 +2831,13 @@
         <v>7.41</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="CH5" t="n">
         <v>1.44</v>
@@ -2849,61 +2849,61 @@
         <v>1.84</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="CU5" t="n">
         <v>1.43</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="DB5" t="n">
         <v>1.34</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DD5" t="n">
         <v>3.22</v>
@@ -2912,43 +2912,43 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="DH5" t="n">
-        <v>86.5</v>
+        <v>88.17</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.44</v>
+        <v>4.53</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="DM5" t="n">
-        <v>45.56</v>
+        <v>45.29</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="DP5" t="n">
-        <v>14.07</v>
+        <v>14.12</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.82</v>
+        <v>12.53</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.32</v>
+        <v>7.18</v>
       </c>
       <c r="DS5" t="n">
         <v>0.06</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>45.63</v>
+        <v>45.89</v>
       </c>
       <c r="DW5" t="n">
         <v>0.06</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.68</v>
+        <v>11.64</v>
       </c>
       <c r="DY5" t="n">
-        <v>8</v>
+        <v>7.82</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.68</v>
+        <v>3.82</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.12</v>
+        <v>18.47</v>
       </c>
       <c r="EB5" t="n">
         <v>1.33</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="6">
@@ -3003,7 +3003,7 @@
         <v>0.12</v>
       </c>
       <c r="F6" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>2.5</v>
@@ -3015,7 +3015,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="K6" t="n">
         <v>7.25</v>
@@ -3078,7 +3078,7 @@
         <v>1.65</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AF6" t="n">
         <v>0.11</v>
@@ -3315,7 +3315,7 @@
         <v>0.11</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="DG6" t="n">
         <v>2.35</v>
@@ -3327,7 +3327,7 @@
         <v>0.12</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="DK6" t="n">
         <v>6.12</v>
@@ -3384,7 +3384,7 @@
         <v>1.57</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="7">
@@ -3628,7 +3628,7 @@
         <v>3.78</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.97</v>
+        <v>3.96</v>
       </c>
       <c r="CC7" t="n">
         <v>2.28</v>
@@ -3688,10 +3688,10 @@
         <v>1.49</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CX7" t="n">
         <v>1.61</v>
@@ -3703,7 +3703,7 @@
         <v>2.3</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DB7" t="n">
         <v>1.29</v>
@@ -3797,67 +3797,67 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F8" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="G8" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="H8" t="n">
-        <v>80.12</v>
+        <v>82.67</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>43.62</v>
+        <v>42.11</v>
       </c>
       <c r="N8" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="O8" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>10.25</v>
+        <v>10.11</v>
       </c>
       <c r="Q8" t="n">
-        <v>14.12</v>
+        <v>13.44</v>
       </c>
       <c r="R8" t="n">
-        <v>5.88</v>
+        <v>5.67</v>
       </c>
       <c r="S8" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="T8" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -3869,22 +3869,22 @@
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>13.25</v>
+        <v>13.56</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.119999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.12</v>
+        <v>5.11</v>
       </c>
       <c r="AC8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3968,67 +3968,67 @@
         <v>2</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.31</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="BL8" t="n">
         <v>1.06</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.62</v>
+        <v>3.71</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.19</v>
+        <v>4.12</v>
       </c>
       <c r="BR8" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS8" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BU8" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV8" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW8" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY8" t="n">
-        <v>3.96</v>
+        <v>3.71</v>
       </c>
       <c r="BZ8" t="n">
-        <v>4.01</v>
+        <v>3.77</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="CB8" t="n">
         <v>3.82</v>
@@ -4043,7 +4043,7 @@
         <v>1.35</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CG8" t="n">
         <v>3.06</v>
@@ -4058,13 +4058,13 @@
         <v>1.75</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CN8" t="n">
         <v>1.68</v>
@@ -4085,7 +4085,7 @@
         <v>2.83</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="CU8" t="n">
         <v>1.47</v>
@@ -4097,19 +4097,19 @@
         <v>1.81</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DC8" t="n">
         <v>1.96</v>
@@ -4121,43 +4121,43 @@
         <v>0.06</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="DH8" t="n">
-        <v>85.94</v>
+        <v>86.94</v>
       </c>
       <c r="DI8" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DM8" t="n">
-        <v>40.62</v>
+        <v>40</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.82</v>
+        <v>0.77</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="DP8" t="n">
-        <v>10.12</v>
+        <v>10.06</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.43</v>
+        <v>14.06</v>
       </c>
       <c r="DR8" t="n">
-        <v>7</v>
+        <v>6.82</v>
       </c>
       <c r="DS8" t="n">
         <v>0.06</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>43.44</v>
+        <v>43.41</v>
       </c>
       <c r="DW8" t="n">
         <v>0.06</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.93</v>
+        <v>12.18</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.06</v>
+        <v>8.23</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="EA8" t="n">
-        <v>15</v>
+        <v>14.71</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4290,139 +4290,139 @@
         <v>1.25</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AH9" t="n">
         <v>2</v>
       </c>
       <c r="AI9" t="n">
-        <v>75.75</v>
+        <v>77.56</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AN9" t="n">
-        <v>29.12</v>
+        <v>29.56</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AR9" t="n">
-        <v>11.5</v>
+        <v>11.22</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.880000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.38</v>
+        <v>3.11</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>51</v>
+        <v>51.67</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.880000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.62</v>
+        <v>5.67</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="BD9" t="n">
-        <v>16.12</v>
+        <v>16.44</v>
       </c>
       <c r="BE9" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.38</v>
+        <v>3.29</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.380000000000001</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.38</v>
+        <v>3.29</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BN9" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.56</v>
+        <v>4.59</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.81</v>
+        <v>4.71</v>
       </c>
       <c r="BR9" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS9" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BU9" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BV9" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BW9" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY9" t="n">
         <v>4.63</v>
@@ -4431,46 +4431,46 @@
         <v>4.84</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.14</v>
+        <v>4.1</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.43</v>
+        <v>4.39</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="CD9" t="n">
-        <v>6.51</v>
+        <v>6.28</v>
       </c>
       <c r="CE9" t="n">
         <v>1.31</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.73</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CO9" t="n">
         <v>1.21</v>
@@ -4479,19 +4479,19 @@
         <v>1.77</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CR9" t="n">
         <v>1.37</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CT9" t="n">
         <v>3.17</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CV9" t="n">
         <v>2.15</v>
@@ -4515,49 +4515,49 @@
         <v>1.29</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="DE9" t="n">
         <v>0.06</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="DH9" t="n">
-        <v>76</v>
+        <v>76.94</v>
       </c>
       <c r="DI9" t="n">
         <v>-0.12</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DM9" t="n">
-        <v>33.37</v>
+        <v>33.35</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DP9" t="n">
-        <v>11</v>
+        <v>10.82</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.5</v>
+        <v>11.35</v>
       </c>
       <c r="DR9" t="n">
         <v>9</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>48.75</v>
+        <v>49.24</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.94</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.75</v>
+        <v>5.77</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.18</v>
+        <v>3.11</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.19</v>
+        <v>16.35</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="10">
@@ -4669,7 +4669,7 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>52.44</v>
+        <v>52.56</v>
       </c>
       <c r="Y10" t="n">
         <v>0.33</v>
@@ -4831,7 +4831,7 @@
         <v>2.05</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CA10" t="n">
         <v>4.3</v>
@@ -4888,13 +4888,13 @@
         <v>1.35</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CT10" t="n">
         <v>3.26</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CV10" t="n">
         <v>2.46</v>
@@ -4903,23 +4903,23 @@
         <v>1.61</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DB10" t="inlineStr"/>
       <c r="DC10" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="DE10" t="n">
         <v>0.17</v>
@@ -4973,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>53.17</v>
+        <v>53.24</v>
       </c>
       <c r="DW10" t="n">
         <v>0.29</v>
@@ -5004,13 +5004,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
         <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
         <v>0.12</v>
@@ -5094,139 +5094,139 @@
         <v>1.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AI11" t="n">
-        <v>71.5</v>
+        <v>70</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AN11" t="n">
-        <v>25.25</v>
+        <v>25.44</v>
       </c>
       <c r="AO11" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>42.22</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>18.11</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BL11" t="n">
         <v>0.88</v>
       </c>
-      <c r="AP11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>11.88</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>0.9399999999999999</v>
-      </c>
       <c r="BM11" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BO11" t="n">
         <v>1.06</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.31</v>
+        <v>5.35</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.44</v>
+        <v>4.35</v>
       </c>
       <c r="BR11" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS11" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT11" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BU11" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV11" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX11" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BY11" t="n">
         <v>4.6</v>
@@ -5235,28 +5235,28 @@
         <v>5.22</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.02</v>
+        <v>4.17</v>
       </c>
       <c r="CC11" t="n">
-        <v>4.98</v>
+        <v>5.65</v>
       </c>
       <c r="CD11" t="n">
-        <v>5.42</v>
+        <v>6.15</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CI11" t="n">
         <v>1.92</v>
@@ -5265,10 +5265,10 @@
         <v>1.85</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CM11" t="n">
         <v>2.4</v>
@@ -5277,31 +5277,31 @@
         <v>1.87</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="CR11" t="n">
         <v>1.39</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="CT11" t="n">
         <v>3.07</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CX11" t="n">
         <v>1.55</v>
@@ -5313,91 +5313,91 @@
         <v>2.41</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="DB11" t="n">
         <v>1.31</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="DH11" t="n">
-        <v>77.5</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DM11" t="n">
-        <v>29.56</v>
+        <v>29.41</v>
       </c>
       <c r="DN11" t="n">
         <v>0.82</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.44</v>
+        <v>13.59</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.43</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DS11" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DT11" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>42.38</v>
+        <v>42.47</v>
       </c>
       <c r="DW11" t="n">
         <v>0.06</v>
       </c>
       <c r="DX11" t="n">
-        <v>9.75</v>
+        <v>10.06</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.12</v>
+        <v>7.06</v>
       </c>
       <c r="DZ11" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.44</v>
+        <v>18.71</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="12">
@@ -5500,7 +5500,7 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
         <v>2.5</v>
@@ -5524,7 +5524,7 @@
         <v>37.12</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AP12" t="n">
         <v>1.12</v>
@@ -5635,13 +5635,13 @@
         <v>2.35</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="CA12" t="n">
         <v>3.78</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.05</v>
+        <v>4.03</v>
       </c>
       <c r="CC12" t="n">
         <v>3.79</v>
@@ -5692,7 +5692,7 @@
         <v>1.36</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CT12" t="n">
         <v>3.21</v>
@@ -5701,10 +5701,10 @@
         <v>1.54</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CX12" t="n">
         <v>1.56</v>
@@ -5722,16 +5722,16 @@
         <v>1.29</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="DE12" t="n">
         <v>0.12</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="DG12" t="n">
         <v>2.35</v>
@@ -5755,7 +5755,7 @@
         <v>35.11</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="DO12" t="n">
         <v>2.06</v>
@@ -5915,7 +5915,7 @@
         <v>0.11</v>
       </c>
       <c r="AK13" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="AL13" t="n">
         <v>6.22</v>
@@ -5927,7 +5927,7 @@
         <v>43.78</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.89</v>
+        <v>1.11</v>
       </c>
       <c r="AP13" t="n">
         <v>2.78</v>
@@ -5957,7 +5957,7 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>55.11</v>
+        <v>55</v>
       </c>
       <c r="AZ13" t="n">
         <v>0.44</v>
@@ -5978,7 +5978,7 @@
         <v>1.36</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.22</v>
+        <v>2.44</v>
       </c>
       <c r="BG13" t="n">
         <v>2.47</v>
@@ -6044,13 +6044,13 @@
         <v>3.7</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
       <c r="CC13" t="n">
         <v>2.61</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="CE13" t="n">
         <v>1.32</v>
@@ -6095,7 +6095,7 @@
         <v>1.37</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CT13" t="n">
         <v>3.16</v>
@@ -6110,25 +6110,25 @@
         <v>1.75</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="DB13" t="n">
         <v>1.3</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="DE13" t="n">
         <v>0.06</v>
@@ -6146,7 +6146,7 @@
         <v>0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="DK13" t="n">
         <v>6.17</v>
@@ -6158,7 +6158,7 @@
         <v>45.88</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.71</v>
+        <v>0.82</v>
       </c>
       <c r="DO13" t="n">
         <v>2.7</v>
@@ -6182,7 +6182,7 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>55.76</v>
+        <v>55.71</v>
       </c>
       <c r="DW13" t="n">
         <v>0.29</v>
@@ -6203,7 +6203,7 @@
         <v>1.47</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="14">
@@ -6213,94 +6213,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F14" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="G14" t="n">
         <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>119.25</v>
+        <v>118.22</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="K14" t="n">
-        <v>5.12</v>
+        <v>5.22</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M14" t="n">
-        <v>56.75</v>
+        <v>55.89</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="P14" t="n">
-        <v>12.62</v>
+        <v>13.11</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.75</v>
+        <v>10</v>
       </c>
       <c r="R14" t="n">
-        <v>4.88</v>
+        <v>4.56</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>62.12</v>
+        <v>61.44</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="Z14" t="n">
-        <v>15.12</v>
+        <v>14.67</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.5</v>
+        <v>8.33</v>
       </c>
       <c r="AB14" t="n">
-        <v>6.62</v>
+        <v>6.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>14.38</v>
+        <v>14.67</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6384,70 +6384,70 @@
         <v>2.25</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.19</v>
+        <v>3.12</v>
       </c>
       <c r="BH14" t="n">
         <v>9</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.19</v>
+        <v>3.12</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BN14" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BU14" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV14" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW14" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BX14" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.21</v>
+        <v>4.33</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.3</v>
+        <v>4.44</v>
       </c>
       <c r="CC14" t="n">
         <v>2.05</v>
@@ -6462,151 +6462,151 @@
         <v>2.39</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CR14" t="n">
         <v>1.35</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CT14" t="n">
         <v>3.27</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DB14" t="n">
         <v>1.27</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="DE14" t="n">
         <v>0.06</v>
       </c>
       <c r="DF14" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="DH14" t="n">
-        <v>109.68</v>
+        <v>109.7</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.44</v>
+        <v>5.47</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="DM14" t="n">
-        <v>50.44</v>
+        <v>50.35</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="DP14" t="n">
-        <v>11.81</v>
+        <v>12.12</v>
       </c>
       <c r="DQ14" t="n">
-        <v>9.82</v>
+        <v>10.41</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.63</v>
+        <v>5.42</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>59.87</v>
+        <v>59.64</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.12</v>
+        <v>0.23</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.31</v>
+        <v>14.12</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.5</v>
+        <v>8.41</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.81</v>
+        <v>5.7</v>
       </c>
       <c r="EA14" t="n">
-        <v>15.13</v>
+        <v>15.24</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -6616,94 +6616,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
         <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F15" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="G15" t="n">
-        <v>5.14</v>
+        <v>4.62</v>
       </c>
       <c r="H15" t="n">
-        <v>144.14</v>
+        <v>145.88</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="J15" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="K15" t="n">
-        <v>7.14</v>
+        <v>7.12</v>
       </c>
       <c r="L15" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="M15" t="n">
-        <v>79.14</v>
+        <v>77.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="P15" t="n">
-        <v>10</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.289999999999999</v>
+        <v>7.75</v>
       </c>
       <c r="R15" t="n">
-        <v>4.43</v>
+        <v>4.12</v>
       </c>
       <c r="S15" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="U15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>71</v>
+        <v>70.88</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.43</v>
+        <v>21.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>13.57</v>
+        <v>13.62</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.86</v>
+        <v>7.62</v>
       </c>
       <c r="AC15" t="n">
         <v>19</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF15" t="n">
         <v>0.22</v>
@@ -6790,67 +6790,67 @@
         <v>3.06</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.380000000000001</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BI15" t="n">
         <v>3.06</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BL15" t="n">
         <v>1.12</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.25</v>
+        <v>4.41</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.12</v>
+        <v>4.88</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT15" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BU15" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV15" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BW15" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX15" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CA15" t="n">
-        <v>6.04</v>
+        <v>6.13</v>
       </c>
       <c r="CB15" t="n">
-        <v>6.51</v>
+        <v>6.52</v>
       </c>
       <c r="CC15" t="n">
         <v>1.48</v>
@@ -6862,28 +6862,28 @@
         <v>1.2</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CG15" t="n">
-        <v>4.09</v>
+        <v>4.1</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CN15" t="n">
         <v>1.84</v>
@@ -6892,16 +6892,16 @@
         <v>1.11</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CR15" t="n">
         <v>1.34</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CT15" t="n">
         <v>3.34</v>
@@ -6910,10 +6910,10 @@
         <v>1.79</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CX15" t="n">
         <v>1.58</v>
@@ -6929,85 +6929,85 @@
       </c>
       <c r="DB15" t="inlineStr"/>
       <c r="DC15" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF15" t="n">
         <v>0.88</v>
       </c>
       <c r="DG15" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="DH15" t="n">
-        <v>135.62</v>
+        <v>136.94</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="DK15" t="n">
-        <v>6.25</v>
+        <v>6.29</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="DM15" t="n">
-        <v>70.18000000000001</v>
+        <v>69.94</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="DP15" t="n">
-        <v>10</v>
+        <v>9.82</v>
       </c>
       <c r="DQ15" t="n">
-        <v>8.81</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DR15" t="n">
-        <v>4.44</v>
+        <v>4.29</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>69.69</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>17.69</v>
+        <v>17.82</v>
       </c>
       <c r="DY15" t="n">
-        <v>10.81</v>
+        <v>11</v>
       </c>
       <c r="DZ15" t="n">
-        <v>6.88</v>
+        <v>6.82</v>
       </c>
       <c r="EA15" t="n">
-        <v>17.31</v>
+        <v>17.41</v>
       </c>
       <c r="EB15" t="n">
         <v>2.11</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="16">
@@ -7017,13 +7017,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
         <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7110,136 +7110,136 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AI16" t="n">
-        <v>82</v>
+        <v>79.56</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN16" t="n">
-        <v>31.75</v>
+        <v>30.67</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11.12</v>
+        <v>10.33</v>
       </c>
       <c r="AR16" t="n">
-        <v>10.88</v>
+        <v>10.33</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.380000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>52.88</v>
+        <v>50.33</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA16" t="n">
-        <v>10.25</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.88</v>
+        <v>6.44</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="BD16" t="n">
-        <v>18.25</v>
+        <v>18.11</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="BG16" t="n">
         <v>3.12</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.880000000000001</v>
+        <v>9.76</v>
       </c>
       <c r="BI16" t="n">
         <v>3.12</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BL16" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.31</v>
+        <v>4.47</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.38</v>
+        <v>4.18</v>
       </c>
       <c r="BR16" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS16" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT16" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU16" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV16" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BW16" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BX16" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY16" t="n">
         <v>2.02</v>
@@ -7248,73 +7248,73 @@
         <v>2.17</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.7</v>
+        <v>3.93</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.74</v>
+        <v>3.91</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.34</v>
+        <v>5.97</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.09</v>
+        <v>5.49</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.16</v>
+        <v>3.22</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="CR16" t="n">
         <v>1.37</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="CT16" t="n">
         <v>3.2</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CX16" t="n">
         <v>1.66</v>
@@ -7332,85 +7332,85 @@
         <v>1.3</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="DD16" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="DH16" t="n">
-        <v>90.12</v>
+        <v>88.36</v>
       </c>
       <c r="DI16" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.75</v>
+        <v>4.53</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="DM16" t="n">
-        <v>41.62</v>
+        <v>40.47</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="DO16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>11</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>53.88</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>17.06</v>
+      </c>
+      <c r="EB16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="EC16" t="n">
         <v>1.88</v>
-      </c>
-      <c r="DP16" t="n">
-        <v>11.43</v>
-      </c>
-      <c r="DQ16" t="n">
-        <v>11.63</v>
-      </c>
-      <c r="DR16" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="DS16" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DT16" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV16" t="n">
-        <v>55.38</v>
-      </c>
-      <c r="DW16" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DX16" t="n">
-        <v>12.43</v>
-      </c>
-      <c r="DY16" t="n">
-        <v>8.82</v>
-      </c>
-      <c r="DZ16" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="EA16" t="n">
-        <v>17.07</v>
-      </c>
-      <c r="EB16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="EC16" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -7654,13 +7654,13 @@
         <v>3.71</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CC17" t="n">
         <v>3.41</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="CE17" t="n">
         <v>1.32</v>
@@ -7720,7 +7720,7 @@
         <v>1.67</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CY17" t="n">
         <v>1.98</v>
@@ -7735,10 +7735,10 @@
         <v>1.28</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="DE17" t="n">
         <v>0.11</v>
@@ -7847,7 +7847,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="K18" t="n">
         <v>4.88</v>
@@ -7859,7 +7859,7 @@
         <v>42.88</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="O18" t="n">
         <v>1.88</v>
@@ -7910,7 +7910,7 @@
         <v>1.48</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -8057,7 +8057,7 @@
         <v>3.73</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="CC18" t="n">
         <v>3.76</v>
@@ -8108,19 +8108,19 @@
         <v>1.37</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CU18" t="n">
         <v>1.51</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CX18" t="n">
         <v>1.67</v>
@@ -8141,7 +8141,7 @@
         <v>1.81</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
@@ -8159,7 +8159,7 @@
         <v>0.12</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="DK18" t="n">
         <v>3.94</v>
@@ -8171,7 +8171,7 @@
         <v>42.53</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.53</v>
+        <v>0.59</v>
       </c>
       <c r="DO18" t="n">
         <v>1.53</v>
@@ -8216,7 +8216,7 @@
         <v>1.3</v>
       </c>
       <c r="EC18" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="19">
@@ -8238,7 +8238,7 @@
         <v>0.22</v>
       </c>
       <c r="F19" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="G19" t="n">
         <v>2.44</v>
@@ -8250,7 +8250,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="K19" t="n">
         <v>4.78</v>
@@ -8313,13 +8313,13 @@
         <v>1.54</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AH19" t="n">
         <v>1.5</v>
@@ -8343,7 +8343,7 @@
         <v>37.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.38</v>
+        <v>0.62</v>
       </c>
       <c r="AP19" t="n">
         <v>2.62</v>
@@ -8550,7 +8550,7 @@
         <v>0.12</v>
       </c>
       <c r="DF19" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="DG19" t="n">
         <v>2</v>
@@ -8562,7 +8562,7 @@
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="DK19" t="n">
         <v>4.47</v>
@@ -8574,7 +8574,7 @@
         <v>42.23</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.41</v>
+        <v>0.52</v>
       </c>
       <c r="DO19" t="n">
         <v>2.47</v>
@@ -8619,7 +8619,7 @@
         <v>1.32</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -1613,13 +1613,13 @@
         <v>4.25</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.54</v>
+        <v>4.53</v>
       </c>
       <c r="CC2" t="n">
         <v>8.68</v>
       </c>
       <c r="CD2" t="n">
-        <v>9.19</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="CE2" t="n">
         <v>1.39</v>
@@ -1664,7 +1664,7 @@
         <v>1.45</v>
       </c>
       <c r="CS2" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CT2" t="n">
         <v>2.85</v>
@@ -1673,22 +1673,22 @@
         <v>1.46</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CW2" t="n">
         <v>1.99</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DB2" t="n">
         <v>1.36</v>
@@ -2022,7 +2022,7 @@
         <v>4.95</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="CE3" t="n">
         <v>1.38</v>
@@ -2067,10 +2067,10 @@
         <v>1.41</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CU3" t="n">
         <v>1.45</v>
@@ -2082,25 +2082,25 @@
         <v>1.85</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DB3" t="n">
         <v>1.33</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="DE3" t="n">
         <v>0.06</v>
@@ -2470,13 +2470,13 @@
         <v>1.39</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CT4" t="n">
         <v>3.1</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV4" t="n">
         <v>2.18</v>
@@ -2485,16 +2485,16 @@
         <v>1.75</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DB4" t="n">
         <v>1.32</v>
@@ -2503,7 +2503,7 @@
         <v>1.9</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="DE4" t="n">
         <v>0.17</v>
@@ -2816,7 +2816,7 @@
         <v>2.85</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.07</v>
+        <v>3.11</v>
       </c>
       <c r="CA5" t="n">
         <v>4.06</v>
@@ -2873,7 +2873,7 @@
         <v>1.42</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CT5" t="n">
         <v>2.94</v>
@@ -2882,22 +2882,22 @@
         <v>1.43</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CW5" t="n">
         <v>1.91</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="DB5" t="n">
         <v>1.34</v>
@@ -4097,16 +4097,16 @@
         <v>1.81</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="DB8" t="n">
         <v>1.33</v>
@@ -4115,7 +4115,7 @@
         <v>1.96</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="DE8" t="n">
         <v>0.06</v>
@@ -4485,10 +4485,10 @@
         <v>1.37</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CU9" t="n">
         <v>1.56</v>
@@ -4500,16 +4500,16 @@
         <v>1.77</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="DB9" t="n">
         <v>1.29</v>
@@ -4518,7 +4518,7 @@
         <v>1.74</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DE9" t="n">
         <v>0.06</v>
@@ -5238,13 +5238,13 @@
         <v>4</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="CC11" t="n">
         <v>5.65</v>
       </c>
       <c r="CD11" t="n">
-        <v>6.15</v>
+        <v>5.99</v>
       </c>
       <c r="CE11" t="n">
         <v>1.35</v>
@@ -5289,31 +5289,31 @@
         <v>1.39</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CT11" t="n">
         <v>3.07</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CY11" t="n">
         <v>1.91</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DB11" t="n">
         <v>1.31</v>
@@ -5322,7 +5322,7 @@
         <v>1.9</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="DE11" t="n">
         <v>0.17</v>
@@ -6447,7 +6447,7 @@
         <v>4.33</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.44</v>
+        <v>4.43</v>
       </c>
       <c r="CC14" t="n">
         <v>2.05</v>
@@ -6498,31 +6498,31 @@
         <v>1.35</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CT14" t="n">
         <v>3.27</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="CX14" t="n">
         <v>1.64</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DB14" t="n">
         <v>1.27</v>
@@ -6531,7 +6531,7 @@
         <v>1.71</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="DE14" t="n">
         <v>0.06</v>
@@ -6850,7 +6850,7 @@
         <v>6.13</v>
       </c>
       <c r="CB15" t="n">
-        <v>6.52</v>
+        <v>6.71</v>
       </c>
       <c r="CC15" t="n">
         <v>1.48</v>
@@ -6901,28 +6901,28 @@
         <v>1.34</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CT15" t="n">
         <v>3.34</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CV15" t="n">
         <v>2.09</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="DA15" t="n">
         <v>1.92</v>
@@ -6932,7 +6932,7 @@
         <v>1.48</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DE15" t="n">
         <v>0.17</v>
@@ -7251,13 +7251,13 @@
         <v>3.93</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.91</v>
+        <v>4.11</v>
       </c>
       <c r="CC16" t="n">
         <v>5.97</v>
       </c>
       <c r="CD16" t="n">
-        <v>5.49</v>
+        <v>5.45</v>
       </c>
       <c r="CE16" t="n">
         <v>1.31</v>
@@ -7302,13 +7302,13 @@
         <v>1.37</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="CT16" t="n">
         <v>3.2</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="CV16" t="n">
         <v>2.22</v>
@@ -7317,16 +7317,16 @@
         <v>1.73</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="DB16" t="n">
         <v>1.3</v>
@@ -7335,7 +7335,7 @@
         <v>1.81</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>0.11</v>
@@ -3484,52 +3484,52 @@
         <v>1.56</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG7" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="AI7" t="n">
-        <v>110.62</v>
+        <v>105.78</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.75</v>
+        <v>3.44</v>
       </c>
       <c r="AL7" t="n">
-        <v>6.38</v>
+        <v>5.89</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="AN7" t="n">
-        <v>58.12</v>
+        <v>55.22</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13</v>
+        <v>12.22</v>
       </c>
       <c r="AR7" t="n">
-        <v>13.75</v>
+        <v>13.78</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.5</v>
+        <v>7.56</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>59.5</v>
+        <v>57.22</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BA7" t="n">
-        <v>14.12</v>
+        <v>13.33</v>
       </c>
       <c r="BB7" t="n">
-        <v>9.119999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="BC7" t="n">
-        <v>5</v>
+        <v>4.89</v>
       </c>
       <c r="BD7" t="n">
-        <v>18.25</v>
+        <v>17.11</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.59</v>
+        <v>10.33</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="BO7" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.53</v>
+        <v>5.33</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.06</v>
+        <v>5</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT7" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BU7" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV7" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BW7" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BX7" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BY7" t="n">
         <v>2.18</v>
@@ -3625,28 +3625,28 @@
         <v>2.18</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.78</v>
+        <v>3.91</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.96</v>
+        <v>4.08</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.28</v>
+        <v>3.13</v>
       </c>
       <c r="CD7" t="n">
-        <v>2.3</v>
+        <v>3.17</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CI7" t="n">
         <v>2.1</v>
@@ -3658,40 +3658,40 @@
         <v>1.56</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CN7" t="n">
         <v>1.81</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="CR7" t="n">
         <v>1.37</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="CT7" t="n">
         <v>3.17</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CX7" t="n">
         <v>1.61</v>
@@ -3700,7 +3700,7 @@
         <v>2</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="DA7" t="n">
         <v>1.83</v>
@@ -3709,85 +3709,85 @@
         <v>1.29</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.77</v>
+        <v>2.67</v>
       </c>
       <c r="DH7" t="n">
-        <v>107.35</v>
+        <v>105.11</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.71</v>
+        <v>2.61</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.06</v>
+        <v>5.84</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.52</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM7" t="n">
-        <v>54.58</v>
+        <v>53.33</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.29</v>
+        <v>3.16</v>
       </c>
       <c r="DP7" t="n">
-        <v>12</v>
+        <v>11.66</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.24</v>
+        <v>13.28</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.35</v>
+        <v>6.44</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>55.12</v>
+        <v>54.22</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DX7" t="n">
-        <v>14.53</v>
+        <v>14.11</v>
       </c>
       <c r="DY7" t="n">
-        <v>9.640000000000001</v>
+        <v>9.27</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.88</v>
+        <v>4.84</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.29</v>
+        <v>16.78</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>0.11</v>
@@ -3890,49 +3890,49 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AI8" t="n">
-        <v>91.75</v>
+        <v>89</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>37.62</v>
+        <v>38</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AR8" t="n">
-        <v>14.75</v>
+        <v>14.89</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.119999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>43.88</v>
+        <v>43.22</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA8" t="n">
-        <v>10.62</v>
+        <v>11</v>
       </c>
       <c r="BB8" t="n">
-        <v>8</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="BD8" t="n">
-        <v>15.5</v>
+        <v>14.44</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="BF8" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.289999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL8" t="n">
         <v>1.06</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.65</v>
+        <v>0.78</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.12</v>
+        <v>4.06</v>
       </c>
       <c r="BR8" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS8" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT8" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BU8" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BV8" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW8" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX8" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY8" t="n">
         <v>3.71</v>
@@ -4028,70 +4028,70 @@
         <v>3.77</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.74</v>
+        <v>3.77</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.82</v>
+        <v>3.85</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.26</v>
+        <v>4.33</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.49</v>
+        <v>4.56</v>
       </c>
       <c r="CE8" t="n">
         <v>1.35</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CI8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CO8" t="n">
         <v>1.26</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="CR8" t="n">
         <v>1.41</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="CT8" t="n">
         <v>3</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CW8" t="n">
         <v>1.81</v>
@@ -4112,52 +4112,52 @@
         <v>1.33</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="DE8" t="n">
         <v>0.06</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DH8" t="n">
-        <v>86.94</v>
+        <v>85.84</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DM8" t="n">
-        <v>40</v>
+        <v>40.06</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="DP8" t="n">
-        <v>10.06</v>
+        <v>10</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.06</v>
+        <v>14.16</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.82</v>
+        <v>6.94</v>
       </c>
       <c r="DS8" t="n">
         <v>0.06</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>43.41</v>
+        <v>43.11</v>
       </c>
       <c r="DW8" t="n">
         <v>0.06</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.18</v>
+        <v>12.28</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.23</v>
+        <v>8.33</v>
       </c>
       <c r="DZ8" t="n">
         <v>3.94</v>
       </c>
       <c r="EA8" t="n">
-        <v>14.71</v>
+        <v>14.22</v>
       </c>
       <c r="EB8" t="n">
         <v>1.34</v>
       </c>
       <c r="EC8" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="9">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F10" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="G10" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="H10" t="n">
-        <v>106.33</v>
+        <v>106.7</v>
       </c>
       <c r="I10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J10" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="K10" t="n">
-        <v>4.67</v>
+        <v>4.6</v>
       </c>
       <c r="L10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="M10" t="n">
-        <v>47.89</v>
+        <v>50.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="O10" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="P10" t="n">
-        <v>11.89</v>
+        <v>12.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.33</v>
+        <v>12</v>
       </c>
       <c r="R10" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="S10" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="T10" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="U10" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V10" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>52.56</v>
+        <v>53.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.779999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.22</v>
+        <v>4.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>19.78</v>
+        <v>19.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AF10" t="n">
         <v>0.12</v>
@@ -4774,67 +4774,67 @@
         <v>3.12</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.35</v>
+        <v>3.39</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.94</v>
+        <v>8.83</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.35</v>
+        <v>3.39</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="BP10" t="n">
         <v>3.94</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.65</v>
+        <v>3.61</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT10" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU10" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BV10" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BW10" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX10" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.3</v>
+        <v>4.29</v>
       </c>
       <c r="CB10" t="n">
         <v>4.31</v>
@@ -4849,10 +4849,10 @@
         <v>1.25</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="CH10" t="n">
         <v>1.62</v>
@@ -4864,10 +4864,10 @@
         <v>1.57</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CM10" t="n">
         <v>2.27</v>
@@ -4894,13 +4894,13 @@
         <v>3.26</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CX10" t="n">
         <v>1.58</v>
@@ -4919,82 +4919,82 @@
         <v>1.58</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="DH10" t="n">
-        <v>107.47</v>
+        <v>107.61</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.94</v>
+        <v>2.83</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.65</v>
+        <v>4.61</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DM10" t="n">
-        <v>49.65</v>
+        <v>50.83</v>
       </c>
       <c r="DN10" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="DP10" t="n">
-        <v>13</v>
+        <v>13.17</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.65</v>
+        <v>11.5</v>
       </c>
       <c r="DR10" t="n">
-        <v>7</v>
+        <v>7.17</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>53.24</v>
+        <v>53.72</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.47</v>
+        <v>12.56</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.41</v>
+        <v>8.33</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.06</v>
+        <v>4.22</v>
       </c>
       <c r="EA10" t="n">
         <v>20</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="11">
@@ -6616,94 +6616,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
         <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F15" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>4.62</v>
+        <v>4.44</v>
       </c>
       <c r="H15" t="n">
-        <v>145.88</v>
+        <v>145</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="J15" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="K15" t="n">
-        <v>7.12</v>
+        <v>6.78</v>
       </c>
       <c r="L15" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="M15" t="n">
-        <v>77.5</v>
+        <v>75.78</v>
       </c>
       <c r="N15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="O15" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="P15" t="n">
-        <v>9.619999999999999</v>
+        <v>10.11</v>
       </c>
       <c r="Q15" t="n">
-        <v>7.75</v>
+        <v>7.56</v>
       </c>
       <c r="R15" t="n">
-        <v>4.12</v>
+        <v>3.78</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="T15" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="U15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>70.88</v>
+        <v>69.78</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.25</v>
+        <v>20.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>13.62</v>
+        <v>12.78</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.62</v>
+        <v>7.56</v>
       </c>
       <c r="AC15" t="n">
-        <v>19</v>
+        <v>18.11</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AF15" t="n">
         <v>0.22</v>
@@ -6790,67 +6790,67 @@
         <v>3.06</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.289999999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="BI15" t="n">
         <v>3.06</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL15" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.41</v>
+        <v>4.28</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.88</v>
+        <v>4.83</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT15" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BU15" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV15" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BW15" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX15" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CA15" t="n">
-        <v>6.13</v>
+        <v>6.12</v>
       </c>
       <c r="CB15" t="n">
-        <v>6.71</v>
+        <v>6.68</v>
       </c>
       <c r="CC15" t="n">
         <v>1.48</v>
@@ -6862,10 +6862,10 @@
         <v>1.2</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CG15" t="n">
-        <v>4.1</v>
+        <v>4.08</v>
       </c>
       <c r="CH15" t="n">
         <v>1.77</v>
@@ -6880,13 +6880,13 @@
         <v>1.52</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CM15" t="n">
         <v>2.37</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CO15" t="n">
         <v>1.11</v>
@@ -6910,13 +6910,13 @@
         <v>1.81</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY15" t="n">
         <v>1.9</v>
@@ -6932,82 +6932,82 @@
         <v>1.48</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="DH15" t="n">
-        <v>136.94</v>
+        <v>137</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DK15" t="n">
-        <v>6.29</v>
+        <v>6.17</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM15" t="n">
-        <v>69.94</v>
+        <v>69.5</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="DP15" t="n">
-        <v>9.82</v>
+        <v>10.06</v>
       </c>
       <c r="DQ15" t="n">
-        <v>8.529999999999999</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="DR15" t="n">
-        <v>4.29</v>
+        <v>4.11</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>69.70999999999999</v>
+        <v>69.22</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>17.82</v>
+        <v>17.55</v>
       </c>
       <c r="DY15" t="n">
-        <v>11</v>
+        <v>10.73</v>
       </c>
       <c r="DZ15" t="n">
-        <v>6.82</v>
+        <v>6.84</v>
       </c>
       <c r="EA15" t="n">
-        <v>17.41</v>
+        <v>17.06</v>
       </c>
       <c r="EB15" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="16">

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="G2" t="n">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="H2" t="n">
-        <v>76.25</v>
+        <v>75.22</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="K2" t="n">
-        <v>4.62</v>
+        <v>4.78</v>
       </c>
       <c r="L2" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="M2" t="n">
-        <v>34.25</v>
+        <v>33.78</v>
       </c>
       <c r="N2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="P2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.38</v>
+        <v>11</v>
       </c>
       <c r="R2" t="n">
-        <v>8.380000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="S2" t="n">
-        <v>0.88</v>
+        <v>1.33</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="U2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>44.12</v>
+        <v>43</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z2" t="n">
-        <v>11</v>
+        <v>10.56</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.38</v>
+        <v>6.11</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.62</v>
+        <v>4.44</v>
       </c>
       <c r="AC2" t="n">
-        <v>18.25</v>
+        <v>17.44</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>1.22</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.470000000000001</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.41</v>
+        <v>0.61</v>
       </c>
       <c r="BL2" t="n">
         <v>1.06</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.82</v>
+        <v>1.06</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.06</v>
+        <v>3.94</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.41</v>
+        <v>5.44</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT2" t="n">
-        <v>29.41</v>
+        <v>33.33</v>
       </c>
       <c r="BU2" t="n">
-        <v>17.65</v>
+        <v>22.22</v>
       </c>
       <c r="BV2" t="n">
-        <v>11.76</v>
+        <v>16.67</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="BX2" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.71</v>
+        <v>3.92</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.53</v>
+        <v>4.51</v>
       </c>
       <c r="CC2" t="n">
         <v>8.68</v>
@@ -1622,13 +1622,13 @@
         <v>9.119999999999999</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CH2" t="n">
         <v>1.43</v>
@@ -1637,13 +1637,13 @@
         <v>1.83</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CK2" t="n">
         <v>1.66</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CM2" t="n">
         <v>2.12</v>
@@ -1652,22 +1652,22 @@
         <v>1.68</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="CU2" t="n">
         <v>1.46</v>
@@ -1676,7 +1676,7 @@
         <v>1.9</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CX2" t="n">
         <v>1.67</v>
@@ -1685,61 +1685,61 @@
         <v>2.09</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DA2" t="n">
         <v>1.75</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="DE2" t="n">
         <v>0.06</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="DH2" t="n">
-        <v>74</v>
+        <v>73.61</v>
       </c>
       <c r="DI2" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.76</v>
+        <v>3.89</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DM2" t="n">
-        <v>31.17</v>
+        <v>31.11</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.41</v>
+        <v>11.28</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.35</v>
+        <v>11.16</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.710000000000001</v>
+        <v>8.66</v>
       </c>
       <c r="DS2" t="n">
         <v>0.11</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>42</v>
+        <v>41.56</v>
       </c>
       <c r="DW2" t="n">
         <v>0.06</v>
       </c>
       <c r="DX2" t="n">
-        <v>9.24</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DY2" t="n">
-        <v>5.71</v>
+        <v>5.61</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.53</v>
+        <v>16.22</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,139 +1872,139 @@
         <v>2.22</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AI3" t="n">
-        <v>91.88</v>
+        <v>96.56</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.38</v>
+        <v>4.44</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AN3" t="n">
-        <v>37.25</v>
+        <v>37.56</v>
       </c>
       <c r="AO3" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13.38</v>
+        <v>14.11</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.38</v>
+        <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>8</v>
+        <v>8.56</v>
       </c>
       <c r="AT3" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>45.75</v>
+        <v>46.44</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.5</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.88</v>
+        <v>6.67</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.62</v>
+        <v>3.22</v>
       </c>
       <c r="BD3" t="n">
-        <v>18.88</v>
+        <v>19.78</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="BF3" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.82</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL3" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.94</v>
+        <v>3.89</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.88</v>
+        <v>5.72</v>
       </c>
       <c r="BR3" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS3" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BT3" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BU3" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV3" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX3" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BY3" t="n">
         <v>3.31</v>
@@ -2013,31 +2013,31 @@
         <v>3.69</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.84</v>
+        <v>3.87</v>
       </c>
       <c r="CC3" t="n">
-        <v>4.95</v>
+        <v>5.25</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.24</v>
+        <v>5.48</v>
       </c>
       <c r="CE3" t="n">
         <v>1.38</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CI3" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.81</v>
@@ -2046,22 +2046,22 @@
         <v>1.57</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CO3" t="n">
         <v>1.28</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="CR3" t="n">
         <v>1.41</v>
@@ -2079,7 +2079,7 @@
         <v>2.04</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CX3" t="n">
         <v>1.63</v>
@@ -2088,94 +2088,94 @@
         <v>2.05</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DB3" t="n">
         <v>1.33</v>
       </c>
       <c r="DC3" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="DE3" t="n">
         <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.23</v>
+        <v>3.16</v>
       </c>
       <c r="DH3" t="n">
-        <v>90.06</v>
+        <v>92.5</v>
       </c>
       <c r="DI3" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.12</v>
+        <v>5.11</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DM3" t="n">
-        <v>40.77</v>
+        <v>40.72</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.77</v>
+        <v>0.84</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.71</v>
+        <v>14.06</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.88</v>
+        <v>14.16</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.59</v>
+        <v>6.94</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>44.35</v>
+        <v>44.78</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DX3" t="n">
-        <v>11.24</v>
+        <v>10.89</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.47</v>
+        <v>7.34</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.76</v>
+        <v>3.56</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.36</v>
+        <v>18.83</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
         <v>0.33</v>
@@ -2278,136 +2278,136 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AH4" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AI4" t="n">
-        <v>91.25</v>
+        <v>90.33</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.25</v>
+        <v>2.89</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN4" t="n">
-        <v>38.75</v>
+        <v>41.78</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13.38</v>
+        <v>12.89</v>
       </c>
       <c r="AR4" t="n">
-        <v>12</v>
+        <v>12.67</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.62</v>
+        <v>6.89</v>
       </c>
       <c r="AT4" t="n">
         <v>2</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>43.75</v>
+        <v>42.11</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.119999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="BD4" t="n">
-        <v>19.75</v>
+        <v>19.11</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="BG4" t="n">
         <v>2.94</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.710000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="BI4" t="n">
         <v>2.94</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.06</v>
+        <v>4.83</v>
       </c>
       <c r="BR4" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS4" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT4" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU4" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV4" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW4" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX4" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
         <v>3</v>
@@ -2416,25 +2416,25 @@
         <v>3.38</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.64</v>
+        <v>3.66</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.75</v>
+        <v>3.91</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.73</v>
+        <v>3.91</v>
       </c>
       <c r="CE4" t="n">
         <v>1.35</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CH4" t="n">
         <v>1.47</v>
@@ -2443,7 +2443,7 @@
         <v>2.07</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CK4" t="n">
         <v>1.65</v>
@@ -2452,13 +2452,13 @@
         <v>2.11</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CN4" t="n">
         <v>1.73</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CP4" t="n">
         <v>1.84</v>
@@ -2479,106 +2479,106 @@
         <v>1.49</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CW4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DA4" t="n">
         <v>1.75</v>
-      </c>
-      <c r="CX4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CY4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="CZ4" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="DA4" t="n">
-        <v>1.74</v>
       </c>
       <c r="DB4" t="n">
         <v>1.32</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="DH4" t="n">
-        <v>96.06</v>
+        <v>95.33</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.53</v>
+        <v>4.28</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM4" t="n">
-        <v>39.64</v>
+        <v>41.11</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.53</v>
+        <v>13.28</v>
       </c>
       <c r="DQ4" t="n">
-        <v>10.94</v>
+        <v>11.34</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.29</v>
+        <v>7.39</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.24</v>
+        <v>43.39</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.12</v>
+        <v>11.72</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.06</v>
+        <v>7.78</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.06</v>
+        <v>3.94</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.65</v>
+        <v>18.39</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2681,49 +2681,49 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AI5" t="n">
-        <v>77.12</v>
+        <v>78.56</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.62</v>
+        <v>3.89</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>36.75</v>
+        <v>35.22</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13.75</v>
+        <v>13.78</v>
       </c>
       <c r="AR5" t="n">
-        <v>12.75</v>
+        <v>13.33</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.880000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>41.38</v>
+        <v>41.89</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.619999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.5</v>
+        <v>6.11</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="BD5" t="n">
-        <v>14.62</v>
+        <v>14.89</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.880000000000001</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL5" t="n">
         <v>1.06</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5</v>
+        <v>5.33</v>
       </c>
       <c r="BR5" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS5" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BT5" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BU5" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV5" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX5" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
         <v>2.85</v>
@@ -2822,133 +2822,133 @@
         <v>4.06</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.06</v>
+        <v>4.07</v>
       </c>
       <c r="CC5" t="n">
-        <v>6.77</v>
+        <v>6.59</v>
       </c>
       <c r="CD5" t="n">
-        <v>7.41</v>
+        <v>7.18</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CH5" t="n">
         <v>1.44</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CL5" t="n">
         <v>2.07</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CO5" t="n">
         <v>1.27</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CS5" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="DB5" t="n">
         <v>1.34</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.88</v>
+        <v>1.06</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="DH5" t="n">
-        <v>88.17</v>
+        <v>88.28</v>
       </c>
       <c r="DI5" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.53</v>
+        <v>4.61</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM5" t="n">
-        <v>45.29</v>
+        <v>44.06</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="DP5" t="n">
-        <v>14.12</v>
+        <v>14.11</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.53</v>
+        <v>12.83</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.18</v>
+        <v>7.22</v>
       </c>
       <c r="DS5" t="n">
         <v>0.06</v>
@@ -2966,22 +2966,22 @@
         <v>0.06</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.64</v>
+        <v>11.38</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.82</v>
+        <v>7.56</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.47</v>
+        <v>18.39</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="H6" t="n">
-        <v>82.75</v>
+        <v>84</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="K6" t="n">
-        <v>7.25</v>
+        <v>6.56</v>
       </c>
       <c r="L6" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="M6" t="n">
-        <v>43.62</v>
+        <v>44.22</v>
       </c>
       <c r="N6" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="O6" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="P6" t="n">
-        <v>12.25</v>
+        <v>13</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.62</v>
+        <v>12.56</v>
       </c>
       <c r="R6" t="n">
-        <v>5</v>
+        <v>5.22</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="U6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>49.25</v>
+        <v>49.11</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.88</v>
+        <v>15.33</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.25</v>
+        <v>9.56</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.62</v>
+        <v>5.78</v>
       </c>
       <c r="AC6" t="n">
-        <v>17.75</v>
+        <v>17.78</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AF6" t="n">
         <v>0.11</v>
@@ -3162,70 +3162,70 @@
         <v>2.11</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.53</v>
+        <v>10.28</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.41</v>
+        <v>4.33</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.06</v>
+        <v>4.94</v>
       </c>
       <c r="BR6" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS6" t="n">
-        <v>82.34999999999999</v>
+        <v>77.78</v>
       </c>
       <c r="BT6" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BU6" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BV6" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.93</v>
+        <v>3.97</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="CC6" t="n">
         <v>2.79</v>
@@ -3237,37 +3237,37 @@
         <v>1.31</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CO6" t="n">
         <v>1.21</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CQ6" t="n">
         <v>2.74</v>
@@ -3285,10 +3285,10 @@
         <v>1.56</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CX6" t="n">
         <v>1.59</v>
@@ -3297,7 +3297,7 @@
         <v>1.98</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="DA6" t="n">
         <v>1.85</v>
@@ -3306,85 +3306,85 @@
         <v>1.27</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="DE6" t="n">
         <v>0.11</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="DH6" t="n">
-        <v>85.83</v>
+        <v>86.28</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DK6" t="n">
-        <v>6.12</v>
+        <v>5.84</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="DM6" t="n">
-        <v>43.12</v>
+        <v>43.44</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.76</v>
+        <v>2.61</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.29</v>
+        <v>13.61</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.12</v>
+        <v>12.56</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.29</v>
+        <v>6.33</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>49.29</v>
+        <v>49.22</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.06</v>
+        <v>14.33</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.76</v>
+        <v>8.94</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.29</v>
+        <v>5.39</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.94</v>
+        <v>17</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="7">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4290,139 +4290,139 @@
         <v>1.25</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AH9" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AI9" t="n">
-        <v>77.56</v>
+        <v>76.7</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.11</v>
+        <v>3.8</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN9" t="n">
-        <v>29.56</v>
+        <v>30.3</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9.779999999999999</v>
+        <v>10</v>
       </c>
       <c r="AR9" t="n">
-        <v>11.22</v>
+        <v>11.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.779999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>51.67</v>
+        <v>51.8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.779999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.67</v>
+        <v>5.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="BD9" t="n">
-        <v>16.44</v>
+        <v>16.8</v>
       </c>
       <c r="BE9" t="n">
         <v>0.99</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.289999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BN9" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.59</v>
+        <v>4.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.71</v>
+        <v>4.56</v>
       </c>
       <c r="BR9" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS9" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT9" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU9" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BV9" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BW9" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX9" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY9" t="n">
         <v>4.63</v>
@@ -4431,16 +4431,16 @@
         <v>4.84</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.1</v>
+        <v>4.14</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.39</v>
+        <v>4.42</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="CD9" t="n">
-        <v>6.28</v>
+        <v>6.4</v>
       </c>
       <c r="CE9" t="n">
         <v>1.31</v>
@@ -4449,37 +4449,37 @@
         <v>2.52</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="CH9" t="n">
         <v>1.52</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.73</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CO9" t="n">
         <v>1.21</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="CR9" t="n">
         <v>1.37</v>
@@ -4494,22 +4494,22 @@
         <v>1.56</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CY9" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="DB9" t="n">
         <v>1.29</v>
@@ -4518,7 +4518,7 @@
         <v>1.74</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="DE9" t="n">
         <v>0.06</v>
@@ -4527,73 +4527,73 @@
         <v>1.11</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="DH9" t="n">
-        <v>76.94</v>
+        <v>76.5</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.11</v>
+        <v>3.94</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM9" t="n">
-        <v>33.35</v>
+        <v>33.55</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="DP9" t="n">
-        <v>10.82</v>
+        <v>10.89</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.35</v>
+        <v>11.33</v>
       </c>
       <c r="DR9" t="n">
-        <v>9</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>49.24</v>
+        <v>49.44</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.880000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.77</v>
+        <v>5.84</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.35</v>
+        <v>16.56</v>
       </c>
       <c r="EB9" t="n">
         <v>1.02</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="10">
@@ -5004,58 +5004,58 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F11" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="G11" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="H11" t="n">
-        <v>83.5</v>
+        <v>83.67</v>
       </c>
       <c r="I11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J11" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="K11" t="n">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="L11" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>33.88</v>
+        <v>34.11</v>
       </c>
       <c r="N11" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="O11" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="P11" t="n">
-        <v>11.12</v>
+        <v>11.67</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.88</v>
+        <v>13</v>
       </c>
       <c r="R11" t="n">
-        <v>9.75</v>
+        <v>9.33</v>
       </c>
       <c r="S11" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
@@ -5070,28 +5070,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>42.75</v>
+        <v>43.33</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.75</v>
+        <v>10.11</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.75</v>
+        <v>7.33</v>
       </c>
       <c r="AB11" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AC11" t="n">
-        <v>19.38</v>
+        <v>19.89</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AF11" t="n">
         <v>0.22</v>
@@ -5175,70 +5175,70 @@
         <v>2</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.710000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="BO11" t="n">
         <v>1.06</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.35</v>
+        <v>5.11</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.35</v>
+        <v>4.22</v>
       </c>
       <c r="BR11" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS11" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT11" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BU11" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV11" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX11" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.6</v>
+        <v>4.42</v>
       </c>
       <c r="BZ11" t="n">
-        <v>5.22</v>
+        <v>4.95</v>
       </c>
       <c r="CA11" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.16</v>
+        <v>4.1</v>
       </c>
       <c r="CC11" t="n">
         <v>5.65</v>
@@ -5247,10 +5247,10 @@
         <v>5.99</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CG11" t="n">
         <v>3.04</v>
@@ -5265,106 +5265,106 @@
         <v>1.85</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CN11" t="n">
         <v>1.87</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV11" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CW11" t="n">
         <v>1.88</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY11" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DC11" t="n">
         <v>1.91</v>
       </c>
-      <c r="CZ11" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="DA11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="DB11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="DC11" t="n">
-        <v>1.9</v>
-      </c>
       <c r="DD11" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF11" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DH11" t="n">
-        <v>76.34999999999999</v>
+        <v>76.83</v>
       </c>
       <c r="DI11" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM11" t="n">
-        <v>29.41</v>
+        <v>29.78</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="DP11" t="n">
-        <v>12</v>
+        <v>12.23</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.59</v>
+        <v>13.61</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.289999999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DS11" t="n">
         <v>0.06</v>
@@ -5376,28 +5376,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>42.47</v>
+        <v>42.78</v>
       </c>
       <c r="DW11" t="n">
         <v>0.06</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.06</v>
+        <v>9.77</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.06</v>
+        <v>6.89</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.71</v>
+        <v>19</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="12">
@@ -5407,13 +5407,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
         <v>0.22</v>
@@ -5500,136 +5500,136 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="AI12" t="n">
-        <v>87.75</v>
+        <v>90</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AN12" t="n">
-        <v>37.12</v>
+        <v>39.22</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.25</v>
+        <v>13.67</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.5</v>
+        <v>12.44</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.62</v>
+        <v>7.44</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="AU12" t="n">
         <v>1</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>47.75</v>
+        <v>48.78</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.75</v>
+        <v>10.33</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="BD12" t="n">
-        <v>17.38</v>
+        <v>17.56</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.94</v>
+        <v>3.11</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.65</v>
+        <v>10.78</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.94</v>
+        <v>3.11</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BL12" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.41</v>
+        <v>4.44</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.35</v>
+        <v>5.5</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT12" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU12" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BV12" t="n">
-        <v>17.65</v>
+        <v>22.22</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.88</v>
+        <v>11.11</v>
       </c>
       <c r="BX12" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY12" t="n">
         <v>2.35</v>
@@ -5638,25 +5638,25 @@
         <v>2.54</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.03</v>
+        <v>4</v>
       </c>
       <c r="CC12" t="n">
         <v>3.79</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.15</v>
+        <v>5.02</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="CH12" t="n">
         <v>1.51</v>
@@ -5674,7 +5674,7 @@
         <v>1.92</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CN12" t="n">
         <v>1.89</v>
@@ -5683,10 +5683,10 @@
         <v>1.21</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="CR12" t="n">
         <v>1.36</v>
@@ -5701,73 +5701,73 @@
         <v>1.54</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DB12" t="n">
         <v>1.29</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF12" t="n">
         <v>1.06</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="DH12" t="n">
-        <v>79.59</v>
+        <v>81.17</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.94</v>
+        <v>5.06</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DM12" t="n">
-        <v>35.11</v>
+        <v>36.28</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="DO12" t="n">
         <v>2.06</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.41</v>
+        <v>12.67</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.18</v>
+        <v>12.16</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.7</v>
+        <v>6.66</v>
       </c>
       <c r="DS12" t="n">
         <v>0.11</v>
@@ -5779,25 +5779,25 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.53</v>
+        <v>48.06</v>
       </c>
       <c r="DW12" t="n">
         <v>0.11</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.59</v>
+        <v>11.77</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.53</v>
+        <v>7.61</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.06</v>
+        <v>4.16</v>
       </c>
       <c r="EA12" t="n">
-        <v>15.77</v>
+        <v>15.94</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="EC12" t="n">
         <v>2.06</v>
@@ -5810,10 +5810,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
@@ -5822,49 +5822,49 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="G13" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="H13" t="n">
-        <v>93</v>
+        <v>96.22</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="K13" t="n">
-        <v>6.12</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>48.25</v>
+        <v>49.33</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="O13" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="P13" t="n">
-        <v>13.88</v>
+        <v>14.33</v>
       </c>
       <c r="Q13" t="n">
-        <v>13.25</v>
+        <v>12.78</v>
       </c>
       <c r="R13" t="n">
-        <v>5.88</v>
+        <v>5.78</v>
       </c>
       <c r="S13" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="T13" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5876,28 +5876,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>56.5</v>
+        <v>58.11</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z13" t="n">
-        <v>14.38</v>
+        <v>14.89</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.5</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.88</v>
+        <v>5</v>
       </c>
       <c r="AC13" t="n">
-        <v>17.5</v>
+        <v>17.67</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AF13" t="n">
         <v>0.11</v>
@@ -5981,70 +5981,70 @@
         <v>2.44</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.82</v>
+        <v>10.5</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.29</v>
+        <v>4.28</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.53</v>
+        <v>6.22</v>
       </c>
       <c r="BR13" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS13" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BT13" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU13" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV13" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX13" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="CC13" t="n">
         <v>2.61</v>
@@ -6059,13 +6059,13 @@
         <v>2.53</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CH13" t="n">
         <v>1.49</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.69</v>
@@ -6074,19 +6074,19 @@
         <v>1.52</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CO13" t="n">
         <v>1.23</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CQ13" t="n">
         <v>2.84</v>
@@ -6095,7 +6095,7 @@
         <v>1.37</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CT13" t="n">
         <v>3.16</v>
@@ -6104,10 +6104,10 @@
         <v>1.49</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CX13" t="n">
         <v>1.57</v>
@@ -6119,7 +6119,7 @@
         <v>2.37</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="DB13" t="n">
         <v>1.3</v>
@@ -6128,49 +6128,49 @@
         <v>1.84</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="DE13" t="n">
         <v>0.06</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.47</v>
+        <v>3.33</v>
       </c>
       <c r="DH13" t="n">
-        <v>90.23999999999999</v>
+        <v>92</v>
       </c>
       <c r="DI13" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="DK13" t="n">
-        <v>6.17</v>
+        <v>6.11</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM13" t="n">
-        <v>45.88</v>
+        <v>46.56</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.82</v>
+        <v>0.77</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.41</v>
+        <v>14.61</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.06</v>
+        <v>13.78</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.47</v>
+        <v>6.39</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6182,28 +6182,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>55.71</v>
+        <v>56.56</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.65</v>
+        <v>13</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.82</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.83</v>
+        <v>4.89</v>
       </c>
       <c r="EA13" t="n">
-        <v>17.59</v>
+        <v>17.67</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="14">
@@ -6213,13 +6213,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
         <v>0.11</v>
@@ -6306,49 +6306,49 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.38</v>
+        <v>3.11</v>
       </c>
       <c r="AI14" t="n">
-        <v>100.12</v>
+        <v>101.56</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.75</v>
+        <v>5.33</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AN14" t="n">
-        <v>44.12</v>
+        <v>44</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11</v>
+        <v>10.67</v>
       </c>
       <c r="AR14" t="n">
-        <v>10.88</v>
+        <v>10.67</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.38</v>
+        <v>6.44</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6360,82 +6360,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>57.62</v>
+        <v>58.56</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA14" t="n">
-        <v>13.5</v>
+        <v>14.56</v>
       </c>
       <c r="BB14" t="n">
-        <v>8.5</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BC14" t="n">
-        <v>5</v>
+        <v>5.67</v>
       </c>
       <c r="BD14" t="n">
-        <v>15.88</v>
+        <v>15.78</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.12</v>
+        <v>3.33</v>
       </c>
       <c r="BH14" t="n">
-        <v>9</v>
+        <v>8.94</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.12</v>
+        <v>3.33</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.53</v>
+        <v>0.72</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BN14" t="n">
         <v>1.94</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="BP14" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5</v>
+        <v>5.06</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT14" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU14" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BV14" t="n">
-        <v>17.65</v>
+        <v>22.22</v>
       </c>
       <c r="BW14" t="n">
-        <v>17.65</v>
+        <v>22.22</v>
       </c>
       <c r="BX14" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BY14" t="n">
         <v>1.75</v>
@@ -6444,16 +6444,16 @@
         <v>1.77</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.43</v>
+        <v>4.41</v>
       </c>
       <c r="CC14" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="CE14" t="n">
         <v>1.3</v>
@@ -6462,13 +6462,13 @@
         <v>2.39</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.73</v>
@@ -6477,7 +6477,7 @@
         <v>1.64</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CM14" t="n">
         <v>2.14</v>
@@ -6486,43 +6486,43 @@
         <v>1.73</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="CR14" t="n">
         <v>1.35</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CU14" t="n">
         <v>1.55</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CX14" t="n">
         <v>1.64</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DB14" t="n">
         <v>1.27</v>
@@ -6531,82 +6531,82 @@
         <v>1.71</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="DE14" t="n">
         <v>0.06</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.18</v>
+        <v>3.06</v>
       </c>
       <c r="DH14" t="n">
-        <v>109.7</v>
+        <v>109.89</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.47</v>
+        <v>5.28</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="DM14" t="n">
-        <v>50.35</v>
+        <v>49.94</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.12</v>
+        <v>11.89</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.41</v>
+        <v>10.34</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.42</v>
+        <v>5.5</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>59.64</v>
+        <v>60</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.12</v>
+        <v>14.62</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.41</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="EA14" t="n">
-        <v>15.24</v>
+        <v>15.22</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="EC14" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="15">
@@ -7017,13 +7017,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" t="n">
         <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7107,139 +7107,139 @@
         <v>2.38</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AG16" t="n">
         <v>1</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AI16" t="n">
-        <v>79.56</v>
+        <v>82.5</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AL16" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AN16" t="n">
-        <v>30.67</v>
+        <v>31.3</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.33</v>
+        <v>10.7</v>
       </c>
       <c r="AR16" t="n">
-        <v>10.33</v>
+        <v>10.9</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.44</v>
+        <v>9</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>50.33</v>
+        <v>50.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.779999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.44</v>
+        <v>6.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="BD16" t="n">
-        <v>18.11</v>
+        <v>17.8</v>
       </c>
       <c r="BE16" t="n">
         <v>1.08</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.76</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BL16" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.47</v>
+        <v>4.28</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.18</v>
+        <v>4.06</v>
       </c>
       <c r="BR16" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS16" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT16" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU16" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV16" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BW16" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BX16" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY16" t="n">
         <v>2.02</v>
@@ -7248,31 +7248,31 @@
         <v>2.17</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.93</v>
+        <v>3.89</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.11</v>
+        <v>4.06</v>
       </c>
       <c r="CC16" t="n">
-        <v>5.97</v>
+        <v>5.62</v>
       </c>
       <c r="CD16" t="n">
-        <v>5.45</v>
+        <v>5.19</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.71</v>
@@ -7281,7 +7281,7 @@
         <v>1.59</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CM16" t="n">
         <v>2.2</v>
@@ -7290,31 +7290,31 @@
         <v>1.76</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="CR16" t="n">
         <v>1.37</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CX16" t="n">
         <v>1.65</v>
@@ -7332,85 +7332,85 @@
         <v>1.3</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.93</v>
+        <v>2.97</v>
       </c>
       <c r="DE16" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="DH16" t="n">
-        <v>88.36</v>
+        <v>89.5</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.53</v>
+        <v>4.39</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="DM16" t="n">
-        <v>40.47</v>
+        <v>40.28</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.59</v>
+        <v>0.66</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DP16" t="n">
-        <v>11</v>
+        <v>11.17</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.29</v>
+        <v>11.56</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.64</v>
+        <v>7.5</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53.88</v>
+        <v>53.78</v>
       </c>
       <c r="DW16" t="n">
         <v>0.11</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.06</v>
+        <v>11.94</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.470000000000001</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.06</v>
+        <v>16.95</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="17">
@@ -7420,94 +7420,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>3.67</v>
       </c>
       <c r="H17" t="n">
-        <v>100.5</v>
+        <v>102.44</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="K17" t="n">
-        <v>5.25</v>
+        <v>5.78</v>
       </c>
       <c r="L17" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="M17" t="n">
-        <v>51.25</v>
+        <v>53.67</v>
       </c>
       <c r="N17" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="O17" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="P17" t="n">
-        <v>12.25</v>
+        <v>12.89</v>
       </c>
       <c r="Q17" t="n">
-        <v>14.12</v>
+        <v>14.11</v>
       </c>
       <c r="R17" t="n">
-        <v>7</v>
+        <v>6.89</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="U17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>50.62</v>
+        <v>51</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z17" t="n">
-        <v>15.75</v>
+        <v>16.11</v>
       </c>
       <c r="AA17" t="n">
-        <v>10</v>
+        <v>10.22</v>
       </c>
       <c r="AB17" t="n">
-        <v>5.75</v>
+        <v>5.89</v>
       </c>
       <c r="AC17" t="n">
-        <v>18.38</v>
+        <v>19.22</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AF17" t="n">
         <v>0.11</v>
@@ -7591,70 +7591,70 @@
         <v>1.44</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.41</v>
+        <v>10.72</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.35</v>
+        <v>4.39</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.94</v>
+        <v>5.28</v>
       </c>
       <c r="BR17" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS17" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT17" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BU17" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BV17" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.43</v>
+        <v>2.34</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="CC17" t="n">
         <v>3.41</v>
@@ -7666,10 +7666,10 @@
         <v>1.32</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CH17" t="n">
         <v>1.5</v>
@@ -7678,19 +7678,19 @@
         <v>2.21</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CK17" t="n">
         <v>1.61</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CO17" t="n">
         <v>1.23</v>
@@ -7699,16 +7699,16 @@
         <v>1.77</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="CR17" t="n">
         <v>1.36</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CU17" t="n">
         <v>1.52</v>
@@ -7723,13 +7723,13 @@
         <v>1.59</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="DB17" t="n">
         <v>1.28</v>
@@ -7738,49 +7738,49 @@
         <v>1.8</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="DE17" t="n">
         <v>0.11</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.35</v>
+        <v>2.72</v>
       </c>
       <c r="DH17" t="n">
-        <v>94.88</v>
+        <v>96.16</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.41</v>
+        <v>5.67</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM17" t="n">
-        <v>45.12</v>
+        <v>46.67</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.47</v>
+        <v>11.84</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.11</v>
+        <v>12.22</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.18</v>
+        <v>8.06</v>
       </c>
       <c r="DS17" t="n">
         <v>0.11</v>
@@ -7792,28 +7792,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>51</v>
+        <v>51.16</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.71</v>
+        <v>13.06</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.18</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.53</v>
+        <v>4.66</v>
       </c>
       <c r="EA17" t="n">
-        <v>18</v>
+        <v>18.44</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="18">
@@ -7823,10 +7823,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
         <v>9</v>
@@ -7835,82 +7835,82 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="H18" t="n">
-        <v>104.25</v>
+        <v>104.78</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="K18" t="n">
-        <v>4.88</v>
+        <v>4.78</v>
       </c>
       <c r="L18" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="M18" t="n">
-        <v>42.88</v>
+        <v>45.56</v>
       </c>
       <c r="N18" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="O18" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>10.25</v>
+        <v>10.44</v>
       </c>
       <c r="Q18" t="n">
-        <v>12.88</v>
+        <v>12.78</v>
       </c>
       <c r="R18" t="n">
-        <v>7.38</v>
+        <v>7.11</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="U18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>53.75</v>
+        <v>53</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z18" t="n">
-        <v>12.5</v>
+        <v>12.67</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.12</v>
+        <v>7.22</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.38</v>
+        <v>5.44</v>
       </c>
       <c r="AC18" t="n">
-        <v>14.5</v>
+        <v>14.56</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7994,70 +7994,70 @@
         <v>2.44</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BH18" t="n">
-        <v>7.71</v>
+        <v>7.56</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.82</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.41</v>
+        <v>4.28</v>
       </c>
       <c r="BR18" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS18" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT18" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU18" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV18" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BW18" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX18" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.73</v>
+        <v>3.79</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.83</v>
+        <v>3.88</v>
       </c>
       <c r="CC18" t="n">
         <v>3.76</v>
@@ -8072,25 +8072,25 @@
         <v>2.55</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CJ18" t="n">
         <v>1.7</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CN18" t="n">
         <v>1.74</v>
@@ -8099,10 +8099,10 @@
         <v>1.22</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="CR18" t="n">
         <v>1.37</v>
@@ -8117,22 +8117,22 @@
         <v>1.51</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DB18" t="n">
         <v>1.29</v>
@@ -8141,82 +8141,82 @@
         <v>1.81</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="DH18" t="n">
-        <v>100.3</v>
+        <v>100.78</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="DK18" t="n">
         <v>3.94</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DM18" t="n">
-        <v>42.53</v>
+        <v>43.89</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="DP18" t="n">
-        <v>11.41</v>
+        <v>11.44</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.47</v>
+        <v>13.39</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.24</v>
+        <v>7.11</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>52.94</v>
+        <v>52.61</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX18" t="n">
-        <v>10.94</v>
+        <v>11.12</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.7</v>
+        <v>6.78</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.24</v>
+        <v>4.33</v>
       </c>
       <c r="EA18" t="n">
-        <v>15.77</v>
+        <v>15.72</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="19">
@@ -8226,94 +8226,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
         <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="F19" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="G19" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="H19" t="n">
-        <v>89.89</v>
+        <v>89.3</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="K19" t="n">
-        <v>4.78</v>
+        <v>4.9</v>
       </c>
       <c r="L19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="M19" t="n">
-        <v>46.44</v>
+        <v>45.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="O19" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="P19" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.22</v>
+        <v>12.7</v>
       </c>
       <c r="R19" t="n">
-        <v>6.11</v>
+        <v>6</v>
       </c>
       <c r="S19" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="T19" t="n">
-        <v>1.56</v>
+        <v>1.9</v>
       </c>
       <c r="U19" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V19" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>40.89</v>
+        <v>41.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z19" t="n">
-        <v>14.22</v>
+        <v>15</v>
       </c>
       <c r="AA19" t="n">
-        <v>9.779999999999999</v>
+        <v>10</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.44</v>
+        <v>5</v>
       </c>
       <c r="AC19" t="n">
-        <v>17.11</v>
+        <v>16.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8397,70 +8397,70 @@
         <v>3.12</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.71</v>
+        <v>2.89</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.94</v>
+        <v>10.11</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.71</v>
+        <v>2.89</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.47</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.82</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="BO19" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.71</v>
+        <v>4.72</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.24</v>
+        <v>5.39</v>
       </c>
       <c r="BR19" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS19" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT19" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU19" t="n">
-        <v>29.41</v>
+        <v>33.33</v>
       </c>
       <c r="BV19" t="n">
-        <v>5.88</v>
+        <v>11.11</v>
       </c>
       <c r="BW19" t="n">
-        <v>5.88</v>
+        <v>11.11</v>
       </c>
       <c r="BX19" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="CC19" t="n">
         <v>3.55</v>
@@ -8472,7 +8472,7 @@
         <v>1.37</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CG19" t="n">
         <v>2.97</v>
@@ -8481,7 +8481,7 @@
         <v>1.42</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.79</v>
@@ -8496,13 +8496,13 @@
         <v>2.2</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CO19" t="n">
         <v>1.28</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CQ19" t="n">
         <v>3.32</v>
@@ -8523,19 +8523,19 @@
         <v>2.04</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DB19" t="n">
         <v>1.33</v>
@@ -8544,82 +8544,82 @@
         <v>2.03</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DG19" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="DH19" t="n">
-        <v>86.88</v>
+        <v>86.72</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.47</v>
+        <v>4.55</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM19" t="n">
-        <v>42.23</v>
+        <v>41.78</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.47</v>
+        <v>14.33</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.53</v>
+        <v>11.83</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.76</v>
+        <v>6.67</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>40.35</v>
+        <v>40.5</v>
       </c>
       <c r="DW19" t="n">
         <v>0.11</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.94</v>
+        <v>12.5</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.18</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.76</v>
+        <v>4.11</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.17</v>
+        <v>16.11</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>4.22</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>88.44</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="K3" t="n">
-        <v>5.78</v>
+        <v>5.4</v>
       </c>
       <c r="L3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="M3" t="n">
-        <v>43.89</v>
+        <v>44.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>14</v>
+        <v>13.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>14.33</v>
+        <v>14.1</v>
       </c>
       <c r="R3" t="n">
-        <v>5.33</v>
+        <v>5.5</v>
       </c>
       <c r="S3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>43.11</v>
+        <v>41.9</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.89</v>
+        <v>11.5</v>
       </c>
       <c r="AA3" t="n">
         <v>8</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.89</v>
+        <v>3.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>17.89</v>
+        <v>17.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
         <v>0.11</v>
@@ -1953,70 +1953,70 @@
         <v>2.33</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.609999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BO3" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BP3" t="n">
         <v>3.89</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.72</v>
+        <v>5.68</v>
       </c>
       <c r="BR3" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS3" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BT3" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BU3" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV3" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX3" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.31</v>
+        <v>3.91</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.69</v>
+        <v>4.34</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.82</v>
+        <v>3.92</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="CC3" t="n">
         <v>5.25</v>
@@ -2025,19 +2025,19 @@
         <v>5.48</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.81</v>
@@ -2049,49 +2049,49 @@
         <v>2.05</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="CR3" t="n">
         <v>1.41</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="CT3" t="n">
         <v>2.98</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CW3" t="n">
         <v>1.86</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DB3" t="n">
         <v>1.33</v>
@@ -2103,46 +2103,46 @@
         <v>3.26</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="DH3" t="n">
-        <v>92.5</v>
+        <v>91.84</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.11</v>
+        <v>4.95</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DM3" t="n">
-        <v>40.72</v>
+        <v>41.21</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.06</v>
+        <v>13.84</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.16</v>
+        <v>14.05</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.94</v>
+        <v>6.95</v>
       </c>
       <c r="DS3" t="n">
         <v>0.16</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>44.78</v>
+        <v>44.05</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.89</v>
+        <v>10.74</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.34</v>
+        <v>7.37</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.56</v>
+        <v>3.37</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.83</v>
+        <v>18.79</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="4">
@@ -6616,13 +6616,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" t="n">
         <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
         <v>0.11</v>
@@ -6706,139 +6706,139 @@
         <v>1.11</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="AI15" t="n">
         <v>129</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.56</v>
+        <v>5.7</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
       <c r="AN15" t="n">
-        <v>63.22</v>
+        <v>61.7</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="AR15" t="n">
-        <v>9.220000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.44</v>
+        <v>5</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AU15" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>68.67</v>
+        <v>68.7</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>14.78</v>
+        <v>14.9</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.67</v>
+        <v>8.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>6.11</v>
+        <v>6.3</v>
       </c>
       <c r="BD15" t="n">
-        <v>16</v>
+        <v>15.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.06</v>
+        <v>2.95</v>
       </c>
       <c r="BH15" t="n">
         <v>9.109999999999999</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.06</v>
+        <v>2.95</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BL15" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.28</v>
+        <v>4.26</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.83</v>
+        <v>4.84</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>72.22</v>
+        <v>68.42</v>
       </c>
       <c r="BT15" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BU15" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV15" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BW15" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX15" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BY15" t="n">
         <v>1.21</v>
@@ -6847,31 +6847,31 @@
         <v>1.24</v>
       </c>
       <c r="CA15" t="n">
-        <v>6.12</v>
+        <v>6.1</v>
       </c>
       <c r="CB15" t="n">
-        <v>6.68</v>
+        <v>6.61</v>
       </c>
       <c r="CC15" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="CD15" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="CE15" t="n">
         <v>1.2</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CG15" t="n">
-        <v>4.08</v>
+        <v>4.05</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.78</v>
@@ -6880,13 +6880,13 @@
         <v>1.52</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CM15" t="n">
         <v>2.37</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CO15" t="n">
         <v>1.11</v>
@@ -6895,25 +6895,25 @@
         <v>1.43</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CR15" t="n">
         <v>1.34</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CT15" t="n">
         <v>3.34</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CX15" t="n">
         <v>1.56</v>
@@ -6941,40 +6941,40 @@
         <v>0.84</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.78</v>
+        <v>3.73</v>
       </c>
       <c r="DH15" t="n">
-        <v>137</v>
+        <v>136.58</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DK15" t="n">
-        <v>6.17</v>
+        <v>6.21</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.39</v>
+        <v>0.48</v>
       </c>
       <c r="DM15" t="n">
-        <v>69.5</v>
+        <v>68.37</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.06</v>
+        <v>10.16</v>
       </c>
       <c r="DQ15" t="n">
-        <v>8.390000000000001</v>
+        <v>8.48</v>
       </c>
       <c r="DR15" t="n">
-        <v>4.11</v>
+        <v>4.42</v>
       </c>
       <c r="DS15" t="n">
         <v>0.16</v>
@@ -6986,28 +6986,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>69.22</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>17.55</v>
+        <v>17.47</v>
       </c>
       <c r="DY15" t="n">
-        <v>10.73</v>
+        <v>10.58</v>
       </c>
       <c r="DZ15" t="n">
-        <v>6.84</v>
+        <v>6.9</v>
       </c>
       <c r="EA15" t="n">
-        <v>17.06</v>
+        <v>16.89</v>
       </c>
       <c r="EB15" t="n">
         <v>2.09</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="16">

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
         <v>0.11</v>
@@ -1472,136 +1472,136 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AI2" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AL2" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN2" t="n">
-        <v>28.44</v>
+        <v>28.9</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.56</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.33</v>
+        <v>11.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>40.11</v>
+        <v>39.8</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.67</v>
+        <v>7.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.11</v>
+        <v>5.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>15</v>
+        <v>15.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.390000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.94</v>
+        <v>3.79</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.44</v>
+        <v>5.26</v>
       </c>
       <c r="BR2" t="n">
-        <v>100</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BT2" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BU2" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV2" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX2" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BY2" t="n">
         <v>3.65</v>
@@ -1610,25 +1610,25 @@
         <v>3.92</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.24</v>
+        <v>4.19</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.51</v>
+        <v>4.45</v>
       </c>
       <c r="CC2" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="CD2" t="n">
         <v>8.68</v>
       </c>
-      <c r="CD2" t="n">
-        <v>9.119999999999999</v>
-      </c>
       <c r="CE2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="CG2" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="CH2" t="n">
         <v>1.43</v>
@@ -1643,46 +1643,46 @@
         <v>1.66</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CM2" t="n">
         <v>2.12</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CO2" t="n">
         <v>1.3</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.43</v>
+        <v>3.45</v>
       </c>
       <c r="CR2" t="n">
         <v>1.44</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV2" t="n">
         <v>1.9</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CX2" t="n">
         <v>1.67</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.21</v>
@@ -1691,88 +1691,88 @@
         <v>1.75</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF2" t="n">
         <v>0.89</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="DH2" t="n">
-        <v>73.61</v>
+        <v>73</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.89</v>
+        <v>3.74</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DM2" t="n">
-        <v>31.11</v>
+        <v>31.21</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.28</v>
+        <v>11.05</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.16</v>
+        <v>11.32</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.66</v>
+        <v>8.74</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>41.56</v>
+        <v>41.32</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX2" t="n">
-        <v>9.119999999999999</v>
+        <v>9</v>
       </c>
       <c r="DY2" t="n">
-        <v>5.61</v>
+        <v>5.63</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.5</v>
+        <v>3.37</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.22</v>
+        <v>16.58</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="3">
@@ -2010,13 +2010,13 @@
         <v>3.91</v>
       </c>
       <c r="BZ3" t="n">
-        <v>4.34</v>
+        <v>4.22</v>
       </c>
       <c r="CA3" t="n">
         <v>3.92</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.94</v>
+        <v>3.93</v>
       </c>
       <c r="CC3" t="n">
         <v>5.25</v>
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F4" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="G4" t="n">
-        <v>2.78</v>
+        <v>2.4</v>
       </c>
       <c r="H4" t="n">
-        <v>100.33</v>
+        <v>102.4</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="K4" t="n">
-        <v>5.67</v>
+        <v>5.4</v>
       </c>
       <c r="L4" t="n">
-        <v>0.44</v>
+        <v>0.3</v>
       </c>
       <c r="M4" t="n">
-        <v>40.44</v>
+        <v>39.6</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="O4" t="n">
-        <v>2.89</v>
+        <v>2.5</v>
       </c>
       <c r="P4" t="n">
-        <v>13.67</v>
+        <v>13.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="R4" t="n">
-        <v>7.89</v>
+        <v>7.4</v>
       </c>
       <c r="S4" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="U4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>44.67</v>
+        <v>45.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>14.78</v>
+        <v>14.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>17.67</v>
+        <v>17.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,70 +2356,70 @@
         <v>1.89</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.44</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="BL4" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.61</v>
+        <v>3.37</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.83</v>
+        <v>4.53</v>
       </c>
       <c r="BR4" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS4" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT4" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BU4" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BV4" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW4" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BY4" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.66</v>
+        <v>3.62</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="CC4" t="n">
         <v>3.91</v>
@@ -2431,76 +2431,76 @@
         <v>1.35</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.13</v>
+        <v>3.09</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.72</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CN4" t="n">
         <v>1.73</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.01</v>
+        <v>3.06</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.2</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="DD4" t="n">
         <v>3.12</v>
@@ -2509,13 +2509,13 @@
         <v>0.16</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.28</v>
+        <v>2.11</v>
       </c>
       <c r="DH4" t="n">
-        <v>95.33</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
@@ -2524,61 +2524,61 @@
         <v>2.05</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.28</v>
+        <v>4.21</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.33</v>
+        <v>0.26</v>
       </c>
       <c r="DM4" t="n">
-        <v>41.11</v>
+        <v>40.63</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.28</v>
+        <v>13.42</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.34</v>
+        <v>11.58</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.39</v>
+        <v>7.16</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>43.39</v>
+        <v>44</v>
       </c>
       <c r="DW4" t="n">
         <v>0.16</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.72</v>
+        <v>11.79</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.78</v>
+        <v>7.79</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.39</v>
+        <v>18.32</v>
       </c>
       <c r="EB4" t="n">
         <v>1.32</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="5">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
@@ -2600,82 +2600,82 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="G5" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="H5" t="n">
-        <v>98</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J5" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="K5" t="n">
-        <v>5.33</v>
+        <v>5.3</v>
       </c>
       <c r="L5" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="M5" t="n">
-        <v>52.89</v>
+        <v>50.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="O5" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="P5" t="n">
-        <v>14.44</v>
+        <v>13.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.33</v>
+        <v>13.1</v>
       </c>
       <c r="R5" t="n">
-        <v>5.67</v>
+        <v>6.4</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="T5" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>49.89</v>
+        <v>49.6</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>13.44</v>
+        <v>12.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.44</v>
+        <v>4.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>21.89</v>
+        <v>21.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,67 +2759,67 @@
         <v>2.11</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.279999999999999</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.33</v>
+        <v>5.42</v>
       </c>
       <c r="BR5" t="n">
-        <v>83.33</v>
+        <v>78.95</v>
       </c>
       <c r="BS5" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BT5" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BU5" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV5" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.11</v>
+        <v>3.24</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.06</v>
+        <v>4.05</v>
       </c>
       <c r="CB5" t="n">
         <v>4.07</v>
@@ -2834,67 +2834,67 @@
         <v>1.35</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CL5" t="n">
         <v>2.07</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="CR5" t="n">
         <v>1.41</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="CT5" t="n">
         <v>2.97</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CX5" t="n">
         <v>1.62</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="DA5" t="n">
         <v>1.8</v>
@@ -2903,85 +2903,85 @@
         <v>1.34</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DH5" t="n">
-        <v>88.28</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.61</v>
+        <v>4.63</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="DM5" t="n">
-        <v>44.06</v>
+        <v>43.26</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="DP5" t="n">
-        <v>14.11</v>
+        <v>13.84</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.83</v>
+        <v>13.21</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.22</v>
+        <v>7.53</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>45.89</v>
+        <v>45.95</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.38</v>
+        <v>11.16</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.56</v>
+        <v>7.47</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.83</v>
+        <v>3.68</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.39</v>
+        <v>18.53</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
         <v>0.11</v>
@@ -3081,139 +3081,139 @@
         <v>1.56</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AI6" t="n">
-        <v>88.56</v>
+        <v>89.5</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.11</v>
+        <v>4.8</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN6" t="n">
-        <v>42.67</v>
+        <v>41.9</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>14.22</v>
+        <v>14.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.56</v>
+        <v>13.1</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.44</v>
+        <v>7.1</v>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>49.33</v>
+        <v>49</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>13.33</v>
+        <v>12.7</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BC6" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BD6" t="n">
-        <v>16.22</v>
+        <v>15.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.28</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BL6" t="n">
         <v>0.89</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.33</v>
+        <v>4.16</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.94</v>
+        <v>4.84</v>
       </c>
       <c r="BR6" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT6" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BU6" t="n">
-        <v>11.11</v>
+        <v>15.79</v>
       </c>
       <c r="BV6" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BY6" t="n">
         <v>1.99</v>
@@ -3222,40 +3222,40 @@
         <v>2.01</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.97</v>
+        <v>3.96</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.79</v>
+        <v>2.87</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="CE6" t="n">
         <v>1.31</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CG6" t="n">
         <v>3.28</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CK6" t="n">
         <v>1.56</v>
       </c>
       <c r="CL6" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CM6" t="n">
         <v>2.25</v>
@@ -3264,13 +3264,13 @@
         <v>1.79</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CR6" t="n">
         <v>1.35</v>
@@ -3285,10 +3285,10 @@
         <v>1.56</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CX6" t="n">
         <v>1.59</v>
@@ -3300,58 +3300,58 @@
         <v>2.33</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DB6" t="n">
         <v>1.27</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="DH6" t="n">
-        <v>86.28</v>
+        <v>86.89</v>
       </c>
       <c r="DI6" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.84</v>
+        <v>5.63</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="DM6" t="n">
-        <v>43.44</v>
+        <v>43</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.61</v>
+        <v>2.52</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.61</v>
+        <v>13.74</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.56</v>
+        <v>12.84</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.33</v>
+        <v>6.21</v>
       </c>
       <c r="DS6" t="n">
         <v>0.16</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>49.22</v>
+        <v>49.05</v>
       </c>
       <c r="DW6" t="n">
         <v>0.16</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.33</v>
+        <v>13.95</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.94</v>
+        <v>8.74</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.39</v>
+        <v>5.21</v>
       </c>
       <c r="EA6" t="n">
-        <v>17</v>
+        <v>16.63</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="H7" t="n">
-        <v>104.44</v>
+        <v>104</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="K7" t="n">
-        <v>5.78</v>
+        <v>6</v>
       </c>
       <c r="L7" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="M7" t="n">
-        <v>51.44</v>
+        <v>53.3</v>
       </c>
       <c r="N7" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="O7" t="n">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>11.11</v>
+        <v>11.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.78</v>
+        <v>12.8</v>
       </c>
       <c r="R7" t="n">
-        <v>5.33</v>
+        <v>5.8</v>
       </c>
       <c r="S7" t="n">
-        <v>0.89</v>
+        <v>1.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="U7" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V7" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>51.22</v>
+        <v>50.8</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>14.89</v>
+        <v>15.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.11</v>
+        <v>10.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.78</v>
+        <v>4.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>16.44</v>
+        <v>16.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AF7" t="n">
         <v>0.22</v>
@@ -3565,70 +3565,70 @@
         <v>2.56</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.22</v>
+        <v>3.32</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.33</v>
+        <v>10.26</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.22</v>
+        <v>3.32</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.33</v>
+        <v>0.42</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.33</v>
+        <v>5.37</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5</v>
+        <v>4.89</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT7" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BU7" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="BV7" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="BW7" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BX7" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.91</v>
+        <v>3.89</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.08</v>
+        <v>4.04</v>
       </c>
       <c r="CC7" t="n">
         <v>3.13</v>
@@ -3637,13 +3637,13 @@
         <v>3.17</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="CH7" t="n">
         <v>1.48</v>
@@ -3661,7 +3661,7 @@
         <v>2.05</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CN7" t="n">
         <v>1.81</v>
@@ -3670,91 +3670,91 @@
         <v>1.23</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CW7" t="n">
         <v>1.75</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CY7" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="DB7" t="n">
         <v>1.29</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="DE7" t="n">
         <v>0.16</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="DH7" t="n">
-        <v>105.11</v>
+        <v>104.84</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.84</v>
+        <v>5.95</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="DM7" t="n">
-        <v>53.33</v>
+        <v>54.21</v>
       </c>
       <c r="DN7" t="n">
         <v>0.89</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.16</v>
+        <v>3.26</v>
       </c>
       <c r="DP7" t="n">
-        <v>11.66</v>
+        <v>11.63</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.28</v>
+        <v>13.26</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.44</v>
+        <v>6.63</v>
       </c>
       <c r="DS7" t="n">
         <v>0.16</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>54.22</v>
+        <v>53.84</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DX7" t="n">
-        <v>14.11</v>
+        <v>14.42</v>
       </c>
       <c r="DY7" t="n">
-        <v>9.27</v>
+        <v>9.52</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.84</v>
+        <v>4.9</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.78</v>
+        <v>17</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
         <v>0.11</v>
@@ -3887,52 +3887,52 @@
         <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AI8" t="n">
-        <v>89</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK8" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN8" t="n">
-        <v>38</v>
+        <v>38.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.890000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>14.89</v>
+        <v>15.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.220000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>43.22</v>
+        <v>42</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.220000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="BD8" t="n">
-        <v>14.44</v>
+        <v>14.9</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.220000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="BO8" t="n">
         <v>1.11</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.72</v>
+        <v>3.79</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.06</v>
+        <v>4.21</v>
       </c>
       <c r="BR8" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BU8" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BV8" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW8" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX8" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BY8" t="n">
         <v>3.71</v>
@@ -4028,22 +4028,22 @@
         <v>3.77</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.56</v>
+        <v>4.58</v>
       </c>
       <c r="CE8" t="n">
         <v>1.35</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CG8" t="n">
         <v>3.08</v>
@@ -4052,7 +4052,7 @@
         <v>1.46</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.74</v>
@@ -4061,10 +4061,10 @@
         <v>1.67</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CN8" t="n">
         <v>1.69</v>
@@ -4076,7 +4076,7 @@
         <v>1.88</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CR8" t="n">
         <v>1.41</v>
@@ -4094,19 +4094,19 @@
         <v>2.1</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="DB8" t="n">
         <v>1.33</v>
@@ -4118,22 +4118,22 @@
         <v>3.13</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="DH8" t="n">
-        <v>85.84</v>
+        <v>82.53</v>
       </c>
       <c r="DI8" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DK8" t="n">
         <v>3.16</v>
@@ -4142,55 +4142,55 @@
         <v>0.16</v>
       </c>
       <c r="DM8" t="n">
-        <v>40.06</v>
+        <v>40.21</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="DP8" t="n">
-        <v>10</v>
+        <v>9.84</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.16</v>
+        <v>14.37</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.94</v>
+        <v>7.42</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>43.11</v>
+        <v>42.47</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.28</v>
+        <v>11.95</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="EA8" t="n">
-        <v>14.22</v>
+        <v>14.47</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="9">
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
@@ -4212,82 +4212,82 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="G9" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="H9" t="n">
-        <v>76.25</v>
+        <v>79.56</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.25</v>
+        <v>-0.22</v>
       </c>
       <c r="J9" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="K9" t="n">
-        <v>4.12</v>
+        <v>4.33</v>
       </c>
       <c r="L9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M9" t="n">
-        <v>37.62</v>
+        <v>38.56</v>
       </c>
       <c r="N9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="O9" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="P9" t="n">
-        <v>12</v>
+        <v>11.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.5</v>
+        <v>10.78</v>
       </c>
       <c r="R9" t="n">
-        <v>8.119999999999999</v>
+        <v>7.44</v>
       </c>
       <c r="S9" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="T9" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>46.5</v>
+        <v>47.22</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z9" t="n">
-        <v>9</v>
+        <v>9.67</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.88</v>
+        <v>6.22</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.12</v>
+        <v>3.44</v>
       </c>
       <c r="AC9" t="n">
-        <v>16.25</v>
+        <v>16.44</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF9" t="n">
         <v>0.1</v>
@@ -4371,70 +4371,70 @@
         <v>1.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.28</v>
+        <v>3.47</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.06</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.28</v>
+        <v>3.47</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BN9" t="n">
         <v>1.89</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.56</v>
+        <v>4.63</v>
       </c>
       <c r="BR9" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BU9" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BV9" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="BW9" t="n">
-        <v>11.11</v>
+        <v>15.79</v>
       </c>
       <c r="BX9" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BY9" t="n">
-        <v>4.63</v>
+        <v>4.66</v>
       </c>
       <c r="BZ9" t="n">
-        <v>4.84</v>
+        <v>4.91</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.42</v>
+        <v>4.39</v>
       </c>
       <c r="CC9" t="n">
         <v>5.7</v>
@@ -4443,13 +4443,13 @@
         <v>6.4</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CH9" t="n">
         <v>1.52</v>
@@ -4458,13 +4458,13 @@
         <v>2.04</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CK9" t="n">
         <v>1.61</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CM9" t="n">
         <v>2.21</v>
@@ -4476,28 +4476,28 @@
         <v>1.21</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CX9" t="n">
         <v>1.62</v>
@@ -4506,7 +4506,7 @@
         <v>2.03</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DA9" t="n">
         <v>1.8</v>
@@ -4515,85 +4515,85 @@
         <v>1.29</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="DH9" t="n">
-        <v>76.5</v>
+        <v>78.05</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.94</v>
+        <v>4.05</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM9" t="n">
-        <v>33.55</v>
+        <v>34.21</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="DP9" t="n">
-        <v>10.89</v>
+        <v>10.84</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.33</v>
+        <v>11</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.050000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>49.44</v>
+        <v>49.63</v>
       </c>
       <c r="DW9" t="n">
         <v>0.16</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.890000000000001</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.84</v>
+        <v>6</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.05</v>
+        <v>3.21</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.56</v>
+        <v>16.63</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
         <v>0.2</v>
@@ -4693,139 +4693,139 @@
         <v>1.7</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG10" t="n">
         <v>2</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="AI10" t="n">
-        <v>108.75</v>
+        <v>109.11</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.62</v>
+        <v>4.78</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN10" t="n">
-        <v>51.62</v>
+        <v>52.44</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.25</v>
+        <v>14.89</v>
       </c>
       <c r="AR10" t="n">
-        <v>10.88</v>
+        <v>10.67</v>
       </c>
       <c r="AS10" t="n">
-        <v>7</v>
+        <v>6.78</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>54</v>
+        <v>53.89</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA10" t="n">
-        <v>11.88</v>
+        <v>11.67</v>
       </c>
       <c r="BB10" t="n">
         <v>8</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.88</v>
+        <v>3.67</v>
       </c>
       <c r="BD10" t="n">
-        <v>20.25</v>
+        <v>20</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.39</v>
+        <v>3.21</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.83</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.39</v>
+        <v>3.21</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BM10" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.61</v>
+        <v>3.79</v>
       </c>
       <c r="BR10" t="n">
-        <v>100</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS10" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BT10" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BU10" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BV10" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BW10" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX10" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BY10" t="n">
         <v>2</v>
@@ -4834,31 +4834,31 @@
         <v>2.03</v>
       </c>
       <c r="CA10" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="CB10" t="n">
         <v>4.29</v>
       </c>
-      <c r="CB10" t="n">
-        <v>4.31</v>
-      </c>
       <c r="CC10" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CF10" t="n">
         <v>2.27</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.57</v>
@@ -4867,7 +4867,7 @@
         <v>1.57</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CM10" t="n">
         <v>2.27</v>
@@ -4879,16 +4879,16 @@
         <v>1.15</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CR10" t="n">
         <v>1.35</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CT10" t="n">
         <v>3.26</v>
@@ -4897,10 +4897,10 @@
         <v>1.66</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CX10" t="n">
         <v>1.58</v>
@@ -4925,76 +4925,76 @@
         <v>0.16</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="DH10" t="n">
-        <v>107.61</v>
+        <v>107.84</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.61</v>
+        <v>4.69</v>
       </c>
       <c r="DL10" t="n">
         <v>0.16</v>
       </c>
       <c r="DM10" t="n">
-        <v>50.83</v>
+        <v>51.26</v>
       </c>
       <c r="DN10" t="n">
         <v>0.95</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.17</v>
+        <v>13.53</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.5</v>
+        <v>11.37</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.17</v>
+        <v>7.05</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>53.72</v>
+        <v>53.68</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.56</v>
+        <v>12.42</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.33</v>
+        <v>8.32</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.22</v>
+        <v>4.11</v>
       </c>
       <c r="EA10" t="n">
-        <v>20</v>
+        <v>19.89</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="11">
@@ -5004,58 +5004,58 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="G11" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="H11" t="n">
-        <v>83.67</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="J11" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="K11" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M11" t="n">
-        <v>34.11</v>
+        <v>38.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="O11" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="P11" t="n">
-        <v>11.67</v>
+        <v>11.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="R11" t="n">
-        <v>9.33</v>
+        <v>8.9</v>
       </c>
       <c r="S11" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
@@ -5070,28 +5070,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>43.33</v>
+        <v>44.6</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.11</v>
+        <v>11.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.33</v>
+        <v>8.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="AC11" t="n">
-        <v>19.89</v>
+        <v>20.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AF11" t="n">
         <v>0.22</v>
@@ -5175,70 +5175,70 @@
         <v>2</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.61</v>
+        <v>2.74</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.33</v>
+        <v>9.16</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.61</v>
+        <v>2.74</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.72</v>
+        <v>0.84</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.11</v>
+        <v>4.95</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="BR11" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT11" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BU11" t="n">
-        <v>22.22</v>
+        <v>26.32</v>
       </c>
       <c r="BV11" t="n">
-        <v>11.11</v>
+        <v>15.79</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX11" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.42</v>
+        <v>4.27</v>
       </c>
       <c r="BZ11" t="n">
-        <v>4.95</v>
+        <v>4.73</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.1</v>
+        <v>4.07</v>
       </c>
       <c r="CC11" t="n">
         <v>5.65</v>
@@ -5253,16 +5253,16 @@
         <v>2.74</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CH11" t="n">
         <v>1.44</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CK11" t="n">
         <v>1.52</v>
@@ -5271,19 +5271,19 @@
         <v>1.99</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CN11" t="n">
         <v>1.87</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP11" t="n">
         <v>1.91</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CR11" t="n">
         <v>1.4</v>
@@ -5298,10 +5298,10 @@
         <v>1.48</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CX11" t="n">
         <v>1.55</v>
@@ -5310,94 +5310,94 @@
         <v>1.92</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="DA11" t="n">
         <v>1.9</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="DC11" t="n">
         <v>1.91</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="DE11" t="n">
         <v>0.16</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="DH11" t="n">
-        <v>76.83</v>
+        <v>80.05</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DK11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>32.26</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>43.47</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="DZ11" t="n">
         <v>3</v>
       </c>
-      <c r="DL11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DM11" t="n">
-        <v>29.78</v>
-      </c>
-      <c r="DN11" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="DO11" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="DP11" t="n">
-        <v>12.23</v>
-      </c>
-      <c r="DQ11" t="n">
-        <v>13.61</v>
-      </c>
-      <c r="DR11" t="n">
-        <v>9.109999999999999</v>
-      </c>
-      <c r="DS11" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="DT11" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="DU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV11" t="n">
-        <v>42.78</v>
-      </c>
-      <c r="DW11" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="DX11" t="n">
-        <v>9.77</v>
-      </c>
-      <c r="DY11" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="DZ11" t="n">
-        <v>2.89</v>
-      </c>
       <c r="EA11" t="n">
-        <v>19</v>
+        <v>19.53</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="12">
@@ -5407,13 +5407,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
         <v>0.22</v>
@@ -5500,136 +5500,136 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AI12" t="n">
-        <v>90</v>
+        <v>89.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AL12" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN12" t="n">
-        <v>39.22</v>
+        <v>38.3</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.67</v>
+        <v>13.8</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.44</v>
+        <v>12.3</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.44</v>
+        <v>7.7</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>48.78</v>
+        <v>48.3</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.33</v>
+        <v>10</v>
       </c>
       <c r="BB12" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>17.56</v>
+        <v>17.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.11</v>
+        <v>3.21</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.78</v>
+        <v>10.53</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.11</v>
+        <v>3.21</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.72</v>
+        <v>0.84</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.44</v>
+        <v>4.32</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.5</v>
+        <v>5.42</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT12" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BU12" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BV12" t="n">
-        <v>22.22</v>
+        <v>26.32</v>
       </c>
       <c r="BW12" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX12" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BY12" t="n">
         <v>2.35</v>
@@ -5638,25 +5638,25 @@
         <v>2.54</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="CB12" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.79</v>
+        <v>3.65</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.02</v>
+        <v>4.78</v>
       </c>
       <c r="CE12" t="n">
         <v>1.32</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CH12" t="n">
         <v>1.51</v>
@@ -5668,10 +5668,10 @@
         <v>1.66</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CM12" t="n">
         <v>2.42</v>
@@ -5683,10 +5683,10 @@
         <v>1.21</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CR12" t="n">
         <v>1.36</v>
@@ -5707,13 +5707,13 @@
         <v>1.7</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY12" t="n">
         <v>1.89</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="DA12" t="n">
         <v>1.94</v>
@@ -5722,85 +5722,85 @@
         <v>1.29</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="DH12" t="n">
-        <v>81.17</v>
+        <v>81.37</v>
       </c>
       <c r="DI12" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.06</v>
+        <v>4.89</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM12" t="n">
-        <v>36.28</v>
+        <v>35.95</v>
       </c>
       <c r="DN12" t="n">
         <v>1.11</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.67</v>
+        <v>12.79</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.16</v>
+        <v>12.11</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.66</v>
+        <v>6.84</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48.06</v>
+        <v>47.84</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.77</v>
+        <v>11.53</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.61</v>
+        <v>7.37</v>
       </c>
       <c r="DZ12" t="n">
         <v>4.16</v>
       </c>
       <c r="EA12" t="n">
-        <v>15.94</v>
+        <v>16.16</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="13">
@@ -5810,13 +5810,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5900,139 +5900,139 @@
         <v>1.67</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="AI13" t="n">
-        <v>87.78</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="AL13" t="n">
-        <v>6.22</v>
+        <v>6</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN13" t="n">
-        <v>43.78</v>
+        <v>42</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14.89</v>
+        <v>13.9</v>
       </c>
       <c r="AR13" t="n">
-        <v>14.78</v>
+        <v>14.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>55</v>
+        <v>54.2</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BA13" t="n">
-        <v>11.11</v>
+        <v>11.3</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.33</v>
+        <v>6</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.78</v>
+        <v>5.3</v>
       </c>
       <c r="BD13" t="n">
-        <v>17.67</v>
+        <v>17.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.5</v>
+        <v>10.47</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
       <c r="BL13" t="n">
         <v>0.89</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.28</v>
+        <v>4.26</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.22</v>
+        <v>6.21</v>
       </c>
       <c r="BR13" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS13" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BT13" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BU13" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="BV13" t="n">
-        <v>16.67</v>
+        <v>21.05</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.56</v>
+        <v>10.53</v>
       </c>
       <c r="BX13" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BY13" t="n">
         <v>2.05</v>
@@ -6047,40 +6047,40 @@
         <v>3.84</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.61</v>
+        <v>2.51</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="CE13" t="n">
         <v>1.32</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CH13" t="n">
         <v>1.49</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CO13" t="n">
         <v>1.23</v>
@@ -6089,121 +6089,121 @@
         <v>1.78</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="CR13" t="n">
         <v>1.37</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CZ13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>90.37</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="DJ13" t="n">
         <v>2.37</v>
       </c>
-      <c r="DA13" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="DB13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="DC13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="DD13" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="DE13" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="DF13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="DG13" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="DH13" t="n">
-        <v>92</v>
-      </c>
-      <c r="DI13" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="DJ13" t="n">
-        <v>2.5</v>
-      </c>
       <c r="DK13" t="n">
-        <v>6.11</v>
+        <v>6</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DM13" t="n">
-        <v>46.56</v>
+        <v>45.47</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.78</v>
+        <v>2.69</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.61</v>
+        <v>14.1</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.78</v>
+        <v>13.53</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.39</v>
+        <v>6.32</v>
       </c>
       <c r="DS13" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DT13" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>56.56</v>
+        <v>56.05</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DX13" t="n">
         <v>13</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.109999999999999</v>
+        <v>7.84</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.89</v>
+        <v>5.16</v>
       </c>
       <c r="EA13" t="n">
-        <v>17.67</v>
+        <v>17.58</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="14">
@@ -6213,94 +6213,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
         <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="F14" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="H14" t="n">
-        <v>118.22</v>
+        <v>113.2</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="K14" t="n">
-        <v>5.22</v>
+        <v>4.9</v>
       </c>
       <c r="L14" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M14" t="n">
-        <v>55.89</v>
+        <v>53</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="O14" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>13.11</v>
+        <v>13.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="R14" t="n">
-        <v>4.56</v>
+        <v>4.6</v>
       </c>
       <c r="S14" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="U14" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="V14" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>61.44</v>
+        <v>60.7</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>14.67</v>
+        <v>14.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="AB14" t="n">
-        <v>6.33</v>
+        <v>6.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>14.67</v>
+        <v>14.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6384,70 +6384,70 @@
         <v>2.11</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.33</v>
+        <v>3.37</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.94</v>
+        <v>8.68</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.33</v>
+        <v>3.37</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.89</v>
+        <v>3.74</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.06</v>
+        <v>4.95</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT14" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BU14" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BV14" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW14" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BX14" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.32</v>
+        <v>4.29</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.41</v>
+        <v>4.37</v>
       </c>
       <c r="CC14" t="n">
         <v>2</v>
@@ -6462,22 +6462,22 @@
         <v>2.39</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CM14" t="n">
         <v>2.14</v>
@@ -6486,13 +6486,13 @@
         <v>1.73</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CP14" t="n">
         <v>1.65</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CR14" t="n">
         <v>1.35</v>
@@ -6507,16 +6507,16 @@
         <v>1.55</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CX14" t="n">
         <v>1.64</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.23</v>
@@ -6528,85 +6528,85 @@
         <v>1.27</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="DH14" t="n">
-        <v>109.89</v>
+        <v>107.69</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.34</v>
+        <v>2.21</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.28</v>
+        <v>5.1</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DM14" t="n">
-        <v>49.94</v>
+        <v>48.74</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="DP14" t="n">
-        <v>11.89</v>
+        <v>12.21</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.34</v>
+        <v>10.63</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.5</v>
+        <v>5.47</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>60</v>
+        <v>59.69</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.62</v>
+        <v>14.37</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.609999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="DZ14" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="EA14" t="n">
-        <v>15.22</v>
+        <v>15</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="15">
@@ -6850,13 +6850,13 @@
         <v>6.1</v>
       </c>
       <c r="CB15" t="n">
-        <v>6.61</v>
+        <v>6.59</v>
       </c>
       <c r="CC15" t="n">
         <v>1.46</v>
       </c>
       <c r="CD15" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CE15" t="n">
         <v>1.2</v>
@@ -6901,7 +6901,7 @@
         <v>1.34</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CT15" t="n">
         <v>3.34</v>
@@ -6910,10 +6910,10 @@
         <v>1.8</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CX15" t="n">
         <v>1.56</v>
@@ -7017,10 +7017,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>10</v>
@@ -7029,82 +7029,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="G16" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="H16" t="n">
-        <v>98.25</v>
+        <v>102.67</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="K16" t="n">
-        <v>6.25</v>
+        <v>5.78</v>
       </c>
       <c r="L16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M16" t="n">
-        <v>51.5</v>
+        <v>50.44</v>
       </c>
       <c r="N16" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="O16" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="P16" t="n">
-        <v>11.75</v>
+        <v>12</v>
       </c>
       <c r="Q16" t="n">
-        <v>12.38</v>
+        <v>11.78</v>
       </c>
       <c r="R16" t="n">
-        <v>5.62</v>
+        <v>5.78</v>
       </c>
       <c r="S16" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="U16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>57.88</v>
+        <v>58.44</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z16" t="n">
-        <v>14.62</v>
+        <v>13.89</v>
       </c>
       <c r="AA16" t="n">
-        <v>10.75</v>
+        <v>10.33</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.88</v>
+        <v>3.56</v>
       </c>
       <c r="AC16" t="n">
-        <v>15.88</v>
+        <v>16.33</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AF16" t="n">
         <v>0.1</v>
@@ -7188,70 +7188,70 @@
         <v>1.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.11</v>
+        <v>2.95</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.390000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.11</v>
+        <v>2.95</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.28</v>
+        <v>4.11</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.06</v>
+        <v>3.95</v>
       </c>
       <c r="BR16" t="n">
-        <v>94.44</v>
+        <v>89.47</v>
       </c>
       <c r="BS16" t="n">
-        <v>77.78</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT16" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BU16" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV16" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BW16" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BX16" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.89</v>
+        <v>3.86</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.06</v>
+        <v>4.02</v>
       </c>
       <c r="CC16" t="n">
         <v>5.62</v>
@@ -7260,157 +7260,157 @@
         <v>5.19</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="CH16" t="n">
         <v>1.5</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CO16" t="n">
         <v>1.24</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.91</v>
+        <v>2.97</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CX16" t="n">
         <v>1.65</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DA16" t="n">
         <v>1.76</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DH16" t="n">
-        <v>89.5</v>
+        <v>92.05</v>
       </c>
       <c r="DI16" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.39</v>
+        <v>4.26</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DM16" t="n">
-        <v>40.28</v>
+        <v>40.37</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.17</v>
+        <v>11.32</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.56</v>
+        <v>11.32</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.5</v>
+        <v>7.47</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53.78</v>
+        <v>54.26</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.94</v>
+        <v>11.74</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.390000000000001</v>
+        <v>8.31</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.56</v>
+        <v>3.42</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.95</v>
+        <v>17.1</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="17">
@@ -7420,94 +7420,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F17" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="G17" t="n">
-        <v>3.67</v>
+        <v>3.9</v>
       </c>
       <c r="H17" t="n">
-        <v>102.44</v>
+        <v>103.3</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="K17" t="n">
-        <v>5.78</v>
+        <v>6.1</v>
       </c>
       <c r="L17" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M17" t="n">
-        <v>53.67</v>
+        <v>64.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="O17" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="P17" t="n">
-        <v>12.89</v>
+        <v>13.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>14.11</v>
+        <v>13.4</v>
       </c>
       <c r="R17" t="n">
-        <v>6.89</v>
+        <v>6.6</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="T17" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="U17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>51</v>
+        <v>52.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>16.11</v>
+        <v>16.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>10.22</v>
+        <v>10.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>5.89</v>
+        <v>5.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>19.22</v>
+        <v>20.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AF17" t="n">
         <v>0.11</v>
@@ -7591,64 +7591,64 @@
         <v>1.44</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.72</v>
+        <v>10.79</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.39</v>
+        <v>4.42</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.28</v>
+        <v>5.37</v>
       </c>
       <c r="BR17" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT17" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BU17" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BV17" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="CA17" t="n">
         <v>3.73</v>
@@ -7666,22 +7666,22 @@
         <v>1.32</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CH17" t="n">
         <v>1.5</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.64</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CL17" t="n">
         <v>2.06</v>
@@ -7699,7 +7699,7 @@
         <v>1.77</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CR17" t="n">
         <v>1.36</v>
@@ -7714,19 +7714,19 @@
         <v>1.52</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="DA17" t="n">
         <v>1.87</v>
@@ -7738,19 +7738,19 @@
         <v>1.8</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="DH17" t="n">
-        <v>96.16</v>
+        <v>96.95</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
@@ -7759,61 +7759,61 @@
         <v>2.05</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.67</v>
+        <v>5.84</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DM17" t="n">
-        <v>46.67</v>
+        <v>52.74</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.73</v>
+        <v>0.79</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.84</v>
+        <v>12.16</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.22</v>
+        <v>11.95</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.06</v>
+        <v>7.84</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>51.16</v>
+        <v>52.1</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.06</v>
+        <v>13.53</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.390000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.66</v>
+        <v>4.68</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.44</v>
+        <v>19.11</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="18">
@@ -7823,13 +7823,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C18" t="n">
         <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7916,136 +7916,136 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>94</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="BN18" t="n">
         <v>1.89</v>
       </c>
-      <c r="AI18" t="n">
-        <v>96.78</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>42.22</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>12.44</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>7.11</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>52.22</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>9.56</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>16.89</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>1.83</v>
-      </c>
       <c r="BO18" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.28</v>
+        <v>4.21</v>
       </c>
       <c r="BR18" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS18" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT18" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BU18" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="BV18" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="BW18" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX18" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BY18" t="n">
         <v>2.02</v>
@@ -8054,28 +8054,28 @@
         <v>2.03</v>
       </c>
       <c r="CA18" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="CD18" t="n">
         <v>3.79</v>
-      </c>
-      <c r="CB18" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="CC18" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="CD18" t="n">
-        <v>3.88</v>
       </c>
       <c r="CE18" t="n">
         <v>1.33</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI18" t="n">
         <v>2.1</v>
@@ -8084,106 +8084,106 @@
         <v>1.7</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CM18" t="n">
         <v>2.16</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CO18" t="n">
         <v>1.22</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CR18" t="n">
         <v>1.37</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CW18" t="n">
         <v>1.73</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.34</v>
+        <v>2.21</v>
       </c>
       <c r="DH18" t="n">
-        <v>100.78</v>
+        <v>99.11</v>
       </c>
       <c r="DI18" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.94</v>
+        <v>3.79</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DM18" t="n">
-        <v>43.89</v>
+        <v>42.69</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="DP18" t="n">
-        <v>11.44</v>
+        <v>11.52</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.39</v>
+        <v>13.26</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.11</v>
+        <v>7.32</v>
       </c>
       <c r="DS18" t="n">
         <v>0.16</v>
@@ -8195,28 +8195,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>52.61</v>
+        <v>52.63</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.12</v>
+        <v>11.32</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.78</v>
+        <v>6.89</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.33</v>
+        <v>4.42</v>
       </c>
       <c r="EA18" t="n">
-        <v>15.72</v>
+        <v>15.53</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="19">
@@ -8226,13 +8226,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
         <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
         <v>0.3</v>
@@ -8319,136 +8319,136 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AI19" t="n">
-        <v>83.5</v>
+        <v>85.22</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="AL19" t="n">
-        <v>4.12</v>
+        <v>3.89</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.62</v>
+        <v>0.44</v>
       </c>
       <c r="AN19" t="n">
-        <v>37.5</v>
+        <v>36.11</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.62</v>
+        <v>2.22</v>
       </c>
       <c r="AQ19" t="n">
-        <v>15</v>
+        <v>15.11</v>
       </c>
       <c r="AR19" t="n">
-        <v>10.75</v>
+        <v>11.33</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.5</v>
+        <v>7.78</v>
       </c>
       <c r="AT19" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>39.75</v>
+        <v>40.33</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA19" t="n">
-        <v>9.380000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.38</v>
+        <v>6</v>
       </c>
       <c r="BC19" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="BD19" t="n">
-        <v>15.12</v>
+        <v>15.44</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.11</v>
+        <v>9.84</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.72</v>
+        <v>4.42</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.39</v>
+        <v>5.05</v>
       </c>
       <c r="BR19" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS19" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT19" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BU19" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BV19" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW19" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX19" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BY19" t="n">
         <v>2.62</v>
@@ -8457,31 +8457,31 @@
         <v>2.69</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.68</v>
+        <v>3.64</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.61</v>
+        <v>3.51</v>
       </c>
       <c r="CE19" t="n">
         <v>1.37</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.79</v>
@@ -8490,136 +8490,136 @@
         <v>1.62</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CM19" t="n">
         <v>2.2</v>
       </c>
       <c r="CN19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="CP19" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>3</v>
+      </c>
+      <c r="CT19" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CW19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CX19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CY19" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CZ19" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="DA19" t="n">
         <v>1.76</v>
       </c>
-      <c r="CO19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="CP19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="CQ19" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="CR19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="CS19" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="CT19" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="CU19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="CV19" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="CW19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="CX19" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="CY19" t="n">
+      <c r="DB19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DC19" t="n">
         <v>2.06</v>
-      </c>
-      <c r="CZ19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="DA19" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="DB19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DC19" t="n">
-        <v>2.03</v>
       </c>
       <c r="DD19" t="n">
         <v>3.39</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="DH19" t="n">
-        <v>86.72</v>
+        <v>87.37</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.55</v>
+        <v>4.42</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.33</v>
+        <v>0.26</v>
       </c>
       <c r="DM19" t="n">
-        <v>41.78</v>
+        <v>40.89</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.33</v>
+        <v>14.42</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.83</v>
+        <v>12.05</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.67</v>
+        <v>6.84</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>40.5</v>
+        <v>40.74</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.5</v>
+        <v>12.26</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.390000000000001</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.11</v>
+        <v>4.16</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.11</v>
+        <v>16.21</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="8.4" customWidth="1" min="76" max="76"/>
+    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="G2" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="H2" t="n">
-        <v>75.22</v>
+        <v>71.7</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="K2" t="n">
-        <v>4.78</v>
+        <v>4.7</v>
       </c>
       <c r="L2" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="M2" t="n">
-        <v>33.78</v>
+        <v>33.1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="P2" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="Q2" t="n">
         <v>11</v>
       </c>
       <c r="R2" t="n">
-        <v>8.33</v>
+        <v>8.1</v>
       </c>
       <c r="S2" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="U2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>43</v>
+        <v>45.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>10.56</v>
+        <v>11.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.11</v>
+        <v>6.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.44</v>
+        <v>4.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>17.44</v>
+        <v>17.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>1.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.050000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BL2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="BO2" t="n">
         <v>1</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.79</v>
+        <v>3.65</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.26</v>
+        <v>5.3</v>
       </c>
       <c r="BR2" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS2" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BT2" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BU2" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV2" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX2" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.19</v>
+        <v>4.15</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="CC2" t="n">
         <v>8.26</v>
@@ -1628,7 +1628,7 @@
         <v>2.76</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="CH2" t="n">
         <v>1.43</v>
@@ -1646,19 +1646,19 @@
         <v>2.18</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CN2" t="n">
         <v>1.69</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="CR2" t="n">
         <v>1.44</v>
@@ -1676,19 +1676,19 @@
         <v>1.9</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CY2" t="n">
         <v>2.1</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DB2" t="n">
         <v>1.36</v>
@@ -1703,43 +1703,43 @@
         <v>0.05</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="DH2" t="n">
-        <v>73</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="DI2" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM2" t="n">
-        <v>31.21</v>
+        <v>31</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="DP2" t="n">
         <v>11.05</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.32</v>
+        <v>11.3</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.74</v>
+        <v>8.6</v>
       </c>
       <c r="DS2" t="n">
         <v>0.1</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>41.32</v>
+        <v>42.6</v>
       </c>
       <c r="DW2" t="n">
         <v>0.05</v>
       </c>
       <c r="DX2" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="DY2" t="n">
-        <v>5.63</v>
+        <v>5.85</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.37</v>
+        <v>3.55</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.58</v>
+        <v>16.65</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
         <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,139 +1872,139 @@
         <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AI3" t="n">
-        <v>96.56</v>
+        <v>89</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.44</v>
+        <v>4.4</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AN3" t="n">
-        <v>37.56</v>
+        <v>37.1</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14.11</v>
+        <v>14</v>
       </c>
       <c r="AR3" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.56</v>
+        <v>8.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>46.44</v>
+        <v>46.8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.890000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.67</v>
+        <v>6.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="BD3" t="n">
-        <v>19.78</v>
+        <v>19.7</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.58</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.89</v>
+        <v>3.95</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.68</v>
+        <v>5.6</v>
       </c>
       <c r="BR3" t="n">
-        <v>94.73999999999999</v>
+        <v>90</v>
       </c>
       <c r="BS3" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BT3" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BU3" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV3" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX3" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BY3" t="n">
         <v>3.91</v>
@@ -2013,40 +2013,40 @@
         <v>4.22</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.93</v>
+        <v>3.91</v>
       </c>
       <c r="CC3" t="n">
-        <v>5.25</v>
+        <v>5.23</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.48</v>
+        <v>5.44</v>
       </c>
       <c r="CE3" t="n">
         <v>1.37</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CM3" t="n">
         <v>2.3</v>
@@ -2058,10 +2058,10 @@
         <v>1.27</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.16</v>
+        <v>3.22</v>
       </c>
       <c r="CR3" t="n">
         <v>1.41</v>
@@ -2076,28 +2076,28 @@
         <v>1.46</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DD3" t="n">
         <v>3.26</v>
@@ -2106,76 +2106,76 @@
         <v>0.05</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="DH3" t="n">
-        <v>91.84</v>
+        <v>88.3</v>
       </c>
       <c r="DI3" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="DM3" t="n">
-        <v>41.21</v>
+        <v>40.8</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.84</v>
+        <v>13.8</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.05</v>
+        <v>13.95</v>
       </c>
       <c r="DR3" t="n">
         <v>6.95</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>44.05</v>
+        <v>44.35</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.74</v>
+        <v>10.6</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.37</v>
+        <v>7.3</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.37</v>
+        <v>3.3</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.79</v>
+        <v>18.8</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
         <v>0.3</v>
@@ -2278,136 +2278,136 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
-        <v>90.33</v>
+        <v>84.3</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN4" t="n">
-        <v>41.78</v>
+        <v>38.8</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.89</v>
+        <v>13.7</v>
       </c>
       <c r="AR4" t="n">
-        <v>12.67</v>
+        <v>12.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.89</v>
+        <v>6.5</v>
       </c>
       <c r="AT4" t="n">
         <v>2</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>42.11</v>
+        <v>41.9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.67</v>
+        <v>9</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.56</v>
+        <v>6</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="BD4" t="n">
-        <v>19.11</v>
+        <v>18.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.210000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.37</v>
+        <v>3.55</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.53</v>
+        <v>4.5</v>
       </c>
       <c r="BR4" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS4" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT4" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BU4" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BV4" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW4" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX4" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
         <v>2.98</v>
@@ -2416,16 +2416,16 @@
         <v>3.36</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.91</v>
+        <v>3.83</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.91</v>
+        <v>3.84</v>
       </c>
       <c r="CE4" t="n">
         <v>1.35</v>
@@ -2434,7 +2434,7 @@
         <v>2.65</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CH4" t="n">
         <v>1.46</v>
@@ -2446,13 +2446,13 @@
         <v>1.72</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CL4" t="n">
         <v>2.13</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CN4" t="n">
         <v>1.73</v>
@@ -2461,7 +2461,7 @@
         <v>1.26</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CQ4" t="n">
         <v>3.06</v>
@@ -2470,25 +2470,25 @@
         <v>1.4</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="CU4" t="n">
         <v>1.48</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CX4" t="n">
         <v>1.67</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.2</v>
@@ -2500,85 +2500,85 @@
         <v>1.33</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DH4" t="n">
-        <v>96.68000000000001</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.21</v>
+        <v>4.25</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM4" t="n">
-        <v>40.63</v>
+        <v>39.2</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.42</v>
+        <v>13.8</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.58</v>
+        <v>11.7</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.16</v>
+        <v>6.95</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44</v>
+        <v>43.8</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.79</v>
+        <v>11.8</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.79</v>
+        <v>7.9</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.32</v>
+        <v>17.9</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
         <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2681,49 +2681,49 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AI5" t="n">
-        <v>78.56</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>35.22</v>
+        <v>34.9</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13.78</v>
+        <v>13.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>13.33</v>
+        <v>14</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.779999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>41.89</v>
+        <v>42.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.33</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.11</v>
+        <v>6.1</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="BD5" t="n">
-        <v>14.89</v>
+        <v>15.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.369999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="BL5" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.42</v>
+        <v>5.35</v>
       </c>
       <c r="BR5" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BS5" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BT5" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BU5" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV5" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX5" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BY5" t="n">
         <v>2.93</v>
@@ -2819,25 +2819,25 @@
         <v>3.24</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.05</v>
+        <v>4.09</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.07</v>
+        <v>4.1</v>
       </c>
       <c r="CC5" t="n">
-        <v>6.59</v>
+        <v>6.58</v>
       </c>
       <c r="CD5" t="n">
-        <v>7.18</v>
+        <v>7.21</v>
       </c>
       <c r="CE5" t="n">
         <v>1.35</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="CH5" t="n">
         <v>1.45</v>
@@ -2852,22 +2852,22 @@
         <v>1.65</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CO5" t="n">
         <v>1.26</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="CR5" t="n">
         <v>1.41</v>
@@ -2882,7 +2882,7 @@
         <v>1.45</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CW5" t="n">
         <v>1.88</v>
@@ -2903,52 +2903,52 @@
         <v>1.34</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="DH5" t="n">
-        <v>88.20999999999999</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="DI5" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.63</v>
+        <v>4.55</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM5" t="n">
-        <v>43.26</v>
+        <v>42.7</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="DP5" t="n">
-        <v>13.84</v>
+        <v>13.65</v>
       </c>
       <c r="DQ5" t="n">
-        <v>13.21</v>
+        <v>13.55</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.53</v>
+        <v>7.7</v>
       </c>
       <c r="DS5" t="n">
         <v>0.05</v>
@@ -2966,22 +2966,22 @@
         <v>0.05</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.16</v>
+        <v>11</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.47</v>
+        <v>7.4</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.53</v>
+        <v>18.8</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="H6" t="n">
-        <v>84</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="K6" t="n">
-        <v>6.56</v>
+        <v>6.3</v>
       </c>
       <c r="L6" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="M6" t="n">
-        <v>44.22</v>
+        <v>46.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="O6" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="P6" t="n">
-        <v>13</v>
+        <v>13.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.56</v>
+        <v>12.3</v>
       </c>
       <c r="R6" t="n">
-        <v>5.22</v>
+        <v>5.2</v>
       </c>
       <c r="S6" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="T6" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="U6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>49.11</v>
+        <v>49.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>15.33</v>
+        <v>15.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.56</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.78</v>
+        <v>5.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>17.78</v>
+        <v>17.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AF6" t="n">
         <v>0.1</v>
@@ -3162,70 +3162,70 @@
         <v>2.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.949999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.16</v>
+        <v>4.1</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.84</v>
+        <v>4.8</v>
       </c>
       <c r="BR6" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS6" t="n">
-        <v>78.95</v>
+        <v>75</v>
       </c>
       <c r="BT6" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BU6" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BV6" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="CC6" t="n">
         <v>2.87</v>
@@ -3237,7 +3237,7 @@
         <v>1.31</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CG6" t="n">
         <v>3.28</v>
@@ -3246,7 +3246,7 @@
         <v>1.53</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.66</v>
@@ -3255,10 +3255,10 @@
         <v>1.56</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CN6" t="n">
         <v>1.79</v>
@@ -3267,10 +3267,10 @@
         <v>1.2</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CR6" t="n">
         <v>1.35</v>
@@ -3285,10 +3285,10 @@
         <v>1.56</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CX6" t="n">
         <v>1.59</v>
@@ -3306,7 +3306,7 @@
         <v>1.27</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DD6" t="n">
         <v>2.77</v>
@@ -3315,76 +3315,76 @@
         <v>0.1</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="DH6" t="n">
-        <v>86.89</v>
+        <v>87.7</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.63</v>
+        <v>5.55</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM6" t="n">
-        <v>43</v>
+        <v>44.1</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.74</v>
+        <v>14.05</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.84</v>
+        <v>12.7</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.21</v>
+        <v>6.15</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>49.05</v>
+        <v>49.3</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.95</v>
+        <v>14</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.74</v>
+        <v>8.9</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.21</v>
+        <v>5.1</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.63</v>
+        <v>16.75</v>
       </c>
       <c r="EB6" t="n">
         <v>1.56</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>0.1</v>
@@ -3484,52 +3484,52 @@
         <v>1.6</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.67</v>
+        <v>2.9</v>
       </c>
       <c r="AI7" t="n">
-        <v>105.78</v>
+        <v>103.5</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>5.89</v>
+        <v>6</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AN7" t="n">
-        <v>55.22</v>
+        <v>57.3</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12.22</v>
+        <v>12.1</v>
       </c>
       <c r="AR7" t="n">
-        <v>13.78</v>
+        <v>13.9</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.56</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>57.22</v>
+        <v>57.3</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>13.33</v>
+        <v>13.1</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.44</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.89</v>
+        <v>4.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>17.11</v>
+        <v>17.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.26</v>
+        <v>10.2</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="BO7" t="n">
         <v>1</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.37</v>
+        <v>5.25</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.89</v>
+        <v>4.95</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>73.68000000000001</v>
+        <v>70</v>
       </c>
       <c r="BT7" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BU7" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BV7" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BW7" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BX7" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BY7" t="n">
         <v>2.2</v>
@@ -3625,22 +3625,22 @@
         <v>2.22</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.89</v>
+        <v>3.88</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.04</v>
+        <v>4.01</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="CD7" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CE7" t="n">
         <v>1.34</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CG7" t="n">
         <v>3.13</v>
@@ -3649,7 +3649,7 @@
         <v>1.48</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.72</v>
@@ -3658,10 +3658,10 @@
         <v>1.56</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CN7" t="n">
         <v>1.81</v>
@@ -3670,7 +3670,7 @@
         <v>1.23</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CQ7" t="n">
         <v>2.89</v>
@@ -3697,97 +3697,97 @@
         <v>1.62</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="DB7" t="n">
         <v>1.29</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="DH7" t="n">
-        <v>104.84</v>
+        <v>103.75</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="DM7" t="n">
-        <v>54.21</v>
+        <v>55.3</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="DP7" t="n">
-        <v>11.63</v>
+        <v>11.6</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.26</v>
+        <v>13.35</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.63</v>
+        <v>6.4</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>53.84</v>
+        <v>54.05</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX7" t="n">
-        <v>14.42</v>
+        <v>14.25</v>
       </c>
       <c r="DY7" t="n">
-        <v>9.52</v>
+        <v>9.4</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="EA7" t="n">
-        <v>17</v>
+        <v>17.05</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="8">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F8" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="G8" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="H8" t="n">
-        <v>82.67</v>
+        <v>85.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>42.11</v>
+        <v>42.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="P8" t="n">
-        <v>10.11</v>
+        <v>10.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.44</v>
+        <v>13.9</v>
       </c>
       <c r="R8" t="n">
-        <v>5.67</v>
+        <v>5.8</v>
       </c>
       <c r="S8" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>43</v>
+        <v>44.4</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>13.56</v>
+        <v>12.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.44</v>
+        <v>7.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.11</v>
+        <v>5</v>
       </c>
       <c r="AC8" t="n">
-        <v>14</v>
+        <v>14.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AF8" t="n">
         <v>0.1</v>
@@ -3968,70 +3968,70 @@
         <v>1.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.42</v>
+        <v>8.25</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="BL8" t="n">
         <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.79</v>
+        <v>3.65</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="BR8" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS8" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT8" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BU8" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BV8" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW8" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX8" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BY8" t="n">
-        <v>3.71</v>
+        <v>3.53</v>
       </c>
       <c r="BZ8" t="n">
-        <v>3.77</v>
+        <v>3.59</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="CC8" t="n">
         <v>4.31</v>
@@ -4043,19 +4043,19 @@
         <v>1.35</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CH8" t="n">
         <v>1.46</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CK8" t="n">
         <v>1.67</v>
@@ -4073,28 +4073,28 @@
         <v>1.26</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="CR8" t="n">
         <v>1.41</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="CT8" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CX8" t="n">
         <v>1.72</v>
@@ -4106,58 +4106,58 @@
         <v>2.13</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="DB8" t="n">
         <v>1.33</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="DE8" t="n">
         <v>0.1</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="DH8" t="n">
-        <v>82.53</v>
+        <v>83.95</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DM8" t="n">
-        <v>40.21</v>
+        <v>40.7</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.84</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.37</v>
+        <v>14.55</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.42</v>
+        <v>7.4</v>
       </c>
       <c r="DS8" t="n">
         <v>0.05</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>42.47</v>
+        <v>43.2</v>
       </c>
       <c r="DW8" t="n">
         <v>0.05</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.95</v>
+        <v>11.6</v>
       </c>
       <c r="DY8" t="n">
-        <v>8</v>
+        <v>7.65</v>
       </c>
       <c r="DZ8" t="n">
         <v>3.95</v>
       </c>
       <c r="EA8" t="n">
-        <v>14.47</v>
+        <v>14.6</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
         <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4290,139 +4290,139 @@
         <v>1.22</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AI9" t="n">
-        <v>76.7</v>
+        <v>71.55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN9" t="n">
-        <v>30.3</v>
+        <v>28.91</v>
       </c>
       <c r="AO9" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>50.09</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>16.64</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BK9" t="n">
         <v>0.7</v>
       </c>
-      <c r="AP9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>9.109999999999999</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>0.74</v>
-      </c>
       <c r="BL9" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.47</v>
+        <v>4.3</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.63</v>
+        <v>4.7</v>
       </c>
       <c r="BR9" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS9" t="n">
-        <v>84.20999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT9" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BU9" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BV9" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BW9" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BX9" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BY9" t="n">
         <v>4.66</v>
@@ -4431,31 +4431,31 @@
         <v>4.91</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.12</v>
+        <v>4.09</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.39</v>
+        <v>4.33</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="CD9" t="n">
-        <v>6.4</v>
+        <v>6.15</v>
       </c>
       <c r="CE9" t="n">
         <v>1.32</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.74</v>
@@ -4467,19 +4467,19 @@
         <v>2.15</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CN9" t="n">
         <v>1.77</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="CR9" t="n">
         <v>1.38</v>
@@ -4500,22 +4500,22 @@
         <v>1.79</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="DD9" t="n">
         <v>2.86</v>
@@ -4527,73 +4527,73 @@
         <v>1.1</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="DH9" t="n">
-        <v>78.05</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.1</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DM9" t="n">
-        <v>34.21</v>
+        <v>33.25</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="DP9" t="n">
-        <v>10.84</v>
+        <v>10.85</v>
       </c>
       <c r="DQ9" t="n">
         <v>11</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.68</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>49.63</v>
+        <v>48.8</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.210000000000001</v>
+        <v>9</v>
       </c>
       <c r="DY9" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.21</v>
+        <v>3.05</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.63</v>
+        <v>16.55</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="10">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="H10" t="n">
-        <v>106.7</v>
+        <v>104.91</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J10" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="K10" t="n">
-        <v>4.6</v>
+        <v>4.64</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="M10" t="n">
-        <v>50.2</v>
+        <v>48.55</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="O10" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="P10" t="n">
-        <v>12.3</v>
+        <v>12.55</v>
       </c>
       <c r="Q10" t="n">
-        <v>12</v>
+        <v>11.73</v>
       </c>
       <c r="R10" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="S10" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="T10" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>53.5</v>
+        <v>52.82</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.1</v>
+        <v>13.18</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.6</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.5</v>
+        <v>4.64</v>
       </c>
       <c r="AC10" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="AD10" t="n">
         <v>1.51</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AF10" t="n">
         <v>0.11</v>
@@ -4774,58 +4774,58 @@
         <v>3.11</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.949999999999999</v>
+        <v>8.85</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.79</v>
+        <v>3.7</v>
       </c>
       <c r="BR10" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS10" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BT10" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BU10" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BV10" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BW10" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX10" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BY10" t="n">
         <v>2</v>
@@ -4834,10 +4834,10 @@
         <v>2.03</v>
       </c>
       <c r="CA10" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="CB10" t="n">
         <v>4.27</v>
-      </c>
-      <c r="CB10" t="n">
-        <v>4.29</v>
       </c>
       <c r="CC10" t="n">
         <v>2.04</v>
@@ -4852,13 +4852,13 @@
         <v>2.27</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="CH10" t="n">
         <v>1.61</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.57</v>
@@ -4870,7 +4870,7 @@
         <v>2.04</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CN10" t="n">
         <v>1.8</v>
@@ -4879,16 +4879,16 @@
         <v>1.15</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CR10" t="n">
         <v>1.35</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CT10" t="n">
         <v>3.26</v>
@@ -4897,7 +4897,7 @@
         <v>1.66</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="CW10" t="n">
         <v>1.61</v>
@@ -4906,95 +4906,95 @@
         <v>1.58</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DB10" t="inlineStr"/>
       <c r="DC10" t="n">
         <v>1.58</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="DH10" t="n">
-        <v>107.84</v>
+        <v>106.8</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.69</v>
+        <v>4.7</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DM10" t="n">
-        <v>51.26</v>
+        <v>50.3</v>
       </c>
       <c r="DN10" t="n">
         <v>0.95</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.53</v>
+        <v>13.6</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.37</v>
+        <v>11.25</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.05</v>
+        <v>6.9</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>53.68</v>
+        <v>53.3</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.42</v>
+        <v>12.5</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.32</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.11</v>
+        <v>4.2</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.89</v>
+        <v>20</v>
       </c>
       <c r="EB10" t="n">
         <v>1.45</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="11">
@@ -5004,13 +5004,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="n">
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>0.1</v>
@@ -5094,139 +5094,139 @@
         <v>1.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AH11" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AI11" t="n">
-        <v>70</v>
+        <v>70.8</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN11" t="n">
-        <v>25.44</v>
+        <v>25</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12.78</v>
+        <v>13.3</v>
       </c>
       <c r="AR11" t="n">
-        <v>14.22</v>
+        <v>14</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.890000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>42.22</v>
+        <v>42.3</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.44</v>
+        <v>9.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.44</v>
+        <v>6.6</v>
       </c>
       <c r="BC11" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="BD11" t="n">
-        <v>18.11</v>
+        <v>18.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="BF11" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.16</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.95</v>
+        <v>4.75</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="BR11" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS11" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT11" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV11" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX11" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BY11" t="n">
         <v>4.27</v>
@@ -5235,31 +5235,31 @@
         <v>4.73</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.07</v>
+        <v>4.04</v>
       </c>
       <c r="CC11" t="n">
-        <v>5.65</v>
+        <v>5.49</v>
       </c>
       <c r="CD11" t="n">
-        <v>5.99</v>
+        <v>5.83</v>
       </c>
       <c r="CE11" t="n">
         <v>1.36</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="CH11" t="n">
         <v>1.44</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.84</v>
@@ -5271,31 +5271,31 @@
         <v>1.99</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="CR11" t="n">
         <v>1.4</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV11" t="n">
         <v>2.02</v>
@@ -5304,67 +5304,67 @@
         <v>1.87</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DC11" t="n">
         <v>1.92</v>
       </c>
-      <c r="CZ11" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="DA11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="DB11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="DC11" t="n">
-        <v>1.91</v>
-      </c>
       <c r="DD11" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="DH11" t="n">
-        <v>80.05</v>
+        <v>79.95</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DM11" t="n">
-        <v>32.26</v>
+        <v>31.7</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.16</v>
+        <v>12.45</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.68</v>
+        <v>13.6</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DS11" t="n">
         <v>0.05</v>
@@ -5376,28 +5376,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>43.47</v>
+        <v>43.45</v>
       </c>
       <c r="DW11" t="n">
         <v>0.05</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.31</v>
+        <v>10.3</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.31</v>
+        <v>7.35</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.53</v>
+        <v>19.6</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="12">
@@ -5407,94 +5407,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
         <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F12" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="G12" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>72.33</v>
+        <v>70</v>
       </c>
       <c r="I12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J12" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="K12" t="n">
-        <v>5.11</v>
+        <v>5.2</v>
       </c>
       <c r="L12" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="M12" t="n">
-        <v>33.33</v>
+        <v>30.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>11.67</v>
+        <v>12</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.89</v>
+        <v>12.8</v>
       </c>
       <c r="R12" t="n">
-        <v>5.89</v>
+        <v>6.1</v>
       </c>
       <c r="S12" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T12" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="U12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>47.33</v>
+        <v>48.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>13.22</v>
+        <v>13.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.220000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB12" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>14.33</v>
+        <v>14.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5578,70 +5578,70 @@
         <v>2.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.53</v>
+        <v>10.55</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.32</v>
+        <v>4.45</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.42</v>
+        <v>5.35</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT12" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BU12" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BV12" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BW12" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX12" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.97</v>
+        <v>3.95</v>
       </c>
       <c r="CC12" t="n">
         <v>3.65</v>
@@ -5653,13 +5653,13 @@
         <v>1.32</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI12" t="n">
         <v>2.18</v>
@@ -5671,7 +5671,7 @@
         <v>1.49</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CM12" t="n">
         <v>2.42</v>
@@ -5686,7 +5686,7 @@
         <v>1.76</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CR12" t="n">
         <v>1.36</v>
@@ -5695,28 +5695,28 @@
         <v>2.59</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CU12" t="n">
         <v>1.54</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CX12" t="n">
         <v>1.56</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.38</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="DB12" t="n">
         <v>1.29</v>
@@ -5731,43 +5731,43 @@
         <v>0.1</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.47</v>
+        <v>2.35</v>
       </c>
       <c r="DH12" t="n">
-        <v>81.37</v>
+        <v>79.75</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.89</v>
+        <v>4.95</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DM12" t="n">
-        <v>35.95</v>
+        <v>34.55</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.79</v>
+        <v>12.9</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.11</v>
+        <v>12.55</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.84</v>
+        <v>6.9</v>
       </c>
       <c r="DS12" t="n">
         <v>0.1</v>
@@ -5779,28 +5779,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.84</v>
+        <v>48.45</v>
       </c>
       <c r="DW12" t="n">
         <v>0.1</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.53</v>
+        <v>11.7</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.37</v>
+        <v>7.4</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.16</v>
+        <v>4.3</v>
       </c>
       <c r="EA12" t="n">
-        <v>16.16</v>
+        <v>16.35</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="13">
@@ -5810,10 +5810,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
@@ -5822,49 +5822,49 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="G13" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>96.22</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M13" t="n">
-        <v>49.33</v>
+        <v>47</v>
       </c>
       <c r="N13" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="O13" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="P13" t="n">
-        <v>14.33</v>
+        <v>14.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>12.78</v>
+        <v>12.6</v>
       </c>
       <c r="R13" t="n">
-        <v>5.78</v>
+        <v>6.2</v>
       </c>
       <c r="S13" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="T13" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5876,28 +5876,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>58.11</v>
+        <v>56.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>14.89</v>
+        <v>13.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.890000000000001</v>
+        <v>9</v>
       </c>
       <c r="AB13" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>17.67</v>
+        <v>17.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AF13" t="n">
         <v>0.1</v>
@@ -5981,58 +5981,58 @@
         <v>2.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.47</v>
+        <v>10.4</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.26</v>
+        <v>4.2</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.21</v>
+        <v>6.2</v>
       </c>
       <c r="BR13" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS13" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BT13" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BU13" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BV13" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW13" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX13" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BY13" t="n">
         <v>2.05</v>
@@ -6044,7 +6044,7 @@
         <v>3.72</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="CC13" t="n">
         <v>2.51</v>
@@ -6053,19 +6053,19 @@
         <v>2.64</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF13" t="n">
         <v>2.52</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CH13" t="n">
         <v>1.49</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.7</v>
@@ -6110,22 +6110,22 @@
         <v>1.77</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DD13" t="n">
         <v>3.07</v>
@@ -6134,43 +6134,43 @@
         <v>0.05</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.31</v>
+        <v>3.2</v>
       </c>
       <c r="DH13" t="n">
-        <v>90.37</v>
+        <v>88</v>
       </c>
       <c r="DI13" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="DK13" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM13" t="n">
-        <v>45.47</v>
+        <v>44.5</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.1</v>
+        <v>14.15</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.53</v>
+        <v>13.4</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.32</v>
+        <v>6.5</v>
       </c>
       <c r="DS13" t="n">
         <v>0.05</v>
@@ -6182,28 +6182,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>56.05</v>
+        <v>55.35</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX13" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.84</v>
+        <v>7.5</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5.16</v>
+        <v>5</v>
       </c>
       <c r="EA13" t="n">
-        <v>17.58</v>
+        <v>17.55</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="14">
@@ -6213,13 +6213,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
         <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
         <v>0.2</v>
@@ -6306,136 +6306,136 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="AI14" t="n">
-        <v>101.56</v>
+        <v>100.1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.33</v>
+        <v>5.2</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN14" t="n">
-        <v>44</v>
+        <v>44.2</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>10.67</v>
+        <v>11.1</v>
       </c>
       <c r="AR14" t="n">
-        <v>10.67</v>
+        <v>10.7</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.44</v>
+        <v>6.4</v>
       </c>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>58.56</v>
+        <v>57.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA14" t="n">
-        <v>14.56</v>
+        <v>14.9</v>
       </c>
       <c r="BB14" t="n">
-        <v>8.890000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.67</v>
+        <v>5.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>15.78</v>
+        <v>15.9</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.68</v>
+        <v>8.65</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.95</v>
+        <v>4.85</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT14" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BU14" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BV14" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW14" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BX14" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BY14" t="n">
         <v>1.77</v>
@@ -6444,16 +6444,16 @@
         <v>1.81</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.29</v>
+        <v>4.25</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="CC14" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="CE14" t="n">
         <v>1.3</v>
@@ -6462,37 +6462,37 @@
         <v>2.39</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CL14" t="n">
         <v>2.12</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP14" t="n">
         <v>1.65</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CR14" t="n">
         <v>1.35</v>
@@ -6504,7 +6504,7 @@
         <v>3.28</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV14" t="n">
         <v>2.2</v>
@@ -6513,16 +6513,16 @@
         <v>1.76</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DB14" t="n">
         <v>1.27</v>
@@ -6531,82 +6531,82 @@
         <v>1.7</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF14" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="DG14" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="DH14" t="n">
-        <v>107.69</v>
+        <v>106.65</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM14" t="n">
-        <v>48.74</v>
+        <v>48.6</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.21</v>
+        <v>12.35</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.63</v>
+        <v>10.65</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.47</v>
+        <v>5.5</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>59.69</v>
+        <v>59.1</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.37</v>
+        <v>14.55</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.42</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.95</v>
+        <v>5.85</v>
       </c>
       <c r="EA14" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="EB14" t="n">
         <v>1.6</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="15">
@@ -6616,13 +6616,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15" t="n">
         <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
         <v>0.11</v>
@@ -6706,139 +6706,139 @@
         <v>1.11</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="AI15" t="n">
-        <v>129</v>
+        <v>126.82</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.7</v>
+        <v>5.73</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.3</v>
+        <v>0.18</v>
       </c>
       <c r="AN15" t="n">
-        <v>61.7</v>
+        <v>61.45</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.6</v>
+        <v>2.27</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.2</v>
+        <v>9.82</v>
       </c>
       <c r="AR15" t="n">
-        <v>9.300000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="AS15" t="n">
-        <v>5</v>
+        <v>4.91</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>68.7</v>
+        <v>68.64</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="BA15" t="n">
-        <v>14.9</v>
+        <v>14.73</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.6</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="BC15" t="n">
-        <v>6.3</v>
+        <v>6.09</v>
       </c>
       <c r="BD15" t="n">
-        <v>15.8</v>
+        <v>16.27</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="BG15" t="n">
         <v>2.95</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.109999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BI15" t="n">
         <v>2.95</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BL15" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.26</v>
+        <v>4</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.84</v>
+        <v>4.55</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT15" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BU15" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV15" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BW15" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX15" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BY15" t="n">
         <v>1.21</v>
@@ -6847,73 +6847,73 @@
         <v>1.24</v>
       </c>
       <c r="CA15" t="n">
-        <v>6.1</v>
+        <v>6.01</v>
       </c>
       <c r="CB15" t="n">
-        <v>6.59</v>
+        <v>6.48</v>
       </c>
       <c r="CC15" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CD15" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CE15" t="n">
         <v>1.2</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CG15" t="n">
-        <v>4.05</v>
+        <v>4.03</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CO15" t="n">
         <v>1.11</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CR15" t="n">
         <v>1.34</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CT15" t="n">
         <v>3.34</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CX15" t="n">
         <v>1.56</v>
@@ -6929,85 +6929,85 @@
       </c>
       <c r="DB15" t="inlineStr"/>
       <c r="DC15" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.73</v>
+        <v>3.5</v>
       </c>
       <c r="DH15" t="n">
-        <v>136.58</v>
+        <v>135</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="DK15" t="n">
-        <v>6.21</v>
+        <v>6.2</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.48</v>
+        <v>0.4</v>
       </c>
       <c r="DM15" t="n">
-        <v>68.37</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.16</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="DQ15" t="n">
-        <v>8.48</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="DR15" t="n">
-        <v>4.42</v>
+        <v>4.4</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>69.20999999999999</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="DW15" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DX15" t="n">
-        <v>17.47</v>
+        <v>17.25</v>
       </c>
       <c r="DY15" t="n">
-        <v>10.58</v>
+        <v>10.5</v>
       </c>
       <c r="DZ15" t="n">
-        <v>6.9</v>
+        <v>6.75</v>
       </c>
       <c r="EA15" t="n">
-        <v>16.89</v>
+        <v>17.1</v>
       </c>
       <c r="EB15" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="16">
@@ -7017,10 +7017,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
         <v>10</v>
@@ -7029,82 +7029,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="G16" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="H16" t="n">
-        <v>102.67</v>
+        <v>101.3</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="K16" t="n">
-        <v>5.78</v>
+        <v>5.6</v>
       </c>
       <c r="L16" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="M16" t="n">
-        <v>50.44</v>
+        <v>49.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="O16" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="P16" t="n">
         <v>12</v>
       </c>
       <c r="Q16" t="n">
-        <v>11.78</v>
+        <v>12</v>
       </c>
       <c r="R16" t="n">
-        <v>5.78</v>
+        <v>6.4</v>
       </c>
       <c r="S16" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="T16" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="U16" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="V16" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>58.44</v>
+        <v>57.8</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>13.89</v>
+        <v>13.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>10.33</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>16.33</v>
+        <v>16.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AF16" t="n">
         <v>0.1</v>
@@ -7188,67 +7188,67 @@
         <v>1.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.050000000000001</v>
+        <v>9</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.11</v>
+        <v>4.15</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BR16" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS16" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT16" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BU16" t="n">
-        <v>26.32</v>
+        <v>30</v>
       </c>
       <c r="BV16" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BW16" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BX16" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BY16" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.14</v>
+        <v>2.39</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="CB16" t="n">
         <v>4.02</v>
@@ -7272,19 +7272,19 @@
         <v>1.5</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.72</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CL16" t="n">
         <v>2.14</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CN16" t="n">
         <v>1.75</v>
@@ -7296,16 +7296,16 @@
         <v>1.81</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CR16" t="n">
         <v>1.38</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CU16" t="n">
         <v>1.52</v>
@@ -7317,16 +7317,16 @@
         <v>1.75</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DB16" t="n">
         <v>1.31</v>
@@ -7335,82 +7335,82 @@
         <v>1.85</v>
       </c>
       <c r="DD16" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="DE16" t="n">
         <v>0.05</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="DG16" t="n">
         <v>2</v>
       </c>
       <c r="DH16" t="n">
-        <v>92.05</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="DM16" t="n">
-        <v>40.37</v>
+        <v>40.25</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.32</v>
+        <v>11.35</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.32</v>
+        <v>11.45</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.47</v>
+        <v>7.7</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>54.26</v>
+        <v>54.15</v>
       </c>
       <c r="DW16" t="n">
         <v>0.1</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.74</v>
+        <v>11.6</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.31</v>
+        <v>8.15</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.1</v>
+        <v>16.95</v>
       </c>
       <c r="EB16" t="n">
         <v>1.27</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="17">
@@ -7420,13 +7420,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" t="n">
         <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
         <v>0.1</v>
@@ -7510,16 +7510,16 @@
         <v>1.9</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AI17" t="n">
-        <v>89.89</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
@@ -7528,121 +7528,121 @@
         <v>2</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.56</v>
+        <v>5.2</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AN17" t="n">
-        <v>39.67</v>
+        <v>38.9</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AQ17" t="n">
-        <v>10.78</v>
+        <v>10.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>10.33</v>
+        <v>10.8</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.220000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>51.33</v>
+        <v>51.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BA17" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.56</v>
+        <v>6.3</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>17.67</v>
+        <v>17.7</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.79</v>
+        <v>10.6</v>
       </c>
       <c r="BI17" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.42</v>
+        <v>4.45</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.37</v>
+        <v>5.2</v>
       </c>
       <c r="BR17" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS17" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT17" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BU17" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BV17" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BY17" t="n">
         <v>2.29</v>
@@ -7651,34 +7651,34 @@
         <v>2.38</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="CB17" t="n">
         <v>3.83</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.41</v>
+        <v>3.38</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.49</v>
+        <v>3.51</v>
       </c>
       <c r="CE17" t="n">
         <v>1.32</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CK17" t="n">
         <v>1.6</v>
@@ -7687,37 +7687,37 @@
         <v>2.06</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="CR17" t="n">
         <v>1.36</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="CT17" t="n">
         <v>3.2</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CX17" t="n">
         <v>1.58</v>
@@ -7726,31 +7726,31 @@
         <v>1.95</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DB17" t="n">
         <v>1.28</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="DE17" t="n">
         <v>0.1</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="DH17" t="n">
-        <v>96.95</v>
+        <v>96.84999999999999</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
@@ -7759,28 +7759,28 @@
         <v>2.05</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.84</v>
+        <v>5.65</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM17" t="n">
-        <v>52.74</v>
+        <v>51.7</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.16</v>
+        <v>12</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.95</v>
+        <v>12.1</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.84</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DS17" t="n">
         <v>0.1</v>
@@ -7792,28 +7792,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.53</v>
+        <v>13.25</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.84</v>
+        <v>8.6</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.68</v>
+        <v>4.65</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.11</v>
+        <v>19.05</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="18">
@@ -7823,10 +7823,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
         <v>10</v>
@@ -7838,79 +7838,79 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>2.78</v>
+        <v>2.4</v>
       </c>
       <c r="H18" t="n">
-        <v>104.78</v>
+        <v>102.5</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="K18" t="n">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="L18" t="n">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="M18" t="n">
-        <v>45.56</v>
+        <v>44.8</v>
       </c>
       <c r="N18" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="P18" t="n">
-        <v>10.44</v>
+        <v>10.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>12.78</v>
+        <v>12</v>
       </c>
       <c r="R18" t="n">
-        <v>7.11</v>
+        <v>7</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="T18" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="U18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>53</v>
+        <v>50.9</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>12.67</v>
+        <v>12.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.22</v>
+        <v>7</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.44</v>
+        <v>5.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>14.56</v>
+        <v>14.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7994,70 +7994,70 @@
         <v>2.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="BH18" t="n">
-        <v>7.63</v>
+        <v>7.8</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="BO18" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.21</v>
+        <v>3.95</v>
       </c>
       <c r="BR18" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS18" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT18" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BU18" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BV18" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BW18" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX18" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.03</v>
+        <v>2.36</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="CC18" t="n">
         <v>3.68</v>
@@ -8069,19 +8069,19 @@
         <v>1.33</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CK18" t="n">
         <v>1.67</v>
@@ -8099,25 +8099,25 @@
         <v>1.22</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="CR18" t="n">
         <v>1.37</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="CT18" t="n">
         <v>3.14</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CW18" t="n">
         <v>1.73</v>
@@ -8138,85 +8138,85 @@
         <v>1.3</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="DH18" t="n">
-        <v>99.11</v>
+        <v>98.25</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.79</v>
+        <v>3.85</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="DM18" t="n">
-        <v>42.69</v>
+        <v>42.45</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="DP18" t="n">
-        <v>11.52</v>
+        <v>11.35</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.26</v>
+        <v>12.85</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.32</v>
+        <v>7.25</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>52.63</v>
+        <v>51.6</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.32</v>
+        <v>11.2</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.89</v>
+        <v>6.8</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.42</v>
+        <v>4.4</v>
       </c>
       <c r="EA18" t="n">
-        <v>15.53</v>
+        <v>15.3</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -8226,94 +8226,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="G19" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="H19" t="n">
-        <v>89.3</v>
+        <v>83.73</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="K19" t="n">
-        <v>4.9</v>
+        <v>4.91</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="M19" t="n">
-        <v>45.2</v>
+        <v>44.36</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="O19" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="P19" t="n">
-        <v>13.8</v>
+        <v>13.64</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.7</v>
+        <v>12.73</v>
       </c>
       <c r="R19" t="n">
-        <v>6</v>
+        <v>6.09</v>
       </c>
       <c r="S19" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="T19" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>41.1</v>
+        <v>41.91</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z19" t="n">
-        <v>15</v>
+        <v>14.73</v>
       </c>
       <c r="AA19" t="n">
-        <v>10</v>
+        <v>9.82</v>
       </c>
       <c r="AB19" t="n">
-        <v>5</v>
+        <v>4.91</v>
       </c>
       <c r="AC19" t="n">
-        <v>16.9</v>
+        <v>17.27</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8397,70 +8397,70 @@
         <v>3.11</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.84</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.42</v>
+        <v>4.45</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="BR19" t="n">
-        <v>94.73999999999999</v>
+        <v>90</v>
       </c>
       <c r="BS19" t="n">
-        <v>68.42</v>
+        <v>65</v>
       </c>
       <c r="BT19" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BU19" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BV19" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW19" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX19" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.69</v>
+        <v>2.61</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="CC19" t="n">
         <v>3.45</v>
@@ -8469,28 +8469,28 @@
         <v>3.51</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="CH19" t="n">
         <v>1.41</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CM19" t="n">
         <v>2.2</v>
@@ -8499,13 +8499,13 @@
         <v>1.75</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="CR19" t="n">
         <v>1.43</v>
@@ -8520,106 +8520,106 @@
         <v>1.41</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="DD19" t="n">
         <v>3.39</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="DH19" t="n">
-        <v>87.37</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.42</v>
+        <v>4.45</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM19" t="n">
-        <v>40.89</v>
+        <v>40.65</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.42</v>
+        <v>14.3</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.05</v>
+        <v>12.1</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.84</v>
+        <v>6.85</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>40.74</v>
+        <v>41.2</v>
       </c>
       <c r="DW19" t="n">
         <v>0.1</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.26</v>
+        <v>12.25</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.109999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.21</v>
+        <v>16.45</v>
       </c>
       <c r="EB19" t="n">
         <v>1.36</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -2299,7 +2299,7 @@
         <v>0.2</v>
       </c>
       <c r="AN4" t="n">
-        <v>38.8</v>
+        <v>39.1</v>
       </c>
       <c r="AO4" t="n">
         <v>0.8</v>
@@ -2350,7 +2350,7 @@
         <v>18.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="BF4" t="n">
         <v>2</v>
@@ -2530,7 +2530,7 @@
         <v>0.25</v>
       </c>
       <c r="DM4" t="n">
-        <v>39.2</v>
+        <v>39.35</v>
       </c>
       <c r="DN4" t="n">
         <v>0.7</v>
@@ -5440,7 +5440,7 @@
         <v>0.8</v>
       </c>
       <c r="M12" t="n">
-        <v>30.8</v>
+        <v>32.1</v>
       </c>
       <c r="N12" t="n">
         <v>1</v>
@@ -5491,7 +5491,7 @@
         <v>14.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
@@ -5752,7 +5752,7 @@
         <v>0.5</v>
       </c>
       <c r="DM12" t="n">
-        <v>34.55</v>
+        <v>35.2</v>
       </c>
       <c r="DN12" t="n">
         <v>1.15</v>
@@ -5797,7 +5797,7 @@
         <v>16.35</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="EC12" t="n">
         <v>2.25</v>
@@ -5891,7 +5891,7 @@
         <v>4.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="AD13" t="n">
         <v>1.54</v>
@@ -6197,7 +6197,7 @@
         <v>5</v>
       </c>
       <c r="EA13" t="n">
-        <v>17.55</v>
+        <v>17.6</v>
       </c>
       <c r="EB13" t="n">
         <v>1.46</v>

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
+    <col width="8.4" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="H4" t="n">
-        <v>102.4</v>
+        <v>102.27</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="K4" t="n">
-        <v>5.4</v>
+        <v>5.55</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="M4" t="n">
-        <v>39.6</v>
+        <v>39.36</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="O4" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="P4" t="n">
-        <v>13.9</v>
+        <v>13.64</v>
       </c>
       <c r="Q4" t="n">
-        <v>10.6</v>
+        <v>10.55</v>
       </c>
       <c r="R4" t="n">
-        <v>7.4</v>
+        <v>7.55</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>45.7</v>
+        <v>45.36</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z4" t="n">
-        <v>14.6</v>
+        <v>14.36</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.8</v>
+        <v>4.82</v>
       </c>
       <c r="AC4" t="n">
-        <v>17.6</v>
+        <v>17.18</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,70 +2356,70 @@
         <v>2</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.300000000000001</v>
+        <v>9.52</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BL4" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.55</v>
+        <v>3.67</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="BR4" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS4" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT4" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BU4" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BV4" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW4" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.36</v>
+        <v>3.28</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="CC4" t="n">
         <v>3.83</v>
@@ -2431,13 +2431,13 @@
         <v>1.35</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CI4" t="n">
         <v>2.06</v>
@@ -2449,22 +2449,22 @@
         <v>1.65</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CO4" t="n">
         <v>1.26</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="CR4" t="n">
         <v>1.4</v>
@@ -2479,43 +2479,43 @@
         <v>1.48</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DB4" t="n">
         <v>1.33</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="DD4" t="n">
         <v>3.11</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="DH4" t="n">
-        <v>93.34999999999999</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
@@ -2524,61 +2524,61 @@
         <v>2.1</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.25</v>
+        <v>4.38</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DM4" t="n">
-        <v>39.35</v>
+        <v>39.24</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.8</v>
+        <v>13.67</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.7</v>
+        <v>11.62</v>
       </c>
       <c r="DR4" t="n">
-        <v>6.95</v>
+        <v>7.05</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>43.8</v>
+        <v>43.71</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.8</v>
+        <v>11.81</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.9</v>
+        <v>7.86</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.9</v>
+        <v>17.67</v>
       </c>
       <c r="EB4" t="n">
         <v>1.31</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="5">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H6" t="n">
-        <v>85.90000000000001</v>
+        <v>88.36</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="K6" t="n">
-        <v>6.3</v>
+        <v>6.09</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="M6" t="n">
-        <v>46.3</v>
+        <v>46.18</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="O6" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="P6" t="n">
-        <v>13.7</v>
+        <v>13.64</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.3</v>
+        <v>12.73</v>
       </c>
       <c r="R6" t="n">
-        <v>5.2</v>
+        <v>5.55</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>49.6</v>
+        <v>49.73</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>15.3</v>
+        <v>14.73</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.5</v>
+        <v>5.27</v>
       </c>
       <c r="AC6" t="n">
-        <v>17.9</v>
+        <v>18.09</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AF6" t="n">
         <v>0.1</v>
@@ -3162,70 +3162,70 @@
         <v>2.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.8</v>
+        <v>4.86</v>
       </c>
       <c r="BR6" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT6" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BU6" t="n">
-        <v>15</v>
+        <v>19.05</v>
       </c>
       <c r="BV6" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BY6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BZ6" t="n">
         <v>1.92</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>1.95</v>
       </c>
       <c r="CA6" t="n">
         <v>4</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="CC6" t="n">
         <v>2.87</v>
@@ -3237,7 +3237,7 @@
         <v>1.31</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CG6" t="n">
         <v>3.28</v>
@@ -3246,7 +3246,7 @@
         <v>1.53</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.66</v>
@@ -3255,22 +3255,22 @@
         <v>1.56</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CM6" t="n">
         <v>2.27</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CO6" t="n">
         <v>1.2</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CR6" t="n">
         <v>1.35</v>
@@ -3285,10 +3285,10 @@
         <v>1.56</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CX6" t="n">
         <v>1.59</v>
@@ -3297,94 +3297,94 @@
         <v>1.98</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DB6" t="n">
         <v>1.27</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DH6" t="n">
-        <v>87.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="DI6" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.55</v>
+        <v>5.48</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DM6" t="n">
-        <v>44.1</v>
+        <v>44.14</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.7</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.05</v>
+        <v>14</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.7</v>
+        <v>12.91</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.15</v>
+        <v>6.29</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>49.3</v>
+        <v>49.38</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DX6" t="n">
-        <v>14</v>
+        <v>13.76</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.9</v>
+        <v>8.76</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.75</v>
+        <v>16.9</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
         <v>0.1</v>
@@ -3484,52 +3484,52 @@
         <v>1.6</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG7" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AI7" t="n">
-        <v>103.5</v>
+        <v>103.18</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
       <c r="AL7" t="n">
         <v>6</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AN7" t="n">
-        <v>57.3</v>
+        <v>57</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12.1</v>
+        <v>11.82</v>
       </c>
       <c r="AR7" t="n">
-        <v>13.9</v>
+        <v>13.73</v>
       </c>
       <c r="AS7" t="n">
-        <v>7</v>
+        <v>6.64</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>57.3</v>
+        <v>57.36</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BA7" t="n">
-        <v>13.1</v>
+        <v>13.36</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.300000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.8</v>
+        <v>4.55</v>
       </c>
       <c r="BD7" t="n">
-        <v>17.2</v>
+        <v>17.91</v>
       </c>
       <c r="BE7" t="n">
         <v>1.58</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.2</v>
+        <v>10.05</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="BO7" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="BQ7" t="n">
         <v>4.95</v>
       </c>
       <c r="BR7" t="n">
-        <v>100</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS7" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="BT7" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BU7" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV7" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BW7" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BX7" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BY7" t="n">
         <v>2.2</v>
@@ -3625,16 +3625,16 @@
         <v>2.22</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.01</v>
+        <v>4.04</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.16</v>
+        <v>3.01</v>
       </c>
       <c r="CD7" t="n">
-        <v>3.18</v>
+        <v>3.03</v>
       </c>
       <c r="CE7" t="n">
         <v>1.34</v>
@@ -3649,7 +3649,7 @@
         <v>1.48</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.72</v>
@@ -3658,7 +3658,7 @@
         <v>1.56</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CM7" t="n">
         <v>2.27</v>
@@ -3676,22 +3676,22 @@
         <v>2.89</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CT7" t="n">
         <v>3.14</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CX7" t="n">
         <v>1.62</v>
@@ -3712,82 +3712,82 @@
         <v>1.81</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="DH7" t="n">
-        <v>103.75</v>
+        <v>103.57</v>
       </c>
       <c r="DI7" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="DK7" t="n">
         <v>6</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="DM7" t="n">
-        <v>55.3</v>
+        <v>55.24</v>
       </c>
       <c r="DN7" t="n">
         <v>0.9</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="DP7" t="n">
-        <v>11.6</v>
+        <v>11.48</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.35</v>
+        <v>13.29</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.4</v>
+        <v>6.24</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>54.05</v>
+        <v>54.24</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX7" t="n">
-        <v>14.25</v>
+        <v>14.33</v>
       </c>
       <c r="DY7" t="n">
-        <v>9.4</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.85</v>
+        <v>4.72</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.05</v>
+        <v>17.43</v>
       </c>
       <c r="EB7" t="n">
         <v>1.64</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
         <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
         <v>0.1</v>
@@ -3887,52 +3887,52 @@
         <v>2.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG8" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.8</v>
+        <v>2.09</v>
       </c>
       <c r="AI8" t="n">
-        <v>82.40000000000001</v>
+        <v>84.45</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AN8" t="n">
-        <v>38.5</v>
+        <v>39.82</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.6</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AR8" t="n">
-        <v>15.2</v>
+        <v>14.82</v>
       </c>
       <c r="AS8" t="n">
-        <v>9</v>
+        <v>9.09</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>42</v>
+        <v>43.45</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA8" t="n">
-        <v>10.5</v>
+        <v>10.73</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.6</v>
+        <v>7.91</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="BD8" t="n">
-        <v>14.9</v>
+        <v>14.73</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.25</v>
+        <v>8.52</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL8" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.65</v>
+        <v>3.76</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.2</v>
+        <v>4.38</v>
       </c>
       <c r="BR8" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BU8" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BV8" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW8" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX8" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BY8" t="n">
         <v>3.53</v>
@@ -4028,31 +4028,31 @@
         <v>3.59</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.82</v>
+        <v>3.79</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.31</v>
+        <v>4.2</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.58</v>
+        <v>4.46</v>
       </c>
       <c r="CE8" t="n">
         <v>1.35</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.75</v>
@@ -4061,22 +4061,22 @@
         <v>1.67</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CO8" t="n">
         <v>1.26</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="CR8" t="n">
         <v>1.41</v>
@@ -4094,70 +4094,70 @@
         <v>2.09</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DA8" t="n">
         <v>1.69</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DD8" t="n">
         <v>3.15</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="DH8" t="n">
-        <v>83.95</v>
+        <v>84.95</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DM8" t="n">
-        <v>40.7</v>
+        <v>41.29</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="DP8" t="n">
         <v>9.949999999999999</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.55</v>
+        <v>14.38</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.4</v>
+        <v>7.52</v>
       </c>
       <c r="DS8" t="n">
         <v>0.05</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>43.2</v>
+        <v>43.9</v>
       </c>
       <c r="DW8" t="n">
         <v>0.05</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.6</v>
+        <v>11.67</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.65</v>
+        <v>7.81</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.95</v>
+        <v>3.86</v>
       </c>
       <c r="EA8" t="n">
-        <v>14.6</v>
+        <v>14.53</v>
       </c>
       <c r="EB8" t="n">
         <v>1.31</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="9">
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
         <v>11</v>
@@ -4212,82 +4212,82 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="G9" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="H9" t="n">
-        <v>79.56</v>
+        <v>81.2</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.22</v>
+        <v>-0.2</v>
       </c>
       <c r="J9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="K9" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="M9" t="n">
-        <v>38.56</v>
+        <v>37.6</v>
       </c>
       <c r="N9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="P9" t="n">
-        <v>11.78</v>
+        <v>11.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.78</v>
+        <v>10.6</v>
       </c>
       <c r="R9" t="n">
-        <v>7.44</v>
+        <v>7.7</v>
       </c>
       <c r="S9" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="U9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>47.22</v>
+        <v>46.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.67</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.22</v>
+        <v>6</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>16.44</v>
+        <v>17.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF9" t="n">
         <v>0.09</v>
@@ -4371,70 +4371,70 @@
         <v>1.64</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.35</v>
+        <v>3.19</v>
       </c>
       <c r="BH9" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.35</v>
+        <v>3.19</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.3</v>
+        <v>4.19</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.7</v>
+        <v>4.71</v>
       </c>
       <c r="BR9" t="n">
-        <v>95</v>
+        <v>90.48</v>
       </c>
       <c r="BS9" t="n">
-        <v>80</v>
+        <v>76.19</v>
       </c>
       <c r="BT9" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BU9" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BV9" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BW9" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BX9" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BY9" t="n">
-        <v>4.66</v>
+        <v>4.81</v>
       </c>
       <c r="BZ9" t="n">
-        <v>4.91</v>
+        <v>5.04</v>
       </c>
       <c r="CA9" t="n">
         <v>4.09</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.33</v>
+        <v>4.34</v>
       </c>
       <c r="CC9" t="n">
         <v>5.5</v>
@@ -4455,7 +4455,7 @@
         <v>1.51</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.74</v>
@@ -4467,7 +4467,7 @@
         <v>2.15</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CN9" t="n">
         <v>1.77</v>
@@ -4476,28 +4476,28 @@
         <v>1.22</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CQ9" t="n">
         <v>2.88</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CU9" t="n">
         <v>1.54</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CX9" t="n">
         <v>1.63</v>
@@ -4518,82 +4518,82 @@
         <v>1.78</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DE9" t="n">
         <v>0.05</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="DH9" t="n">
-        <v>75.15000000000001</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="DI9" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="DK9" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DM9" t="n">
-        <v>33.25</v>
+        <v>33.05</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="DP9" t="n">
-        <v>10.85</v>
+        <v>10.9</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.449999999999999</v>
+        <v>8.52</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>48.8</v>
+        <v>48.48</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX9" t="n">
-        <v>9</v>
+        <v>8.85</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.95</v>
+        <v>5.86</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.55</v>
+        <v>17</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="10">
@@ -5004,61 +5004,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="G11" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="H11" t="n">
-        <v>89.09999999999999</v>
+        <v>90.55</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J11" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="M11" t="n">
-        <v>38.4</v>
+        <v>40</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="O11" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="P11" t="n">
-        <v>11.6</v>
+        <v>11.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="R11" t="n">
-        <v>8.9</v>
+        <v>8.82</v>
       </c>
       <c r="S11" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -5070,28 +5070,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>44.6</v>
+        <v>45.45</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>11.1</v>
+        <v>11.27</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.1</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="AB11" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="AC11" t="n">
-        <v>20.8</v>
+        <v>20.64</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AF11" t="n">
         <v>0.2</v>
@@ -5175,70 +5175,70 @@
         <v>2.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="BH11" t="n">
         <v>8.949999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.75</v>
+        <v>4.81</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.2</v>
+        <v>4.14</v>
       </c>
       <c r="BR11" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>75</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BU11" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV11" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW11" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX11" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.27</v>
+        <v>4.31</v>
       </c>
       <c r="BZ11" t="n">
-        <v>4.73</v>
+        <v>4.74</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.91</v>
+        <v>3.9</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.04</v>
+        <v>4.03</v>
       </c>
       <c r="CC11" t="n">
         <v>5.49</v>
@@ -5250,13 +5250,13 @@
         <v>1.36</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI11" t="n">
         <v>1.93</v>
@@ -5265,25 +5265,25 @@
         <v>1.84</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CO11" t="n">
         <v>1.27</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="CR11" t="n">
         <v>1.4</v>
@@ -5304,67 +5304,67 @@
         <v>1.87</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="DB11" t="n">
         <v>1.32</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF11" t="n">
         <v>1.1</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="DH11" t="n">
-        <v>79.95</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ11" t="n">
         <v>2</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DM11" t="n">
-        <v>31.7</v>
+        <v>32.86</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.45</v>
+        <v>12.48</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.6</v>
+        <v>13.48</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.699999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="DS11" t="n">
         <v>0.05</v>
@@ -5376,28 +5376,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>43.45</v>
+        <v>43.95</v>
       </c>
       <c r="DW11" t="n">
         <v>0.05</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.3</v>
+        <v>10.43</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.35</v>
+        <v>7.52</v>
       </c>
       <c r="DZ11" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.6</v>
+        <v>19.57</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="12">
@@ -5810,13 +5810,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5900,139 +5900,139 @@
         <v>1.6</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="AI13" t="n">
-        <v>85.09999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="AL13" t="n">
-        <v>6</v>
+        <v>5.82</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN13" t="n">
-        <v>42</v>
+        <v>41.55</v>
       </c>
       <c r="AO13" t="n">
         <v>1</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13.9</v>
+        <v>13.64</v>
       </c>
       <c r="AR13" t="n">
-        <v>14.2</v>
+        <v>14.09</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.8</v>
+        <v>7.36</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>54.2</v>
+        <v>53.45</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="BA13" t="n">
-        <v>11.3</v>
+        <v>11.18</v>
       </c>
       <c r="BB13" t="n">
-        <v>6</v>
+        <v>6.09</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.3</v>
+        <v>5.09</v>
       </c>
       <c r="BD13" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.4</v>
+        <v>10.33</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.2</v>
+        <v>4.29</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.2</v>
+        <v>6.05</v>
       </c>
       <c r="BR13" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS13" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BT13" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BU13" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV13" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW13" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX13" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BY13" t="n">
         <v>2.05</v>
@@ -6041,55 +6041,55 @@
         <v>2.29</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.51</v>
+        <v>2.44</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="CE13" t="n">
         <v>1.33</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CK13" t="n">
         <v>1.53</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CO13" t="n">
         <v>1.23</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="CR13" t="n">
         <v>1.37</v>
@@ -6104,22 +6104,22 @@
         <v>1.48</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CX13" t="n">
         <v>1.59</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DB13" t="n">
         <v>1.3</v>
@@ -6128,49 +6128,49 @@
         <v>1.86</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="DE13" t="n">
         <v>0.05</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="DH13" t="n">
-        <v>88</v>
+        <v>88.52</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.8</v>
+        <v>5.72</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM13" t="n">
-        <v>44.5</v>
+        <v>44.15</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.15</v>
+        <v>14</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.4</v>
+        <v>13.38</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.5</v>
+        <v>6.81</v>
       </c>
       <c r="DS13" t="n">
         <v>0.05</v>
@@ -6182,28 +6182,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>55.35</v>
+        <v>54.9</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.5</v>
+        <v>12.38</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.5</v>
+        <v>7.48</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="EA13" t="n">
-        <v>17.6</v>
+        <v>17.86</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="14">
@@ -7420,13 +7420,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C17" t="n">
         <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
         <v>0.1</v>
@@ -7510,16 +7510,16 @@
         <v>1.9</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AI17" t="n">
-        <v>90.40000000000001</v>
+        <v>89.27</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
@@ -7528,121 +7528,121 @@
         <v>2</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.2</v>
+        <v>5.09</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AN17" t="n">
-        <v>38.9</v>
+        <v>39.45</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ17" t="n">
-        <v>10.6</v>
+        <v>11.18</v>
       </c>
       <c r="AR17" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.5</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="AT17" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>51.6</v>
+        <v>51.36</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BA17" t="n">
-        <v>9.800000000000001</v>
+        <v>10.18</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.3</v>
+        <v>6.91</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
       <c r="BD17" t="n">
-        <v>17.7</v>
+        <v>18</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.6</v>
+        <v>10.48</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN17" t="n">
         <v>1.9</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.2</v>
+        <v>5.24</v>
       </c>
       <c r="BR17" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT17" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BU17" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BV17" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BY17" t="n">
         <v>2.29</v>
@@ -7654,19 +7654,19 @@
         <v>3.74</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.51</v>
+        <v>3.68</v>
       </c>
       <c r="CE17" t="n">
         <v>1.32</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CG17" t="n">
         <v>3.28</v>
@@ -7690,16 +7690,16 @@
         <v>2.26</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CO17" t="n">
         <v>1.22</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CR17" t="n">
         <v>1.36</v>
@@ -7714,16 +7714,16 @@
         <v>1.53</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CW17" t="n">
         <v>1.67</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.36</v>
@@ -7735,22 +7735,22 @@
         <v>1.28</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DF17" t="n">
         <v>1.05</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="DH17" t="n">
-        <v>96.84999999999999</v>
+        <v>95.95</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
@@ -7759,61 +7759,61 @@
         <v>2.05</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.65</v>
+        <v>5.57</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DM17" t="n">
-        <v>51.7</v>
+        <v>51.38</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="DP17" t="n">
-        <v>12</v>
+        <v>12.24</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.1</v>
+        <v>12.14</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.050000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>52.2</v>
+        <v>52.05</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.25</v>
+        <v>13.28</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.6</v>
+        <v>8.81</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.65</v>
+        <v>4.47</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.05</v>
+        <v>19.14</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="18">

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="H2" t="n">
-        <v>71.7</v>
+        <v>71.73</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="M2" t="n">
-        <v>33.1</v>
+        <v>32.45</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="O2" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="P2" t="n">
-        <v>12.8</v>
+        <v>12.64</v>
       </c>
       <c r="Q2" t="n">
-        <v>11</v>
+        <v>11.45</v>
       </c>
       <c r="R2" t="n">
-        <v>8.1</v>
+        <v>8.09</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>45.4</v>
+        <v>45.91</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z2" t="n">
-        <v>11.2</v>
+        <v>11.27</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.5</v>
+        <v>6.64</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.7</v>
+        <v>4.64</v>
       </c>
       <c r="AC2" t="n">
-        <v>17.5</v>
+        <v>16.91</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>1.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.949999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL2" t="n">
         <v>0.95</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BO2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.65</v>
+        <v>3.52</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.3</v>
+        <v>5.38</v>
       </c>
       <c r="BR2" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BT2" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BU2" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV2" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW2" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX2" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.4</v>
+        <v>4.34</v>
       </c>
       <c r="CC2" t="n">
         <v>8.26</v>
@@ -1622,16 +1622,16 @@
         <v>8.68</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CI2" t="n">
         <v>1.83</v>
@@ -1640,10 +1640,10 @@
         <v>1.92</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CM2" t="n">
         <v>2.11</v>
@@ -1655,10 +1655,10 @@
         <v>1.31</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.47</v>
+        <v>3.52</v>
       </c>
       <c r="CR2" t="n">
         <v>1.44</v>
@@ -1676,16 +1676,16 @@
         <v>1.9</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DA2" t="n">
         <v>1.74</v>
@@ -1694,7 +1694,7 @@
         <v>1.36</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="DD2" t="n">
         <v>3.14</v>
@@ -1703,76 +1703,76 @@
         <v>0.05</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="DH2" t="n">
-        <v>71.34999999999999</v>
+        <v>71.38</v>
       </c>
       <c r="DI2" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM2" t="n">
-        <v>31</v>
+        <v>30.76</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DP2" t="n">
         <v>11.05</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.3</v>
+        <v>11.52</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.6</v>
+        <v>8.57</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>42.6</v>
+        <v>43</v>
       </c>
       <c r="DW2" t="n">
         <v>0.05</v>
       </c>
       <c r="DX2" t="n">
-        <v>9.4</v>
+        <v>9.52</v>
       </c>
       <c r="DY2" t="n">
-        <v>5.85</v>
+        <v>5.95</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.55</v>
+        <v>3.57</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.65</v>
+        <v>16.38</v>
       </c>
       <c r="EB2" t="n">
         <v>1.07</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
         <v>10</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>4.27</v>
       </c>
       <c r="H3" t="n">
-        <v>87.59999999999999</v>
+        <v>90.27</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="K3" t="n">
-        <v>5.4</v>
+        <v>5.55</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="M3" t="n">
-        <v>44.5</v>
+        <v>45.91</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="P3" t="n">
-        <v>13.6</v>
+        <v>13.09</v>
       </c>
       <c r="Q3" t="n">
-        <v>14.1</v>
+        <v>13.82</v>
       </c>
       <c r="R3" t="n">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>41.9</v>
+        <v>42.55</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.5</v>
+        <v>11.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>8</v>
+        <v>8.18</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="AC3" t="n">
-        <v>17.9</v>
+        <v>18.18</v>
       </c>
       <c r="AD3" t="n">
         <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AF3" t="n">
         <v>0.1</v>
@@ -1953,70 +1953,70 @@
         <v>2.3</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.550000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.6</v>
+        <v>5.71</v>
       </c>
       <c r="BR3" t="n">
-        <v>90</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS3" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BT3" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BU3" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV3" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW3" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX3" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.91</v>
+        <v>3.78</v>
       </c>
       <c r="BZ3" t="n">
-        <v>4.22</v>
+        <v>4.06</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.91</v>
+        <v>3.88</v>
       </c>
       <c r="CC3" t="n">
         <v>5.23</v>
@@ -2025,13 +2025,13 @@
         <v>5.44</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="CH3" t="n">
         <v>1.44</v>
@@ -2046,28 +2046,28 @@
         <v>1.58</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CN3" t="n">
         <v>1.8</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="CR3" t="n">
         <v>1.41</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="CT3" t="n">
         <v>2.98</v>
@@ -2097,85 +2097,85 @@
         <v>1.34</v>
       </c>
       <c r="DC3" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="DE3" t="n">
         <v>0.05</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.95</v>
+        <v>3.14</v>
       </c>
       <c r="DH3" t="n">
-        <v>88.3</v>
+        <v>89.67</v>
       </c>
       <c r="DI3" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM3" t="n">
-        <v>40.8</v>
+        <v>41.71</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.8</v>
+        <v>13.52</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.95</v>
+        <v>13.81</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.95</v>
+        <v>6.85</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>44.35</v>
+        <v>44.57</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.6</v>
+        <v>10.67</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.3</v>
+        <v>7.43</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="EB3" t="n">
         <v>1.2</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="4">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
@@ -2600,82 +2600,82 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="H5" t="n">
-        <v>96.90000000000001</v>
+        <v>96.09</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="K5" t="n">
-        <v>5.3</v>
+        <v>5.64</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="M5" t="n">
-        <v>50.5</v>
+        <v>50.27</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="O5" t="n">
-        <v>2.7</v>
+        <v>3.09</v>
       </c>
       <c r="P5" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="R5" t="n">
-        <v>6.4</v>
+        <v>6.18</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>49.6</v>
+        <v>49.73</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.699999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.1</v>
+        <v>4.36</v>
       </c>
       <c r="AC5" t="n">
-        <v>21.8</v>
+        <v>21.55</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>2.1</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.25</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="BL5" t="n">
         <v>0.95</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.35</v>
+        <v>5.29</v>
       </c>
       <c r="BR5" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BS5" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BT5" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BU5" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV5" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW5" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX5" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.93</v>
+        <v>3.02</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.24</v>
+        <v>3.34</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.09</v>
+        <v>4.06</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.1</v>
+        <v>4.08</v>
       </c>
       <c r="CC5" t="n">
         <v>6.58</v>
@@ -2834,31 +2834,31 @@
         <v>1.35</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CH5" t="n">
         <v>1.45</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CK5" t="n">
         <v>1.65</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CO5" t="n">
         <v>1.26</v>
@@ -2888,67 +2888,67 @@
         <v>1.88</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DC5" t="n">
         <v>1.94</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DH5" t="n">
-        <v>87.65000000000001</v>
+        <v>87.67</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ5" t="n">
         <v>1.85</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.55</v>
+        <v>4.76</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="DM5" t="n">
-        <v>42.7</v>
+        <v>42.95</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="DP5" t="n">
-        <v>13.65</v>
+        <v>13.71</v>
       </c>
       <c r="DQ5" t="n">
-        <v>13.55</v>
+        <v>13.48</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.7</v>
+        <v>7.52</v>
       </c>
       <c r="DS5" t="n">
         <v>0.05</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>45.95</v>
+        <v>46.19</v>
       </c>
       <c r="DW5" t="n">
         <v>0.05</v>
       </c>
       <c r="DX5" t="n">
-        <v>11</v>
+        <v>11.19</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.4</v>
+        <v>7.43</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.6</v>
+        <v>3.76</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.8</v>
+        <v>18.81</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="6">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
         <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
         <v>0.18</v>
@@ -4693,139 +4693,139 @@
         <v>1.64</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="AI10" t="n">
-        <v>109.11</v>
+        <v>107.9</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.78</v>
+        <v>4.9</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AN10" t="n">
-        <v>52.44</v>
+        <v>50.3</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AP10" t="n">
         <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.89</v>
+        <v>14.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>10.67</v>
+        <v>10.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.78</v>
+        <v>7.7</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>53.89</v>
+        <v>54.1</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA10" t="n">
-        <v>11.67</v>
+        <v>11.5</v>
       </c>
       <c r="BB10" t="n">
         <v>8</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>20</v>
+        <v>20.3</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.85</v>
+        <v>9.1</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BP10" t="n">
-        <v>4</v>
+        <v>4.19</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.7</v>
+        <v>3.81</v>
       </c>
       <c r="BR10" t="n">
-        <v>95</v>
+        <v>90.48</v>
       </c>
       <c r="BS10" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BT10" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BU10" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BV10" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BW10" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX10" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BY10" t="n">
         <v>2</v>
@@ -4834,16 +4834,16 @@
         <v>2.03</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.27</v>
+        <v>4.26</v>
       </c>
       <c r="CC10" t="n">
         <v>2.04</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CE10" t="n">
         <v>1.26</v>
@@ -4852,28 +4852,28 @@
         <v>2.27</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.62</v>
+        <v>3.63</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CM10" t="n">
         <v>2.29</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CO10" t="n">
         <v>1.15</v>
@@ -4888,7 +4888,7 @@
         <v>1.35</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CT10" t="n">
         <v>3.26</v>
@@ -4897,104 +4897,104 @@
         <v>1.66</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DB10" t="inlineStr"/>
       <c r="DC10" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="DH10" t="n">
-        <v>106.8</v>
+        <v>106.33</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.7</v>
+        <v>4.76</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DM10" t="n">
-        <v>50.3</v>
+        <v>49.38</v>
       </c>
       <c r="DN10" t="n">
         <v>0.95</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.6</v>
+        <v>13.48</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.25</v>
+        <v>11.19</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.9</v>
+        <v>7.33</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>53.3</v>
+        <v>53.43</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.5</v>
+        <v>12.38</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.300000000000001</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="EA10" t="n">
-        <v>20</v>
+        <v>20.14</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="11">
@@ -5407,88 +5407,88 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
         <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="G12" t="n">
         <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>70</v>
+        <v>72.27</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J12" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="K12" t="n">
-        <v>5.2</v>
+        <v>5.45</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="M12" t="n">
-        <v>32.1</v>
+        <v>32.55</v>
       </c>
       <c r="N12" t="n">
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="P12" t="n">
-        <v>12</v>
+        <v>11.82</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.8</v>
+        <v>12.64</v>
       </c>
       <c r="R12" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>48.6</v>
+        <v>48.18</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z12" t="n">
-        <v>13.4</v>
+        <v>13.36</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.2</v>
+        <v>5.09</v>
       </c>
       <c r="AC12" t="n">
-        <v>14.9</v>
+        <v>15.82</v>
       </c>
       <c r="AD12" t="n">
         <v>1.3</v>
@@ -5578,67 +5578,67 @@
         <v>2.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.55</v>
+        <v>10.71</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.45</v>
+        <v>4.62</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.35</v>
+        <v>5.38</v>
       </c>
       <c r="BR12" t="n">
-        <v>100</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS12" t="n">
-        <v>80</v>
+        <v>76.19</v>
       </c>
       <c r="BT12" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BU12" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BV12" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BW12" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX12" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="CB12" t="n">
         <v>3.95</v>
@@ -5653,19 +5653,19 @@
         <v>1.32</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CK12" t="n">
         <v>1.49</v>
@@ -5683,124 +5683,124 @@
         <v>1.21</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="CR12" t="n">
         <v>1.36</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="CT12" t="n">
         <v>3.22</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CX12" t="n">
         <v>1.56</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DB12" t="n">
         <v>1.29</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="DH12" t="n">
-        <v>79.75</v>
+        <v>80.47</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.95</v>
+        <v>5.09</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DM12" t="n">
-        <v>35.2</v>
+        <v>35.29</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.9</v>
+        <v>12.76</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.55</v>
+        <v>12.48</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.9</v>
+        <v>6.81</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48.45</v>
+        <v>48.24</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.7</v>
+        <v>11.76</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.4</v>
+        <v>7.47</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.3</v>
+        <v>4.29</v>
       </c>
       <c r="EA12" t="n">
-        <v>16.35</v>
+        <v>16.76</v>
       </c>
       <c r="EB12" t="n">
         <v>1.23</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="13">
@@ -6213,13 +6213,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" t="n">
         <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
         <v>0.2</v>
@@ -6306,136 +6306,136 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="AI14" t="n">
-        <v>100.1</v>
+        <v>99.64</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.2</v>
+        <v>4.91</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN14" t="n">
-        <v>44.2</v>
+        <v>43</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11.1</v>
+        <v>11.73</v>
       </c>
       <c r="AR14" t="n">
-        <v>10.7</v>
+        <v>10.73</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.4</v>
+        <v>7.09</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.1</v>
+        <v>1.45</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>57.5</v>
+        <v>56.09</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA14" t="n">
-        <v>14.9</v>
+        <v>14.36</v>
       </c>
       <c r="BB14" t="n">
-        <v>9.4</v>
+        <v>9.09</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.5</v>
+        <v>5.27</v>
       </c>
       <c r="BD14" t="n">
-        <v>15.9</v>
+        <v>15.73</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.65</v>
+        <v>8.57</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BN14" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.85</v>
+        <v>4.81</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT14" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BU14" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BV14" t="n">
-        <v>20</v>
+        <v>23.81</v>
       </c>
       <c r="BW14" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BX14" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BY14" t="n">
         <v>1.77</v>
@@ -6444,31 +6444,31 @@
         <v>1.81</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.25</v>
+        <v>4.28</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="CC14" t="n">
-        <v>1.98</v>
+        <v>2.33</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.12</v>
+        <v>2.52</v>
       </c>
       <c r="CE14" t="n">
         <v>1.3</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.71</v>
@@ -6477,133 +6477,133 @@
         <v>1.64</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CN14" t="n">
         <v>1.72</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CR14" t="n">
         <v>1.35</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="CT14" t="n">
         <v>3.28</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CX14" t="n">
         <v>1.65</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.22</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DB14" t="n">
         <v>1.27</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="DE14" t="n">
         <v>0.1</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="DH14" t="n">
-        <v>106.65</v>
+        <v>106.1</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.05</v>
+        <v>4.91</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM14" t="n">
-        <v>48.6</v>
+        <v>47.76</v>
       </c>
       <c r="DN14" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.35</v>
+        <v>12.62</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.65</v>
+        <v>10.67</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>59.1</v>
+        <v>58.29</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.55</v>
+        <v>14.28</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.699999999999999</v>
+        <v>8.57</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.85</v>
+        <v>5.71</v>
       </c>
       <c r="EA14" t="n">
-        <v>15.1</v>
+        <v>15.05</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="EC14" t="n">
         <v>1.95</v>
@@ -6616,94 +6616,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
         <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>4.44</v>
+        <v>4.2</v>
       </c>
       <c r="H15" t="n">
-        <v>145</v>
+        <v>140.1</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="K15" t="n">
-        <v>6.78</v>
+        <v>6.6</v>
       </c>
       <c r="L15" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="M15" t="n">
-        <v>75.78</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="O15" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="P15" t="n">
-        <v>10.11</v>
+        <v>10.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>7.56</v>
+        <v>8.6</v>
       </c>
       <c r="R15" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="S15" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="U15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>69.78</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.33</v>
+        <v>20.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>12.78</v>
+        <v>13</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.56</v>
+        <v>7.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>18.11</v>
+        <v>17.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AF15" t="n">
         <v>0.18</v>
@@ -6787,70 +6787,70 @@
         <v>1</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL15" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BP15" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT15" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BU15" t="n">
-        <v>25</v>
+        <v>28.57</v>
       </c>
       <c r="BV15" t="n">
-        <v>25</v>
+        <v>28.57</v>
       </c>
       <c r="BW15" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX15" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="CA15" t="n">
-        <v>6.01</v>
+        <v>5.95</v>
       </c>
       <c r="CB15" t="n">
-        <v>6.48</v>
+        <v>6.42</v>
       </c>
       <c r="CC15" t="n">
         <v>1.47</v>
@@ -6859,31 +6859,31 @@
         <v>1.52</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CF15" t="n">
         <v>2.1</v>
       </c>
       <c r="CG15" t="n">
-        <v>4.03</v>
+        <v>4.02</v>
       </c>
       <c r="CH15" t="n">
         <v>1.75</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CN15" t="n">
         <v>1.83</v>
@@ -6901,7 +6901,7 @@
         <v>1.34</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CT15" t="n">
         <v>3.34</v>
@@ -6910,16 +6910,16 @@
         <v>1.79</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CX15" t="n">
         <v>1.56</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.39</v>
@@ -6929,85 +6929,85 @@
       </c>
       <c r="DB15" t="inlineStr"/>
       <c r="DC15" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="DD15" t="n">
         <v>2.19</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="DH15" t="n">
-        <v>135</v>
+        <v>133.14</v>
       </c>
       <c r="DI15" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="DK15" t="n">
-        <v>6.2</v>
+        <v>6.14</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="DM15" t="n">
-        <v>67.90000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="DP15" t="n">
-        <v>9.949999999999999</v>
+        <v>10</v>
       </c>
       <c r="DQ15" t="n">
-        <v>8.449999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="DR15" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>69.15000000000001</v>
+        <v>68.62</v>
       </c>
       <c r="DW15" t="n">
         <v>0.05</v>
       </c>
       <c r="DX15" t="n">
-        <v>17.25</v>
+        <v>17.48</v>
       </c>
       <c r="DY15" t="n">
-        <v>10.5</v>
+        <v>10.72</v>
       </c>
       <c r="DZ15" t="n">
-        <v>6.75</v>
+        <v>6.76</v>
       </c>
       <c r="EA15" t="n">
-        <v>17.1</v>
+        <v>16.95</v>
       </c>
       <c r="EB15" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="16">
@@ -7017,13 +7017,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" t="n">
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7107,139 +7107,139 @@
         <v>2.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG16" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AI16" t="n">
-        <v>82.5</v>
+        <v>80.81999999999999</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AN16" t="n">
-        <v>31.3</v>
+        <v>31</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.7</v>
+        <v>10.73</v>
       </c>
       <c r="AR16" t="n">
-        <v>10.9</v>
+        <v>10.64</v>
       </c>
       <c r="AS16" t="n">
         <v>9</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>50.5</v>
+        <v>50.55</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.5</v>
+        <v>6.18</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="BD16" t="n">
-        <v>17.8</v>
+        <v>17.36</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="BG16" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="BH16" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="BI16" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BR16" t="n">
-        <v>90</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>75</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT16" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BU16" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV16" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BW16" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BX16" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BY16" t="n">
         <v>2.2</v>
@@ -7248,31 +7248,31 @@
         <v>2.39</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.84</v>
+        <v>3.81</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.02</v>
+        <v>3.98</v>
       </c>
       <c r="CC16" t="n">
-        <v>5.62</v>
+        <v>5.35</v>
       </c>
       <c r="CD16" t="n">
-        <v>5.19</v>
+        <v>5</v>
       </c>
       <c r="CE16" t="n">
         <v>1.33</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.72</v>
@@ -7281,34 +7281,34 @@
         <v>1.61</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CM16" t="n">
         <v>2.18</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="CR16" t="n">
         <v>1.38</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CV16" t="n">
         <v>2.19</v>
@@ -7332,85 +7332,85 @@
         <v>1.31</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="DE16" t="n">
         <v>0.05</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="DG16" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DH16" t="n">
-        <v>91.90000000000001</v>
+        <v>90.56999999999999</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DM16" t="n">
-        <v>40.25</v>
+        <v>39.67</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.35</v>
+        <v>11.33</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.45</v>
+        <v>11.29</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.7</v>
+        <v>7.76</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>54.15</v>
+        <v>54</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.6</v>
+        <v>11.38</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.15</v>
+        <v>7.9</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.95</v>
+        <v>16.76</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="17">
@@ -7823,13 +7823,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" t="n">
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7916,136 +7916,136 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AI18" t="n">
-        <v>94</v>
+        <v>93.09</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK18" t="n">
         <v>3</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN18" t="n">
-        <v>40.1</v>
+        <v>40.36</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12.5</v>
+        <v>12.45</v>
       </c>
       <c r="AR18" t="n">
-        <v>13.7</v>
+        <v>13.82</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.5</v>
+        <v>7.64</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>52.3</v>
+        <v>52</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="BA18" t="n">
-        <v>10.1</v>
+        <v>10.09</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.6</v>
+        <v>6.64</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BD18" t="n">
-        <v>16.4</v>
+        <v>17.27</v>
       </c>
       <c r="BE18" t="n">
         <v>1.18</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="BG18" t="n">
         <v>2.9</v>
       </c>
       <c r="BH18" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BI18" t="n">
         <v>2.9</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="BQ18" t="n">
         <v>3.95</v>
       </c>
       <c r="BR18" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS18" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT18" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BU18" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV18" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BW18" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX18" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BY18" t="n">
         <v>2.32</v>
@@ -8054,55 +8054,55 @@
         <v>2.36</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.88</v>
+        <v>3.87</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.68</v>
+        <v>3.53</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.79</v>
+        <v>3.62</v>
       </c>
       <c r="CE18" t="n">
         <v>1.33</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CH18" t="n">
         <v>1.49</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CO18" t="n">
         <v>1.22</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CR18" t="n">
         <v>1.37</v>
@@ -8117,7 +8117,7 @@
         <v>1.51</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CW18" t="n">
         <v>1.73</v>
@@ -8138,85 +8138,85 @@
         <v>1.3</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="DG18" t="n">
         <v>2.05</v>
       </c>
       <c r="DH18" t="n">
-        <v>98.25</v>
+        <v>97.56999999999999</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.85</v>
+        <v>3.81</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DM18" t="n">
-        <v>42.45</v>
+        <v>42.47</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="DP18" t="n">
-        <v>11.35</v>
+        <v>11.38</v>
       </c>
       <c r="DQ18" t="n">
-        <v>12.85</v>
+        <v>12.95</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.25</v>
+        <v>7.34</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>51.6</v>
+        <v>51.48</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.2</v>
+        <v>11.14</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.8</v>
+        <v>6.81</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="EA18" t="n">
-        <v>15.3</v>
+        <v>15.81</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="EC18" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="19">
@@ -8226,13 +8226,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C19" t="n">
         <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
         <v>0.27</v>
@@ -8319,136 +8319,136 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AI19" t="n">
-        <v>85.22</v>
+        <v>88</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="AL19" t="n">
-        <v>3.89</v>
+        <v>4</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN19" t="n">
-        <v>36.11</v>
+        <v>38.6</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>15.11</v>
+        <v>15.2</v>
       </c>
       <c r="AR19" t="n">
-        <v>11.33</v>
+        <v>11.3</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.78</v>
+        <v>7.6</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>40.33</v>
+        <v>41.2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA19" t="n">
-        <v>9.220000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="BB19" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>15.44</v>
+        <v>16.1</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.45</v>
+        <v>4.29</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BR19" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS19" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BT19" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BU19" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV19" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW19" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX19" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BY19" t="n">
         <v>2.52</v>
@@ -8457,43 +8457,43 @@
         <v>2.61</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.45</v>
+        <v>3.29</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.51</v>
+        <v>3.36</v>
       </c>
       <c r="CE19" t="n">
         <v>1.38</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CN19" t="n">
         <v>1.75</v>
@@ -8502,10 +8502,10 @@
         <v>1.3</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="CR19" t="n">
         <v>1.43</v>
@@ -8520,19 +8520,19 @@
         <v>1.41</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DA19" t="n">
         <v>1.75</v>
@@ -8541,85 +8541,85 @@
         <v>1.35</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DD19" t="n">
         <v>3.39</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DG19" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="DH19" t="n">
-        <v>84.40000000000001</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.45</v>
+        <v>4.48</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM19" t="n">
-        <v>40.65</v>
+        <v>41.62</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.3</v>
+        <v>14.38</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.1</v>
+        <v>12.05</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.85</v>
+        <v>6.81</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>41.2</v>
+        <v>41.57</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.25</v>
+        <v>12.24</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.1</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.15</v>
+        <v>4.19</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.45</v>
+        <v>16.71</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="n">
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
         <v>0.27</v>
@@ -2278,136 +2278,136 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH4" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AI4" t="n">
-        <v>84.3</v>
+        <v>82.55</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN4" t="n">
-        <v>39.1</v>
+        <v>39</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13.7</v>
+        <v>13.55</v>
       </c>
       <c r="AR4" t="n">
-        <v>12.8</v>
+        <v>12.18</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AT4" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>41.9</v>
+        <v>40.82</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA4" t="n">
-        <v>9</v>
+        <v>9.18</v>
       </c>
       <c r="BB4" t="n">
-        <v>6</v>
+        <v>6.09</v>
       </c>
       <c r="BC4" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="BD4" t="n">
-        <v>18.2</v>
+        <v>18.55</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="BF4" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.52</v>
+        <v>9.73</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BL4" t="n">
         <v>1.05</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.67</v>
+        <v>3.82</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.67</v>
+        <v>4.77</v>
       </c>
       <c r="BR4" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS4" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BU4" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BV4" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX4" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
         <v>2.9</v>
@@ -2416,22 +2416,22 @@
         <v>3.28</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.58</v>
+        <v>3.61</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.83</v>
+        <v>3.98</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.84</v>
+        <v>4.03</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CG4" t="n">
         <v>3.07</v>
@@ -2440,10 +2440,10 @@
         <v>1.45</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CK4" t="n">
         <v>1.65</v>
@@ -2452,10 +2452,10 @@
         <v>2.15</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CO4" t="n">
         <v>1.26</v>
@@ -2464,7 +2464,7 @@
         <v>1.87</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CR4" t="n">
         <v>1.4</v>
@@ -2479,10 +2479,10 @@
         <v>1.48</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CX4" t="n">
         <v>1.68</v>
@@ -2500,85 +2500,85 @@
         <v>1.33</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="DE4" t="n">
         <v>0.14</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="DH4" t="n">
-        <v>93.70999999999999</v>
+        <v>92.41</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.38</v>
+        <v>4.23</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM4" t="n">
-        <v>39.24</v>
+        <v>39.18</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.67</v>
+        <v>13.6</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.62</v>
+        <v>11.36</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.05</v>
+        <v>7.28</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>43.71</v>
+        <v>43.09</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.81</v>
+        <v>11.77</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.86</v>
+        <v>7.82</v>
       </c>
       <c r="DZ4" t="n">
         <v>3.95</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.67</v>
+        <v>17.86</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="5">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
         <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
         <v>0.09</v>
@@ -3081,139 +3081,139 @@
         <v>1.64</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AI6" t="n">
-        <v>89.5</v>
+        <v>89.27</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.8</v>
+        <v>4.82</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN6" t="n">
-        <v>41.9</v>
+        <v>40.91</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="AQ6" t="n">
-        <v>14.4</v>
+        <v>13.91</v>
       </c>
       <c r="AR6" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.1</v>
+        <v>6.91</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>49</v>
+        <v>48.36</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA6" t="n">
-        <v>12.7</v>
+        <v>13.09</v>
       </c>
       <c r="BB6" t="n">
-        <v>8</v>
+        <v>8.27</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.7</v>
+        <v>4.82</v>
       </c>
       <c r="BD6" t="n">
-        <v>15.6</v>
+        <v>16.18</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.57</v>
+        <v>2.68</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.710000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.57</v>
+        <v>2.68</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="BP6" t="n">
         <v>4</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.86</v>
+        <v>4.82</v>
       </c>
       <c r="BR6" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS6" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT6" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BU6" t="n">
-        <v>19.05</v>
+        <v>22.73</v>
       </c>
       <c r="BV6" t="n">
-        <v>4.76</v>
+        <v>9.09</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BY6" t="n">
         <v>1.9</v>
@@ -3222,37 +3222,37 @@
         <v>1.92</v>
       </c>
       <c r="CA6" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="CB6" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="CE6" t="n">
         <v>1.31</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="CH6" t="n">
         <v>1.53</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.66</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CL6" t="n">
         <v>2.02</v>
@@ -3261,16 +3261,16 @@
         <v>2.27</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CO6" t="n">
         <v>1.2</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="CR6" t="n">
         <v>1.35</v>
@@ -3285,10 +3285,10 @@
         <v>1.56</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CX6" t="n">
         <v>1.59</v>
@@ -3309,82 +3309,82 @@
         <v>1.73</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="DE6" t="n">
         <v>0.09</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="DH6" t="n">
-        <v>88.90000000000001</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.48</v>
+        <v>5.45</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM6" t="n">
-        <v>44.14</v>
+        <v>43.54</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="DP6" t="n">
-        <v>14</v>
+        <v>13.78</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.91</v>
+        <v>12.86</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.29</v>
+        <v>6.23</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>49.38</v>
+        <v>49.04</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.76</v>
+        <v>13.91</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.76</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.9</v>
+        <v>17.14</v>
       </c>
       <c r="EB6" t="n">
         <v>1.54</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
         <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>104</v>
+        <v>108.27</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>6.64</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="M7" t="n">
-        <v>53.3</v>
+        <v>56</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="P7" t="n">
-        <v>11.1</v>
+        <v>10.64</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.8</v>
+        <v>12.73</v>
       </c>
       <c r="R7" t="n">
-        <v>5.8</v>
+        <v>5.45</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T7" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>50.8</v>
+        <v>52.55</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z7" t="n">
-        <v>15.4</v>
+        <v>15.82</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.5</v>
+        <v>10.91</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.9</v>
+        <v>4.91</v>
       </c>
       <c r="AC7" t="n">
-        <v>16.9</v>
+        <v>17.27</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AF7" t="n">
         <v>0.18</v>
@@ -3565,67 +3565,67 @@
         <v>2.55</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.05</v>
+        <v>10.23</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BM7" t="n">
         <v>1</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.1</v>
+        <v>5.18</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.95</v>
+        <v>5.05</v>
       </c>
       <c r="BR7" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS7" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT7" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BU7" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV7" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BW7" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BX7" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.89</v>
+        <v>3.91</v>
       </c>
       <c r="CB7" t="n">
         <v>4.04</v>
@@ -3640,7 +3640,7 @@
         <v>1.34</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CG7" t="n">
         <v>3.13</v>
@@ -3649,16 +3649,16 @@
         <v>1.48</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CK7" t="n">
         <v>1.56</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CM7" t="n">
         <v>2.27</v>
@@ -3667,13 +3667,13 @@
         <v>1.81</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CP7" t="n">
         <v>1.79</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="CR7" t="n">
         <v>1.37</v>
@@ -3688,10 +3688,10 @@
         <v>1.5</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CX7" t="n">
         <v>1.62</v>
@@ -3709,52 +3709,52 @@
         <v>1.29</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="DH7" t="n">
-        <v>103.57</v>
+        <v>105.72</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="DK7" t="n">
-        <v>6</v>
+        <v>6.32</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="DM7" t="n">
-        <v>55.24</v>
+        <v>56.5</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.14</v>
+        <v>3.32</v>
       </c>
       <c r="DP7" t="n">
-        <v>11.48</v>
+        <v>11.23</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.29</v>
+        <v>13.23</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.24</v>
+        <v>6.05</v>
       </c>
       <c r="DS7" t="n">
         <v>0.14</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>54.24</v>
+        <v>54.96</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DX7" t="n">
-        <v>14.33</v>
+        <v>14.59</v>
       </c>
       <c r="DY7" t="n">
-        <v>9.619999999999999</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.72</v>
+        <v>4.73</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.43</v>
+        <v>17.59</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F10" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="G10" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="H10" t="n">
-        <v>104.91</v>
+        <v>104.92</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J10" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="K10" t="n">
-        <v>4.64</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="M10" t="n">
-        <v>48.55</v>
+        <v>48</v>
       </c>
       <c r="N10" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="O10" t="n">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="P10" t="n">
-        <v>12.55</v>
+        <v>12.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.73</v>
+        <v>11.42</v>
       </c>
       <c r="R10" t="n">
-        <v>7</v>
+        <v>6.92</v>
       </c>
       <c r="S10" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="U10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>52.82</v>
+        <v>52.33</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.18</v>
+        <v>13.08</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.550000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.64</v>
+        <v>4.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>20</v>
+        <v>20.08</v>
       </c>
       <c r="AD10" t="n">
         <v>1.51</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AF10" t="n">
         <v>0.1</v>
@@ -4774,70 +4774,70 @@
         <v>3</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.1</v>
+        <v>9.23</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BN10" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.19</v>
+        <v>4.32</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.81</v>
+        <v>3.86</v>
       </c>
       <c r="BR10" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS10" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BT10" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BU10" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BV10" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BW10" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX10" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BY10" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.23</v>
+        <v>4.25</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.26</v>
+        <v>4.29</v>
       </c>
       <c r="CC10" t="n">
         <v>2.04</v>
@@ -4852,13 +4852,13 @@
         <v>2.27</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.63</v>
+        <v>3.64</v>
       </c>
       <c r="CH10" t="n">
         <v>1.62</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.56</v>
@@ -4897,10 +4897,10 @@
         <v>1.66</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CX10" t="n">
         <v>1.57</v>
@@ -4925,76 +4925,76 @@
         <v>0.14</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="DG10" t="n">
         <v>1.91</v>
       </c>
       <c r="DH10" t="n">
-        <v>106.33</v>
+        <v>106.27</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.71</v>
+        <v>2.82</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.76</v>
+        <v>4.95</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="DM10" t="n">
-        <v>49.38</v>
+        <v>49.05</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.19</v>
+        <v>2.41</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.48</v>
+        <v>13.55</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.19</v>
+        <v>11.05</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.33</v>
+        <v>7.27</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>53.43</v>
+        <v>53.13</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.38</v>
+        <v>12.36</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.289999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.1</v>
+        <v>4.18</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.14</v>
+        <v>20.18</v>
       </c>
       <c r="EB10" t="n">
         <v>1.43</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="11">
@@ -5004,13 +5004,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
         <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
         <v>0.09</v>
@@ -5094,139 +5094,139 @@
         <v>1.55</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AI11" t="n">
-        <v>70.8</v>
+        <v>75</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN11" t="n">
-        <v>25</v>
+        <v>28.18</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AP11" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.3</v>
+        <v>12.82</v>
       </c>
       <c r="AR11" t="n">
-        <v>14</v>
+        <v>14.09</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.5</v>
+        <v>8.09</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>42.3</v>
+        <v>43.27</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.5</v>
+        <v>9.82</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="BD11" t="n">
-        <v>18.4</v>
+        <v>18</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.67</v>
+        <v>2.73</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.949999999999999</v>
+        <v>9.09</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.67</v>
+        <v>2.73</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.81</v>
+        <v>4.91</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.14</v>
+        <v>4.18</v>
       </c>
       <c r="BR11" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS11" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT11" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>23.81</v>
+        <v>27.27</v>
       </c>
       <c r="BV11" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX11" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BY11" t="n">
         <v>4.31</v>
@@ -5235,40 +5235,40 @@
         <v>4.74</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.03</v>
+        <v>4.07</v>
       </c>
       <c r="CC11" t="n">
-        <v>5.49</v>
+        <v>5.59</v>
       </c>
       <c r="CD11" t="n">
-        <v>5.83</v>
+        <v>5.91</v>
       </c>
       <c r="CE11" t="n">
         <v>1.36</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CK11" t="n">
         <v>1.53</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CM11" t="n">
         <v>2.37</v>
@@ -5277,31 +5277,31 @@
         <v>1.85</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="CR11" t="n">
         <v>1.4</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="CT11" t="n">
         <v>3.03</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CV11" t="n">
         <v>2.02</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CX11" t="n">
         <v>1.57</v>
@@ -5325,76 +5325,76 @@
         <v>3.14</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="DH11" t="n">
-        <v>81.15000000000001</v>
+        <v>82.78</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ11" t="n">
         <v>2</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DM11" t="n">
-        <v>32.86</v>
+        <v>34.09</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.48</v>
+        <v>12.28</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.48</v>
+        <v>13.54</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.67</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>43.95</v>
+        <v>44.36</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.43</v>
+        <v>10.54</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.52</v>
+        <v>7.68</v>
       </c>
       <c r="DZ11" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.57</v>
+        <v>19.32</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="EC11" t="n">
         <v>1.91</v>
@@ -6213,94 +6213,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
         <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="G14" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="H14" t="n">
-        <v>113.2</v>
+        <v>110.09</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="K14" t="n">
-        <v>4.9</v>
+        <v>4.91</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M14" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="P14" t="n">
-        <v>13.6</v>
+        <v>13.36</v>
       </c>
       <c r="Q14" t="n">
-        <v>10.6</v>
+        <v>10.55</v>
       </c>
       <c r="R14" t="n">
-        <v>4.6</v>
+        <v>5.18</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="T14" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>60.7</v>
+        <v>59.18</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z14" t="n">
-        <v>14.2</v>
+        <v>13.82</v>
       </c>
       <c r="AA14" t="n">
-        <v>8</v>
+        <v>7.64</v>
       </c>
       <c r="AB14" t="n">
-        <v>6.2</v>
+        <v>6.18</v>
       </c>
       <c r="AC14" t="n">
-        <v>14.3</v>
+        <v>14.64</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6384,70 +6384,70 @@
         <v>2.27</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.57</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.76</v>
+        <v>3.68</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.81</v>
+        <v>4.91</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT14" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BU14" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BV14" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BW14" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BX14" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.28</v>
+        <v>4.26</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="CC14" t="n">
         <v>2.33</v>
@@ -6471,16 +6471,16 @@
         <v>2.13</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CK14" t="n">
         <v>1.64</v>
       </c>
       <c r="CL14" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="CM14" t="n">
         <v>2.13</v>
-      </c>
-      <c r="CM14" t="n">
-        <v>2.14</v>
       </c>
       <c r="CN14" t="n">
         <v>1.72</v>
@@ -6507,22 +6507,22 @@
         <v>1.56</v>
       </c>
       <c r="CV14" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="CZ14" t="n">
         <v>2.21</v>
       </c>
-      <c r="CW14" t="n">
+      <c r="DA14" t="n">
         <v>1.75</v>
-      </c>
-      <c r="CX14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="CY14" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="CZ14" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="DA14" t="n">
-        <v>1.76</v>
       </c>
       <c r="DB14" t="n">
         <v>1.27</v>
@@ -6534,79 +6534,79 @@
         <v>2.69</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="DG14" t="n">
         <v>2.86</v>
       </c>
       <c r="DH14" t="n">
-        <v>106.1</v>
+        <v>104.86</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.29</v>
+        <v>2.37</v>
       </c>
       <c r="DK14" t="n">
         <v>4.91</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM14" t="n">
-        <v>47.76</v>
+        <v>47.5</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.62</v>
+        <v>12.54</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.67</v>
+        <v>10.64</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.9</v>
+        <v>6.14</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>58.29</v>
+        <v>57.64</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.28</v>
+        <v>14.09</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.57</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.71</v>
+        <v>5.72</v>
       </c>
       <c r="EA14" t="n">
-        <v>15.05</v>
+        <v>15.19</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="15">
@@ -6616,13 +6616,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" t="n">
         <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
         <v>0.1</v>
@@ -6706,139 +6706,139 @@
         <v>1.2</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG15" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>125.33</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>17.42</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="BJ15" t="n">
         <v>0.73</v>
       </c>
-      <c r="AH15" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>126.82</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK15" t="n">
+      <c r="BK15" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BL15" t="n">
         <v>1.18</v>
       </c>
-      <c r="AL15" t="n">
-        <v>5.73</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>61.45</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>9.82</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>9.18</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>68.64</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>14.73</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>8.640000000000001</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>16.27</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1.14</v>
-      </c>
       <c r="BM15" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.52</v>
+        <v>4.77</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT15" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BU15" t="n">
-        <v>28.57</v>
+        <v>31.82</v>
       </c>
       <c r="BV15" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BW15" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX15" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BY15" t="n">
         <v>1.24</v>
@@ -6847,43 +6847,43 @@
         <v>1.26</v>
       </c>
       <c r="CA15" t="n">
-        <v>5.95</v>
+        <v>5.93</v>
       </c>
       <c r="CB15" t="n">
-        <v>6.42</v>
+        <v>6.39</v>
       </c>
       <c r="CC15" t="n">
         <v>1.47</v>
       </c>
       <c r="CD15" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CG15" t="n">
-        <v>4.02</v>
+        <v>4.03</v>
       </c>
       <c r="CH15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="CJ15" t="n">
         <v>1.75</v>
       </c>
-      <c r="CI15" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="CJ15" t="n">
-        <v>1.76</v>
-      </c>
       <c r="CK15" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CN15" t="n">
         <v>1.83</v>
@@ -6892,7 +6892,7 @@
         <v>1.11</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CQ15" t="n">
         <v>2.13</v>
@@ -6901,19 +6901,19 @@
         <v>1.34</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CT15" t="n">
         <v>3.34</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CX15" t="n">
         <v>1.56</v>
@@ -6932,49 +6932,49 @@
         <v>1.48</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="DE15" t="n">
         <v>0.14</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.43</v>
+        <v>3.55</v>
       </c>
       <c r="DH15" t="n">
-        <v>133.14</v>
+        <v>132.04</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="DK15" t="n">
-        <v>6.14</v>
+        <v>6.23</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="DM15" t="n">
-        <v>66.90000000000001</v>
+        <v>67.23</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="DP15" t="n">
-        <v>10</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="DQ15" t="n">
-        <v>8.9</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DR15" t="n">
-        <v>4.38</v>
+        <v>4.55</v>
       </c>
       <c r="DS15" t="n">
         <v>0.14</v>
@@ -6986,28 +6986,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>68.62</v>
+        <v>68.55</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>17.48</v>
+        <v>17.68</v>
       </c>
       <c r="DY15" t="n">
-        <v>10.72</v>
+        <v>10.91</v>
       </c>
       <c r="DZ15" t="n">
-        <v>6.76</v>
+        <v>6.77</v>
       </c>
       <c r="EA15" t="n">
-        <v>16.95</v>
+        <v>17.55</v>
       </c>
       <c r="EB15" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="16">
@@ -7017,10 +7017,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
         <v>11</v>
@@ -7029,82 +7029,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="G16" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="H16" t="n">
-        <v>101.3</v>
+        <v>103.82</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="K16" t="n">
-        <v>5.6</v>
+        <v>5.36</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="M16" t="n">
-        <v>49.2</v>
+        <v>47.45</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="O16" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="P16" t="n">
-        <v>12</v>
+        <v>12.09</v>
       </c>
       <c r="Q16" t="n">
-        <v>12</v>
+        <v>11.73</v>
       </c>
       <c r="R16" t="n">
-        <v>6.4</v>
+        <v>6.27</v>
       </c>
       <c r="S16" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>57.8</v>
+        <v>57.82</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z16" t="n">
-        <v>13.4</v>
+        <v>13.18</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="AC16" t="n">
-        <v>16.1</v>
+        <v>16.27</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AF16" t="n">
         <v>0.09</v>
@@ -7188,70 +7188,70 @@
         <v>1.82</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.86</v>
+        <v>2.95</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.1</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.86</v>
+        <v>2.95</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="BR16" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BS16" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT16" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BU16" t="n">
-        <v>28.57</v>
+        <v>31.82</v>
       </c>
       <c r="BV16" t="n">
-        <v>23.81</v>
+        <v>27.27</v>
       </c>
       <c r="BW16" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BX16" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.39</v>
+        <v>2.54</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="CC16" t="n">
         <v>5.35</v>
@@ -7263,10 +7263,10 @@
         <v>1.33</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CH16" t="n">
         <v>1.49</v>
@@ -7281,7 +7281,7 @@
         <v>1.61</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CM16" t="n">
         <v>2.18</v>
@@ -7293,10 +7293,10 @@
         <v>1.25</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CR16" t="n">
         <v>1.38</v>
@@ -7335,76 +7335,76 @@
         <v>1.86</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="DH16" t="n">
-        <v>90.56999999999999</v>
+        <v>92.31999999999999</v>
       </c>
       <c r="DI16" t="n">
         <v>0.14</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.24</v>
+        <v>4.18</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="DM16" t="n">
-        <v>39.67</v>
+        <v>39.22</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.33</v>
+        <v>11.41</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.29</v>
+        <v>11.18</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.76</v>
+        <v>7.64</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>54</v>
+        <v>54.18</v>
       </c>
       <c r="DW16" t="n">
         <v>0.09</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.38</v>
+        <v>11.36</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.9</v>
+        <v>7.77</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.47</v>
+        <v>3.59</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.76</v>
+        <v>16.81</v>
       </c>
       <c r="EB16" t="n">
         <v>1.26</v>
@@ -7420,94 +7420,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
         <v>11</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="G17" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="H17" t="n">
-        <v>103.3</v>
+        <v>100.91</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="J17" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="K17" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M17" t="n">
-        <v>64.5</v>
+        <v>61</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="O17" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="P17" t="n">
-        <v>13.4</v>
+        <v>13.09</v>
       </c>
       <c r="Q17" t="n">
-        <v>13.4</v>
+        <v>13</v>
       </c>
       <c r="R17" t="n">
-        <v>6.6</v>
+        <v>6.82</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>52.8</v>
+        <v>51</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z17" t="n">
-        <v>16.7</v>
+        <v>16.36</v>
       </c>
       <c r="AA17" t="n">
-        <v>10.9</v>
+        <v>10.73</v>
       </c>
       <c r="AB17" t="n">
-        <v>5.8</v>
+        <v>5.64</v>
       </c>
       <c r="AC17" t="n">
-        <v>20.4</v>
+        <v>20.18</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AF17" t="n">
         <v>0.18</v>
@@ -7591,70 +7591,70 @@
         <v>1.55</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.48</v>
+        <v>10.59</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.33</v>
+        <v>4.27</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.24</v>
+        <v>5.45</v>
       </c>
       <c r="BR17" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS17" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BU17" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BV17" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.29</v>
+        <v>2.66</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.74</v>
+        <v>3.81</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.86</v>
+        <v>3.94</v>
       </c>
       <c r="CC17" t="n">
         <v>3.44</v>
@@ -7663,61 +7663,61 @@
         <v>3.68</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="CR17" t="n">
         <v>1.36</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="CT17" t="n">
         <v>3.2</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="CV17" t="n">
         <v>2.34</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CX17" t="n">
         <v>1.57</v>
@@ -7735,52 +7735,52 @@
         <v>1.28</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="DH17" t="n">
-        <v>95.95</v>
+        <v>95.09</v>
       </c>
       <c r="DI17" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.57</v>
+        <v>5.54</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DM17" t="n">
-        <v>51.38</v>
+        <v>50.22</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.24</v>
+        <v>12.14</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.14</v>
+        <v>12</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.09</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DS17" t="n">
         <v>0.09</v>
@@ -7792,28 +7792,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>52.05</v>
+        <v>51.18</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.28</v>
+        <v>13.27</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.81</v>
+        <v>8.82</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.47</v>
+        <v>4.45</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.14</v>
+        <v>19.09</v>
       </c>
       <c r="EB17" t="n">
         <v>1.52</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="18">
@@ -7823,13 +7823,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C18" t="n">
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7916,136 +7916,136 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="AI18" t="n">
-        <v>93.09</v>
+        <v>94.25</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK18" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AN18" t="n">
-        <v>40.36</v>
+        <v>41.33</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12.45</v>
+        <v>12.25</v>
       </c>
       <c r="AR18" t="n">
-        <v>13.82</v>
+        <v>13.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.64</v>
+        <v>7.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>52</v>
+        <v>52.33</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BA18" t="n">
-        <v>10.09</v>
+        <v>10.25</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.64</v>
+        <v>6.75</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>17.27</v>
+        <v>17.42</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="BH18" t="n">
-        <v>8</v>
+        <v>8.09</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BL18" t="n">
         <v>1.14</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.43</v>
+        <v>3.36</v>
       </c>
       <c r="BQ18" t="n">
-        <v>3.95</v>
+        <v>4.09</v>
       </c>
       <c r="BR18" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS18" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT18" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BU18" t="n">
-        <v>28.57</v>
+        <v>31.82</v>
       </c>
       <c r="BV18" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BW18" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX18" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BY18" t="n">
         <v>2.32</v>
@@ -8060,10 +8060,10 @@
         <v>3.87</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.53</v>
+        <v>3.56</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.62</v>
+        <v>3.64</v>
       </c>
       <c r="CE18" t="n">
         <v>1.33</v>
@@ -8078,19 +8078,19 @@
         <v>1.49</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CK18" t="n">
         <v>1.68</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CN18" t="n">
         <v>1.72</v>
@@ -8099,10 +8099,10 @@
         <v>1.22</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CR18" t="n">
         <v>1.37</v>
@@ -8117,19 +8117,19 @@
         <v>1.51</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CW18" t="n">
         <v>1.73</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DA18" t="n">
         <v>1.72</v>
@@ -8138,82 +8138,82 @@
         <v>1.3</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="DH18" t="n">
-        <v>97.56999999999999</v>
+        <v>98</v>
       </c>
       <c r="DI18" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.81</v>
+        <v>3.86</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="DM18" t="n">
-        <v>42.47</v>
+        <v>42.91</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="DP18" t="n">
-        <v>11.38</v>
+        <v>11.32</v>
       </c>
       <c r="DQ18" t="n">
-        <v>12.95</v>
+        <v>12.82</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.34</v>
+        <v>7.27</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>51.48</v>
+        <v>51.68</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.14</v>
+        <v>11.18</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.81</v>
+        <v>6.86</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="EA18" t="n">
-        <v>15.81</v>
+        <v>15.96</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="EC18" t="n">
         <v>1.95</v>

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="n">
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
         <v>0.09</v>
@@ -1472,136 +1472,136 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AI2" t="n">
-        <v>71</v>
+        <v>73.45</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN2" t="n">
-        <v>28.9</v>
+        <v>29.73</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.6</v>
+        <v>11.18</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>39.8</v>
+        <v>39.91</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.6</v>
+        <v>7.82</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.2</v>
+        <v>5.36</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="BD2" t="n">
-        <v>15.8</v>
+        <v>15.55</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.9</v>
+        <v>8.73</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL2" t="n">
         <v>0.95</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BO2" t="n">
         <v>0.95</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.38</v>
+        <v>5.27</v>
       </c>
       <c r="BR2" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS2" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BT2" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BU2" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BV2" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX2" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BY2" t="n">
         <v>3.52</v>
@@ -1610,31 +1610,31 @@
         <v>3.78</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.1</v>
+        <v>4.06</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.34</v>
+        <v>4.29</v>
       </c>
       <c r="CC2" t="n">
-        <v>8.26</v>
+        <v>7.9</v>
       </c>
       <c r="CD2" t="n">
-        <v>8.68</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="CE2" t="n">
         <v>1.4</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CH2" t="n">
         <v>1.42</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.92</v>
@@ -1646,34 +1646,34 @@
         <v>2.19</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CP2" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="CR2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="CU2" t="n">
         <v>1.44</v>
       </c>
-      <c r="CS2" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>1.45</v>
-      </c>
       <c r="CV2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CW2" t="n">
         <v>1.99</v>
@@ -1682,64 +1682,64 @@
         <v>1.69</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="DD2" t="n">
         <v>3.14</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF2" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="DH2" t="n">
-        <v>71.38</v>
+        <v>72.59</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.72</v>
+        <v>3.64</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DM2" t="n">
-        <v>30.76</v>
+        <v>31.09</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.05</v>
+        <v>10.91</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.52</v>
+        <v>11.32</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.57</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DS2" t="n">
         <v>0.09</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>43</v>
+        <v>42.91</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX2" t="n">
-        <v>9.52</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DY2" t="n">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.38</v>
+        <v>16.23</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,139 +1872,139 @@
         <v>1.91</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AI3" t="n">
-        <v>89</v>
+        <v>88.27</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.4</v>
+        <v>4.27</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AN3" t="n">
-        <v>37.1</v>
+        <v>37.18</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14</v>
+        <v>13.82</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.8</v>
+        <v>13.73</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.4</v>
+        <v>8.18</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>46.8</v>
+        <v>46</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.699999999999999</v>
+        <v>10.09</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="BD3" t="n">
-        <v>19.7</v>
+        <v>19.73</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.619999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.38</v>
+        <v>0.45</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BO3" t="n">
         <v>0.86</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.71</v>
+        <v>5.68</v>
       </c>
       <c r="BR3" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BS3" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BT3" t="n">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="BU3" t="n">
-        <v>19.05</v>
+        <v>22.73</v>
       </c>
       <c r="BV3" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX3" t="n">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="BY3" t="n">
         <v>3.78</v>
@@ -2013,28 +2013,28 @@
         <v>4.06</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.86</v>
+        <v>3.83</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.88</v>
+        <v>3.84</v>
       </c>
       <c r="CC3" t="n">
-        <v>5.23</v>
+        <v>4.98</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.44</v>
+        <v>5.17</v>
       </c>
       <c r="CE3" t="n">
         <v>1.38</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI3" t="n">
         <v>1.96</v>
@@ -2049,31 +2049,31 @@
         <v>2.08</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CO3" t="n">
         <v>1.28</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="CR3" t="n">
         <v>1.41</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV3" t="n">
         <v>2.02</v>
@@ -2082,100 +2082,100 @@
         <v>1.87</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DB3" t="n">
         <v>1.34</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DD3" t="n">
         <v>3.28</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.14</v>
+        <v>3.09</v>
       </c>
       <c r="DH3" t="n">
-        <v>89.67</v>
+        <v>89.27</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="DK3" t="n">
-        <v>5</v>
+        <v>4.91</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="DM3" t="n">
-        <v>41.71</v>
+        <v>41.54</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.52</v>
+        <v>13.46</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.81</v>
+        <v>13.78</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.85</v>
+        <v>6.82</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>44.57</v>
+        <v>44.28</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.67</v>
+        <v>10.82</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.43</v>
+        <v>7.59</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.9</v>
+        <v>18.95</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="4">
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>40.82</v>
+        <v>40.91</v>
       </c>
       <c r="AZ4" t="n">
         <v>0.18</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>43.09</v>
+        <v>43.14</v>
       </c>
       <c r="DW4" t="n">
         <v>0.13</v>
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
@@ -2600,82 +2600,82 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="G5" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="H5" t="n">
-        <v>96.09</v>
+        <v>92.5</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="J5" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="K5" t="n">
-        <v>5.64</v>
+        <v>5.25</v>
       </c>
       <c r="L5" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="M5" t="n">
-        <v>50.27</v>
+        <v>47.08</v>
       </c>
       <c r="N5" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="O5" t="n">
-        <v>3.09</v>
+        <v>2.92</v>
       </c>
       <c r="P5" t="n">
-        <v>14</v>
+        <v>13.42</v>
       </c>
       <c r="Q5" t="n">
-        <v>13</v>
+        <v>13.25</v>
       </c>
       <c r="R5" t="n">
-        <v>6.18</v>
+        <v>6.5</v>
       </c>
       <c r="S5" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="T5" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="U5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>49.73</v>
+        <v>48.33</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="Z5" t="n">
-        <v>13</v>
+        <v>12.33</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.640000000000001</v>
+        <v>8.17</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.36</v>
+        <v>4.17</v>
       </c>
       <c r="AC5" t="n">
-        <v>21.55</v>
+        <v>20.67</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>2.1</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.380000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BL5" t="n">
         <v>0.95</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.29</v>
+        <v>5.41</v>
       </c>
       <c r="BR5" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BT5" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BU5" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BV5" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX5" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.08</v>
+        <v>4.04</v>
       </c>
       <c r="CC5" t="n">
         <v>6.58</v>
@@ -2834,10 +2834,10 @@
         <v>1.35</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CH5" t="n">
         <v>1.45</v>
@@ -2846,13 +2846,13 @@
         <v>1.95</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CM5" t="n">
         <v>2.2</v>
@@ -2864,10 +2864,10 @@
         <v>1.26</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="CR5" t="n">
         <v>1.41</v>
@@ -2885,25 +2885,25 @@
         <v>2.01</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CX5" t="n">
         <v>1.63</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DA5" t="n">
         <v>1.79</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="DD5" t="n">
         <v>3.14</v>
@@ -2912,76 +2912,76 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="DH5" t="n">
-        <v>87.67</v>
+        <v>86.09</v>
       </c>
       <c r="DI5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>41.54</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>45.59</v>
+      </c>
+      <c r="DW5" t="n">
         <v>0.09</v>
       </c>
-      <c r="DJ5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="DK5" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="DL5" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="DM5" t="n">
-        <v>42.95</v>
-      </c>
-      <c r="DN5" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="DO5" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="DP5" t="n">
-        <v>13.71</v>
-      </c>
-      <c r="DQ5" t="n">
-        <v>13.48</v>
-      </c>
-      <c r="DR5" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="DS5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="DT5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="DU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV5" t="n">
-        <v>46.19</v>
-      </c>
-      <c r="DW5" t="n">
-        <v>0.05</v>
-      </c>
       <c r="DX5" t="n">
-        <v>11.19</v>
+        <v>10.91</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.43</v>
+        <v>7.23</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.76</v>
+        <v>3.68</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.81</v>
+        <v>18.46</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="6">
@@ -3460,7 +3460,7 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>52.55</v>
+        <v>52.45</v>
       </c>
       <c r="Y7" t="n">
         <v>0.09</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>54.96</v>
+        <v>54.9</v>
       </c>
       <c r="DW7" t="n">
         <v>0.22</v>
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
         <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="H8" t="n">
-        <v>85.5</v>
+        <v>86</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>42.9</v>
+        <v>42.27</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="P8" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.9</v>
+        <v>13.36</v>
       </c>
       <c r="R8" t="n">
-        <v>5.8</v>
+        <v>5.64</v>
       </c>
       <c r="S8" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>44.4</v>
+        <v>45.73</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.7</v>
+        <v>12.27</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.7</v>
+        <v>7.55</v>
       </c>
       <c r="AB8" t="n">
-        <v>5</v>
+        <v>4.73</v>
       </c>
       <c r="AC8" t="n">
-        <v>14.3</v>
+        <v>15.09</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
         <v>0.09</v>
@@ -3968,70 +3968,70 @@
         <v>1.45</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.52</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BL8" t="n">
         <v>1.05</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="BO8" t="n">
         <v>1.05</v>
       </c>
       <c r="BP8" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>95.45</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>86.36</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>40.91</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>31.82</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="CB8" t="n">
         <v>3.76</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>95.23999999999999</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>9.52</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>9.52</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>52.38</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="CB8" t="n">
-        <v>3.79</v>
       </c>
       <c r="CC8" t="n">
         <v>4.2</v>
@@ -4040,157 +4040,157 @@
         <v>4.46</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CN8" t="n">
         <v>1.68</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="DB8" t="n">
         <v>1.34</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="DD8" t="n">
         <v>3.15</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DH8" t="n">
-        <v>84.95</v>
+        <v>85.22</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DM8" t="n">
-        <v>41.29</v>
+        <v>41.04</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.949999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.38</v>
+        <v>14.09</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.52</v>
+        <v>7.36</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>43.9</v>
+        <v>44.59</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.67</v>
+        <v>11.5</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.81</v>
+        <v>7.73</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="EA8" t="n">
-        <v>14.53</v>
+        <v>14.91</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="9">
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
         <v>11</v>
@@ -4212,82 +4212,82 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="H9" t="n">
-        <v>81.2</v>
+        <v>85.64</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2</v>
+        <v>-0.09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="K9" t="n">
         <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M9" t="n">
-        <v>37.6</v>
+        <v>38.18</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="O9" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="P9" t="n">
-        <v>11.8</v>
+        <v>11.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.6</v>
+        <v>10.73</v>
       </c>
       <c r="R9" t="n">
-        <v>7.7</v>
+        <v>7.55</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>46.7</v>
+        <v>48.09</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.300000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AA9" t="n">
-        <v>6</v>
+        <v>6.27</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="AC9" t="n">
-        <v>17.4</v>
+        <v>17.36</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AF9" t="n">
         <v>0.09</v>
@@ -4371,70 +4371,70 @@
         <v>1.64</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.9</v>
+        <v>8.82</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.19</v>
+        <v>4.09</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.71</v>
+        <v>4.73</v>
       </c>
       <c r="BR9" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS9" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT9" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BU9" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BV9" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BW9" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BX9" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BY9" t="n">
-        <v>4.81</v>
+        <v>4.65</v>
       </c>
       <c r="BZ9" t="n">
-        <v>5.04</v>
+        <v>4.88</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.09</v>
+        <v>4.05</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.34</v>
+        <v>4.29</v>
       </c>
       <c r="CC9" t="n">
         <v>5.5</v>
@@ -4443,16 +4443,16 @@
         <v>6.15</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI9" t="n">
         <v>2.02</v>
@@ -4461,139 +4461,139 @@
         <v>1.74</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="CV9" t="n">
         <v>2.1</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DB9" t="n">
         <v>1.3</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="DD9" t="n">
         <v>2.87</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF9" t="n">
         <v>1.09</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="DH9" t="n">
-        <v>76.15000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DK9" t="n">
         <v>3.86</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM9" t="n">
-        <v>33.05</v>
+        <v>33.54</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="DP9" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.9</v>
+        <v>10.96</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.52</v>
+        <v>8.41</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>48.48</v>
+        <v>49.09</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.85</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.86</v>
+        <v>6</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="EA9" t="n">
         <v>17</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="10">
@@ -5407,13 +5407,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
         <v>0.18</v>
@@ -5500,136 +5500,136 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="AI12" t="n">
-        <v>89.5</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.7</v>
+        <v>4.73</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AN12" t="n">
-        <v>38.3</v>
+        <v>38.18</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.8</v>
+        <v>13.64</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.3</v>
+        <v>12.64</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.7</v>
+        <v>7.64</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>48.3</v>
+        <v>47.82</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA12" t="n">
         <v>10</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.6</v>
+        <v>6.64</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="BD12" t="n">
-        <v>17.8</v>
+        <v>17.45</v>
       </c>
       <c r="BE12" t="n">
         <v>1.15</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.71</v>
+        <v>10.82</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BL12" t="n">
         <v>1.05</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.62</v>
+        <v>4.73</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.38</v>
+        <v>5.41</v>
       </c>
       <c r="BR12" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS12" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT12" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BU12" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BV12" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BW12" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX12" t="n">
-        <v>66.67</v>
+        <v>63.64</v>
       </c>
       <c r="BY12" t="n">
         <v>2.41</v>
@@ -5641,28 +5641,28 @@
         <v>3.74</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.65</v>
+        <v>3.72</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.78</v>
+        <v>4.73</v>
       </c>
       <c r="CE12" t="n">
         <v>1.32</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="CH12" t="n">
         <v>1.51</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.65</v>
@@ -5674,10 +5674,10 @@
         <v>1.94</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CO12" t="n">
         <v>1.21</v>
@@ -5686,19 +5686,19 @@
         <v>1.75</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CR12" t="n">
         <v>1.36</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV12" t="n">
         <v>2.32</v>
@@ -5707,13 +5707,13 @@
         <v>1.68</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CY12" t="n">
         <v>1.89</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="DA12" t="n">
         <v>1.94</v>
@@ -5725,49 +5725,49 @@
         <v>1.78</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="DE12" t="n">
         <v>0.09</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="DH12" t="n">
-        <v>80.47</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="DK12" t="n">
         <v>5.09</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="DM12" t="n">
-        <v>35.29</v>
+        <v>35.36</v>
       </c>
       <c r="DN12" t="n">
         <v>1.14</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.76</v>
+        <v>12.73</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.48</v>
+        <v>12.64</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.81</v>
+        <v>6.82</v>
       </c>
       <c r="DS12" t="n">
         <v>0.09</v>
@@ -5779,28 +5779,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48.24</v>
+        <v>48</v>
       </c>
       <c r="DW12" t="n">
         <v>0.09</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.76</v>
+        <v>11.68</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.47</v>
+        <v>7.45</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.29</v>
+        <v>4.22</v>
       </c>
       <c r="EA12" t="n">
-        <v>16.76</v>
+        <v>16.64</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="13">
@@ -5810,10 +5810,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
         <v>11</v>
@@ -5822,49 +5822,49 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="H13" t="n">
-        <v>90.90000000000001</v>
+        <v>91.73</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="K13" t="n">
-        <v>5.6</v>
+        <v>5.82</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="M13" t="n">
-        <v>47</v>
+        <v>45.73</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="O13" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="P13" t="n">
-        <v>14.4</v>
+        <v>14.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>12.6</v>
+        <v>12.55</v>
       </c>
       <c r="R13" t="n">
-        <v>6.2</v>
+        <v>6.18</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5876,28 +5876,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>56.5</v>
+        <v>56.55</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.7</v>
+        <v>13.27</v>
       </c>
       <c r="AA13" t="n">
-        <v>9</v>
+        <v>8.82</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.7</v>
+        <v>4.45</v>
       </c>
       <c r="AC13" t="n">
-        <v>17.7</v>
+        <v>17.18</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AF13" t="n">
         <v>0.09</v>
@@ -5981,70 +5981,70 @@
         <v>2.09</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.33</v>
+        <v>10.45</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.29</v>
+        <v>4.41</v>
       </c>
       <c r="BQ13" t="n">
         <v>6.05</v>
       </c>
       <c r="BR13" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS13" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BT13" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BU13" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV13" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW13" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX13" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="CC13" t="n">
         <v>2.44</v>
@@ -6074,7 +6074,7 @@
         <v>1.53</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CM13" t="n">
         <v>2.36</v>
@@ -6089,7 +6089,7 @@
         <v>1.8</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="CR13" t="n">
         <v>1.37</v>
@@ -6098,7 +6098,7 @@
         <v>2.72</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="CU13" t="n">
         <v>1.48</v>
@@ -6107,7 +6107,7 @@
         <v>2.16</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CX13" t="n">
         <v>1.59</v>
@@ -6116,10 +6116,10 @@
         <v>1.97</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DB13" t="n">
         <v>1.3</v>
@@ -6128,82 +6128,82 @@
         <v>1.86</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.09</v>
+        <v>3.14</v>
       </c>
       <c r="DH13" t="n">
-        <v>88.52</v>
+        <v>89.05</v>
       </c>
       <c r="DI13" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.72</v>
+        <v>5.82</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DM13" t="n">
-        <v>44.15</v>
+        <v>43.64</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="DP13" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.38</v>
+        <v>13.32</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.81</v>
+        <v>6.77</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>54.9</v>
+        <v>55</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.38</v>
+        <v>12.22</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.48</v>
+        <v>7.45</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.9</v>
+        <v>4.77</v>
       </c>
       <c r="EA13" t="n">
-        <v>17.86</v>
+        <v>17.59</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="14">
@@ -8226,13 +8226,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19" t="n">
         <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
         <v>0.27</v>
@@ -8319,136 +8319,136 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.6</v>
+        <v>2.18</v>
       </c>
       <c r="AI19" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="AL19" t="n">
-        <v>4</v>
+        <v>4.55</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN19" t="n">
-        <v>38.6</v>
+        <v>43.91</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AP19" t="n">
         <v>2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>15.2</v>
+        <v>15.27</v>
       </c>
       <c r="AR19" t="n">
-        <v>11.3</v>
+        <v>10.91</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.6</v>
+        <v>7.36</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>41.2</v>
+        <v>43.55</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA19" t="n">
-        <v>9.5</v>
+        <v>10.91</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.1</v>
+        <v>7</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.4</v>
+        <v>3.91</v>
       </c>
       <c r="BD19" t="n">
-        <v>16.1</v>
+        <v>16.55</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="BF19" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.710000000000001</v>
+        <v>9.77</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="BL19" t="n">
         <v>0.86</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="BO19" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.29</v>
+        <v>4.23</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.1</v>
+        <v>5.23</v>
       </c>
       <c r="BR19" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS19" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BT19" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BU19" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV19" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW19" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX19" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BY19" t="n">
         <v>2.52</v>
@@ -8457,25 +8457,25 @@
         <v>2.61</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.55</v>
+        <v>3.52</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.36</v>
+        <v>3.27</v>
       </c>
       <c r="CE19" t="n">
         <v>1.38</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CH19" t="n">
         <v>1.4</v>
@@ -8490,22 +8490,22 @@
         <v>1.64</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CO19" t="n">
         <v>1.3</v>
       </c>
       <c r="CP19" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="CR19" t="n">
         <v>1.43</v>
@@ -8523,25 +8523,25 @@
         <v>2</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CX19" t="n">
         <v>1.66</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="DD19" t="n">
         <v>3.39</v>
@@ -8550,76 +8550,76 @@
         <v>0.14</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.14</v>
+        <v>2.41</v>
       </c>
       <c r="DH19" t="n">
-        <v>85.76000000000001</v>
+        <v>88.36</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.48</v>
+        <v>4.73</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DM19" t="n">
-        <v>41.62</v>
+        <v>44.14</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.38</v>
+        <v>14.46</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.05</v>
+        <v>11.82</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.81</v>
+        <v>6.72</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>41.57</v>
+        <v>42.73</v>
       </c>
       <c r="DW19" t="n">
         <v>0.09</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.24</v>
+        <v>12.82</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.050000000000001</v>
+        <v>8.41</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.19</v>
+        <v>4.41</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.71</v>
+        <v>16.91</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
         <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="G2" t="n">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="H2" t="n">
-        <v>71.73</v>
+        <v>72.83</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="K2" t="n">
-        <v>4.55</v>
+        <v>4.25</v>
       </c>
       <c r="L2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="M2" t="n">
-        <v>32.45</v>
+        <v>32.17</v>
       </c>
       <c r="N2" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="P2" t="n">
-        <v>12.64</v>
+        <v>12.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.45</v>
+        <v>11.42</v>
       </c>
       <c r="R2" t="n">
-        <v>8.09</v>
+        <v>8</v>
       </c>
       <c r="S2" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="U2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>45.91</v>
+        <v>45.83</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z2" t="n">
-        <v>11.27</v>
+        <v>10.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.64</v>
+        <v>6.33</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.64</v>
+        <v>4.42</v>
       </c>
       <c r="AC2" t="n">
-        <v>16.91</v>
+        <v>17.92</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>1.09</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.73</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.45</v>
+        <v>3.39</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.27</v>
+        <v>5.3</v>
       </c>
       <c r="BR2" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS2" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BT2" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BU2" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BV2" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX2" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.78</v>
+        <v>3.86</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.06</v>
+        <v>4.03</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.29</v>
+        <v>4.26</v>
       </c>
       <c r="CC2" t="n">
         <v>7.9</v>
@@ -1628,10 +1628,10 @@
         <v>2.79</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CI2" t="n">
         <v>1.82</v>
@@ -1643,13 +1643,13 @@
         <v>1.67</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CO2" t="n">
         <v>1.32</v>
@@ -1664,10 +1664,10 @@
         <v>1.45</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CU2" t="n">
         <v>1.44</v>
@@ -1706,73 +1706,73 @@
         <v>0.96</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="DH2" t="n">
-        <v>72.59</v>
+        <v>73.13</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.64</v>
+        <v>3.52</v>
       </c>
       <c r="DL2" t="n">
         <v>0.22</v>
       </c>
       <c r="DM2" t="n">
-        <v>31.09</v>
+        <v>31</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.91</v>
+        <v>11.04</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.32</v>
+        <v>11.31</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.539999999999999</v>
+        <v>8.48</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>42.91</v>
+        <v>43</v>
       </c>
       <c r="DW2" t="n">
         <v>0.04</v>
       </c>
       <c r="DX2" t="n">
-        <v>9.539999999999999</v>
+        <v>9.35</v>
       </c>
       <c r="DY2" t="n">
-        <v>6</v>
+        <v>5.87</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.23</v>
+        <v>16.79</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="G3" t="n">
-        <v>4.27</v>
+        <v>4.17</v>
       </c>
       <c r="H3" t="n">
-        <v>90.27</v>
+        <v>91.33</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="K3" t="n">
-        <v>5.55</v>
+        <v>5.42</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="M3" t="n">
-        <v>45.91</v>
+        <v>45.92</v>
       </c>
       <c r="N3" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="O3" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>13.09</v>
+        <v>13.42</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.82</v>
+        <v>14.5</v>
       </c>
       <c r="R3" t="n">
-        <v>5.45</v>
+        <v>5.58</v>
       </c>
       <c r="S3" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="T3" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="U3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>42.55</v>
+        <v>42.58</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.55</v>
+        <v>11.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.18</v>
+        <v>8.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.18</v>
+        <v>18.42</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AF3" t="n">
         <v>0.18</v>
@@ -1953,70 +1953,70 @@
         <v>2.36</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.5</v>
+        <v>9.48</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.41</v>
+        <v>0.52</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.86</v>
+        <v>0.96</v>
       </c>
       <c r="BP3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>86.95999999999999</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>56.52</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>39.13</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>21.74</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>34.78</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="CB3" t="n">
         <v>3.82</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>86.36</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>54.55</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>36.36</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>22.73</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>36.36</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>3.84</v>
       </c>
       <c r="CC3" t="n">
         <v>4.98</v>
@@ -2031,34 +2031,34 @@
         <v>2.81</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CH3" t="n">
         <v>1.43</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.82</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CO3" t="n">
         <v>1.28</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CQ3" t="n">
         <v>3.27</v>
@@ -2067,31 +2067,31 @@
         <v>1.41</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="CU3" t="n">
         <v>1.45</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DB3" t="n">
         <v>1.34</v>
@@ -2106,40 +2106,40 @@
         <v>0.09</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="DG3" t="n">
         <v>3.09</v>
       </c>
       <c r="DH3" t="n">
-        <v>89.27</v>
+        <v>89.87</v>
       </c>
       <c r="DI3" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.91</v>
+        <v>4.87</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DM3" t="n">
-        <v>41.54</v>
+        <v>41.74</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.46</v>
+        <v>13.61</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.78</v>
+        <v>14.13</v>
       </c>
       <c r="DR3" t="n">
         <v>6.82</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>44.28</v>
+        <v>44.22</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.82</v>
+        <v>10.83</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.59</v>
+        <v>7.65</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.22</v>
+        <v>3.17</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.95</v>
+        <v>19.05</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="F4" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="H4" t="n">
-        <v>102.27</v>
+        <v>100.5</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="K4" t="n">
-        <v>5.55</v>
+        <v>5.33</v>
       </c>
       <c r="L4" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M4" t="n">
-        <v>39.36</v>
+        <v>37.75</v>
       </c>
       <c r="N4" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="O4" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="P4" t="n">
-        <v>13.64</v>
+        <v>13.33</v>
       </c>
       <c r="Q4" t="n">
-        <v>10.55</v>
+        <v>11.08</v>
       </c>
       <c r="R4" t="n">
-        <v>7.55</v>
+        <v>8.17</v>
       </c>
       <c r="S4" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="T4" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="U4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>45.36</v>
+        <v>44.25</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>14.36</v>
+        <v>14.17</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.550000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.82</v>
+        <v>4.75</v>
       </c>
       <c r="AC4" t="n">
-        <v>17.18</v>
+        <v>16.33</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,70 +2356,70 @@
         <v>1.91</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.73</v>
+        <v>9.52</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.77</v>
+        <v>4.65</v>
       </c>
       <c r="BR4" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS4" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT4" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BU4" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BV4" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.68</v>
+        <v>3.69</v>
       </c>
       <c r="CC4" t="n">
         <v>3.98</v>
@@ -2428,19 +2428,19 @@
         <v>4.03</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CG4" t="n">
         <v>3.07</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.73</v>
@@ -2449,7 +2449,7 @@
         <v>1.65</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CM4" t="n">
         <v>2.18</v>
@@ -2461,10 +2461,10 @@
         <v>1.26</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="CR4" t="n">
         <v>1.4</v>
@@ -2479,10 +2479,10 @@
         <v>1.48</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CX4" t="n">
         <v>1.68</v>
@@ -2500,85 +2500,85 @@
         <v>1.33</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="DH4" t="n">
-        <v>92.41</v>
+        <v>91.92</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.23</v>
+        <v>4.17</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DM4" t="n">
-        <v>39.18</v>
+        <v>38.35</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.6</v>
+        <v>13.44</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.36</v>
+        <v>11.61</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.28</v>
+        <v>7.61</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>43.14</v>
+        <v>42.65</v>
       </c>
       <c r="DW4" t="n">
         <v>0.13</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.77</v>
+        <v>11.78</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.82</v>
+        <v>7.83</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.86</v>
+        <v>17.39</v>
       </c>
       <c r="EB4" t="n">
         <v>1.3</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
         <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2681,49 +2681,49 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AI5" t="n">
-        <v>78.40000000000001</v>
+        <v>82.73</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>34.9</v>
+        <v>37.18</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13.4</v>
+        <v>13.36</v>
       </c>
       <c r="AR5" t="n">
-        <v>14</v>
+        <v>14.27</v>
       </c>
       <c r="AS5" t="n">
-        <v>9</v>
+        <v>8.73</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>42.3</v>
+        <v>44.91</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.91</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="BD5" t="n">
-        <v>15.8</v>
+        <v>17</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.449999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.05</v>
+        <v>4.22</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.41</v>
+        <v>5.3</v>
       </c>
       <c r="BR5" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BS5" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BT5" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BU5" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BV5" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BY5" t="n">
         <v>3.01</v>
@@ -2819,37 +2819,37 @@
         <v>3.36</v>
       </c>
       <c r="CA5" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.04</v>
+        <v>4.02</v>
       </c>
       <c r="CC5" t="n">
-        <v>6.58</v>
+        <v>6.23</v>
       </c>
       <c r="CD5" t="n">
-        <v>7.21</v>
+        <v>6.84</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.82</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CL5" t="n">
         <v>2.08</v>
@@ -2861,28 +2861,28 @@
         <v>1.74</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CW5" t="n">
         <v>1.89</v>
@@ -2891,7 +2891,7 @@
         <v>1.63</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.26</v>
@@ -2903,7 +2903,7 @@
         <v>1.34</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DD5" t="n">
         <v>3.14</v>
@@ -2912,43 +2912,43 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="DH5" t="n">
-        <v>86.09</v>
+        <v>87.83</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.59</v>
+        <v>4.65</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DM5" t="n">
-        <v>41.54</v>
+        <v>42.35</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.46</v>
+        <v>2.57</v>
       </c>
       <c r="DP5" t="n">
-        <v>13.41</v>
+        <v>13.39</v>
       </c>
       <c r="DQ5" t="n">
-        <v>13.59</v>
+        <v>13.74</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.64</v>
+        <v>7.57</v>
       </c>
       <c r="DS5" t="n">
         <v>0.04</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>45.59</v>
+        <v>46.69</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.91</v>
+        <v>10.69</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.23</v>
+        <v>7.13</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.68</v>
+        <v>3.57</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.46</v>
+        <v>18.91</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="H6" t="n">
-        <v>88.36</v>
+        <v>89</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="K6" t="n">
-        <v>6.09</v>
+        <v>6.17</v>
       </c>
       <c r="L6" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="M6" t="n">
-        <v>46.18</v>
+        <v>46.75</v>
       </c>
       <c r="N6" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="O6" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="P6" t="n">
-        <v>13.64</v>
+        <v>13.58</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.73</v>
+        <v>12.67</v>
       </c>
       <c r="R6" t="n">
-        <v>5.55</v>
+        <v>5.42</v>
       </c>
       <c r="S6" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="T6" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>49.73</v>
+        <v>49.92</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.73</v>
+        <v>15</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.449999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.27</v>
+        <v>5.42</v>
       </c>
       <c r="AC6" t="n">
-        <v>18.09</v>
+        <v>17.58</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AF6" t="n">
         <v>0.09</v>
@@ -3162,70 +3162,70 @@
         <v>2.09</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.640000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.5</v>
+        <v>0.61</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BP6" t="n">
-        <v>4</v>
+        <v>4.04</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.82</v>
+        <v>4.78</v>
       </c>
       <c r="BR6" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS6" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT6" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BU6" t="n">
-        <v>22.73</v>
+        <v>26.09</v>
       </c>
       <c r="BV6" t="n">
-        <v>9.09</v>
+        <v>13.04</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="CC6" t="n">
         <v>2.78</v>
@@ -3237,22 +3237,22 @@
         <v>1.31</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CH6" t="n">
         <v>1.53</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CL6" t="n">
         <v>2.02</v>
@@ -3261,22 +3261,22 @@
         <v>2.27</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CO6" t="n">
         <v>1.2</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="CR6" t="n">
         <v>1.35</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CT6" t="n">
         <v>3.24</v>
@@ -3285,10 +3285,10 @@
         <v>1.56</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CX6" t="n">
         <v>1.59</v>
@@ -3297,7 +3297,7 @@
         <v>1.98</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="DA6" t="n">
         <v>1.85</v>
@@ -3309,19 +3309,19 @@
         <v>1.73</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="DH6" t="n">
-        <v>88.81999999999999</v>
+        <v>89.13</v>
       </c>
       <c r="DI6" t="n">
         <v>0.09</v>
@@ -3330,61 +3330,61 @@
         <v>2.13</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.45</v>
+        <v>5.52</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="DM6" t="n">
-        <v>43.54</v>
+        <v>43.96</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.78</v>
+        <v>13.74</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.86</v>
+        <v>12.83</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.23</v>
+        <v>6.13</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>49.04</v>
+        <v>49.17</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.91</v>
+        <v>14.09</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.859999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.05</v>
+        <v>5.13</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.14</v>
+        <v>16.91</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" t="n">
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
         <v>0.09</v>
@@ -3484,139 +3484,139 @@
         <v>1.45</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AH7" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="AI7" t="n">
-        <v>103.18</v>
+        <v>105</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.27</v>
+        <v>3.08</v>
       </c>
       <c r="AL7" t="n">
-        <v>6</v>
+        <v>6.08</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AN7" t="n">
-        <v>57</v>
+        <v>56.67</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AP7" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11.82</v>
+        <v>11.75</v>
       </c>
       <c r="AR7" t="n">
-        <v>13.73</v>
+        <v>13.67</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.64</v>
+        <v>6.58</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>57.36</v>
+        <v>57.17</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BA7" t="n">
-        <v>13.36</v>
+        <v>13.42</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.82</v>
+        <v>8.83</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.55</v>
+        <v>4.58</v>
       </c>
       <c r="BD7" t="n">
-        <v>17.91</v>
+        <v>17.25</v>
       </c>
       <c r="BE7" t="n">
         <v>1.58</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="BG7" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.23</v>
+        <v>10.13</v>
       </c>
       <c r="BI7" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BM7" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="BO7" t="n">
         <v>0.91</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.18</v>
+        <v>5.04</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.05</v>
+        <v>5.09</v>
       </c>
       <c r="BR7" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS7" t="n">
-        <v>68.18000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="BT7" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BU7" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV7" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BW7" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BX7" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BY7" t="n">
         <v>2.14</v>
@@ -3625,40 +3625,40 @@
         <v>2.17</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.91</v>
+        <v>3.89</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.04</v>
+        <v>4.02</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.01</v>
+        <v>2.92</v>
       </c>
       <c r="CD7" t="n">
-        <v>3.03</v>
+        <v>2.93</v>
       </c>
       <c r="CE7" t="n">
         <v>1.34</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CK7" t="n">
         <v>1.56</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CM7" t="n">
         <v>2.27</v>
@@ -3670,28 +3670,28 @@
         <v>1.24</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CX7" t="n">
         <v>1.62</v>
@@ -3718,76 +3718,76 @@
         <v>0.13</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="DG7" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="DH7" t="n">
-        <v>105.72</v>
+        <v>106.56</v>
       </c>
       <c r="DI7" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.32</v>
+        <v>6.35</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="DM7" t="n">
-        <v>56.5</v>
+        <v>56.35</v>
       </c>
       <c r="DN7" t="n">
         <v>0.87</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.32</v>
+        <v>3.26</v>
       </c>
       <c r="DP7" t="n">
-        <v>11.23</v>
+        <v>11.22</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.23</v>
+        <v>13.22</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.05</v>
+        <v>6.04</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>54.9</v>
+        <v>54.91</v>
       </c>
       <c r="DW7" t="n">
         <v>0.22</v>
       </c>
       <c r="DX7" t="n">
-        <v>14.59</v>
+        <v>14.57</v>
       </c>
       <c r="DY7" t="n">
-        <v>9.869999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.73</v>
+        <v>4.74</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.59</v>
+        <v>17.26</v>
       </c>
       <c r="EB7" t="n">
         <v>1.66</v>
       </c>
       <c r="EC7" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
         <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
         <v>0.18</v>
@@ -3887,139 +3887,139 @@
         <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AI8" t="n">
-        <v>84.45</v>
+        <v>86.83</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.64</v>
+        <v>3.92</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AN8" t="n">
-        <v>39.82</v>
+        <v>42.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.640000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="AR8" t="n">
-        <v>14.82</v>
+        <v>14.75</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.09</v>
+        <v>9</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>43.45</v>
+        <v>44.92</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA8" t="n">
-        <v>10.73</v>
+        <v>11.25</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.91</v>
+        <v>8.25</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="BD8" t="n">
-        <v>14.73</v>
+        <v>14.92</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.359999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.68</v>
+        <v>3.83</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.32</v>
+        <v>4.26</v>
       </c>
       <c r="BR8" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS8" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BU8" t="n">
-        <v>31.82</v>
+        <v>34.78</v>
       </c>
       <c r="BV8" t="n">
-        <v>9.09</v>
+        <v>13.04</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.09</v>
+        <v>13.04</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BY8" t="n">
         <v>3.39</v>
@@ -4028,16 +4028,16 @@
         <v>3.45</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.2</v>
+        <v>4.13</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.46</v>
+        <v>4.38</v>
       </c>
       <c r="CE8" t="n">
         <v>1.36</v>
@@ -4046,46 +4046,46 @@
         <v>2.71</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CI8" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.76</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CL8" t="n">
         <v>2.21</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CO8" t="n">
         <v>1.27</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CR8" t="n">
         <v>1.42</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CU8" t="n">
         <v>1.46</v>
@@ -4097,16 +4097,16 @@
         <v>1.83</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DB8" t="n">
         <v>1.34</v>
@@ -4115,82 +4115,82 @@
         <v>1.99</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="DE8" t="n">
         <v>0.13</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="DH8" t="n">
-        <v>85.22</v>
+        <v>86.43000000000001</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.23</v>
+        <v>3.39</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DM8" t="n">
-        <v>41.04</v>
+        <v>42.39</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.82</v>
+        <v>9.57</v>
       </c>
       <c r="DQ8" t="n">
         <v>14.09</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.36</v>
+        <v>7.39</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>44.59</v>
+        <v>45.31</v>
       </c>
       <c r="DW8" t="n">
         <v>0.04</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.5</v>
+        <v>11.74</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.73</v>
+        <v>7.92</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.78</v>
+        <v>3.83</v>
       </c>
       <c r="EA8" t="n">
-        <v>14.91</v>
+        <v>15</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
         <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4290,139 +4290,139 @@
         <v>1.27</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AH9" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AI9" t="n">
-        <v>71.55</v>
+        <v>71.33</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.73</v>
+        <v>3.5</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN9" t="n">
-        <v>28.91</v>
+        <v>28.75</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10.09</v>
+        <v>10.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>11.18</v>
+        <v>11</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.27</v>
+        <v>9.17</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>50.09</v>
+        <v>48.67</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.449999999999999</v>
+        <v>8</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.73</v>
+        <v>5.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>16.64</v>
+        <v>16.17</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.82</v>
+        <v>8.65</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL9" t="n">
         <v>1.09</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.09</v>
+        <v>4</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.73</v>
+        <v>4.65</v>
       </c>
       <c r="BR9" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS9" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT9" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BU9" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BV9" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BW9" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BX9" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BY9" t="n">
         <v>4.65</v>
@@ -4431,169 +4431,169 @@
         <v>4.88</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.29</v>
+        <v>4.54</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.5</v>
+        <v>6.37</v>
       </c>
       <c r="CD9" t="n">
-        <v>6.15</v>
+        <v>7.33</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="CR9" t="n">
         <v>1.38</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="CT9" t="n">
         <v>3.11</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CX9" t="n">
         <v>1.64</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.25</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="DB9" t="n">
         <v>1.3</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="DE9" t="n">
         <v>0.04</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="DH9" t="n">
-        <v>78.59999999999999</v>
+        <v>78.17</v>
       </c>
       <c r="DI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.86</v>
+        <v>3.74</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DM9" t="n">
-        <v>33.54</v>
+        <v>33.26</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="DP9" t="n">
-        <v>11</v>
+        <v>11.17</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.96</v>
+        <v>10.87</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.41</v>
+        <v>8.4</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>49.09</v>
+        <v>48.39</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.039999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="DY9" t="n">
-        <v>6</v>
+        <v>5.87</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.05</v>
+        <v>2.91</v>
       </c>
       <c r="EA9" t="n">
-        <v>17</v>
+        <v>16.74</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
         <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
         <v>0.17</v>
@@ -4693,139 +4693,139 @@
         <v>1.83</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AI10" t="n">
-        <v>107.9</v>
+        <v>104.64</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.9</v>
+        <v>4.64</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AN10" t="n">
-        <v>50.3</v>
+        <v>49.36</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AP10" t="n">
         <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.5</v>
+        <v>14.27</v>
       </c>
       <c r="AR10" t="n">
-        <v>10.6</v>
+        <v>10.82</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.7</v>
+        <v>8.09</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AU10" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>54.1</v>
+        <v>53.55</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA10" t="n">
-        <v>11.5</v>
+        <v>11.36</v>
       </c>
       <c r="BB10" t="n">
-        <v>8</v>
+        <v>7.73</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="BD10" t="n">
-        <v>20.3</v>
+        <v>20</v>
       </c>
       <c r="BE10" t="n">
         <v>1.34</v>
       </c>
       <c r="BF10" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.14</v>
+        <v>3.22</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.23</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.14</v>
+        <v>3.22</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL10" t="n">
         <v>1.09</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.32</v>
+        <v>4.35</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="BR10" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS10" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BT10" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BU10" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BV10" t="n">
-        <v>22.73</v>
+        <v>26.09</v>
       </c>
       <c r="BW10" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX10" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BY10" t="n">
         <v>1.95</v>
@@ -4834,16 +4834,16 @@
         <v>1.98</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.25</v>
+        <v>4.26</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.29</v>
+        <v>4.27</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.04</v>
+        <v>2.23</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.16</v>
+        <v>2.39</v>
       </c>
       <c r="CE10" t="n">
         <v>1.26</v>
@@ -4852,13 +4852,13 @@
         <v>2.27</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="CH10" t="n">
         <v>1.62</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.56</v>
@@ -4882,13 +4882,13 @@
         <v>1.56</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CR10" t="n">
         <v>1.35</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CT10" t="n">
         <v>3.26</v>
@@ -4916,85 +4916,85 @@
       </c>
       <c r="DB10" t="inlineStr"/>
       <c r="DC10" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="DH10" t="n">
-        <v>106.27</v>
+        <v>104.79</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.95</v>
+        <v>4.83</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DM10" t="n">
-        <v>49.05</v>
+        <v>48.65</v>
       </c>
       <c r="DN10" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.55</v>
+        <v>13.48</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.05</v>
+        <v>11.13</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.27</v>
+        <v>7.48</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>53.13</v>
+        <v>52.91</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.36</v>
+        <v>12.26</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.18</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.18</v>
+        <v>4.22</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.18</v>
+        <v>20.04</v>
       </c>
       <c r="EB10" t="n">
         <v>1.43</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="11">
@@ -5004,94 +5004,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
         <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="F11" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="G11" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="H11" t="n">
-        <v>90.55</v>
+        <v>89.92</v>
       </c>
       <c r="I11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="J11" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="K11" t="n">
-        <v>3.18</v>
+        <v>3.33</v>
       </c>
       <c r="L11" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="M11" t="n">
-        <v>40</v>
+        <v>39.75</v>
       </c>
       <c r="N11" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="O11" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="P11" t="n">
-        <v>11.73</v>
+        <v>12.17</v>
       </c>
       <c r="Q11" t="n">
-        <v>13</v>
+        <v>12.92</v>
       </c>
       <c r="R11" t="n">
-        <v>8.82</v>
+        <v>8.92</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="T11" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>45.45</v>
+        <v>44.08</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>11.27</v>
+        <v>11.08</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.359999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="AC11" t="n">
-        <v>20.64</v>
+        <v>21</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AF11" t="n">
         <v>0.18</v>
@@ -5175,70 +5175,70 @@
         <v>2.27</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.09</v>
+        <v>9.17</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.91</v>
+        <v>5.04</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.18</v>
+        <v>4.13</v>
       </c>
       <c r="BR11" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS11" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BU11" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV11" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW11" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>52.17</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="BZ11" t="n">
         <v>4.55</v>
       </c>
-      <c r="BX11" t="n">
-        <v>54.55</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>4.74</v>
-      </c>
       <c r="CA11" t="n">
-        <v>3.94</v>
+        <v>3.89</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.07</v>
+        <v>4.04</v>
       </c>
       <c r="CC11" t="n">
         <v>5.59</v>
@@ -5250,16 +5250,16 @@
         <v>1.36</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CH11" t="n">
         <v>1.44</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.83</v>
@@ -5268,7 +5268,7 @@
         <v>1.53</v>
       </c>
       <c r="CL11" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CM11" t="n">
         <v>2.37</v>
@@ -5277,22 +5277,22 @@
         <v>1.85</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP11" t="n">
         <v>1.92</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="CR11" t="n">
         <v>1.4</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="CU11" t="n">
         <v>1.48</v>
@@ -5301,37 +5301,37 @@
         <v>2.02</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CX11" t="n">
         <v>1.57</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.37</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DB11" t="n">
         <v>1.32</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DD11" t="n">
         <v>3.14</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="DH11" t="n">
         <v>82.78</v>
@@ -5340,64 +5340,64 @@
         <v>0.13</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.18</v>
+        <v>3.26</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="DM11" t="n">
-        <v>34.09</v>
+        <v>34.22</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.28</v>
+        <v>12.48</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.54</v>
+        <v>13.48</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.460000000000001</v>
+        <v>8.52</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>44.36</v>
+        <v>43.69</v>
       </c>
       <c r="DW11" t="n">
         <v>0.04</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.54</v>
+        <v>10.48</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.68</v>
+        <v>7.65</v>
       </c>
       <c r="DZ11" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.32</v>
+        <v>19.57</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -5407,91 +5407,91 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F12" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="H12" t="n">
-        <v>72.27</v>
+        <v>74.17</v>
       </c>
       <c r="I12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J12" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="K12" t="n">
-        <v>5.45</v>
+        <v>5.25</v>
       </c>
       <c r="L12" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="M12" t="n">
-        <v>32.55</v>
+        <v>32.42</v>
       </c>
       <c r="N12" t="n">
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="P12" t="n">
-        <v>11.82</v>
+        <v>12.08</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.64</v>
+        <v>11.92</v>
       </c>
       <c r="R12" t="n">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="S12" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="T12" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="U12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>48.18</v>
+        <v>47.42</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>13.36</v>
+        <v>12.92</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.27</v>
+        <v>7.92</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.09</v>
+        <v>5</v>
       </c>
       <c r="AC12" t="n">
-        <v>15.82</v>
+        <v>15.67</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
@@ -5578,70 +5578,70 @@
         <v>2.36</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.05</v>
+        <v>3.17</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.82</v>
+        <v>10.78</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.05</v>
+        <v>3.17</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.41</v>
+        <v>0.48</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.73</v>
+        <v>4.83</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.41</v>
+        <v>5.3</v>
       </c>
       <c r="BR12" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS12" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BU12" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BV12" t="n">
-        <v>22.73</v>
+        <v>26.09</v>
       </c>
       <c r="BW12" t="n">
-        <v>9.09</v>
+        <v>13.04</v>
       </c>
       <c r="BX12" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="CC12" t="n">
         <v>3.72</v>
@@ -5653,7 +5653,7 @@
         <v>1.32</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CG12" t="n">
         <v>3.27</v>
@@ -5686,25 +5686,25 @@
         <v>1.75</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CR12" t="n">
         <v>1.36</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="CU12" t="n">
         <v>1.54</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CX12" t="n">
         <v>1.55</v>
@@ -5722,85 +5722,85 @@
         <v>1.29</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="DE12" t="n">
         <v>0.09</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="DH12" t="n">
-        <v>80.54000000000001</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="DI12" t="n">
         <v>0.13</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.09</v>
+        <v>5</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="DM12" t="n">
-        <v>35.36</v>
+        <v>35.17</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.73</v>
+        <v>12.83</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.64</v>
+        <v>12.26</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.82</v>
+        <v>7.13</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48</v>
+        <v>47.61</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.68</v>
+        <v>11.52</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.45</v>
+        <v>7.31</v>
       </c>
       <c r="DZ12" t="n">
         <v>4.22</v>
       </c>
       <c r="EA12" t="n">
-        <v>16.64</v>
+        <v>16.52</v>
       </c>
       <c r="EB12" t="n">
         <v>1.22</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="13">
@@ -5810,13 +5810,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5900,139 +5900,139 @@
         <v>1.73</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.18</v>
+        <v>2.92</v>
       </c>
       <c r="AI13" t="n">
-        <v>86.36</v>
+        <v>84.67</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.82</v>
+        <v>5.5</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AN13" t="n">
-        <v>41.55</v>
+        <v>39.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13.64</v>
+        <v>13.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>14.09</v>
+        <v>13.83</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.36</v>
+        <v>7.42</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>53.45</v>
+        <v>53.17</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BA13" t="n">
-        <v>11.18</v>
+        <v>10.58</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.09</v>
+        <v>5.75</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.09</v>
+        <v>4.83</v>
       </c>
       <c r="BD13" t="n">
-        <v>18</v>
+        <v>17.92</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.45</v>
+        <v>10.26</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.41</v>
+        <v>4.43</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.05</v>
+        <v>5.83</v>
       </c>
       <c r="BR13" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS13" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BT13" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BU13" t="n">
-        <v>27.27</v>
+        <v>30.43</v>
       </c>
       <c r="BV13" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BW13" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX13" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BY13" t="n">
         <v>2.02</v>
@@ -6041,16 +6041,16 @@
         <v>2.26</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.56</v>
+        <v>2.61</v>
       </c>
       <c r="CE13" t="n">
         <v>1.33</v>
@@ -6065,22 +6065,22 @@
         <v>1.48</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.71</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CL13" t="n">
         <v>1.97</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CO13" t="n">
         <v>1.23</v>
@@ -6104,7 +6104,7 @@
         <v>1.48</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CW13" t="n">
         <v>1.77</v>
@@ -6116,10 +6116,10 @@
         <v>1.97</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DB13" t="n">
         <v>1.3</v>
@@ -6134,43 +6134,43 @@
         <v>0.04</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="DH13" t="n">
-        <v>89.05</v>
+        <v>88.05</v>
       </c>
       <c r="DI13" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.82</v>
+        <v>5.65</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DM13" t="n">
-        <v>43.64</v>
+        <v>42.48</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.32</v>
+        <v>13.22</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.77</v>
+        <v>6.83</v>
       </c>
       <c r="DS13" t="n">
         <v>0.04</v>
@@ -6182,25 +6182,25 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>55</v>
+        <v>54.79</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.22</v>
+        <v>11.87</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.45</v>
+        <v>7.22</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.77</v>
+        <v>4.65</v>
       </c>
       <c r="EA13" t="n">
-        <v>17.59</v>
+        <v>17.57</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="EC13" t="n">
         <v>1.91</v>
@@ -6213,13 +6213,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14" t="n">
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
         <v>0.18</v>
@@ -6306,136 +6306,136 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AI14" t="n">
-        <v>99.64</v>
+        <v>102.58</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.91</v>
+        <v>4.67</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN14" t="n">
-        <v>43</v>
+        <v>46.17</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11.73</v>
+        <v>12.17</v>
       </c>
       <c r="AR14" t="n">
-        <v>10.73</v>
+        <v>10.58</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.09</v>
+        <v>7</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>56.09</v>
+        <v>57.08</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA14" t="n">
-        <v>14.36</v>
+        <v>14.58</v>
       </c>
       <c r="BB14" t="n">
-        <v>9.09</v>
+        <v>9.42</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.27</v>
+        <v>5.17</v>
       </c>
       <c r="BD14" t="n">
-        <v>15.73</v>
+        <v>16.25</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.640000000000001</v>
+        <v>8.48</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.91</v>
+        <v>4.78</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT14" t="n">
-        <v>68.18000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="BU14" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BV14" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BW14" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BX14" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BY14" t="n">
         <v>1.78</v>
@@ -6444,31 +6444,31 @@
         <v>1.82</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.38</v>
+        <v>4.35</v>
       </c>
       <c r="CC14" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CH14" t="n">
         <v>1.54</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.7</v>
@@ -6507,7 +6507,7 @@
         <v>1.56</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CW14" t="n">
         <v>1.74</v>
@@ -6537,76 +6537,76 @@
         <v>0.09</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="DH14" t="n">
-        <v>104.86</v>
+        <v>106.17</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.37</v>
+        <v>2.43</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.91</v>
+        <v>4.78</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DM14" t="n">
-        <v>47.5</v>
+        <v>48.96</v>
       </c>
       <c r="DN14" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="DO14" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.54</v>
+        <v>12.74</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.64</v>
+        <v>10.57</v>
       </c>
       <c r="DR14" t="n">
-        <v>6.14</v>
+        <v>6.13</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>57.64</v>
+        <v>58.08</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.09</v>
+        <v>14.22</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.359999999999999</v>
+        <v>8.57</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.72</v>
+        <v>5.65</v>
       </c>
       <c r="EA14" t="n">
-        <v>15.19</v>
+        <v>15.48</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="15">
@@ -6616,94 +6616,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
         <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="G15" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>140.1</v>
+        <v>140.18</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="K15" t="n">
-        <v>6.6</v>
+        <v>6.36</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="M15" t="n">
-        <v>72.90000000000001</v>
+        <v>72</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="O15" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="P15" t="n">
-        <v>10.2</v>
+        <v>10.09</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.6</v>
+        <v>9.18</v>
       </c>
       <c r="R15" t="n">
-        <v>3.8</v>
+        <v>4.09</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="T15" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>68.59999999999999</v>
+        <v>68.45</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.5</v>
+        <v>20.18</v>
       </c>
       <c r="AA15" t="n">
-        <v>13</v>
+        <v>12.73</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.5</v>
+        <v>7.45</v>
       </c>
       <c r="AC15" t="n">
-        <v>17.7</v>
+        <v>17.27</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AF15" t="n">
         <v>0.17</v>
@@ -6790,67 +6790,67 @@
         <v>3.09</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.27</v>
+        <v>9.09</v>
       </c>
       <c r="BI15" t="n">
         <v>3.09</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BL15" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.91</v>
+        <v>3.83</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.77</v>
+        <v>4.7</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT15" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BU15" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BV15" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BW15" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX15" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CA15" t="n">
-        <v>5.93</v>
+        <v>6.05</v>
       </c>
       <c r="CB15" t="n">
-        <v>6.39</v>
+        <v>6.55</v>
       </c>
       <c r="CC15" t="n">
         <v>1.47</v>
@@ -6862,31 +6862,31 @@
         <v>1.2</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CG15" t="n">
-        <v>4.03</v>
+        <v>4.06</v>
       </c>
       <c r="CH15" t="n">
         <v>1.76</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CK15" t="n">
         <v>1.53</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CO15" t="n">
         <v>1.11</v>
@@ -6895,13 +6895,13 @@
         <v>1.43</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CR15" t="n">
         <v>1.34</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CT15" t="n">
         <v>3.34</v>
@@ -6910,104 +6910,104 @@
         <v>1.8</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CX15" t="n">
         <v>1.56</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.39</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="DB15" t="inlineStr"/>
       <c r="DC15" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="DH15" t="n">
-        <v>132.04</v>
+        <v>132.43</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="DK15" t="n">
-        <v>6.23</v>
+        <v>6.13</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="DM15" t="n">
-        <v>67.23</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="DP15" t="n">
-        <v>9.949999999999999</v>
+        <v>9.91</v>
       </c>
       <c r="DQ15" t="n">
-        <v>8.949999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DR15" t="n">
-        <v>4.55</v>
+        <v>4.65</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>68.55</v>
+        <v>68.48</v>
       </c>
       <c r="DW15" t="n">
         <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>17.68</v>
+        <v>17.65</v>
       </c>
       <c r="DY15" t="n">
-        <v>10.91</v>
+        <v>10.87</v>
       </c>
       <c r="DZ15" t="n">
-        <v>6.77</v>
+        <v>6.78</v>
       </c>
       <c r="EA15" t="n">
-        <v>17.55</v>
+        <v>17.35</v>
       </c>
       <c r="EB15" t="n">
         <v>2.08</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -7017,13 +7017,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" t="n">
         <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7107,139 +7107,139 @@
         <v>2.09</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AI16" t="n">
-        <v>80.81999999999999</v>
+        <v>78.67</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AK16" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AL16" t="n">
         <v>3</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AN16" t="n">
-        <v>31</v>
+        <v>30.25</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.73</v>
+        <v>10.42</v>
       </c>
       <c r="AR16" t="n">
-        <v>10.64</v>
+        <v>10.83</v>
       </c>
       <c r="AS16" t="n">
         <v>9</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>50.55</v>
+        <v>50.08</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.550000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.18</v>
+        <v>5.92</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="BD16" t="n">
-        <v>17.36</v>
+        <v>17.17</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.050000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.09</v>
+        <v>4.13</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.09</v>
+        <v>4.35</v>
       </c>
       <c r="BR16" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT16" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BU16" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BV16" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BW16" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BX16" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BY16" t="n">
         <v>2.36</v>
@@ -7248,37 +7248,37 @@
         <v>2.54</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.97</v>
+        <v>3.94</v>
       </c>
       <c r="CC16" t="n">
-        <v>5.35</v>
+        <v>5.23</v>
       </c>
       <c r="CD16" t="n">
-        <v>5</v>
+        <v>4.94</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CL16" t="n">
         <v>2.15</v>
@@ -7293,28 +7293,28 @@
         <v>1.25</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CX16" t="n">
         <v>1.66</v>
@@ -7341,43 +7341,43 @@
         <v>0.04</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="DG16" t="n">
         <v>1.91</v>
       </c>
       <c r="DH16" t="n">
-        <v>92.31999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.09</v>
+        <v>2.22</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.18</v>
+        <v>4.13</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM16" t="n">
-        <v>39.22</v>
+        <v>38.48</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.41</v>
+        <v>11.22</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.18</v>
+        <v>11.26</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.64</v>
+        <v>7.69</v>
       </c>
       <c r="DS16" t="n">
         <v>0.22</v>
@@ -7389,28 +7389,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>54.18</v>
+        <v>53.78</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.36</v>
+        <v>11.09</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.77</v>
+        <v>7.57</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.59</v>
+        <v>3.52</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.81</v>
+        <v>16.74</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="17">
@@ -7420,13 +7420,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" t="n">
         <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
         <v>0.09</v>
@@ -7510,139 +7510,139 @@
         <v>1.73</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.91</v>
+        <v>1.17</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AI17" t="n">
-        <v>89.27</v>
+        <v>89.17</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.09</v>
+        <v>5.08</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AN17" t="n">
-        <v>39.45</v>
+        <v>38.92</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.18</v>
+        <v>12.08</v>
       </c>
       <c r="AR17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.449999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>51.36</v>
+        <v>51.83</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BA17" t="n">
-        <v>10.18</v>
+        <v>10.33</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.91</v>
+        <v>6.75</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.27</v>
+        <v>3.58</v>
       </c>
       <c r="BD17" t="n">
-        <v>18</v>
+        <v>18.67</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.59</v>
+        <v>10.52</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.59</v>
+        <v>0.7</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.27</v>
+        <v>4.22</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.45</v>
+        <v>5.48</v>
       </c>
       <c r="BR17" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS17" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT17" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BU17" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BV17" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BY17" t="n">
         <v>2.66</v>
@@ -7651,43 +7651,43 @@
         <v>2.88</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.68</v>
+        <v>3.59</v>
       </c>
       <c r="CE17" t="n">
         <v>1.31</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CK17" t="n">
         <v>1.59</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CN17" t="n">
         <v>1.79</v>
@@ -7699,19 +7699,19 @@
         <v>1.73</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="CR17" t="n">
         <v>1.36</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="CT17" t="n">
         <v>3.2</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CV17" t="n">
         <v>2.34</v>
@@ -7726,94 +7726,94 @@
         <v>1.94</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DB17" t="n">
         <v>1.28</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="DE17" t="n">
         <v>0.13</v>
       </c>
       <c r="DF17" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="DG17" t="n">
         <v>2.91</v>
       </c>
       <c r="DH17" t="n">
-        <v>95.09</v>
+        <v>94.78</v>
       </c>
       <c r="DI17" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.54</v>
+        <v>5.52</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="DM17" t="n">
-        <v>50.22</v>
+        <v>49.48</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="DO17" t="n">
         <v>2.13</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.14</v>
+        <v>12.56</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12</v>
+        <v>12.22</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.140000000000001</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>51.18</v>
+        <v>51.43</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.27</v>
+        <v>13.21</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.82</v>
+        <v>8.65</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.45</v>
+        <v>4.57</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.09</v>
+        <v>19.39</v>
       </c>
       <c r="EB17" t="n">
         <v>1.52</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="18">
@@ -7823,10 +7823,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
         <v>12</v>
@@ -7838,79 +7838,79 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="H18" t="n">
-        <v>102.5</v>
+        <v>100.09</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="K18" t="n">
-        <v>4.8</v>
+        <v>4.73</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M18" t="n">
-        <v>44.8</v>
+        <v>44.18</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="O18" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="P18" t="n">
-        <v>10.2</v>
+        <v>10.27</v>
       </c>
       <c r="Q18" t="n">
-        <v>12</v>
+        <v>11.91</v>
       </c>
       <c r="R18" t="n">
-        <v>7</v>
+        <v>6.55</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="T18" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>50.9</v>
+        <v>50.82</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z18" t="n">
-        <v>12.3</v>
+        <v>12.36</v>
       </c>
       <c r="AA18" t="n">
-        <v>7</v>
+        <v>6.91</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.3</v>
+        <v>5.45</v>
       </c>
       <c r="AC18" t="n">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7994,70 +7994,70 @@
         <v>2.25</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="BH18" t="n">
-        <v>8.09</v>
+        <v>8</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="BO18" t="n">
         <v>1.09</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.36</v>
+        <v>3.43</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.09</v>
+        <v>3.96</v>
       </c>
       <c r="BR18" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS18" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT18" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BU18" t="n">
-        <v>31.82</v>
+        <v>34.78</v>
       </c>
       <c r="BV18" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BW18" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX18" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BY18" t="n">
         <v>2.32</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="CC18" t="n">
         <v>3.56</v>
@@ -8072,7 +8072,7 @@
         <v>2.55</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CH18" t="n">
         <v>1.49</v>
@@ -8087,7 +8087,7 @@
         <v>1.68</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CM18" t="n">
         <v>2.14</v>
@@ -8132,10 +8132,10 @@
         <v>2.16</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="DC18" t="n">
         <v>1.81</v>
@@ -8147,76 +8147,76 @@
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="DH18" t="n">
-        <v>98</v>
+        <v>97.04000000000001</v>
       </c>
       <c r="DI18" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM18" t="n">
-        <v>42.91</v>
+        <v>42.69</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="DP18" t="n">
-        <v>11.32</v>
+        <v>11.3</v>
       </c>
       <c r="DQ18" t="n">
-        <v>12.82</v>
+        <v>12.74</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.27</v>
+        <v>7.05</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>51.68</v>
+        <v>51.61</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.18</v>
+        <v>11.26</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.86</v>
+        <v>6.83</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.32</v>
+        <v>4.43</v>
       </c>
       <c r="EA18" t="n">
-        <v>15.96</v>
+        <v>16.26</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="19">
@@ -8226,94 +8226,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
         <v>11</v>
       </c>
       <c r="E19" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F19" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>2.64</v>
+        <v>3.08</v>
       </c>
       <c r="H19" t="n">
-        <v>83.73</v>
+        <v>87.83</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="K19" t="n">
-        <v>4.91</v>
+        <v>5.5</v>
       </c>
       <c r="L19" t="n">
-        <v>0.09</v>
+        <v>0.25</v>
       </c>
       <c r="M19" t="n">
-        <v>44.36</v>
+        <v>45.83</v>
       </c>
       <c r="N19" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="O19" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="P19" t="n">
-        <v>13.64</v>
+        <v>13.58</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.73</v>
+        <v>12.25</v>
       </c>
       <c r="R19" t="n">
-        <v>6.09</v>
+        <v>5.83</v>
       </c>
       <c r="S19" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T19" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="U19" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V19" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>41.91</v>
+        <v>43</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>14.73</v>
+        <v>15.42</v>
       </c>
       <c r="AA19" t="n">
-        <v>9.82</v>
+        <v>10.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.91</v>
+        <v>5.33</v>
       </c>
       <c r="AC19" t="n">
-        <v>17.27</v>
+        <v>18.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8397,70 +8397,70 @@
         <v>3.09</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.77</v>
+        <v>10</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.23</v>
+        <v>4.26</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.23</v>
+        <v>5.43</v>
       </c>
       <c r="BR19" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS19" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BT19" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BU19" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV19" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW19" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX19" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="CC19" t="n">
         <v>3.2</v>
@@ -8469,22 +8469,22 @@
         <v>3.27</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="CH19" t="n">
         <v>1.4</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CK19" t="n">
         <v>1.64</v>
@@ -8493,34 +8493,34 @@
         <v>2.13</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CN19" t="n">
         <v>1.74</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="CR19" t="n">
         <v>1.43</v>
       </c>
       <c r="CS19" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CU19" t="n">
         <v>1.41</v>
       </c>
       <c r="CV19" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CW19" t="n">
         <v>1.9</v>
@@ -8547,79 +8547,79 @@
         <v>3.39</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.41</v>
+        <v>2.65</v>
       </c>
       <c r="DH19" t="n">
-        <v>88.36</v>
+        <v>90.3</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.73</v>
+        <v>5.05</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="DM19" t="n">
-        <v>44.14</v>
+        <v>44.91</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.46</v>
+        <v>14.39</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.82</v>
+        <v>11.61</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.72</v>
+        <v>6.56</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>42.73</v>
+        <v>43.26</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.82</v>
+        <v>13.26</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.41</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.41</v>
+        <v>4.65</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.91</v>
+        <v>17.7</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
         <v>0.08</v>
@@ -1472,136 +1472,136 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AH2" t="n">
         <v>2</v>
       </c>
       <c r="AI2" t="n">
-        <v>73.45</v>
+        <v>72.75</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AN2" t="n">
-        <v>29.73</v>
+        <v>29.58</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.18</v>
+        <v>9.25</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.18</v>
+        <v>11</v>
       </c>
       <c r="AS2" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>39.91</v>
+        <v>38.92</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.82</v>
+        <v>7.67</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.36</v>
+        <v>5.25</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="BD2" t="n">
-        <v>15.55</v>
+        <v>15.58</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="BG2" t="n">
         <v>2.17</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BI2" t="n">
         <v>2.17</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="BR2" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS2" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BT2" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BU2" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BV2" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX2" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BY2" t="n">
         <v>3.58</v>
@@ -1610,31 +1610,31 @@
         <v>3.86</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.03</v>
+        <v>4.06</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.26</v>
+        <v>4.29</v>
       </c>
       <c r="CC2" t="n">
-        <v>7.9</v>
+        <v>7.81</v>
       </c>
       <c r="CD2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="CE2" t="n">
         <v>1.4</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.92</v>
@@ -1643,7 +1643,7 @@
         <v>1.67</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CM2" t="n">
         <v>2.11</v>
@@ -1652,13 +1652,13 @@
         <v>1.69</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="CR2" t="n">
         <v>1.45</v>
@@ -1673,7 +1673,7 @@
         <v>1.44</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CW2" t="n">
         <v>1.99</v>
@@ -1703,43 +1703,43 @@
         <v>0.04</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="DH2" t="n">
-        <v>73.13</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.52</v>
+        <v>3.46</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DM2" t="n">
-        <v>31</v>
+        <v>30.88</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.04</v>
+        <v>11</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.31</v>
+        <v>11.21</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.48</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DS2" t="n">
         <v>0.08</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>43</v>
+        <v>42.38</v>
       </c>
       <c r="DW2" t="n">
         <v>0.04</v>
       </c>
       <c r="DX2" t="n">
-        <v>9.35</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="DY2" t="n">
-        <v>5.87</v>
+        <v>5.79</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.79</v>
+        <v>16.75</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="3">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
         <v>11</v>
@@ -2600,49 +2600,49 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="G5" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="H5" t="n">
-        <v>92.5</v>
+        <v>91.62</v>
       </c>
       <c r="I5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="J5" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="K5" t="n">
-        <v>5.25</v>
+        <v>5.08</v>
       </c>
       <c r="L5" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="M5" t="n">
-        <v>47.08</v>
+        <v>46.46</v>
       </c>
       <c r="N5" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="P5" t="n">
-        <v>13.42</v>
+        <v>13.31</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.25</v>
+        <v>13</v>
       </c>
       <c r="R5" t="n">
-        <v>6.5</v>
+        <v>6.85</v>
       </c>
       <c r="S5" t="n">
         <v>0.92</v>
       </c>
       <c r="T5" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="U5" t="n">
         <v>0.08</v>
@@ -2654,28 +2654,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>48.33</v>
+        <v>47.08</v>
       </c>
       <c r="Y5" t="n">
         <v>0.08</v>
       </c>
       <c r="Z5" t="n">
-        <v>12.33</v>
+        <v>12.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.17</v>
+        <v>8.15</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.67</v>
+        <v>20.23</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>2.18</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.52</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.22</v>
+        <v>4.17</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.3</v>
+        <v>5.21</v>
       </c>
       <c r="BR5" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BS5" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BT5" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BV5" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX5" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.01</v>
+        <v>3.59</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.36</v>
+        <v>3.88</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.96</v>
+        <v>4.05</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.02</v>
+        <v>4.1</v>
       </c>
       <c r="CC5" t="n">
         <v>6.23</v>
@@ -2831,16 +2831,16 @@
         <v>6.84</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CI5" t="n">
         <v>1.94</v>
@@ -2849,37 +2849,37 @@
         <v>1.82</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CL5" t="n">
         <v>2.08</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="CR5" t="n">
         <v>1.42</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="CT5" t="n">
         <v>2.96</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CV5" t="n">
         <v>2</v>
@@ -2894,7 +2894,7 @@
         <v>2.03</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="DA5" t="n">
         <v>1.79</v>
@@ -2903,52 +2903,52 @@
         <v>1.34</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="DG5" t="n">
         <v>2.09</v>
       </c>
       <c r="DH5" t="n">
-        <v>87.83</v>
+        <v>87.55</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.65</v>
+        <v>4.58</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="DM5" t="n">
-        <v>42.35</v>
+        <v>42.21</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="DP5" t="n">
-        <v>13.39</v>
+        <v>13.33</v>
       </c>
       <c r="DQ5" t="n">
-        <v>13.74</v>
+        <v>13.58</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.57</v>
+        <v>7.71</v>
       </c>
       <c r="DS5" t="n">
         <v>0.04</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>46.69</v>
+        <v>46.09</v>
       </c>
       <c r="DW5" t="n">
         <v>0.08</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.69</v>
+        <v>10.66</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.13</v>
+        <v>7.16</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.57</v>
+        <v>3.5</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.91</v>
+        <v>18.75</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n">
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
         <v>0.17</v>
@@ -3081,139 +3081,139 @@
         <v>1.67</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="AI6" t="n">
-        <v>89.27</v>
+        <v>88.83</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.82</v>
+        <v>5.08</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AN6" t="n">
-        <v>40.91</v>
+        <v>42.08</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ6" t="n">
-        <v>13.91</v>
+        <v>13.33</v>
       </c>
       <c r="AR6" t="n">
-        <v>13</v>
+        <v>12.67</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.91</v>
+        <v>6.67</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>48.36</v>
+        <v>48.08</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA6" t="n">
-        <v>13.09</v>
+        <v>14.08</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.27</v>
+        <v>9.25</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="BD6" t="n">
-        <v>16.18</v>
+        <v>15.58</v>
       </c>
       <c r="BE6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BN6" t="n">
         <v>1.46</v>
       </c>
-      <c r="BF6" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>9.609999999999999</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1.48</v>
-      </c>
       <c r="BO6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.04</v>
+        <v>4.08</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.78</v>
+        <v>4.79</v>
       </c>
       <c r="BR6" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS6" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT6" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV6" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BY6" t="n">
         <v>1.89</v>
@@ -3222,25 +3222,25 @@
         <v>1.91</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CF6" t="n">
         <v>2.44</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CH6" t="n">
         <v>1.53</v>
@@ -3252,25 +3252,25 @@
         <v>1.65</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CL6" t="n">
         <v>2.02</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CO6" t="n">
         <v>1.2</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CR6" t="n">
         <v>1.35</v>
@@ -3294,13 +3294,13 @@
         <v>1.59</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DB6" t="n">
         <v>1.27</v>
@@ -3312,46 +3312,46 @@
         <v>2.76</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="DH6" t="n">
-        <v>89.13</v>
+        <v>88.92</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.52</v>
+        <v>5.62</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="DM6" t="n">
-        <v>43.96</v>
+        <v>44.42</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.74</v>
+        <v>13.46</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.83</v>
+        <v>12.67</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.13</v>
+        <v>6.04</v>
       </c>
       <c r="DS6" t="n">
         <v>0.17</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>49.17</v>
+        <v>49</v>
       </c>
       <c r="DW6" t="n">
         <v>0.17</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.09</v>
+        <v>14.54</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.949999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.13</v>
+        <v>5.12</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.91</v>
+        <v>16.58</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="7">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
         <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F10" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="G10" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="H10" t="n">
-        <v>104.92</v>
+        <v>110.08</v>
       </c>
       <c r="I10" t="n">
         <v>0.08</v>
       </c>
       <c r="J10" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="K10" t="n">
         <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="M10" t="n">
-        <v>48</v>
+        <v>48.69</v>
       </c>
       <c r="N10" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="P10" t="n">
-        <v>12.75</v>
+        <v>12.46</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.42</v>
+        <v>11.31</v>
       </c>
       <c r="R10" t="n">
-        <v>6.92</v>
+        <v>6.77</v>
       </c>
       <c r="S10" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="T10" t="n">
         <v>2.08</v>
       </c>
       <c r="U10" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="V10" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>52.33</v>
+        <v>53.85</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.08</v>
+        <v>12.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.33</v>
+        <v>8.15</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.75</v>
+        <v>4.69</v>
       </c>
       <c r="AC10" t="n">
-        <v>20.08</v>
+        <v>19.62</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AF10" t="n">
         <v>0.09</v>
@@ -4774,70 +4774,70 @@
         <v>2.82</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.22</v>
+        <v>3.17</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.220000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.22</v>
+        <v>3.17</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="BN10" t="n">
         <v>2</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.35</v>
+        <v>4.29</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="BR10" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS10" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BT10" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BU10" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BV10" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BW10" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX10" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.26</v>
+        <v>4.27</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.27</v>
+        <v>4.3</v>
       </c>
       <c r="CC10" t="n">
         <v>2.23</v>
@@ -4849,19 +4849,19 @@
         <v>1.26</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CK10" t="n">
         <v>1.56</v>
@@ -4882,7 +4882,7 @@
         <v>1.56</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CR10" t="n">
         <v>1.35</v>
@@ -4897,22 +4897,22 @@
         <v>1.66</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.35</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DB10" t="inlineStr"/>
       <c r="DC10" t="n">
@@ -4922,46 +4922,46 @@
         <v>2.41</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="DH10" t="n">
-        <v>104.79</v>
+        <v>107.59</v>
       </c>
       <c r="DI10" t="n">
         <v>0.17</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.83</v>
+        <v>4.84</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM10" t="n">
-        <v>48.65</v>
+        <v>49</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.48</v>
+        <v>13.29</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.13</v>
+        <v>11.09</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.48</v>
+        <v>7.38</v>
       </c>
       <c r="DS10" t="n">
         <v>0.17</v>
@@ -4973,28 +4973,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>52.91</v>
+        <v>53.71</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.26</v>
+        <v>12.17</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.039999999999999</v>
+        <v>7.96</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.04</v>
+        <v>19.79</v>
       </c>
       <c r="EB10" t="n">
         <v>1.43</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="11">
@@ -6616,13 +6616,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" t="n">
         <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E15" t="n">
         <v>0.18</v>
@@ -6706,139 +6706,139 @@
         <v>1.09</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AH15" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AI15" t="n">
-        <v>125.33</v>
+        <v>126.54</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.92</v>
+        <v>5.69</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AN15" t="n">
-        <v>62.5</v>
+        <v>62.62</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.75</v>
+        <v>9.77</v>
       </c>
       <c r="AR15" t="n">
-        <v>9.25</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.17</v>
+        <v>5.38</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>68.5</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="AZ15" t="n">
         <v>0.08</v>
       </c>
       <c r="BA15" t="n">
-        <v>15.33</v>
+        <v>15.85</v>
       </c>
       <c r="BB15" t="n">
-        <v>9.17</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="BC15" t="n">
-        <v>6.17</v>
+        <v>6.38</v>
       </c>
       <c r="BD15" t="n">
-        <v>17.42</v>
+        <v>16.77</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.09</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="BL15" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.83</v>
+        <v>3.79</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.7</v>
+        <v>4.62</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>73.91</v>
+        <v>70.83</v>
       </c>
       <c r="BT15" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BU15" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BV15" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BW15" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX15" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BY15" t="n">
         <v>1.23</v>
@@ -6850,13 +6850,13 @@
         <v>6.05</v>
       </c>
       <c r="CB15" t="n">
-        <v>6.55</v>
+        <v>6.54</v>
       </c>
       <c r="CC15" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="CD15" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="CE15" t="n">
         <v>1.2</v>
@@ -6865,13 +6865,13 @@
         <v>2.08</v>
       </c>
       <c r="CG15" t="n">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="CH15" t="n">
         <v>1.76</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.76</v>
@@ -6880,7 +6880,7 @@
         <v>1.53</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CM15" t="n">
         <v>2.38</v>
@@ -6901,7 +6901,7 @@
         <v>1.34</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CT15" t="n">
         <v>3.34</v>
@@ -6910,104 +6910,104 @@
         <v>1.8</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CX15" t="n">
         <v>1.56</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.39</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="DB15" t="inlineStr"/>
       <c r="DC15" t="n">
         <v>1.47</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.48</v>
+        <v>3.38</v>
       </c>
       <c r="DH15" t="n">
-        <v>132.43</v>
+        <v>132.79</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="DK15" t="n">
-        <v>6.13</v>
+        <v>6</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="DM15" t="n">
-        <v>67.04000000000001</v>
+        <v>66.92</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DP15" t="n">
-        <v>9.91</v>
+        <v>9.92</v>
       </c>
       <c r="DQ15" t="n">
-        <v>9.220000000000001</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DR15" t="n">
-        <v>4.65</v>
+        <v>4.79</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>68.48</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="DW15" t="n">
         <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>17.65</v>
+        <v>17.83</v>
       </c>
       <c r="DY15" t="n">
-        <v>10.87</v>
+        <v>10.96</v>
       </c>
       <c r="DZ15" t="n">
-        <v>6.78</v>
+        <v>6.87</v>
       </c>
       <c r="EA15" t="n">
-        <v>17.35</v>
+        <v>17</v>
       </c>
       <c r="EB15" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="EC15" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="16">
@@ -7420,94 +7420,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F17" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>3.91</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
-        <v>100.91</v>
+        <v>103.75</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J17" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="K17" t="n">
         <v>6</v>
       </c>
       <c r="L17" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M17" t="n">
-        <v>61</v>
+        <v>59.42</v>
       </c>
       <c r="N17" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="O17" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="P17" t="n">
-        <v>13.09</v>
+        <v>12.75</v>
       </c>
       <c r="Q17" t="n">
         <v>13</v>
       </c>
       <c r="R17" t="n">
-        <v>6.82</v>
+        <v>7.08</v>
       </c>
       <c r="S17" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="U17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>51</v>
+        <v>52.17</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z17" t="n">
-        <v>16.36</v>
+        <v>15.83</v>
       </c>
       <c r="AA17" t="n">
-        <v>10.73</v>
+        <v>10.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>5.64</v>
+        <v>5.33</v>
       </c>
       <c r="AC17" t="n">
-        <v>20.18</v>
+        <v>20.42</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AF17" t="n">
         <v>0.17</v>
@@ -7591,70 +7591,70 @@
         <v>1.75</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.13</v>
+        <v>3.04</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.52</v>
+        <v>10.38</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.13</v>
+        <v>3.04</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.22</v>
+        <v>4.08</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.48</v>
+        <v>5.5</v>
       </c>
       <c r="BR17" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS17" t="n">
-        <v>82.61</v>
+        <v>79.17</v>
       </c>
       <c r="BT17" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BU17" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BV17" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="CC17" t="n">
         <v>3.35</v>
@@ -7666,10 +7666,10 @@
         <v>1.31</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CH17" t="n">
         <v>1.52</v>
@@ -7681,22 +7681,22 @@
         <v>1.63</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CO17" t="n">
         <v>1.21</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CQ17" t="n">
         <v>2.78</v>
@@ -7705,7 +7705,7 @@
         <v>1.36</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CT17" t="n">
         <v>3.2</v>
@@ -7714,19 +7714,19 @@
         <v>1.55</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="DA17" t="n">
         <v>1.89</v>
@@ -7735,52 +7735,52 @@
         <v>1.28</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="DH17" t="n">
-        <v>94.78</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="DI17" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.52</v>
+        <v>5.54</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DM17" t="n">
-        <v>49.48</v>
+        <v>49.17</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.56</v>
+        <v>12.42</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.22</v>
+        <v>12.25</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.130000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DS17" t="n">
         <v>0.08</v>
@@ -7792,28 +7792,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>51.43</v>
+        <v>52</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.21</v>
+        <v>13.08</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.65</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.57</v>
+        <v>4.46</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.39</v>
+        <v>19.55</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="18">
@@ -7823,10 +7823,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
         <v>12</v>
@@ -7838,79 +7838,79 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="H18" t="n">
-        <v>100.09</v>
+        <v>98.42</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="J18" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="K18" t="n">
-        <v>4.73</v>
+        <v>4.5</v>
       </c>
       <c r="L18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="M18" t="n">
-        <v>44.18</v>
+        <v>42.67</v>
       </c>
       <c r="N18" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="O18" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="P18" t="n">
-        <v>10.27</v>
+        <v>10.17</v>
       </c>
       <c r="Q18" t="n">
-        <v>11.91</v>
+        <v>11.58</v>
       </c>
       <c r="R18" t="n">
-        <v>6.55</v>
+        <v>7.25</v>
       </c>
       <c r="S18" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="T18" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="U18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>50.82</v>
+        <v>51.17</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z18" t="n">
-        <v>12.36</v>
+        <v>12</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.91</v>
+        <v>6.58</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.45</v>
+        <v>5.42</v>
       </c>
       <c r="AC18" t="n">
-        <v>15</v>
+        <v>14.92</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7994,58 +7994,58 @@
         <v>2.25</v>
       </c>
       <c r="BG18" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BH18" t="n">
-        <v>8</v>
+        <v>8.08</v>
       </c>
       <c r="BI18" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="BR18" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS18" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BT18" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BU18" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BV18" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BW18" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX18" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BY18" t="n">
         <v>2.32</v>
@@ -8054,10 +8054,10 @@
         <v>2.35</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="CC18" t="n">
         <v>3.56</v>
@@ -8066,28 +8066,28 @@
         <v>3.64</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CH18" t="n">
         <v>1.49</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CK18" t="n">
         <v>1.68</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CM18" t="n">
         <v>2.14</v>
@@ -8099,7 +8099,7 @@
         <v>1.22</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CQ18" t="n">
         <v>2.8</v>
@@ -8108,7 +8108,7 @@
         <v>1.37</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CT18" t="n">
         <v>3.14</v>
@@ -8117,19 +8117,19 @@
         <v>1.51</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CX18" t="n">
         <v>1.7</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DA18" t="n">
         <v>1.71</v>
@@ -8147,73 +8147,73 @@
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DH18" t="n">
-        <v>97.04000000000001</v>
+        <v>96.34</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.87</v>
+        <v>3.79</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DM18" t="n">
-        <v>42.69</v>
+        <v>42</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="DP18" t="n">
-        <v>11.3</v>
+        <v>11.21</v>
       </c>
       <c r="DQ18" t="n">
-        <v>12.74</v>
+        <v>12.54</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.05</v>
+        <v>7.38</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>51.61</v>
+        <v>51.75</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.26</v>
+        <v>11.12</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.83</v>
+        <v>6.66</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.43</v>
+        <v>4.46</v>
       </c>
       <c r="EA18" t="n">
-        <v>16.26</v>
+        <v>16.17</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="EC18" t="n">
         <v>1.92</v>
@@ -8226,13 +8226,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C19" t="n">
         <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
         <v>0.25</v>
@@ -8319,136 +8319,136 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AI19" t="n">
-        <v>93</v>
+        <v>93.25</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="AL19" t="n">
-        <v>4.55</v>
+        <v>4.25</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN19" t="n">
-        <v>43.91</v>
+        <v>43.58</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="AP19" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ19" t="n">
-        <v>15.27</v>
+        <v>15.08</v>
       </c>
       <c r="AR19" t="n">
-        <v>10.91</v>
+        <v>10.75</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.36</v>
+        <v>7.5</v>
       </c>
       <c r="AT19" t="n">
         <v>1</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>43.55</v>
+        <v>42.83</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA19" t="n">
-        <v>10.91</v>
+        <v>10.75</v>
       </c>
       <c r="BB19" t="n">
         <v>7</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.91</v>
+        <v>3.75</v>
       </c>
       <c r="BD19" t="n">
-        <v>16.55</v>
+        <v>15.92</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="BH19" t="n">
-        <v>10</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BO19" t="n">
         <v>1.04</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.26</v>
+        <v>4.12</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.43</v>
+        <v>5.46</v>
       </c>
       <c r="BR19" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS19" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BT19" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BU19" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV19" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW19" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX19" t="n">
-        <v>43.48</v>
+        <v>41.67</v>
       </c>
       <c r="BY19" t="n">
         <v>2.48</v>
@@ -8463,163 +8463,163 @@
         <v>3.59</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.27</v>
+        <v>3.31</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CF19" t="n">
         <v>2.86</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CH19" t="n">
         <v>1.4</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CK19" t="n">
         <v>1.64</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="CR19" t="n">
         <v>1.43</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CU19" t="n">
         <v>1.41</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CY19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="CZ19" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="DA19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DB19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DC19" t="n">
         <v>2.1</v>
       </c>
-      <c r="CZ19" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="DA19" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="DB19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="DC19" t="n">
-        <v>2.11</v>
-      </c>
       <c r="DD19" t="n">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="DH19" t="n">
-        <v>90.3</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.05</v>
+        <v>4.88</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DM19" t="n">
-        <v>44.91</v>
+        <v>44.71</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.39</v>
+        <v>14.33</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.61</v>
+        <v>11.5</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.56</v>
+        <v>6.66</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>43.26</v>
+        <v>42.92</v>
       </c>
       <c r="DW19" t="n">
         <v>0.08</v>
       </c>
       <c r="DX19" t="n">
-        <v>13.26</v>
+        <v>13.08</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.609999999999999</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.65</v>
+        <v>4.54</v>
       </c>
       <c r="EA19" t="n">
-        <v>17.7</v>
+        <v>17.33</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,139 +1872,139 @@
         <v>1.83</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="AI3" t="n">
-        <v>88.27</v>
+        <v>90.33</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.27</v>
+        <v>4.5</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="AN3" t="n">
-        <v>37.18</v>
+        <v>37.17</v>
       </c>
       <c r="AO3" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13.82</v>
+        <v>13.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.73</v>
+        <v>13.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.18</v>
+        <v>8</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>46</v>
+        <v>46.33</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.09</v>
+        <v>10.08</v>
       </c>
       <c r="BB3" t="n">
         <v>7</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="BD3" t="n">
-        <v>19.73</v>
+        <v>19.75</v>
       </c>
       <c r="BE3" t="n">
         <v>1.13</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.48</v>
+        <v>9.5</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.7</v>
+        <v>5.71</v>
       </c>
       <c r="BR3" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS3" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BT3" t="n">
-        <v>39.13</v>
+        <v>41.67</v>
       </c>
       <c r="BU3" t="n">
-        <v>21.74</v>
+        <v>25</v>
       </c>
       <c r="BV3" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX3" t="n">
-        <v>34.78</v>
+        <v>37.5</v>
       </c>
       <c r="BY3" t="n">
         <v>3.7</v>
@@ -2013,169 +2013,169 @@
         <v>3.97</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="CC3" t="n">
-        <v>4.98</v>
+        <v>4.92</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.17</v>
+        <v>5.07</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="CH3" t="n">
         <v>1.43</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.82</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CO3" t="n">
         <v>1.28</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="CU3" t="n">
         <v>1.45</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DB3" t="n">
         <v>1.34</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DD3" t="n">
         <v>3.28</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="DH3" t="n">
-        <v>89.87</v>
+        <v>90.83</v>
       </c>
       <c r="DI3" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.87</v>
+        <v>4.96</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="DM3" t="n">
-        <v>41.74</v>
+        <v>41.54</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.61</v>
+        <v>13.46</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.13</v>
+        <v>14</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.82</v>
+        <v>6.79</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>44.22</v>
+        <v>44.46</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.83</v>
+        <v>10.79</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.65</v>
+        <v>7.62</v>
       </c>
       <c r="DZ3" t="n">
         <v>3.17</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.05</v>
+        <v>19.08</v>
       </c>
       <c r="EB3" t="n">
         <v>1.21</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
         <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
         <v>0.33</v>
@@ -2278,136 +2278,136 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AI4" t="n">
-        <v>82.55</v>
+        <v>81</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AN4" t="n">
-        <v>39</v>
+        <v>37.42</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13.55</v>
+        <v>13.33</v>
       </c>
       <c r="AR4" t="n">
-        <v>12.18</v>
+        <v>12.33</v>
       </c>
       <c r="AS4" t="n">
-        <v>7</v>
+        <v>7.17</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>40.91</v>
+        <v>40.33</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.18</v>
+        <v>8.92</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.09</v>
+        <v>6</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.09</v>
+        <v>2.92</v>
       </c>
       <c r="BD4" t="n">
-        <v>18.55</v>
+        <v>18.08</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.52</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BL4" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.65</v>
+        <v>4.96</v>
       </c>
       <c r="BR4" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS4" t="n">
-        <v>82.61</v>
+        <v>79.17</v>
       </c>
       <c r="BT4" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BU4" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BV4" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX4" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BY4" t="n">
         <v>2.99</v>
@@ -2416,31 +2416,31 @@
         <v>3.34</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.62</v>
+        <v>3.63</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.98</v>
+        <v>3.84</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.03</v>
+        <v>3.87</v>
       </c>
       <c r="CE4" t="n">
         <v>1.35</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.73</v>
@@ -2449,13 +2449,13 @@
         <v>1.65</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CO4" t="n">
         <v>1.26</v>
@@ -2464,16 +2464,16 @@
         <v>1.86</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CR4" t="n">
         <v>1.4</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CU4" t="n">
         <v>1.48</v>
@@ -2485,13 +2485,13 @@
         <v>1.78</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DA4" t="n">
         <v>1.73</v>
@@ -2500,85 +2500,85 @@
         <v>1.33</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DH4" t="n">
-        <v>91.92</v>
+        <v>90.75</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM4" t="n">
-        <v>38.35</v>
+        <v>37.58</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="DO4" t="n">
         <v>1.7</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.44</v>
+        <v>13.33</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.61</v>
+        <v>11.7</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.61</v>
+        <v>7.67</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>42.65</v>
+        <v>42.29</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.78</v>
+        <v>11.54</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.83</v>
+        <v>7.71</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.96</v>
+        <v>3.83</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.39</v>
+        <v>17.2</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="5">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
         <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F7" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="G7" t="n">
         <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>108.27</v>
+        <v>106.83</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="K7" t="n">
-        <v>6.64</v>
+        <v>6.42</v>
       </c>
       <c r="L7" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="M7" t="n">
-        <v>56</v>
+        <v>55.33</v>
       </c>
       <c r="N7" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="O7" t="n">
-        <v>3.64</v>
+        <v>3.42</v>
       </c>
       <c r="P7" t="n">
-        <v>10.64</v>
+        <v>10.67</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.73</v>
+        <v>12.92</v>
       </c>
       <c r="R7" t="n">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="S7" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="U7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>52.45</v>
+        <v>54.17</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z7" t="n">
-        <v>15.82</v>
+        <v>15.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.91</v>
+        <v>10.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.91</v>
+        <v>4.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>17.27</v>
+        <v>19.08</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AF7" t="n">
         <v>0.17</v>
@@ -3565,70 +3565,70 @@
         <v>2.42</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.13</v>
+        <v>9.92</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="BL7" t="n">
         <v>1.04</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BN7" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.04</v>
+        <v>4.92</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.09</v>
+        <v>5</v>
       </c>
       <c r="BR7" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS7" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BT7" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV7" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BW7" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BX7" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.89</v>
+        <v>3.94</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.02</v>
+        <v>4.03</v>
       </c>
       <c r="CC7" t="n">
         <v>2.92</v>
@@ -3649,22 +3649,22 @@
         <v>1.47</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.74</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CO7" t="n">
         <v>1.24</v>
@@ -3679,7 +3679,7 @@
         <v>1.38</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CT7" t="n">
         <v>3.12</v>
@@ -3688,19 +3688,19 @@
         <v>1.49</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY7" t="n">
         <v>2.02</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="DA7" t="n">
         <v>1.81</v>
@@ -3712,82 +3712,82 @@
         <v>1.82</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="DH7" t="n">
-        <v>106.56</v>
+        <v>105.92</v>
       </c>
       <c r="DI7" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.35</v>
+        <v>6.25</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="DM7" t="n">
-        <v>56.35</v>
+        <v>56</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.26</v>
+        <v>3.17</v>
       </c>
       <c r="DP7" t="n">
-        <v>11.22</v>
+        <v>11.21</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.22</v>
+        <v>13.3</v>
       </c>
       <c r="DR7" t="n">
         <v>6.04</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>54.91</v>
+        <v>55.67</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX7" t="n">
-        <v>14.57</v>
+        <v>14.34</v>
       </c>
       <c r="DY7" t="n">
-        <v>9.82</v>
+        <v>9.67</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.74</v>
+        <v>4.66</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.26</v>
+        <v>18.16</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
         <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F8" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="G8" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="H8" t="n">
-        <v>86</v>
+        <v>85.42</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="K8" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>42.27</v>
+        <v>41.25</v>
       </c>
       <c r="N8" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="O8" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="P8" t="n">
-        <v>10</v>
+        <v>10.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.36</v>
+        <v>13.08</v>
       </c>
       <c r="R8" t="n">
-        <v>5.64</v>
+        <v>5.5</v>
       </c>
       <c r="S8" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>45.73</v>
+        <v>46.08</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.27</v>
+        <v>12.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.55</v>
+        <v>7.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.73</v>
+        <v>4.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>15.09</v>
+        <v>15.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AF8" t="n">
         <v>0.08</v>
@@ -3968,70 +3968,70 @@
         <v>1.58</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.43</v>
+        <v>8.5</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.35</v>
+        <v>0.42</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BP8" t="n">
         <v>3.83</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.26</v>
+        <v>4.33</v>
       </c>
       <c r="BR8" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS8" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BU8" t="n">
-        <v>34.78</v>
+        <v>37.5</v>
       </c>
       <c r="BV8" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BX8" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BY8" t="n">
-        <v>3.39</v>
+        <v>3.28</v>
       </c>
       <c r="BZ8" t="n">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="CA8" t="n">
         <v>3.67</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="CC8" t="n">
         <v>4.13</v>
@@ -4040,19 +4040,19 @@
         <v>4.38</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.76</v>
@@ -4073,91 +4073,91 @@
         <v>1.27</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="CR8" t="n">
         <v>1.42</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CY8" t="n">
         <v>2.17</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DA8" t="n">
         <v>1.69</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DD8" t="n">
         <v>3.17</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DH8" t="n">
-        <v>86.43000000000001</v>
+        <v>86.12</v>
       </c>
       <c r="DI8" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DM8" t="n">
-        <v>42.39</v>
+        <v>41.88</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.57</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.09</v>
+        <v>13.92</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.39</v>
+        <v>7.25</v>
       </c>
       <c r="DS8" t="n">
         <v>0.08</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>45.31</v>
+        <v>45.5</v>
       </c>
       <c r="DW8" t="n">
         <v>0.04</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.74</v>
+        <v>11.88</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.92</v>
+        <v>8</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.83</v>
+        <v>3.88</v>
       </c>
       <c r="EA8" t="n">
-        <v>15</v>
+        <v>15.08</v>
       </c>
       <c r="EB8" t="n">
         <v>1.32</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="9">
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
         <v>12</v>
@@ -4212,82 +4212,82 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="G9" t="n">
-        <v>2.55</v>
+        <v>3.17</v>
       </c>
       <c r="H9" t="n">
-        <v>85.64</v>
+        <v>89.25</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>4.67</v>
       </c>
       <c r="L9" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="M9" t="n">
-        <v>38.18</v>
+        <v>41.92</v>
       </c>
       <c r="N9" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="P9" t="n">
-        <v>11.91</v>
+        <v>12.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.73</v>
+        <v>10.75</v>
       </c>
       <c r="R9" t="n">
-        <v>7.55</v>
+        <v>7.17</v>
       </c>
       <c r="S9" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="T9" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="U9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>48.09</v>
+        <v>49.58</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.640000000000001</v>
+        <v>10.83</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.27</v>
+        <v>7.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.36</v>
+        <v>3.58</v>
       </c>
       <c r="AC9" t="n">
-        <v>17.36</v>
+        <v>17.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AF9" t="n">
         <v>0.08</v>
@@ -4371,70 +4371,70 @@
         <v>1.67</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.22</v>
+        <v>3.12</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.65</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.22</v>
+        <v>3.12</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="BP9" t="n">
         <v>4</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.65</v>
+        <v>4.96</v>
       </c>
       <c r="BR9" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS9" t="n">
-        <v>78.26000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT9" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BU9" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BV9" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BW9" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BX9" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
-        <v>4.65</v>
+        <v>4.53</v>
       </c>
       <c r="BZ9" t="n">
-        <v>4.88</v>
+        <v>4.8</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.54</v>
+        <v>4.5</v>
       </c>
       <c r="CC9" t="n">
         <v>6.37</v>
@@ -4443,16 +4443,16 @@
         <v>7.33</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI9" t="n">
         <v>2.01</v>
@@ -4467,7 +4467,7 @@
         <v>2.12</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CN9" t="n">
         <v>1.77</v>
@@ -4476,91 +4476,91 @@
         <v>1.22</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="CR9" t="n">
         <v>1.38</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CW9" t="n">
         <v>1.82</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DA9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DC9" t="n">
         <v>1.8</v>
       </c>
-      <c r="DB9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="DC9" t="n">
-        <v>1.78</v>
-      </c>
       <c r="DD9" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="DE9" t="n">
         <v>0.04</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.22</v>
+        <v>2.54</v>
       </c>
       <c r="DH9" t="n">
-        <v>78.17</v>
+        <v>80.29000000000001</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.74</v>
+        <v>4.08</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="DM9" t="n">
-        <v>33.26</v>
+        <v>35.34</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.17</v>
+        <v>11.29</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.87</v>
+        <v>10.88</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.4</v>
+        <v>8.17</v>
       </c>
       <c r="DS9" t="n">
         <v>0.17</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>48.39</v>
+        <v>49.12</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.779999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.87</v>
+        <v>6.38</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.91</v>
+        <v>3.04</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.74</v>
+        <v>16.84</v>
       </c>
       <c r="EB9" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="10">
@@ -5004,13 +5004,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
         <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
         <v>0.17</v>
@@ -5094,139 +5094,139 @@
         <v>1.75</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" t="n">
-        <v>75</v>
+        <v>73.25</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN11" t="n">
-        <v>28.18</v>
+        <v>27.58</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12.82</v>
+        <v>13</v>
       </c>
       <c r="AR11" t="n">
-        <v>14.09</v>
+        <v>13.83</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.09</v>
+        <v>8.42</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>43.27</v>
+        <v>41.92</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.82</v>
+        <v>9.25</v>
       </c>
       <c r="BB11" t="n">
-        <v>7</v>
+        <v>6.58</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="BD11" t="n">
-        <v>18</v>
+        <v>18.42</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>0.98</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.17</v>
+        <v>9</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.04</v>
+        <v>4.92</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.13</v>
+        <v>4.08</v>
       </c>
       <c r="BR11" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS11" t="n">
-        <v>73.91</v>
+        <v>70.83</v>
       </c>
       <c r="BT11" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BU11" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV11" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX11" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
         <v>4.16</v>
@@ -5235,22 +5235,22 @@
         <v>4.55</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.89</v>
+        <v>3.94</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.04</v>
+        <v>4.05</v>
       </c>
       <c r="CC11" t="n">
-        <v>5.59</v>
+        <v>5.81</v>
       </c>
       <c r="CD11" t="n">
-        <v>5.91</v>
+        <v>6.02</v>
       </c>
       <c r="CE11" t="n">
         <v>1.36</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CG11" t="n">
         <v>3.04</v>
@@ -5265,25 +5265,25 @@
         <v>1.83</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CM11" t="n">
         <v>2.37</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CR11" t="n">
         <v>1.4</v>
@@ -5295,10 +5295,10 @@
         <v>3.02</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CW11" t="n">
         <v>1.87</v>
@@ -5322,49 +5322,49 @@
         <v>1.94</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="DE11" t="n">
         <v>0.17</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="DH11" t="n">
-        <v>82.78</v>
+        <v>81.58</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.26</v>
+        <v>3.17</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="DM11" t="n">
-        <v>34.22</v>
+        <v>33.66</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.48</v>
+        <v>12.58</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.48</v>
+        <v>13.38</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.52</v>
+        <v>8.67</v>
       </c>
       <c r="DS11" t="n">
         <v>0.08</v>
@@ -5376,28 +5376,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>43.69</v>
+        <v>43</v>
       </c>
       <c r="DW11" t="n">
         <v>0.04</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.48</v>
+        <v>10.17</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.65</v>
+        <v>7.42</v>
       </c>
       <c r="DZ11" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.57</v>
+        <v>19.71</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="EC11" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="12">
@@ -5407,13 +5407,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
         <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
         <v>0.17</v>
@@ -5500,136 +5500,136 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="AI12" t="n">
-        <v>88.81999999999999</v>
+        <v>91.33</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.73</v>
+        <v>4.83</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="AN12" t="n">
-        <v>38.18</v>
+        <v>38.92</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.64</v>
+        <v>13.17</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.64</v>
+        <v>12.17</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.64</v>
+        <v>7.58</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>47.82</v>
+        <v>48.83</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA12" t="n">
-        <v>10</v>
+        <v>10.08</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.64</v>
+        <v>6.75</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="BD12" t="n">
-        <v>17.45</v>
+        <v>17.58</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.78</v>
+        <v>10.92</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="BJ12" t="n">
         <v>0.83</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="BP12" t="n">
         <v>4.83</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.3</v>
+        <v>5.46</v>
       </c>
       <c r="BR12" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS12" t="n">
-        <v>78.26000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT12" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BU12" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BV12" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BW12" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BX12" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BY12" t="n">
         <v>2.37</v>
@@ -5638,31 +5638,31 @@
         <v>2.56</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.72</v>
+        <v>3.67</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.73</v>
+        <v>4.58</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.65</v>
@@ -5671,7 +5671,7 @@
         <v>1.49</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CM12" t="n">
         <v>2.41</v>
@@ -5683,10 +5683,10 @@
         <v>1.21</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CR12" t="n">
         <v>1.36</v>
@@ -5728,46 +5728,46 @@
         <v>2.92</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="DH12" t="n">
-        <v>81.18000000000001</v>
+        <v>82.75</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="DK12" t="n">
-        <v>5</v>
+        <v>5.04</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="DM12" t="n">
-        <v>35.17</v>
+        <v>35.67</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.83</v>
+        <v>12.62</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.26</v>
+        <v>12.04</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.13</v>
+        <v>7.12</v>
       </c>
       <c r="DS12" t="n">
         <v>0.08</v>
@@ -5779,28 +5779,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.61</v>
+        <v>48.12</v>
       </c>
       <c r="DW12" t="n">
         <v>0.08</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.52</v>
+        <v>11.5</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.31</v>
+        <v>7.34</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.22</v>
+        <v>4.16</v>
       </c>
       <c r="EA12" t="n">
-        <v>16.52</v>
+        <v>16.62</v>
       </c>
       <c r="EB12" t="n">
         <v>1.22</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="13">
@@ -5810,13 +5810,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5900,52 +5900,52 @@
         <v>1.73</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="AI13" t="n">
-        <v>84.67</v>
+        <v>85.31</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.5</v>
+        <v>5.15</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AN13" t="n">
-        <v>39.5</v>
+        <v>39.31</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13.5</v>
+        <v>13.08</v>
       </c>
       <c r="AR13" t="n">
-        <v>13.83</v>
+        <v>14</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.42</v>
+        <v>7.77</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AV13" t="n">
         <v>0.08</v>
@@ -5957,82 +5957,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>53.17</v>
+        <v>52.77</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BA13" t="n">
-        <v>10.58</v>
+        <v>10.69</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.75</v>
+        <v>5.77</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.83</v>
+        <v>4.92</v>
       </c>
       <c r="BD13" t="n">
-        <v>17.92</v>
+        <v>17.62</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="BF13" t="n">
         <v>2.08</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.61</v>
+        <v>2.71</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.26</v>
+        <v>10.21</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.61</v>
+        <v>2.71</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.87</v>
+        <v>0.96</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.83</v>
+        <v>5.71</v>
       </c>
       <c r="BR13" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS13" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BT13" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BU13" t="n">
-        <v>30.43</v>
+        <v>33.33</v>
       </c>
       <c r="BV13" t="n">
-        <v>17.39</v>
+        <v>20.83</v>
       </c>
       <c r="BW13" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX13" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BY13" t="n">
         <v>2.02</v>
@@ -6041,16 +6041,16 @@
         <v>2.26</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="CB13" t="n">
         <v>3.81</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.47</v>
+        <v>2.58</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.61</v>
+        <v>2.72</v>
       </c>
       <c r="CE13" t="n">
         <v>1.33</v>
@@ -6059,25 +6059,25 @@
         <v>2.53</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CH13" t="n">
         <v>1.48</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CK13" t="n">
         <v>1.54</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CN13" t="n">
         <v>1.87</v>
@@ -6086,10 +6086,10 @@
         <v>1.23</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CR13" t="n">
         <v>1.37</v>
@@ -6110,16 +6110,16 @@
         <v>1.77</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DB13" t="n">
         <v>1.3</v>
@@ -6131,46 +6131,46 @@
         <v>3.08</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="DG13" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="DH13" t="n">
-        <v>88.05</v>
+        <v>88.25</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.65</v>
+        <v>5.46</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DM13" t="n">
-        <v>42.48</v>
+        <v>42.25</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.65</v>
+        <v>2.54</v>
       </c>
       <c r="DP13" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.22</v>
+        <v>13.34</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.83</v>
+        <v>7.04</v>
       </c>
       <c r="DS13" t="n">
         <v>0.04</v>
@@ -6182,28 +6182,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>54.79</v>
+        <v>54.5</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX13" t="n">
         <v>11.87</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.22</v>
+        <v>7.17</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="EA13" t="n">
-        <v>17.57</v>
+        <v>17.42</v>
       </c>
       <c r="EB13" t="n">
         <v>1.39</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="14">
@@ -6213,94 +6213,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
         <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F14" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="G14" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="H14" t="n">
-        <v>110.09</v>
+        <v>108</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="K14" t="n">
-        <v>4.91</v>
+        <v>5.17</v>
       </c>
       <c r="L14" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="M14" t="n">
-        <v>52</v>
+        <v>52.67</v>
       </c>
       <c r="N14" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="O14" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="P14" t="n">
-        <v>13.36</v>
+        <v>13.58</v>
       </c>
       <c r="Q14" t="n">
-        <v>10.55</v>
+        <v>10.33</v>
       </c>
       <c r="R14" t="n">
-        <v>5.18</v>
+        <v>5.25</v>
       </c>
       <c r="S14" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T14" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="U14" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="V14" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>59.18</v>
+        <v>58.58</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>13.82</v>
+        <v>14.17</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.64</v>
+        <v>7.92</v>
       </c>
       <c r="AB14" t="n">
-        <v>6.18</v>
+        <v>6.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>14.64</v>
+        <v>14.92</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6384,70 +6384,70 @@
         <v>2.42</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.48</v>
+        <v>8.5</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BN14" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.78</v>
+        <v>4.71</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BT14" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BU14" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BV14" t="n">
-        <v>21.74</v>
+        <v>25</v>
       </c>
       <c r="BW14" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BX14" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="CC14" t="n">
         <v>2.3</v>
@@ -6456,22 +6456,22 @@
         <v>2.47</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF14" t="n">
         <v>2.39</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CH14" t="n">
         <v>1.54</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CK14" t="n">
         <v>1.64</v>
@@ -6480,7 +6480,7 @@
         <v>2.16</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CN14" t="n">
         <v>1.72</v>
@@ -6516,7 +6516,7 @@
         <v>1.66</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.21</v>
@@ -6528,85 +6528,85 @@
         <v>1.27</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="DH14" t="n">
-        <v>106.17</v>
+        <v>105.29</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.78</v>
+        <v>4.92</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="DM14" t="n">
-        <v>48.96</v>
+        <v>49.42</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.74</v>
+        <v>12.88</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.57</v>
+        <v>10.46</v>
       </c>
       <c r="DR14" t="n">
-        <v>6.13</v>
+        <v>6.12</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>58.08</v>
+        <v>57.83</v>
       </c>
       <c r="DW14" t="n">
         <v>0.17</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.22</v>
+        <v>14.38</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.57</v>
+        <v>8.67</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.65</v>
+        <v>5.71</v>
       </c>
       <c r="EA14" t="n">
-        <v>15.48</v>
+        <v>15.58</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="15">
@@ -7017,10 +7017,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D16" t="n">
         <v>12</v>
@@ -7029,82 +7029,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="G16" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="H16" t="n">
-        <v>103.82</v>
+        <v>102.67</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="K16" t="n">
-        <v>5.36</v>
+        <v>5.58</v>
       </c>
       <c r="L16" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="M16" t="n">
-        <v>47.45</v>
+        <v>46.08</v>
       </c>
       <c r="N16" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="O16" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="P16" t="n">
-        <v>12.09</v>
+        <v>11.67</v>
       </c>
       <c r="Q16" t="n">
-        <v>11.73</v>
+        <v>11.42</v>
       </c>
       <c r="R16" t="n">
-        <v>6.27</v>
+        <v>6.58</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="T16" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="U16" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V16" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>57.82</v>
+        <v>56.33</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="Z16" t="n">
-        <v>13.18</v>
+        <v>13.42</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.359999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="AC16" t="n">
-        <v>16.27</v>
+        <v>15.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.09</v>
+        <v>2.33</v>
       </c>
       <c r="AF16" t="n">
         <v>0.08</v>
@@ -7188,70 +7188,70 @@
         <v>2.08</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.13</v>
+        <v>4.17</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.35</v>
+        <v>4.54</v>
       </c>
       <c r="BR16" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS16" t="n">
-        <v>73.91</v>
+        <v>70.83</v>
       </c>
       <c r="BT16" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BU16" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BV16" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BW16" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BX16" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="BZ16" t="n">
         <v>2.54</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="CC16" t="n">
         <v>5.23</v>
@@ -7266,28 +7266,28 @@
         <v>2.66</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CH16" t="n">
         <v>1.48</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.73</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CO16" t="n">
         <v>1.25</v>
@@ -7311,7 +7311,7 @@
         <v>1.5</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CW16" t="n">
         <v>1.76</v>
@@ -7320,10 +7320,10 @@
         <v>1.66</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="DA16" t="n">
         <v>1.75</v>
@@ -7341,76 +7341,76 @@
         <v>0.04</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="DH16" t="n">
-        <v>90.7</v>
+        <v>90.67</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.13</v>
+        <v>4.29</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="DM16" t="n">
-        <v>38.48</v>
+        <v>38.16</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.74</v>
+        <v>0.83</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.22</v>
+        <v>11.04</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.26</v>
+        <v>11.12</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.69</v>
+        <v>7.79</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53.78</v>
+        <v>53.21</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.09</v>
+        <v>11.3</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.57</v>
+        <v>7.67</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.52</v>
+        <v>3.62</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.74</v>
+        <v>16.46</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="17">

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" t="n">
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
         <v>0.08</v>
@@ -1472,49 +1472,49 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AH2" t="n">
         <v>2</v>
       </c>
       <c r="AI2" t="n">
-        <v>72.75</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.67</v>
+        <v>2.77</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AN2" t="n">
-        <v>29.58</v>
+        <v>29.15</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.25</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>11</v>
+        <v>11.23</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.25</v>
+        <v>9.15</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AV2" t="n">
         <v>0.08</v>
@@ -1526,82 +1526,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>38.92</v>
+        <v>39.85</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.67</v>
+        <v>7.92</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.25</v>
+        <v>5.38</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="BD2" t="n">
-        <v>15.58</v>
+        <v>16.08</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.619999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="BR2" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS2" t="n">
-        <v>58.33</v>
+        <v>56</v>
       </c>
       <c r="BT2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BU2" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BV2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX2" t="n">
-        <v>33.33</v>
+        <v>32</v>
       </c>
       <c r="BY2" t="n">
         <v>3.58</v>
@@ -1610,31 +1610,31 @@
         <v>3.86</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.06</v>
+        <v>4.02</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.29</v>
+        <v>4.24</v>
       </c>
       <c r="CC2" t="n">
-        <v>7.81</v>
+        <v>7.46</v>
       </c>
       <c r="CD2" t="n">
-        <v>8.220000000000001</v>
+        <v>7.87</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.92</v>
@@ -1643,7 +1643,7 @@
         <v>1.67</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CM2" t="n">
         <v>2.11</v>
@@ -1652,13 +1652,13 @@
         <v>1.69</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CP2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="CR2" t="n">
         <v>1.45</v>
@@ -1673,10 +1673,10 @@
         <v>1.44</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CX2" t="n">
         <v>1.69</v>
@@ -1685,16 +1685,16 @@
         <v>2.12</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="DD2" t="n">
         <v>3.14</v>
@@ -1706,40 +1706,40 @@
         <v>1</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="DH2" t="n">
-        <v>72.79000000000001</v>
+        <v>72.84</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="DM2" t="n">
-        <v>30.88</v>
+        <v>30.6</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="DP2" t="n">
-        <v>11</v>
+        <v>11.32</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.21</v>
+        <v>11.32</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.619999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="DS2" t="n">
         <v>0.08</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>42.38</v>
+        <v>42.72</v>
       </c>
       <c r="DW2" t="n">
         <v>0.04</v>
       </c>
       <c r="DX2" t="n">
-        <v>9.210000000000001</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="DY2" t="n">
-        <v>5.79</v>
+        <v>5.84</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.75</v>
+        <v>16.96</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="3">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
         <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
         <v>0.15</v>
@@ -4693,139 +4693,139 @@
         <v>1.69</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AI10" t="n">
-        <v>104.64</v>
+        <v>101.92</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.64</v>
+        <v>4.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AN10" t="n">
-        <v>49.36</v>
+        <v>48.08</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AP10" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.27</v>
+        <v>13.58</v>
       </c>
       <c r="AR10" t="n">
-        <v>10.82</v>
+        <v>10.92</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.09</v>
+        <v>8.75</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>53.55</v>
+        <v>51.42</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA10" t="n">
-        <v>11.36</v>
+        <v>11.33</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.73</v>
+        <v>7.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.64</v>
+        <v>3.83</v>
       </c>
       <c r="BD10" t="n">
-        <v>20</v>
+        <v>19.92</v>
       </c>
       <c r="BE10" t="n">
         <v>1.34</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.119999999999999</v>
+        <v>9.16</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="BL10" t="n">
         <v>1.12</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="BN10" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.29</v>
+        <v>4.28</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.88</v>
+        <v>3.96</v>
       </c>
       <c r="BR10" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS10" t="n">
-        <v>66.67</v>
+        <v>68</v>
       </c>
       <c r="BT10" t="n">
-        <v>58.33</v>
+        <v>60</v>
       </c>
       <c r="BU10" t="n">
-        <v>54.17</v>
+        <v>56</v>
       </c>
       <c r="BV10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW10" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX10" t="n">
-        <v>58.33</v>
+        <v>60</v>
       </c>
       <c r="BY10" t="n">
         <v>1.91</v>
@@ -4834,28 +4834,28 @@
         <v>1.94</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.27</v>
+        <v>4.34</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.3</v>
+        <v>4.36</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.23</v>
+        <v>2.63</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.39</v>
+        <v>2.82</v>
       </c>
       <c r="CE10" t="n">
         <v>1.26</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.62</v>
+        <v>3.67</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="CI10" t="n">
         <v>2.36</v>
@@ -4876,31 +4876,31 @@
         <v>1.81</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="CR10" t="n">
         <v>1.35</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CT10" t="n">
         <v>3.26</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CV10" t="n">
         <v>2.46</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CX10" t="n">
         <v>1.58</v>
@@ -4916,85 +4916,85 @@
       </c>
       <c r="DB10" t="inlineStr"/>
       <c r="DC10" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DE10" t="n">
         <v>0.12</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="DG10" t="n">
         <v>1.84</v>
       </c>
       <c r="DH10" t="n">
-        <v>107.59</v>
+        <v>106.16</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.84</v>
+        <v>4.76</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DM10" t="n">
-        <v>49</v>
+        <v>48.4</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.29</v>
+        <v>13</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.09</v>
+        <v>11.12</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.38</v>
+        <v>7.72</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>53.71</v>
+        <v>52.68</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.17</v>
+        <v>12.12</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.96</v>
+        <v>7.84</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.21</v>
+        <v>4.28</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.79</v>
+        <v>19.76</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="11">
@@ -5004,61 +5004,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F11" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="G11" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="H11" t="n">
-        <v>89.92</v>
+        <v>91</v>
       </c>
       <c r="I11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="J11" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="K11" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="M11" t="n">
-        <v>39.75</v>
+        <v>41</v>
       </c>
       <c r="N11" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P11" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="R11" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="T11" t="n">
         <v>0.92</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="P11" t="n">
-        <v>12.17</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>12.92</v>
-      </c>
-      <c r="R11" t="n">
-        <v>8.92</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
       </c>
       <c r="U11" t="n">
         <v>0.08</v>
@@ -5070,28 +5070,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>44.08</v>
+        <v>44.46</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>11.08</v>
+        <v>11.23</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.25</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>21</v>
+        <v>21.38</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AF11" t="n">
         <v>0.17</v>
@@ -5175,70 +5175,70 @@
         <v>2.17</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="BH11" t="n">
-        <v>9</v>
+        <v>8.92</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.92</v>
+        <v>4.84</v>
       </c>
       <c r="BQ11" t="n">
         <v>4.08</v>
       </c>
       <c r="BR11" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS11" t="n">
-        <v>70.83</v>
+        <v>68</v>
       </c>
       <c r="BT11" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BU11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BV11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX11" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.16</v>
+        <v>4</v>
       </c>
       <c r="BZ11" t="n">
-        <v>4.55</v>
+        <v>4.37</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.05</v>
+        <v>4.02</v>
       </c>
       <c r="CC11" t="n">
         <v>5.81</v>
@@ -5247,43 +5247,43 @@
         <v>6.02</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI11" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="CP11" t="n">
         <v>1.93</v>
       </c>
-      <c r="CJ11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="CK11" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="CL11" t="n">
-        <v>2</v>
-      </c>
-      <c r="CM11" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="CN11" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CO11" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="CP11" t="n">
-        <v>1.91</v>
-      </c>
       <c r="CQ11" t="n">
-        <v>3.16</v>
+        <v>3.23</v>
       </c>
       <c r="CR11" t="n">
         <v>1.4</v>
@@ -5298,73 +5298,73 @@
         <v>1.47</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="DD11" t="n">
         <v>3.15</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF11" t="n">
         <v>1.16</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DH11" t="n">
-        <v>81.58</v>
+        <v>82.48</v>
       </c>
       <c r="DI11" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM11" t="n">
-        <v>33.66</v>
+        <v>34.56</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.58</v>
+        <v>12.64</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.38</v>
+        <v>13.6</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.67</v>
+        <v>8.48</v>
       </c>
       <c r="DS11" t="n">
         <v>0.08</v>
@@ -5376,28 +5376,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>43</v>
+        <v>43.24</v>
       </c>
       <c r="DW11" t="n">
         <v>0.04</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.17</v>
+        <v>10.28</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.42</v>
+        <v>7.52</v>
       </c>
       <c r="DZ11" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.71</v>
+        <v>19.96</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="12">
@@ -6616,94 +6616,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
         <v>13</v>
       </c>
       <c r="E15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F15" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="G15" t="n">
         <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>140.18</v>
+        <v>140.08</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="K15" t="n">
-        <v>6.36</v>
+        <v>6.42</v>
       </c>
       <c r="L15" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="M15" t="n">
-        <v>72</v>
+        <v>74.17</v>
       </c>
       <c r="N15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="O15" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="P15" t="n">
-        <v>10.09</v>
+        <v>10.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.18</v>
+        <v>8.92</v>
       </c>
       <c r="R15" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="S15" t="n">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="T15" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="U15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>68.45</v>
+        <v>68.75</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.18</v>
+        <v>20.17</v>
       </c>
       <c r="AA15" t="n">
-        <v>12.73</v>
+        <v>12.83</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.45</v>
+        <v>7.33</v>
       </c>
       <c r="AC15" t="n">
-        <v>17.27</v>
+        <v>17.08</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF15" t="n">
         <v>0.15</v>
@@ -6787,70 +6787,70 @@
         <v>0.85</v>
       </c>
       <c r="BG15" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.960000000000001</v>
+        <v>9</v>
       </c>
       <c r="BI15" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BL15" t="n">
         <v>1.12</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.54</v>
+        <v>0.6</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.62</v>
+        <v>4.68</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>70.83</v>
+        <v>72</v>
       </c>
       <c r="BT15" t="n">
-        <v>54.17</v>
+        <v>56</v>
       </c>
       <c r="BU15" t="n">
-        <v>29.17</v>
+        <v>32</v>
       </c>
       <c r="BV15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW15" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX15" t="n">
-        <v>37.5</v>
+        <v>40</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CA15" t="n">
         <v>6.05</v>
       </c>
       <c r="CB15" t="n">
-        <v>6.54</v>
+        <v>6.5</v>
       </c>
       <c r="CC15" t="n">
         <v>1.45</v>
@@ -6862,40 +6862,40 @@
         <v>1.2</v>
       </c>
       <c r="CF15" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CI15" t="n">
         <v>2.08</v>
       </c>
-      <c r="CG15" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="CH15" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="CI15" t="n">
-        <v>2.06</v>
-      </c>
       <c r="CJ15" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CL15" t="n">
         <v>1.95</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CO15" t="n">
         <v>1.11</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CR15" t="n">
         <v>1.34</v>
@@ -6910,10 +6910,10 @@
         <v>1.8</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CX15" t="n">
         <v>1.56</v>
@@ -6932,19 +6932,19 @@
         <v>1.47</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DE15" t="n">
         <v>0.16</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="DH15" t="n">
-        <v>132.79</v>
+        <v>133.04</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
@@ -6953,28 +6953,28 @@
         <v>1.04</v>
       </c>
       <c r="DK15" t="n">
-        <v>6</v>
+        <v>6.04</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="DM15" t="n">
-        <v>66.92</v>
+        <v>68.16</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="DP15" t="n">
-        <v>9.92</v>
+        <v>10</v>
       </c>
       <c r="DQ15" t="n">
-        <v>9.289999999999999</v>
+        <v>9.16</v>
       </c>
       <c r="DR15" t="n">
-        <v>4.79</v>
+        <v>4.76</v>
       </c>
       <c r="DS15" t="n">
         <v>0.12</v>
@@ -6986,25 +6986,25 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>68.45999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="DW15" t="n">
         <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>17.83</v>
+        <v>17.92</v>
       </c>
       <c r="DY15" t="n">
-        <v>10.96</v>
+        <v>11.08</v>
       </c>
       <c r="DZ15" t="n">
-        <v>6.87</v>
+        <v>6.84</v>
       </c>
       <c r="EA15" t="n">
-        <v>17</v>
+        <v>16.92</v>
       </c>
       <c r="EB15" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="EC15" t="n">
         <v>0.96</v>

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="8.4" customWidth="1" min="76" max="76"/>
+    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1619,7 +1619,7 @@
         <v>7.46</v>
       </c>
       <c r="CD2" t="n">
-        <v>7.87</v>
+        <v>7.88</v>
       </c>
       <c r="CE2" t="n">
         <v>1.41</v>
@@ -1685,16 +1685,16 @@
         <v>2.12</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DB2" t="n">
         <v>1.38</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="DD2" t="n">
         <v>3.14</v>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
         <v>12</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="G3" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>91.33</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="K3" t="n">
-        <v>5.42</v>
+        <v>5.38</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="M3" t="n">
-        <v>45.92</v>
+        <v>44.15</v>
       </c>
       <c r="N3" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="O3" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="P3" t="n">
-        <v>13.42</v>
+        <v>13.15</v>
       </c>
       <c r="Q3" t="n">
-        <v>14.5</v>
+        <v>14.23</v>
       </c>
       <c r="R3" t="n">
-        <v>5.58</v>
+        <v>5.77</v>
       </c>
       <c r="S3" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="T3" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="U3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>42.58</v>
+        <v>41.46</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.5</v>
+        <v>11.38</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.25</v>
+        <v>8.08</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.42</v>
+        <v>17.77</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AF3" t="n">
         <v>0.25</v>
@@ -1953,70 +1953,70 @@
         <v>2.42</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.5</v>
+        <v>9.48</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="BP3" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>84</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>56</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>40</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>24</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>36</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="CA3" t="n">
         <v>3.79</v>
       </c>
-      <c r="BQ3" t="n">
-        <v>5.71</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>58.33</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>41.67</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>25</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>3.8</v>
-      </c>
       <c r="CB3" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="CC3" t="n">
         <v>4.92</v>
@@ -2046,7 +2046,7 @@
         <v>1.58</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CM3" t="n">
         <v>2.28</v>
@@ -2055,16 +2055,16 @@
         <v>1.79</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CP3" t="n">
         <v>1.96</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CS3" t="n">
         <v>2.92</v>
@@ -2073,7 +2073,7 @@
         <v>2.96</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CV3" t="n">
         <v>2.02</v>
@@ -2100,49 +2100,49 @@
         <v>2.03</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="DE3" t="n">
         <v>0.12</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="DH3" t="n">
-        <v>90.83</v>
+        <v>89.88</v>
       </c>
       <c r="DI3" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="DK3" t="n">
         <v>4.96</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="DM3" t="n">
-        <v>41.54</v>
+        <v>40.8</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.46</v>
+        <v>13.32</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14</v>
+        <v>13.88</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.79</v>
+        <v>6.84</v>
       </c>
       <c r="DS3" t="n">
         <v>0.12</v>
@@ -2154,25 +2154,25 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>44.46</v>
+        <v>43.8</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.79</v>
+        <v>10.76</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.62</v>
+        <v>7.56</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.08</v>
+        <v>18.72</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="EC3" t="n">
         <v>2.12</v>
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
         <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="F4" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="G4" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="H4" t="n">
-        <v>100.5</v>
+        <v>100.23</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="K4" t="n">
-        <v>5.33</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="M4" t="n">
-        <v>37.75</v>
+        <v>37.23</v>
       </c>
       <c r="N4" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="O4" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="P4" t="n">
-        <v>13.33</v>
+        <v>13.46</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.08</v>
+        <v>11.54</v>
       </c>
       <c r="R4" t="n">
-        <v>8.17</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="U4" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V4" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>44.25</v>
+        <v>44</v>
       </c>
       <c r="Y4" t="n">
         <v>0.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>14.17</v>
+        <v>13.92</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.42</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.75</v>
+        <v>4.54</v>
       </c>
       <c r="AC4" t="n">
-        <v>16.33</v>
+        <v>17.15</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,70 +2356,70 @@
         <v>1.83</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.789999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BL4" t="n">
         <v>0.96</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.79</v>
+        <v>3.72</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.96</v>
+        <v>4.84</v>
       </c>
       <c r="BR4" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS4" t="n">
-        <v>79.17</v>
+        <v>80</v>
       </c>
       <c r="BT4" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BU4" t="n">
-        <v>29.17</v>
+        <v>28</v>
       </c>
       <c r="BV4" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX4" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.99</v>
+        <v>2.91</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.34</v>
+        <v>3.23</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="CC4" t="n">
         <v>3.84</v>
@@ -2431,7 +2431,7 @@
         <v>1.35</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CG4" t="n">
         <v>3.06</v>
@@ -2452,40 +2452,40 @@
         <v>2.15</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CO4" t="n">
         <v>1.26</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="CR4" t="n">
         <v>1.4</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CY4" t="n">
         <v>2.12</v>
@@ -2500,85 +2500,85 @@
         <v>1.33</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="DE4" t="n">
         <v>0.16</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="DH4" t="n">
-        <v>90.75</v>
+        <v>91</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.16</v>
+        <v>4.04</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM4" t="n">
-        <v>37.58</v>
+        <v>37.32</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.33</v>
+        <v>13.4</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.7</v>
+        <v>11.92</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.67</v>
+        <v>7.84</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>42.29</v>
+        <v>42.24</v>
       </c>
       <c r="DW4" t="n">
         <v>0.16</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.54</v>
+        <v>11.52</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.71</v>
+        <v>7.76</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.83</v>
+        <v>3.76</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.2</v>
+        <v>17.6</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="n">
         <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2681,49 +2681,49 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AI5" t="n">
-        <v>82.73</v>
+        <v>85.25</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AL5" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>37.18</v>
+        <v>38.83</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13.36</v>
+        <v>13.67</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.27</v>
+        <v>14.33</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.73</v>
+        <v>8.58</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>44.91</v>
+        <v>46.08</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.91</v>
+        <v>9.33</v>
       </c>
       <c r="BB5" t="n">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.91</v>
+        <v>2.67</v>
       </c>
       <c r="BD5" t="n">
-        <v>17</v>
+        <v>16.75</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="BG5" t="n">
         <v>2.08</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.380000000000001</v>
+        <v>9.16</v>
       </c>
       <c r="BI5" t="n">
         <v>2.08</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BL5" t="n">
         <v>0.88</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BO5" t="n">
         <v>0.92</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.17</v>
+        <v>4.08</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.21</v>
+        <v>5.08</v>
       </c>
       <c r="BR5" t="n">
-        <v>83.33</v>
+        <v>84</v>
       </c>
       <c r="BS5" t="n">
-        <v>54.17</v>
+        <v>56</v>
       </c>
       <c r="BT5" t="n">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="BU5" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BV5" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX5" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BY5" t="n">
         <v>3.59</v>
@@ -2819,22 +2819,22 @@
         <v>3.88</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.05</v>
+        <v>4.03</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.1</v>
+        <v>4.08</v>
       </c>
       <c r="CC5" t="n">
-        <v>6.23</v>
+        <v>6.03</v>
       </c>
       <c r="CD5" t="n">
-        <v>6.84</v>
+        <v>6.65</v>
       </c>
       <c r="CE5" t="n">
         <v>1.35</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="CG5" t="n">
         <v>3.05</v>
@@ -2867,25 +2867,25 @@
         <v>1.87</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="CR5" t="n">
         <v>1.42</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="CU5" t="n">
         <v>1.45</v>
       </c>
       <c r="CV5" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CX5" t="n">
         <v>1.63</v>
@@ -2894,61 +2894,61 @@
         <v>2.03</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DA5" t="n">
         <v>1.79</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="DH5" t="n">
-        <v>87.55</v>
+        <v>88.56</v>
       </c>
       <c r="DI5" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.58</v>
+        <v>4.52</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM5" t="n">
-        <v>42.21</v>
+        <v>42.8</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="DP5" t="n">
-        <v>13.33</v>
+        <v>13.48</v>
       </c>
       <c r="DQ5" t="n">
-        <v>13.58</v>
+        <v>13.64</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.71</v>
+        <v>7.68</v>
       </c>
       <c r="DS5" t="n">
         <v>0.04</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>46.09</v>
+        <v>46.6</v>
       </c>
       <c r="DW5" t="n">
         <v>0.08</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.66</v>
+        <v>10.8</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.16</v>
+        <v>7.44</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.75</v>
+        <v>18.56</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
         <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F6" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="H6" t="n">
-        <v>89</v>
+        <v>90.31</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="K6" t="n">
-        <v>6.17</v>
+        <v>6.15</v>
       </c>
       <c r="L6" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="M6" t="n">
-        <v>46.75</v>
+        <v>47.31</v>
       </c>
       <c r="N6" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="P6" t="n">
-        <v>13.58</v>
+        <v>13.46</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.67</v>
+        <v>13</v>
       </c>
       <c r="R6" t="n">
-        <v>5.42</v>
+        <v>5.54</v>
       </c>
       <c r="S6" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="T6" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V6" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>49.92</v>
+        <v>50.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>15</v>
+        <v>15.69</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.58</v>
+        <v>10.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.42</v>
+        <v>5.54</v>
       </c>
       <c r="AC6" t="n">
-        <v>17.58</v>
+        <v>17.15</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AF6" t="n">
         <v>0.08</v>
@@ -3162,70 +3162,70 @@
         <v>2.08</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.619999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.08</v>
+        <v>4.12</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="BR6" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS6" t="n">
-        <v>79.17</v>
+        <v>80</v>
       </c>
       <c r="BT6" t="n">
-        <v>62.5</v>
+        <v>64</v>
       </c>
       <c r="BU6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BV6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.97</v>
+        <v>4.05</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.97</v>
+        <v>4.06</v>
       </c>
       <c r="CC6" t="n">
         <v>2.79</v>
@@ -3237,16 +3237,16 @@
         <v>1.3</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.65</v>
@@ -3258,37 +3258,37 @@
         <v>2.02</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CO6" t="n">
         <v>1.2</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="CR6" t="n">
         <v>1.35</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="CT6" t="n">
         <v>3.24</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CX6" t="n">
         <v>1.59</v>
@@ -3306,85 +3306,85 @@
         <v>1.27</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="DE6" t="n">
         <v>0.12</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="DH6" t="n">
-        <v>88.92</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="DI6" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.62</v>
+        <v>5.64</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="DM6" t="n">
-        <v>44.42</v>
+        <v>44.8</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.46</v>
+        <v>13.4</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.67</v>
+        <v>12.84</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.04</v>
+        <v>6.08</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>49</v>
+        <v>49.12</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.54</v>
+        <v>14.92</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.42</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.12</v>
+        <v>5.2</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.58</v>
+        <v>16.4</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
         <v>12</v>
@@ -3409,79 +3409,79 @@
         <v>1.08</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="H7" t="n">
-        <v>106.83</v>
+        <v>109.08</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="K7" t="n">
-        <v>6.42</v>
+        <v>6.31</v>
       </c>
       <c r="L7" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="M7" t="n">
-        <v>55.33</v>
+        <v>57.23</v>
       </c>
       <c r="N7" t="n">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="O7" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="P7" t="n">
-        <v>10.67</v>
+        <v>10.92</v>
       </c>
       <c r="Q7" t="n">
         <v>12.92</v>
       </c>
       <c r="R7" t="n">
-        <v>5.5</v>
+        <v>5.54</v>
       </c>
       <c r="S7" t="n">
         <v>1.08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="U7" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="V7" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>54.17</v>
+        <v>54.46</v>
       </c>
       <c r="Y7" t="n">
         <v>0.08</v>
       </c>
       <c r="Z7" t="n">
-        <v>15.25</v>
+        <v>15</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.5</v>
+        <v>10.46</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.75</v>
+        <v>4.54</v>
       </c>
       <c r="AC7" t="n">
-        <v>19.08</v>
+        <v>18.69</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="AF7" t="n">
         <v>0.17</v>
@@ -3565,19 +3565,19 @@
         <v>2.42</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.92</v>
+        <v>9.76</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL7" t="n">
         <v>1.04</v>
@@ -3589,46 +3589,46 @@
         <v>1.96</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="BP7" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="BQ7" t="n">
         <v>4.92</v>
       </c>
-      <c r="BQ7" t="n">
-        <v>5</v>
-      </c>
       <c r="BR7" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS7" t="n">
-        <v>62.5</v>
+        <v>64</v>
       </c>
       <c r="BT7" t="n">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="BU7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BV7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW7" t="n">
-        <v>20.83</v>
+        <v>20</v>
       </c>
       <c r="BX7" t="n">
-        <v>37.5</v>
+        <v>40</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="CC7" t="n">
         <v>2.92</v>
@@ -3640,7 +3640,7 @@
         <v>1.34</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CG7" t="n">
         <v>3.11</v>
@@ -3649,16 +3649,16 @@
         <v>1.47</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CK7" t="n">
         <v>1.55</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CM7" t="n">
         <v>2.29</v>
@@ -3673,7 +3673,7 @@
         <v>1.8</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CR7" t="n">
         <v>1.38</v>
@@ -3688,10 +3688,10 @@
         <v>1.49</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CX7" t="n">
         <v>1.61</v>
@@ -3709,49 +3709,49 @@
         <v>1.29</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="DE7" t="n">
         <v>0.12</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="DH7" t="n">
-        <v>105.92</v>
+        <v>107.12</v>
       </c>
       <c r="DI7" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.25</v>
+        <v>6.2</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="DM7" t="n">
-        <v>56</v>
+        <v>56.96</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="DP7" t="n">
-        <v>11.21</v>
+        <v>11.32</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.3</v>
+        <v>13.28</v>
       </c>
       <c r="DR7" t="n">
         <v>6.04</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>55.67</v>
+        <v>55.76</v>
       </c>
       <c r="DW7" t="n">
         <v>0.2</v>
       </c>
       <c r="DX7" t="n">
-        <v>14.34</v>
+        <v>14.24</v>
       </c>
       <c r="DY7" t="n">
-        <v>9.67</v>
+        <v>9.68</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.66</v>
+        <v>4.56</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.16</v>
+        <v>18</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="EC7" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
         <v>0.17</v>
@@ -3893,46 +3893,46 @@
         <v>1.08</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AI8" t="n">
-        <v>86.83</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.92</v>
+        <v>3.69</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AN8" t="n">
-        <v>42.5</v>
+        <v>41.15</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.17</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AR8" t="n">
-        <v>14.75</v>
+        <v>14.69</v>
       </c>
       <c r="AS8" t="n">
-        <v>9</v>
+        <v>8.92</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AV8" t="n">
         <v>0.08</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>44.92</v>
+        <v>44.69</v>
       </c>
       <c r="AZ8" t="n">
         <v>0.08</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.25</v>
+        <v>11.08</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.25</v>
+        <v>7.92</v>
       </c>
       <c r="BC8" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="BD8" t="n">
-        <v>14.92</v>
+        <v>14.54</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="BG8" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="BI8" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BL8" t="n">
         <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.33</v>
+        <v>4.28</v>
       </c>
       <c r="BR8" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS8" t="n">
-        <v>87.5</v>
+        <v>88</v>
       </c>
       <c r="BT8" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BU8" t="n">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="BV8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX8" t="n">
-        <v>54.17</v>
+        <v>56</v>
       </c>
       <c r="BY8" t="n">
         <v>3.28</v>
@@ -4028,19 +4028,19 @@
         <v>3.34</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.13</v>
+        <v>4.34</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.38</v>
+        <v>4.54</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CF8" t="n">
         <v>2.74</v>
@@ -4052,10 +4052,10 @@
         <v>1.44</v>
       </c>
       <c r="CI8" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CK8" t="n">
         <v>1.67</v>
@@ -4064,16 +4064,16 @@
         <v>2.21</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CO8" t="n">
         <v>1.27</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CQ8" t="n">
         <v>3.2</v>
@@ -4091,10 +4091,10 @@
         <v>1.45</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CX8" t="n">
         <v>1.73</v>
@@ -4109,13 +4109,13 @@
         <v>1.69</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC8" t="n">
         <v>2</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="DE8" t="n">
         <v>0.12</v>
@@ -4124,40 +4124,40 @@
         <v>1.12</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="DH8" t="n">
-        <v>86.12</v>
+        <v>84.76000000000001</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DM8" t="n">
-        <v>41.88</v>
+        <v>41.2</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.619999999999999</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="DQ8" t="n">
         <v>13.92</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.25</v>
+        <v>7.28</v>
       </c>
       <c r="DS8" t="n">
         <v>0.08</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>45.5</v>
+        <v>45.36</v>
       </c>
       <c r="DW8" t="n">
         <v>0.04</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.88</v>
+        <v>11.76</v>
       </c>
       <c r="DY8" t="n">
-        <v>8</v>
+        <v>7.84</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.88</v>
+        <v>3.92</v>
       </c>
       <c r="EA8" t="n">
-        <v>15.08</v>
+        <v>14.88</v>
       </c>
       <c r="EB8" t="n">
         <v>1.32</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
         <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4293,136 +4293,136 @@
         <v>0.08</v>
       </c>
       <c r="AG9" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AI9" t="n">
-        <v>71.33</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="AJ9" t="n">
         <v>0.08</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AN9" t="n">
-        <v>28.75</v>
+        <v>29.31</v>
       </c>
       <c r="AO9" t="n">
         <v>0.92</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR9" t="n">
-        <v>11</v>
+        <v>11.08</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.17</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AU9" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>48.67</v>
+        <v>48.62</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="BA9" t="n">
-        <v>8</v>
+        <v>7.77</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.5</v>
+        <v>5.46</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="BD9" t="n">
-        <v>16.17</v>
+        <v>15.92</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="BG9" t="n">
         <v>3.12</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.960000000000001</v>
+        <v>9</v>
       </c>
       <c r="BI9" t="n">
         <v>3.12</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BP9" t="n">
-        <v>4</v>
+        <v>4.04</v>
       </c>
       <c r="BQ9" t="n">
         <v>4.96</v>
       </c>
       <c r="BR9" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BT9" t="n">
-        <v>58.33</v>
+        <v>60</v>
       </c>
       <c r="BU9" t="n">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="BV9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BY9" t="n">
         <v>4.53</v>
@@ -4431,43 +4431,43 @@
         <v>4.8</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.23</v>
+        <v>4.3</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.5</v>
+        <v>4.57</v>
       </c>
       <c r="CC9" t="n">
-        <v>6.37</v>
+        <v>6.54</v>
       </c>
       <c r="CD9" t="n">
-        <v>7.33</v>
+        <v>7.54</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CK9" t="n">
         <v>1.61</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CN9" t="n">
         <v>1.77</v>
@@ -4476,22 +4476,22 @@
         <v>1.22</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="CR9" t="n">
         <v>1.38</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="CT9" t="n">
         <v>3.1</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CV9" t="n">
         <v>2.08</v>
@@ -4503,7 +4503,7 @@
         <v>1.65</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.24</v>
@@ -4515,85 +4515,85 @@
         <v>1.31</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="DE9" t="n">
         <v>0.04</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="DH9" t="n">
-        <v>80.29000000000001</v>
+        <v>80.56</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="DK9" t="n">
         <v>4.08</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="DM9" t="n">
-        <v>35.34</v>
+        <v>35.36</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.29</v>
+        <v>11.52</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.88</v>
+        <v>10.92</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.17</v>
+        <v>8.32</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>49.12</v>
+        <v>49.08</v>
       </c>
       <c r="DW9" t="n">
         <v>0.16</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.42</v>
+        <v>9.24</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.38</v>
+        <v>6.32</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.84</v>
+        <v>16.68</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="10">
@@ -5238,7 +5238,7 @@
         <v>3.91</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.02</v>
+        <v>4.01</v>
       </c>
       <c r="CC11" t="n">
         <v>5.81</v>
@@ -5304,16 +5304,16 @@
         <v>1.89</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DB11" t="n">
         <v>1.33</v>
@@ -5407,61 +5407,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
         <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F12" t="n">
         <v>1.08</v>
       </c>
       <c r="G12" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>74.17</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="I12" t="n">
         <v>0.08</v>
       </c>
       <c r="J12" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="K12" t="n">
-        <v>5.25</v>
+        <v>5.38</v>
       </c>
       <c r="L12" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>32.42</v>
+        <v>33.77</v>
       </c>
       <c r="N12" t="n">
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="P12" t="n">
-        <v>12.08</v>
+        <v>11.85</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.92</v>
+        <v>11.62</v>
       </c>
       <c r="R12" t="n">
-        <v>6.67</v>
+        <v>6.46</v>
       </c>
       <c r="S12" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="T12" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="U12" t="n">
         <v>0.08</v>
@@ -5473,25 +5473,25 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>47.42</v>
+        <v>46.85</v>
       </c>
       <c r="Y12" t="n">
         <v>0.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.92</v>
+        <v>13</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.92</v>
+        <v>8.23</v>
       </c>
       <c r="AB12" t="n">
-        <v>5</v>
+        <v>4.77</v>
       </c>
       <c r="AC12" t="n">
-        <v>15.67</v>
+        <v>16.31</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
@@ -5578,70 +5578,70 @@
         <v>2.42</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.92</v>
+        <v>10.8</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
       <c r="BL12" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.83</v>
+        <v>4.8</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.46</v>
+        <v>5.4</v>
       </c>
       <c r="BR12" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BT12" t="n">
-        <v>54.17</v>
+        <v>56</v>
       </c>
       <c r="BU12" t="n">
-        <v>45.83</v>
+        <v>48</v>
       </c>
       <c r="BV12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW12" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX12" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="CC12" t="n">
         <v>3.67</v>
@@ -5659,10 +5659,10 @@
         <v>3.25</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.65</v>
@@ -5674,7 +5674,7 @@
         <v>1.95</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CN12" t="n">
         <v>1.9</v>
@@ -5683,10 +5683,10 @@
         <v>1.21</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CR12" t="n">
         <v>1.36</v>
@@ -5701,10 +5701,10 @@
         <v>1.54</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CX12" t="n">
         <v>1.55</v>
@@ -5713,7 +5713,7 @@
         <v>1.89</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="DA12" t="n">
         <v>1.94</v>
@@ -5725,7 +5725,7 @@
         <v>1.79</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="DE12" t="n">
         <v>0.08</v>
@@ -5734,40 +5734,40 @@
         <v>1.16</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="DH12" t="n">
-        <v>82.75</v>
+        <v>83.44</v>
       </c>
       <c r="DI12" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.04</v>
+        <v>5.12</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM12" t="n">
-        <v>35.67</v>
+        <v>36.24</v>
       </c>
       <c r="DN12" t="n">
         <v>1.12</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.62</v>
+        <v>12.48</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.04</v>
+        <v>11.88</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.12</v>
+        <v>7</v>
       </c>
       <c r="DS12" t="n">
         <v>0.08</v>
@@ -5779,28 +5779,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48.12</v>
+        <v>47.8</v>
       </c>
       <c r="DW12" t="n">
         <v>0.08</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.34</v>
+        <v>7.52</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.16</v>
+        <v>4.08</v>
       </c>
       <c r="EA12" t="n">
-        <v>16.62</v>
+        <v>16.92</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="13">
@@ -5810,10 +5810,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
         <v>13</v>
@@ -5822,82 +5822,82 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="G13" t="n">
-        <v>3.09</v>
+        <v>3.42</v>
       </c>
       <c r="H13" t="n">
-        <v>91.73</v>
+        <v>93.75</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="K13" t="n">
-        <v>5.82</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="M13" t="n">
-        <v>45.73</v>
+        <v>47.25</v>
       </c>
       <c r="N13" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="P13" t="n">
-        <v>14.55</v>
+        <v>13.92</v>
       </c>
       <c r="Q13" t="n">
-        <v>12.55</v>
+        <v>12.17</v>
       </c>
       <c r="R13" t="n">
-        <v>6.18</v>
+        <v>6.42</v>
       </c>
       <c r="S13" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="T13" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>56.55</v>
+        <v>57</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.27</v>
+        <v>13.33</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.82</v>
+        <v>8.92</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.45</v>
+        <v>4.42</v>
       </c>
       <c r="AC13" t="n">
-        <v>17.18</v>
+        <v>17.17</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AF13" t="n">
         <v>0.15</v>
@@ -5981,70 +5981,70 @@
         <v>2.08</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.21</v>
+        <v>10.2</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BL13" t="n">
         <v>0.96</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.71</v>
+        <v>5.8</v>
       </c>
       <c r="BR13" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS13" t="n">
-        <v>58.33</v>
+        <v>60</v>
       </c>
       <c r="BT13" t="n">
-        <v>54.17</v>
+        <v>52</v>
       </c>
       <c r="BU13" t="n">
-        <v>33.33</v>
+        <v>32</v>
       </c>
       <c r="BV13" t="n">
-        <v>20.83</v>
+        <v>20</v>
       </c>
       <c r="BW13" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX13" t="n">
-        <v>45.83</v>
+        <v>48</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="CA13" t="n">
         <v>3.72</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CC13" t="n">
         <v>2.58</v>
@@ -6065,7 +6065,7 @@
         <v>1.48</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.7</v>
@@ -6074,7 +6074,7 @@
         <v>1.54</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CM13" t="n">
         <v>2.34</v>
@@ -6089,22 +6089,22 @@
         <v>1.79</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CR13" t="n">
         <v>1.37</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="CU13" t="n">
         <v>1.48</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CW13" t="n">
         <v>1.77</v>
@@ -6125,82 +6125,82 @@
         <v>1.3</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DD13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DG13" t="n">
         <v>3.08</v>
       </c>
-      <c r="DE13" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DF13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="DG13" t="n">
-        <v>2.92</v>
-      </c>
       <c r="DH13" t="n">
-        <v>88.25</v>
+        <v>89.36</v>
       </c>
       <c r="DI13" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.46</v>
+        <v>5.56</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DM13" t="n">
-        <v>42.25</v>
+        <v>43.12</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="DP13" t="n">
-        <v>13.75</v>
+        <v>13.48</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.34</v>
+        <v>13.12</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.04</v>
+        <v>7.12</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>54.5</v>
+        <v>54.8</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.87</v>
+        <v>11.96</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.17</v>
+        <v>7.28</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.7</v>
+        <v>4.68</v>
       </c>
       <c r="EA13" t="n">
-        <v>17.42</v>
+        <v>17.4</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="EC13" t="n">
         <v>1.92</v>
@@ -6213,13 +6213,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E14" t="n">
         <v>0.17</v>
@@ -6306,49 +6306,49 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.67</v>
+        <v>2.46</v>
       </c>
       <c r="AI14" t="n">
-        <v>102.58</v>
+        <v>100.69</v>
       </c>
       <c r="AJ14" t="n">
         <v>-0.08</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.67</v>
+        <v>4.46</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AN14" t="n">
-        <v>46.17</v>
+        <v>44.77</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AP14" t="n">
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12.17</v>
+        <v>12.31</v>
       </c>
       <c r="AR14" t="n">
-        <v>10.58</v>
+        <v>10.92</v>
       </c>
       <c r="AS14" t="n">
         <v>7</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AV14" t="n">
         <v>0.08</v>
@@ -6360,82 +6360,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>57.08</v>
+        <v>56.62</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BA14" t="n">
-        <v>14.58</v>
+        <v>14.23</v>
       </c>
       <c r="BB14" t="n">
-        <v>9.42</v>
+        <v>9.23</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.17</v>
+        <v>5</v>
       </c>
       <c r="BD14" t="n">
-        <v>16.25</v>
+        <v>15.77</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.71</v>
+        <v>4.6</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="BT14" t="n">
-        <v>66.67</v>
+        <v>64</v>
       </c>
       <c r="BU14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BV14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW14" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BX14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BY14" t="n">
         <v>1.8</v>
@@ -6444,25 +6444,25 @@
         <v>1.83</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.24</v>
+        <v>4.21</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="CC14" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="CE14" t="n">
         <v>1.3</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CH14" t="n">
         <v>1.54</v>
@@ -6477,7 +6477,7 @@
         <v>1.64</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CM14" t="n">
         <v>2.14</v>
@@ -6489,7 +6489,7 @@
         <v>1.19</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CQ14" t="n">
         <v>2.55</v>
@@ -6519,7 +6519,7 @@
         <v>2.09</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DA14" t="n">
         <v>1.75</v>
@@ -6531,34 +6531,34 @@
         <v>1.7</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="DE14" t="n">
         <v>0.08</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="DH14" t="n">
-        <v>105.29</v>
+        <v>104.2</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.92</v>
+        <v>4.8</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM14" t="n">
-        <v>49.42</v>
+        <v>48.56</v>
       </c>
       <c r="DN14" t="n">
         <v>0.92</v>
@@ -6567,13 +6567,13 @@
         <v>2.12</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.88</v>
+        <v>12.92</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.46</v>
+        <v>10.64</v>
       </c>
       <c r="DR14" t="n">
-        <v>6.12</v>
+        <v>6.16</v>
       </c>
       <c r="DS14" t="n">
         <v>0.2</v>
@@ -6585,28 +6585,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>57.83</v>
+        <v>57.56</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.38</v>
+        <v>14.2</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.67</v>
+        <v>8.6</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.71</v>
+        <v>5.6</v>
       </c>
       <c r="EA14" t="n">
-        <v>15.58</v>
+        <v>15.36</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="15">
@@ -7017,13 +7017,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C16" t="n">
         <v>12</v>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7110,136 +7110,136 @@
         <v>0.08</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AI16" t="n">
-        <v>78.67</v>
+        <v>78.23</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AL16" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AN16" t="n">
-        <v>30.25</v>
+        <v>30.31</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.42</v>
+        <v>10.31</v>
       </c>
       <c r="AR16" t="n">
-        <v>10.83</v>
+        <v>10.54</v>
       </c>
       <c r="AS16" t="n">
-        <v>9</v>
+        <v>9.69</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AU16" t="n">
         <v>1.08</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>50.08</v>
+        <v>49.15</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.08</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.17</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.92</v>
+        <v>6.23</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
       <c r="BD16" t="n">
-        <v>17.17</v>
+        <v>16.62</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.5</v>
+        <v>9.52</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.17</v>
+        <v>4.08</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.54</v>
+        <v>4.68</v>
       </c>
       <c r="BR16" t="n">
-        <v>87.5</v>
+        <v>88</v>
       </c>
       <c r="BS16" t="n">
-        <v>70.83</v>
+        <v>72</v>
       </c>
       <c r="BT16" t="n">
-        <v>54.17</v>
+        <v>52</v>
       </c>
       <c r="BU16" t="n">
-        <v>29.17</v>
+        <v>28</v>
       </c>
       <c r="BV16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW16" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX16" t="n">
-        <v>58.33</v>
+        <v>60</v>
       </c>
       <c r="BY16" t="n">
         <v>2.37</v>
@@ -7251,13 +7251,13 @@
         <v>3.76</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="CC16" t="n">
-        <v>5.23</v>
+        <v>5.15</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.94</v>
+        <v>4.91</v>
       </c>
       <c r="CE16" t="n">
         <v>1.34</v>
@@ -7272,7 +7272,7 @@
         <v>1.48</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.73</v>
@@ -7281,7 +7281,7 @@
         <v>1.61</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CM16" t="n">
         <v>2.19</v>
@@ -7296,121 +7296,121 @@
         <v>1.85</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CR16" t="n">
         <v>1.39</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CU16" t="n">
         <v>1.5</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CY16" t="n">
         <v>2.08</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="DE16" t="n">
         <v>0.04</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="DH16" t="n">
-        <v>90.67</v>
+        <v>89.95999999999999</v>
       </c>
       <c r="DI16" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.29</v>
+        <v>4.2</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="DM16" t="n">
-        <v>38.16</v>
+        <v>37.88</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.04</v>
+        <v>10.96</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.12</v>
+        <v>10.96</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.79</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53.21</v>
+        <v>52.6</v>
       </c>
       <c r="DW16" t="n">
         <v>0.12</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.67</v>
+        <v>7.76</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.62</v>
+        <v>3.64</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.46</v>
+        <v>16.2</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="17">
@@ -7420,13 +7420,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" t="n">
         <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
         <v>0.08</v>
@@ -7510,52 +7510,52 @@
         <v>1.67</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AH17" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AI17" t="n">
-        <v>89.17</v>
+        <v>90.38</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.08</v>
+        <v>4.77</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AN17" t="n">
-        <v>38.92</v>
+        <v>39</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.08</v>
+        <v>11.77</v>
       </c>
       <c r="AR17" t="n">
-        <v>11.5</v>
+        <v>11.23</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.33</v>
+        <v>9.31</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AV17" t="n">
         <v>0.08</v>
@@ -7567,82 +7567,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>51.83</v>
+        <v>52.46</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="BA17" t="n">
-        <v>10.33</v>
+        <v>10.46</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.75</v>
+        <v>6.69</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.58</v>
+        <v>3.77</v>
       </c>
       <c r="BD17" t="n">
-        <v>18.67</v>
+        <v>18.31</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.38</v>
+        <v>10.28</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="BP17" t="n">
         <v>4.08</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.5</v>
+        <v>5.44</v>
       </c>
       <c r="BR17" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS17" t="n">
-        <v>79.17</v>
+        <v>80</v>
       </c>
       <c r="BT17" t="n">
-        <v>62.5</v>
+        <v>64</v>
       </c>
       <c r="BU17" t="n">
-        <v>54.17</v>
+        <v>56</v>
       </c>
       <c r="BV17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>54.17</v>
+        <v>52</v>
       </c>
       <c r="BY17" t="n">
         <v>2.6</v>
@@ -7651,16 +7651,16 @@
         <v>2.81</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.35</v>
+        <v>3.29</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.59</v>
+        <v>3.51</v>
       </c>
       <c r="CE17" t="n">
         <v>1.31</v>
@@ -7678,28 +7678,28 @@
         <v>2.23</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CK17" t="n">
         <v>1.58</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CO17" t="n">
         <v>1.21</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CR17" t="n">
         <v>1.36</v>
@@ -7714,10 +7714,10 @@
         <v>1.55</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CX17" t="n">
         <v>1.56</v>
@@ -7726,19 +7726,19 @@
         <v>1.93</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DB17" t="n">
         <v>1.28</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="DE17" t="n">
         <v>0.12</v>
@@ -7747,40 +7747,40 @@
         <v>1.08</v>
       </c>
       <c r="DG17" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="DH17" t="n">
-        <v>96.45999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="DI17" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.54</v>
+        <v>5.36</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="DM17" t="n">
-        <v>49.17</v>
+        <v>48.8</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.42</v>
+        <v>12.24</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.25</v>
+        <v>12.08</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.24</v>
       </c>
       <c r="DS17" t="n">
         <v>0.08</v>
@@ -7792,28 +7792,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>52</v>
+        <v>52.32</v>
       </c>
       <c r="DW17" t="n">
         <v>0.16</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.08</v>
+        <v>13.04</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.619999999999999</v>
+        <v>8.52</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.46</v>
+        <v>4.52</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.55</v>
+        <v>19.32</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="18">
@@ -7823,13 +7823,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" t="n">
         <v>12</v>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7916,136 +7916,136 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="AI18" t="n">
-        <v>94.25</v>
+        <v>96</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="AL18" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AN18" t="n">
-        <v>41.33</v>
+        <v>40.08</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12.25</v>
+        <v>12.15</v>
       </c>
       <c r="AR18" t="n">
-        <v>13.5</v>
+        <v>13.23</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.5</v>
+        <v>7.62</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>52.33</v>
+        <v>53.85</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BA18" t="n">
-        <v>10.25</v>
+        <v>10.46</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.75</v>
+        <v>6.85</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="BD18" t="n">
-        <v>17.42</v>
+        <v>17.54</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="BH18" t="n">
-        <v>8.08</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="BQ18" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>92</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>72</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>60</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>32</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>24</v>
+      </c>
+      <c r="BW18" t="n">
         <v>4</v>
       </c>
-      <c r="BR18" t="n">
-        <v>95.83</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>75</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>25</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>4.17</v>
-      </c>
       <c r="BX18" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="BY18" t="n">
         <v>2.32</v>
@@ -8054,34 +8054,34 @@
         <v>2.35</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.56</v>
+        <v>3.43</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.64</v>
+        <v>3.53</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CH18" t="n">
         <v>1.49</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CK18" t="n">
         <v>1.68</v>
@@ -8099,28 +8099,28 @@
         <v>1.22</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CX18" t="n">
         <v>1.7</v>
@@ -8135,85 +8135,85 @@
         <v>1.71</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="DG18" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="DH18" t="n">
-        <v>96.34</v>
+        <v>97.16</v>
       </c>
       <c r="DI18" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DM18" t="n">
-        <v>42</v>
+        <v>41.32</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DP18" t="n">
-        <v>11.21</v>
+        <v>11.2</v>
       </c>
       <c r="DQ18" t="n">
-        <v>12.54</v>
+        <v>12.44</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.38</v>
+        <v>7.44</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>51.75</v>
+        <v>52.56</v>
       </c>
       <c r="DW18" t="n">
         <v>0.2</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.12</v>
+        <v>11.2</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.66</v>
+        <v>6.72</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.46</v>
+        <v>4.48</v>
       </c>
       <c r="EA18" t="n">
-        <v>16.17</v>
+        <v>16.28</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="EC18" t="n">
         <v>1.92</v>
@@ -8226,94 +8226,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D19" t="n">
         <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="G19" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>87.83</v>
+        <v>88.92</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K19" t="n">
-        <v>5.5</v>
+        <v>5.38</v>
       </c>
       <c r="L19" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="M19" t="n">
-        <v>45.83</v>
+        <v>45.23</v>
       </c>
       <c r="N19" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="O19" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="P19" t="n">
-        <v>13.58</v>
+        <v>13.69</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.25</v>
+        <v>12.38</v>
       </c>
       <c r="R19" t="n">
-        <v>5.83</v>
+        <v>6</v>
       </c>
       <c r="S19" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T19" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="U19" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="V19" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>43</v>
+        <v>43.46</v>
       </c>
       <c r="Y19" t="n">
         <v>0.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>15.42</v>
+        <v>15.15</v>
       </c>
       <c r="AA19" t="n">
         <v>10.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>5.33</v>
+        <v>5.08</v>
       </c>
       <c r="AC19" t="n">
-        <v>18.75</v>
+        <v>18.77</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8397,28 +8397,28 @@
         <v>3.08</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.880000000000001</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BO19" t="n">
         <v>1.04</v>
@@ -8427,40 +8427,40 @@
         <v>4.12</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.46</v>
+        <v>5.32</v>
       </c>
       <c r="BR19" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS19" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="BT19" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BU19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BV19" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BW19" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX19" t="n">
-        <v>41.67</v>
+        <v>40</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="CA19" t="n">
         <v>3.51</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="CC19" t="n">
         <v>3.25</v>
@@ -8472,19 +8472,19 @@
         <v>1.38</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="CH19" t="n">
         <v>1.4</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CK19" t="n">
         <v>1.64</v>
@@ -8505,7 +8505,7 @@
         <v>2.01</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="CR19" t="n">
         <v>1.43</v>
@@ -8520,19 +8520,19 @@
         <v>1.41</v>
       </c>
       <c r="CV19" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CX19" t="n">
         <v>1.65</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DA19" t="n">
         <v>1.75</v>
@@ -8541,52 +8541,52 @@
         <v>1.35</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="DE19" t="n">
         <v>0.12</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="DH19" t="n">
-        <v>90.54000000000001</v>
+        <v>91</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.88</v>
+        <v>4.84</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="DM19" t="n">
-        <v>44.71</v>
+        <v>44.44</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO19" t="n">
         <v>2.12</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.33</v>
+        <v>14.36</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.66</v>
+        <v>6.72</v>
       </c>
       <c r="DS19" t="n">
         <v>0.16</v>
@@ -8598,25 +8598,25 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>42.92</v>
+        <v>43.16</v>
       </c>
       <c r="DW19" t="n">
         <v>0.08</v>
       </c>
       <c r="DX19" t="n">
-        <v>13.08</v>
+        <v>13.04</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.539999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.54</v>
+        <v>4.44</v>
       </c>
       <c r="EA19" t="n">
-        <v>17.33</v>
+        <v>17.4</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="EC19" t="n">
         <v>2.2</v>

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -7576,16 +7576,16 @@
         <v>10.46</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.69</v>
+        <v>6.62</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.77</v>
+        <v>3.85</v>
       </c>
       <c r="BD17" t="n">
         <v>18.31</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BF17" t="n">
         <v>1.69</v>
@@ -7801,16 +7801,16 @@
         <v>13.04</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.52</v>
+        <v>8.48</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.52</v>
+        <v>4.56</v>
       </c>
       <c r="EA17" t="n">
         <v>19.32</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="EC17" t="n">
         <v>1.68</v>

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
+    <col width="8.4" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" t="n">
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,52 +1872,52 @@
         <v>1.85</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AH3" t="n">
         <v>2.08</v>
       </c>
       <c r="AI3" t="n">
-        <v>90.33</v>
+        <v>90.23</v>
       </c>
       <c r="AJ3" t="n">
         <v>0.08</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.5</v>
+        <v>4.31</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AN3" t="n">
-        <v>37.17</v>
+        <v>36.46</v>
       </c>
       <c r="AO3" t="n">
         <v>1.08</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13.5</v>
+        <v>13.77</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.5</v>
+        <v>13.38</v>
       </c>
       <c r="AS3" t="n">
         <v>8</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AV3" t="n">
         <v>0.08</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>46.33</v>
+        <v>46</v>
       </c>
       <c r="AZ3" t="n">
         <v>0.08</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.08</v>
+        <v>9.92</v>
       </c>
       <c r="BB3" t="n">
-        <v>7</v>
+        <v>6.85</v>
       </c>
       <c r="BC3" t="n">
         <v>3.08</v>
       </c>
       <c r="BD3" t="n">
-        <v>19.75</v>
+        <v>19.23</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.48</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BN3" t="n">
         <v>1.12</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.76</v>
+        <v>3.69</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.72</v>
+        <v>5.85</v>
       </c>
       <c r="BR3" t="n">
-        <v>84</v>
+        <v>84.62</v>
       </c>
       <c r="BS3" t="n">
-        <v>56</v>
+        <v>53.85</v>
       </c>
       <c r="BT3" t="n">
-        <v>40</v>
+        <v>38.46</v>
       </c>
       <c r="BU3" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="BV3" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BW3" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX3" t="n">
-        <v>36</v>
+        <v>34.62</v>
       </c>
       <c r="BY3" t="n">
         <v>3.69</v>
@@ -2013,31 +2013,31 @@
         <v>3.95</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.79</v>
+        <v>3.83</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="CC3" t="n">
-        <v>4.92</v>
+        <v>5.04</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.07</v>
+        <v>5.25</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CH3" t="n">
         <v>1.43</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.82</v>
@@ -2055,25 +2055,25 @@
         <v>1.79</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="CR3" t="n">
         <v>1.41</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CV3" t="n">
         <v>2.02</v>
@@ -2097,52 +2097,52 @@
         <v>1.34</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="DE3" t="n">
         <v>0.12</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="DH3" t="n">
-        <v>89.88</v>
+        <v>89.84999999999999</v>
       </c>
       <c r="DI3" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.96</v>
+        <v>4.84</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="DM3" t="n">
-        <v>40.8</v>
+        <v>40.3</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.32</v>
+        <v>13.46</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.88</v>
+        <v>13.8</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.84</v>
+        <v>6.88</v>
       </c>
       <c r="DS3" t="n">
         <v>0.12</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.8</v>
+        <v>43.73</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.76</v>
+        <v>10.65</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.56</v>
+        <v>7.46</v>
       </c>
       <c r="DZ3" t="n">
         <v>3.2</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.72</v>
+        <v>18.5</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="4">
@@ -6213,94 +6213,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
         <v>13</v>
       </c>
       <c r="E14" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="G14" t="n">
-        <v>2.83</v>
+        <v>3.15</v>
       </c>
       <c r="H14" t="n">
-        <v>108</v>
+        <v>108.23</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="K14" t="n">
-        <v>5.17</v>
+        <v>5.46</v>
       </c>
       <c r="L14" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="M14" t="n">
-        <v>52.67</v>
+        <v>53.46</v>
       </c>
       <c r="N14" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="P14" t="n">
-        <v>13.58</v>
+        <v>13.46</v>
       </c>
       <c r="Q14" t="n">
-        <v>10.33</v>
+        <v>10.85</v>
       </c>
       <c r="R14" t="n">
-        <v>5.25</v>
+        <v>5.23</v>
       </c>
       <c r="S14" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="T14" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="U14" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="V14" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>58.58</v>
+        <v>58.54</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="Z14" t="n">
-        <v>14.17</v>
+        <v>14.31</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.92</v>
+        <v>8.31</v>
       </c>
       <c r="AB14" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="AC14" t="n">
-        <v>14.92</v>
+        <v>15.46</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6384,70 +6384,70 @@
         <v>2.46</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BN14" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.76</v>
+        <v>3.69</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.6</v>
+        <v>4.77</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>72</v>
+        <v>69.23</v>
       </c>
       <c r="BT14" t="n">
-        <v>64</v>
+        <v>61.54</v>
       </c>
       <c r="BU14" t="n">
-        <v>48</v>
+        <v>46.15</v>
       </c>
       <c r="BV14" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="BW14" t="n">
-        <v>16</v>
+        <v>15.38</v>
       </c>
       <c r="BX14" t="n">
-        <v>48</v>
+        <v>46.15</v>
       </c>
       <c r="BY14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BZ14" t="n">
         <v>1.8</v>
       </c>
-      <c r="BZ14" t="n">
-        <v>1.83</v>
-      </c>
       <c r="CA14" t="n">
-        <v>4.21</v>
+        <v>4.23</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.3</v>
+        <v>4.32</v>
       </c>
       <c r="CC14" t="n">
         <v>2.29</v>
@@ -6459,25 +6459,25 @@
         <v>1.3</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CH14" t="n">
         <v>1.54</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.69</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CM14" t="n">
         <v>2.14</v>
@@ -6498,19 +6498,19 @@
         <v>1.35</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="CU14" t="n">
         <v>1.56</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CX14" t="n">
         <v>1.66</v>
@@ -6519,7 +6519,7 @@
         <v>2.09</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DA14" t="n">
         <v>1.75</v>
@@ -6531,49 +6531,49 @@
         <v>1.7</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="DE14" t="n">
         <v>0.08</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="DH14" t="n">
-        <v>104.2</v>
+        <v>104.46</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.8</v>
+        <v>4.96</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="DM14" t="n">
-        <v>48.56</v>
+        <v>49.12</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.92</v>
+        <v>12.88</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.64</v>
+        <v>10.88</v>
       </c>
       <c r="DR14" t="n">
-        <v>6.16</v>
+        <v>6.12</v>
       </c>
       <c r="DS14" t="n">
         <v>0.2</v>
@@ -6585,28 +6585,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>57.56</v>
+        <v>57.58</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.2</v>
+        <v>14.27</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.6</v>
+        <v>8.77</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="EA14" t="n">
-        <v>15.36</v>
+        <v>15.62</v>
       </c>
       <c r="EB14" t="n">
         <v>1.58</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="15">

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
         <v>13</v>
@@ -1391,49 +1391,49 @@
         <v>0.08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="G2" t="n">
-        <v>2.67</v>
+        <v>2.77</v>
       </c>
       <c r="H2" t="n">
-        <v>72.83</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="K2" t="n">
-        <v>4.25</v>
+        <v>4.46</v>
       </c>
       <c r="L2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="M2" t="n">
-        <v>32.17</v>
+        <v>33.38</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="O2" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="P2" t="n">
-        <v>12.75</v>
+        <v>12.54</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.42</v>
+        <v>11.54</v>
       </c>
       <c r="R2" t="n">
-        <v>8</v>
+        <v>8.15</v>
       </c>
       <c r="S2" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="T2" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="U2" t="n">
         <v>0.08</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>45.83</v>
+        <v>45.92</v>
       </c>
       <c r="Y2" t="n">
         <v>0.08</v>
       </c>
       <c r="Z2" t="n">
-        <v>10.75</v>
+        <v>10.69</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.33</v>
+        <v>6.54</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.42</v>
+        <v>4.15</v>
       </c>
       <c r="AC2" t="n">
-        <v>17.92</v>
+        <v>18</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1553,67 +1553,67 @@
         <v>2.12</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.56</v>
+        <v>8.73</v>
       </c>
       <c r="BI2" t="n">
         <v>2.12</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.36</v>
+        <v>3.46</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.2</v>
+        <v>5.27</v>
       </c>
       <c r="BR2" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS2" t="n">
-        <v>56</v>
+        <v>57.69</v>
       </c>
       <c r="BT2" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="BU2" t="n">
-        <v>16</v>
+        <v>15.38</v>
       </c>
       <c r="BV2" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BW2" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX2" t="n">
-        <v>32</v>
+        <v>30.77</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.86</v>
+        <v>3.82</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.02</v>
+        <v>3.98</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.24</v>
+        <v>4.2</v>
       </c>
       <c r="CC2" t="n">
         <v>7.46</v>
@@ -1628,7 +1628,7 @@
         <v>2.82</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CH2" t="n">
         <v>1.41</v>
@@ -1643,7 +1643,7 @@
         <v>1.67</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CM2" t="n">
         <v>2.11</v>
@@ -1655,7 +1655,7 @@
         <v>1.32</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CQ2" t="n">
         <v>3.56</v>
@@ -1664,13 +1664,13 @@
         <v>1.45</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CV2" t="n">
         <v>1.89</v>
@@ -1682,10 +1682,10 @@
         <v>1.69</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="DA2" t="n">
         <v>1.73</v>
@@ -1694,10 +1694,10 @@
         <v>1.38</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="DE2" t="n">
         <v>0.04</v>
@@ -1706,40 +1706,40 @@
         <v>1</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="DH2" t="n">
-        <v>72.84</v>
+        <v>73</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.48</v>
+        <v>3.62</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DM2" t="n">
-        <v>30.6</v>
+        <v>31.27</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.32</v>
+        <v>11.27</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.32</v>
+        <v>11.38</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.6</v>
+        <v>8.65</v>
       </c>
       <c r="DS2" t="n">
         <v>0.08</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>42.72</v>
+        <v>42.89</v>
       </c>
       <c r="DW2" t="n">
         <v>0.04</v>
       </c>
       <c r="DX2" t="n">
-        <v>9.279999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DY2" t="n">
-        <v>5.84</v>
+        <v>5.96</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.44</v>
+        <v>3.34</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.96</v>
+        <v>17.04</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="3">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" t="n">
         <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
         <v>0.31</v>
@@ -2278,136 +2278,136 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="AI4" t="n">
-        <v>81</v>
+        <v>83.08</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AL4" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AN4" t="n">
-        <v>37.42</v>
+        <v>38.54</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.83</v>
+        <v>1.08</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13.33</v>
+        <v>12.92</v>
       </c>
       <c r="AR4" t="n">
-        <v>12.33</v>
+        <v>12.08</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.17</v>
+        <v>7.08</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>40.33</v>
+        <v>40.62</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.92</v>
+        <v>9.23</v>
       </c>
       <c r="BB4" t="n">
-        <v>6</v>
+        <v>6.46</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="BD4" t="n">
-        <v>18.08</v>
+        <v>18.23</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.56</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL4" t="n">
         <v>0.96</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.72</v>
+        <v>3.77</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.84</v>
+        <v>4.88</v>
       </c>
       <c r="BR4" t="n">
-        <v>92</v>
+        <v>92.31</v>
       </c>
       <c r="BS4" t="n">
-        <v>80</v>
+        <v>80.77</v>
       </c>
       <c r="BT4" t="n">
-        <v>48</v>
+        <v>46.15</v>
       </c>
       <c r="BU4" t="n">
-        <v>28</v>
+        <v>26.92</v>
       </c>
       <c r="BV4" t="n">
-        <v>16</v>
+        <v>15.38</v>
       </c>
       <c r="BW4" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BX4" t="n">
-        <v>44</v>
+        <v>42.31</v>
       </c>
       <c r="BY4" t="n">
         <v>2.91</v>
@@ -2416,16 +2416,16 @@
         <v>3.23</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.84</v>
+        <v>3.93</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.87</v>
+        <v>3.99</v>
       </c>
       <c r="CE4" t="n">
         <v>1.35</v>
@@ -2434,7 +2434,7 @@
         <v>2.68</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CH4" t="n">
         <v>1.45</v>
@@ -2446,10 +2446,10 @@
         <v>1.73</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CM4" t="n">
         <v>2.18</v>
@@ -2461,16 +2461,16 @@
         <v>1.26</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CR4" t="n">
         <v>1.4</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="CT4" t="n">
         <v>3.04</v>
@@ -2482,103 +2482,103 @@
         <v>2.13</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CX4" t="n">
         <v>1.68</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DB4" t="n">
         <v>1.33</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="DE4" t="n">
         <v>0.16</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="DH4" t="n">
-        <v>91</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.04</v>
+        <v>4.19</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="DM4" t="n">
-        <v>37.32</v>
+        <v>37.88</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.4</v>
+        <v>13.19</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.92</v>
+        <v>11.81</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.84</v>
+        <v>7.77</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>42.24</v>
+        <v>42.31</v>
       </c>
       <c r="DW4" t="n">
         <v>0.16</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.52</v>
+        <v>11.58</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.76</v>
+        <v>7.92</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.76</v>
+        <v>3.66</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.6</v>
+        <v>17.69</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="5">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
         <v>12</v>
@@ -2600,82 +2600,82 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="G5" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="H5" t="n">
-        <v>91.62</v>
+        <v>88.64</v>
       </c>
       <c r="I5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="J5" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="K5" t="n">
-        <v>5.08</v>
+        <v>4.86</v>
       </c>
       <c r="L5" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="M5" t="n">
-        <v>46.46</v>
+        <v>44.71</v>
       </c>
       <c r="N5" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="O5" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="P5" t="n">
-        <v>13.31</v>
+        <v>12.86</v>
       </c>
       <c r="Q5" t="n">
-        <v>13</v>
+        <v>13.21</v>
       </c>
       <c r="R5" t="n">
-        <v>6.85</v>
+        <v>7.14</v>
       </c>
       <c r="S5" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="T5" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="U5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>47.08</v>
+        <v>46.21</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="Z5" t="n">
-        <v>12.15</v>
+        <v>12.14</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.15</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AB5" t="n">
         <v>4</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.23</v>
+        <v>19.93</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>2.08</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.16</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BO5" t="n">
         <v>0.88</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>0.92</v>
       </c>
       <c r="BP5" t="n">
         <v>4.08</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.08</v>
+        <v>4.88</v>
       </c>
       <c r="BR5" t="n">
-        <v>84</v>
+        <v>80.77</v>
       </c>
       <c r="BS5" t="n">
-        <v>56</v>
+        <v>53.85</v>
       </c>
       <c r="BT5" t="n">
-        <v>36</v>
+        <v>34.62</v>
       </c>
       <c r="BU5" t="n">
-        <v>16</v>
+        <v>15.38</v>
       </c>
       <c r="BV5" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BW5" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX5" t="n">
-        <v>44</v>
+        <v>42.31</v>
       </c>
       <c r="BY5" t="n">
         <v>3.59</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.03</v>
+        <v>4.01</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.08</v>
+        <v>4.05</v>
       </c>
       <c r="CC5" t="n">
         <v>6.03</v>
@@ -2837,7 +2837,7 @@
         <v>2.72</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CH5" t="n">
         <v>1.45</v>
@@ -2846,13 +2846,13 @@
         <v>1.94</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CK5" t="n">
         <v>1.64</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CM5" t="n">
         <v>2.21</v>
@@ -2864,22 +2864,22 @@
         <v>1.26</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CR5" t="n">
         <v>1.42</v>
       </c>
       <c r="CS5" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="CT5" t="n">
         <v>2.93</v>
       </c>
-      <c r="CT5" t="n">
-        <v>2.94</v>
-      </c>
       <c r="CU5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CV5" t="n">
         <v>1.99</v>
@@ -2906,49 +2906,49 @@
         <v>1.97</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="DH5" t="n">
-        <v>88.56</v>
+        <v>87.08</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.52</v>
+        <v>4.43</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="DM5" t="n">
-        <v>42.8</v>
+        <v>42</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="DP5" t="n">
-        <v>13.48</v>
+        <v>13.23</v>
       </c>
       <c r="DQ5" t="n">
-        <v>13.64</v>
+        <v>13.73</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.68</v>
+        <v>7.8</v>
       </c>
       <c r="DS5" t="n">
         <v>0.04</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>46.6</v>
+        <v>46.15</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.8</v>
+        <v>10.84</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.44</v>
+        <v>7.46</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.36</v>
+        <v>3.39</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.56</v>
+        <v>18.46</v>
       </c>
       <c r="EB5" t="n">
         <v>1.23</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" t="n">
         <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
         <v>0.15</v>
@@ -3084,136 +3084,136 @@
         <v>0.08</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.42</v>
+        <v>2.69</v>
       </c>
       <c r="AI6" t="n">
-        <v>88.83</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.08</v>
+        <v>5.46</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AN6" t="n">
-        <v>42.08</v>
+        <v>46.54</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.67</v>
+        <v>2.77</v>
       </c>
       <c r="AQ6" t="n">
-        <v>13.33</v>
+        <v>13.15</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.67</v>
+        <v>12.15</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.67</v>
+        <v>6.31</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>48.08</v>
+        <v>49.46</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BA6" t="n">
-        <v>14.08</v>
+        <v>14.54</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.25</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.83</v>
+        <v>4.92</v>
       </c>
       <c r="BD6" t="n">
-        <v>15.58</v>
+        <v>16.15</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.640000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="BL6" t="n">
         <v>0.88</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.12</v>
+        <v>4.15</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="BR6" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS6" t="n">
-        <v>80</v>
+        <v>80.77</v>
       </c>
       <c r="BT6" t="n">
-        <v>64</v>
+        <v>65.38</v>
       </c>
       <c r="BU6" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="BV6" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BY6" t="n">
         <v>1.84</v>
@@ -3228,19 +3228,19 @@
         <v>4.06</v>
       </c>
       <c r="CC6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="CD6" t="n">
         <v>2.79</v>
-      </c>
-      <c r="CD6" t="n">
-        <v>2.89</v>
       </c>
       <c r="CE6" t="n">
         <v>1.3</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CH6" t="n">
         <v>1.54</v>
@@ -3249,19 +3249,19 @@
         <v>2.18</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CK6" t="n">
         <v>1.57</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CO6" t="n">
         <v>1.2</v>
@@ -3276,31 +3276,31 @@
         <v>1.35</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CW6" t="n">
         <v>1.69</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="DB6" t="n">
         <v>1.27</v>
@@ -3309,82 +3309,82 @@
         <v>1.72</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="DE6" t="n">
         <v>0.12</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="DH6" t="n">
-        <v>89.59999999999999</v>
+        <v>91.73</v>
       </c>
       <c r="DI6" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.64</v>
+        <v>5.81</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DM6" t="n">
-        <v>44.8</v>
+        <v>46.92</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.4</v>
+        <v>13.31</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.84</v>
+        <v>12.58</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.08</v>
+        <v>5.93</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>49.12</v>
+        <v>49.77</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.92</v>
+        <v>15.12</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.720000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.2</v>
+        <v>5.23</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.4</v>
+        <v>16.65</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="n">
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
         <v>0.08</v>
@@ -3484,52 +3484,52 @@
         <v>1.77</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="AI7" t="n">
-        <v>105</v>
+        <v>102.08</v>
       </c>
       <c r="AJ7" t="n">
         <v>0.08</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.08</v>
+        <v>3.23</v>
       </c>
       <c r="AL7" t="n">
-        <v>6.08</v>
+        <v>5.77</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AN7" t="n">
-        <v>56.67</v>
+        <v>54.92</v>
       </c>
       <c r="AO7" t="n">
         <v>1.08</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11.75</v>
+        <v>11.38</v>
       </c>
       <c r="AR7" t="n">
-        <v>13.67</v>
+        <v>13.85</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.58</v>
+        <v>6.77</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AV7" t="n">
         <v>0.08</v>
@@ -3541,43 +3541,43 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>57.17</v>
+        <v>55.92</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BA7" t="n">
-        <v>13.42</v>
+        <v>13</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.83</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.58</v>
+        <v>4.46</v>
       </c>
       <c r="BD7" t="n">
-        <v>17.25</v>
+        <v>17.54</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.76</v>
+        <v>9.65</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="BL7" t="n">
         <v>1.04</v>
@@ -3589,34 +3589,34 @@
         <v>1.96</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.84</v>
+        <v>4.69</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.92</v>
+        <v>4.96</v>
       </c>
       <c r="BR7" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS7" t="n">
-        <v>64</v>
+        <v>65.38</v>
       </c>
       <c r="BT7" t="n">
-        <v>36</v>
+        <v>38.46</v>
       </c>
       <c r="BU7" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="BV7" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="BW7" t="n">
-        <v>20</v>
+        <v>19.23</v>
       </c>
       <c r="BX7" t="n">
-        <v>40</v>
+        <v>42.31</v>
       </c>
       <c r="BY7" t="n">
         <v>2.04</v>
@@ -3625,25 +3625,25 @@
         <v>2.07</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.04</v>
+        <v>4.02</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="CD7" t="n">
-        <v>2.93</v>
+        <v>2.97</v>
       </c>
       <c r="CE7" t="n">
         <v>1.34</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CH7" t="n">
         <v>1.47</v>
@@ -3652,13 +3652,13 @@
         <v>2.06</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CM7" t="n">
         <v>2.29</v>
@@ -3673,19 +3673,19 @@
         <v>1.8</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="CR7" t="n">
         <v>1.38</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CT7" t="n">
         <v>3.12</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV7" t="n">
         <v>2.13</v>
@@ -3694,7 +3694,7 @@
         <v>1.81</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CY7" t="n">
         <v>2.02</v>
@@ -3706,55 +3706,55 @@
         <v>1.81</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="DH7" t="n">
-        <v>107.12</v>
+        <v>105.58</v>
       </c>
       <c r="DI7" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.2</v>
+        <v>6.04</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM7" t="n">
-        <v>56.96</v>
+        <v>56.08</v>
       </c>
       <c r="DN7" t="n">
         <v>0.92</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.16</v>
+        <v>3.08</v>
       </c>
       <c r="DP7" t="n">
-        <v>11.32</v>
+        <v>11.15</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.28</v>
+        <v>13.38</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.04</v>
+        <v>6.15</v>
       </c>
       <c r="DS7" t="n">
         <v>0.16</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>55.76</v>
+        <v>55.19</v>
       </c>
       <c r="DW7" t="n">
         <v>0.2</v>
       </c>
       <c r="DX7" t="n">
-        <v>14.24</v>
+        <v>14</v>
       </c>
       <c r="DY7" t="n">
-        <v>9.68</v>
+        <v>9.5</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.56</v>
+        <v>4.5</v>
       </c>
       <c r="EA7" t="n">
-        <v>18</v>
+        <v>18.12</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="8">
@@ -3797,25 +3797,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
         <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F8" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="G8" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="H8" t="n">
-        <v>85.42</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="I8" t="n">
         <v>-0.08</v>
@@ -3824,31 +3824,31 @@
         <v>1.92</v>
       </c>
       <c r="K8" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>41.25</v>
+        <v>40.08</v>
       </c>
       <c r="N8" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="O8" t="n">
         <v>0.92</v>
       </c>
       <c r="P8" t="n">
-        <v>10.08</v>
+        <v>9.77</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.08</v>
+        <v>12.92</v>
       </c>
       <c r="R8" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
@@ -3863,25 +3863,25 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>46.08</v>
+        <v>45.15</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.75</v>
+        <v>7.38</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.75</v>
+        <v>4.62</v>
       </c>
       <c r="AC8" t="n">
-        <v>15.25</v>
+        <v>14.92</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AE8" t="n">
         <v>1.92</v>
@@ -3971,67 +3971,67 @@
         <v>2.96</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="BI8" t="n">
         <v>2.96</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL8" t="n">
         <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.28</v>
+        <v>4.35</v>
       </c>
       <c r="BR8" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS8" t="n">
-        <v>88</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>44</v>
+        <v>46.15</v>
       </c>
       <c r="BU8" t="n">
-        <v>36</v>
+        <v>34.62</v>
       </c>
       <c r="BV8" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BW8" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BX8" t="n">
-        <v>56</v>
+        <v>57.69</v>
       </c>
       <c r="BY8" t="n">
-        <v>3.28</v>
+        <v>3.41</v>
       </c>
       <c r="BZ8" t="n">
-        <v>3.34</v>
+        <v>3.48</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="CC8" t="n">
         <v>4.34</v>
@@ -4052,7 +4052,7 @@
         <v>1.44</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.77</v>
@@ -4061,13 +4061,13 @@
         <v>1.67</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CM8" t="n">
         <v>2.14</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CO8" t="n">
         <v>1.27</v>
@@ -4076,16 +4076,16 @@
         <v>1.92</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="CR8" t="n">
         <v>1.42</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="CU8" t="n">
         <v>1.45</v>
@@ -4094,13 +4094,13 @@
         <v>2.05</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CX8" t="n">
         <v>1.73</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.12</v>
@@ -4112,10 +4112,10 @@
         <v>1.34</v>
       </c>
       <c r="DC8" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="DE8" t="n">
         <v>0.12</v>
@@ -4124,40 +4124,40 @@
         <v>1.12</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="DH8" t="n">
-        <v>84.76000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DJ8" t="n">
         <v>1.8</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.28</v>
+        <v>3.19</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DM8" t="n">
-        <v>41.2</v>
+        <v>40.61</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.720000000000001</v>
+        <v>9.57</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.92</v>
+        <v>13.8</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.28</v>
+        <v>7.46</v>
       </c>
       <c r="DS8" t="n">
         <v>0.08</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>45.36</v>
+        <v>44.92</v>
       </c>
       <c r="DW8" t="n">
         <v>0.04</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.76</v>
+        <v>11.54</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.84</v>
+        <v>7.65</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="EA8" t="n">
-        <v>14.88</v>
+        <v>14.73</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="9">
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
         <v>13</v>
@@ -4212,82 +4212,82 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="H9" t="n">
-        <v>89.25</v>
+        <v>89</v>
       </c>
       <c r="I9" t="n">
         <v>-0.08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="K9" t="n">
-        <v>4.67</v>
+        <v>4.62</v>
       </c>
       <c r="L9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="M9" t="n">
-        <v>41.92</v>
+        <v>41.54</v>
       </c>
       <c r="N9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="O9" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="P9" t="n">
-        <v>12.08</v>
+        <v>11.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.75</v>
+        <v>10.92</v>
       </c>
       <c r="R9" t="n">
-        <v>7.17</v>
+        <v>7.15</v>
       </c>
       <c r="S9" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="T9" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V9" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>49.58</v>
+        <v>49.62</v>
       </c>
       <c r="Y9" t="n">
         <v>0.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.83</v>
+        <v>11.31</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.25</v>
+        <v>7.38</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.58</v>
+        <v>3.92</v>
       </c>
       <c r="AC9" t="n">
-        <v>17.5</v>
+        <v>17.15</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AF9" t="n">
         <v>0.08</v>
@@ -4371,70 +4371,70 @@
         <v>1.77</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.12</v>
+        <v>3.27</v>
       </c>
       <c r="BH9" t="n">
-        <v>9</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.12</v>
+        <v>3.27</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL9" t="n">
         <v>1.08</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.04</v>
+        <v>4.12</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.96</v>
+        <v>4.85</v>
       </c>
       <c r="BR9" t="n">
-        <v>92</v>
+        <v>92.31</v>
       </c>
       <c r="BS9" t="n">
-        <v>76</v>
+        <v>76.92</v>
       </c>
       <c r="BT9" t="n">
-        <v>60</v>
+        <v>61.54</v>
       </c>
       <c r="BU9" t="n">
-        <v>36</v>
+        <v>38.46</v>
       </c>
       <c r="BV9" t="n">
-        <v>24</v>
+        <v>26.92</v>
       </c>
       <c r="BW9" t="n">
-        <v>12</v>
+        <v>15.38</v>
       </c>
       <c r="BX9" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
-        <v>4.53</v>
+        <v>4.48</v>
       </c>
       <c r="BZ9" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.57</v>
+        <v>4.52</v>
       </c>
       <c r="CC9" t="n">
         <v>6.54</v>
@@ -4443,16 +4443,16 @@
         <v>7.54</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF9" t="n">
         <v>2.53</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI9" t="n">
         <v>2</v>
@@ -4464,7 +4464,7 @@
         <v>1.61</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CM9" t="n">
         <v>2.22</v>
@@ -4473,37 +4473,37 @@
         <v>1.77</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CX9" t="n">
         <v>1.65</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.24</v>
@@ -4515,85 +4515,85 @@
         <v>1.31</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="DE9" t="n">
         <v>0.04</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="DH9" t="n">
-        <v>80.56</v>
+        <v>80.77</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DK9" t="n">
         <v>4.08</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="DM9" t="n">
-        <v>35.36</v>
+        <v>35.42</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.52</v>
+        <v>11.46</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.92</v>
+        <v>11</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.32</v>
+        <v>8.26</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>49.08</v>
+        <v>49.12</v>
       </c>
       <c r="DW9" t="n">
         <v>0.16</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.24</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.32</v>
+        <v>6.42</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.92</v>
+        <v>3.12</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.68</v>
+        <v>16.54</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="10">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
         <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F10" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="G10" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="H10" t="n">
-        <v>110.08</v>
+        <v>110.43</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>4.86</v>
       </c>
       <c r="L10" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="M10" t="n">
-        <v>48.69</v>
+        <v>48.93</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="O10" t="n">
-        <v>2.77</v>
+        <v>2.64</v>
       </c>
       <c r="P10" t="n">
-        <v>12.46</v>
+        <v>12.21</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.31</v>
+        <v>11.07</v>
       </c>
       <c r="R10" t="n">
-        <v>6.77</v>
+        <v>7.14</v>
       </c>
       <c r="S10" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="U10" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="V10" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>53.85</v>
+        <v>54</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.85</v>
+        <v>12.64</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.15</v>
+        <v>8</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.69</v>
+        <v>4.64</v>
       </c>
       <c r="AC10" t="n">
-        <v>19.62</v>
+        <v>19.79</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AF10" t="n">
         <v>0.08</v>
@@ -4774,70 +4774,70 @@
         <v>2.83</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.16</v>
+        <v>9.23</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BL10" t="n">
         <v>1.12</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.28</v>
+        <v>4.31</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.96</v>
+        <v>4.04</v>
       </c>
       <c r="BR10" t="n">
-        <v>92</v>
+        <v>92.31</v>
       </c>
       <c r="BS10" t="n">
-        <v>68</v>
+        <v>69.23</v>
       </c>
       <c r="BT10" t="n">
-        <v>60</v>
+        <v>57.69</v>
       </c>
       <c r="BU10" t="n">
-        <v>56</v>
+        <v>53.85</v>
       </c>
       <c r="BV10" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="BW10" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BX10" t="n">
-        <v>60</v>
+        <v>57.69</v>
       </c>
       <c r="BY10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BZ10" t="n">
         <v>1.91</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>1.94</v>
       </c>
       <c r="CA10" t="n">
         <v>4.34</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.36</v>
+        <v>4.35</v>
       </c>
       <c r="CC10" t="n">
         <v>2.63</v>
@@ -4849,19 +4849,19 @@
         <v>1.26</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CK10" t="n">
         <v>1.56</v>
@@ -4882,25 +4882,25 @@
         <v>1.55</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CR10" t="n">
         <v>1.35</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CT10" t="n">
         <v>3.26</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CX10" t="n">
         <v>1.58</v>
@@ -4919,82 +4919,82 @@
         <v>1.57</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="DG10" t="n">
         <v>1.84</v>
       </c>
       <c r="DH10" t="n">
-        <v>106.16</v>
+        <v>106.5</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.76</v>
+        <v>4.69</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM10" t="n">
-        <v>48.4</v>
+        <v>48.54</v>
       </c>
       <c r="DN10" t="n">
         <v>0.92</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="DP10" t="n">
-        <v>13</v>
+        <v>12.84</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.12</v>
+        <v>11</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.72</v>
+        <v>7.88</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>52.68</v>
+        <v>52.81</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.12</v>
+        <v>12.04</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.84</v>
+        <v>7.77</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.28</v>
+        <v>4.27</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.76</v>
+        <v>19.85</v>
       </c>
       <c r="EB10" t="n">
         <v>1.42</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="11">
@@ -5407,13 +5407,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
         <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
         <v>0.15</v>
@@ -5500,49 +5500,49 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AI12" t="n">
-        <v>91.33</v>
+        <v>93.69</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.83</v>
+        <v>4.92</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AN12" t="n">
-        <v>38.92</v>
+        <v>40.46</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.17</v>
+        <v>13.15</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.17</v>
+        <v>12</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.58</v>
+        <v>7.69</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AV12" t="n">
         <v>0.08</v>
@@ -5554,82 +5554,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>48.83</v>
+        <v>49.15</v>
       </c>
       <c r="AZ12" t="n">
         <v>0.08</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.08</v>
+        <v>10.23</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.75</v>
+        <v>6.54</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.33</v>
+        <v>3.69</v>
       </c>
       <c r="BD12" t="n">
-        <v>17.58</v>
+        <v>17.69</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.8</v>
+        <v>10.88</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.4</v>
+        <v>5.46</v>
       </c>
       <c r="BR12" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS12" t="n">
-        <v>76</v>
+        <v>76.92</v>
       </c>
       <c r="BT12" t="n">
-        <v>56</v>
+        <v>53.85</v>
       </c>
       <c r="BU12" t="n">
-        <v>48</v>
+        <v>46.15</v>
       </c>
       <c r="BV12" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="BW12" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BX12" t="n">
-        <v>60</v>
+        <v>57.69</v>
       </c>
       <c r="BY12" t="n">
         <v>2.4</v>
@@ -5638,31 +5638,31 @@
         <v>2.57</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.89</v>
+        <v>3.85</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.67</v>
+        <v>3.57</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.58</v>
+        <v>4.42</v>
       </c>
       <c r="CE12" t="n">
         <v>1.33</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.65</v>
@@ -5674,37 +5674,37 @@
         <v>1.95</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CN12" t="n">
         <v>1.9</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CX12" t="n">
         <v>1.55</v>
@@ -5713,61 +5713,61 @@
         <v>1.89</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="DA12" t="n">
         <v>1.94</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="DE12" t="n">
         <v>0.08</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="DH12" t="n">
-        <v>83.44</v>
+        <v>84.92</v>
       </c>
       <c r="DI12" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.12</v>
+        <v>5.15</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="DM12" t="n">
-        <v>36.24</v>
+        <v>37.12</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.48</v>
+        <v>12.5</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.88</v>
+        <v>11.81</v>
       </c>
       <c r="DR12" t="n">
-        <v>7</v>
+        <v>7.07</v>
       </c>
       <c r="DS12" t="n">
         <v>0.08</v>
@@ -5779,28 +5779,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.8</v>
+        <v>48</v>
       </c>
       <c r="DW12" t="n">
         <v>0.08</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.6</v>
+        <v>11.62</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.52</v>
+        <v>7.38</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.08</v>
+        <v>4.23</v>
       </c>
       <c r="EA12" t="n">
-        <v>16.92</v>
+        <v>17</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="13">
@@ -5810,13 +5810,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C13" t="n">
         <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5900,139 +5900,139 @@
         <v>1.75</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.77</v>
+        <v>2.57</v>
       </c>
       <c r="AI13" t="n">
-        <v>85.31</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.15</v>
+        <v>4.93</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="AN13" t="n">
-        <v>39.31</v>
+        <v>40.93</v>
       </c>
       <c r="AO13" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13.08</v>
+        <v>13.29</v>
       </c>
       <c r="AR13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.77</v>
+        <v>7.86</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>52.77</v>
+        <v>53.64</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BA13" t="n">
-        <v>10.69</v>
+        <v>10.86</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.77</v>
+        <v>6</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.92</v>
+        <v>4.86</v>
       </c>
       <c r="BD13" t="n">
-        <v>17.62</v>
+        <v>18.21</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.2</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.8</v>
+        <v>5.58</v>
       </c>
       <c r="BR13" t="n">
-        <v>92</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>60</v>
+        <v>57.69</v>
       </c>
       <c r="BT13" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="BU13" t="n">
-        <v>32</v>
+        <v>30.77</v>
       </c>
       <c r="BV13" t="n">
-        <v>20</v>
+        <v>19.23</v>
       </c>
       <c r="BW13" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BX13" t="n">
-        <v>48</v>
+        <v>46.15</v>
       </c>
       <c r="BY13" t="n">
         <v>1.99</v>
@@ -6041,25 +6041,25 @@
         <v>2.23</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="CE13" t="n">
         <v>1.33</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CH13" t="n">
         <v>1.48</v>
@@ -6068,142 +6068,142 @@
         <v>2.09</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CK13" t="n">
         <v>1.54</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CM13" t="n">
         <v>2.34</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CO13" t="n">
         <v>1.23</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV13" t="n">
         <v>2.16</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CX13" t="n">
         <v>1.6</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DA13" t="n">
         <v>1.84</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="DE13" t="n">
         <v>0.08</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="DH13" t="n">
-        <v>89.36</v>
+        <v>90.08</v>
       </c>
       <c r="DI13" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.56</v>
+        <v>5.42</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="DM13" t="n">
-        <v>43.12</v>
+        <v>43.85</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.76</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="DP13" t="n">
-        <v>13.48</v>
+        <v>13.58</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.12</v>
+        <v>12.89</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.12</v>
+        <v>7.2</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>54.8</v>
+        <v>55.19</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.96</v>
+        <v>12</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.28</v>
+        <v>7.35</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.68</v>
+        <v>4.66</v>
       </c>
       <c r="EA13" t="n">
-        <v>17.4</v>
+        <v>17.73</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="14">
@@ -7017,13 +7017,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C16" t="n">
         <v>12</v>
       </c>
       <c r="D16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7107,139 +7107,139 @@
         <v>2.33</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="AI16" t="n">
-        <v>78.23</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
       <c r="AN16" t="n">
-        <v>30.31</v>
+        <v>29.71</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.31</v>
+        <v>10.79</v>
       </c>
       <c r="AR16" t="n">
-        <v>10.54</v>
+        <v>10.57</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.69</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>49.15</v>
+        <v>48.43</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.539999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.23</v>
+        <v>6.43</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.31</v>
+        <v>3.21</v>
       </c>
       <c r="BD16" t="n">
-        <v>16.62</v>
+        <v>16.29</v>
       </c>
       <c r="BE16" t="n">
         <v>1.06</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.52</v>
+        <v>9.77</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.08</v>
+        <v>3.88</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.68</v>
+        <v>4.46</v>
       </c>
       <c r="BR16" t="n">
-        <v>88</v>
+        <v>84.62</v>
       </c>
       <c r="BS16" t="n">
-        <v>72</v>
+        <v>69.23</v>
       </c>
       <c r="BT16" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="BU16" t="n">
-        <v>28</v>
+        <v>26.92</v>
       </c>
       <c r="BV16" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="BW16" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BX16" t="n">
-        <v>60</v>
+        <v>57.69</v>
       </c>
       <c r="BY16" t="n">
         <v>2.37</v>
@@ -7251,22 +7251,22 @@
         <v>3.76</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="CC16" t="n">
-        <v>5.15</v>
+        <v>5.11</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.91</v>
+        <v>4.92</v>
       </c>
       <c r="CE16" t="n">
         <v>1.34</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CH16" t="n">
         <v>1.48</v>
@@ -7323,7 +7323,7 @@
         <v>2.08</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DA16" t="n">
         <v>1.76</v>
@@ -7341,76 +7341,76 @@
         <v>0.04</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="DG16" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DH16" t="n">
-        <v>89.95999999999999</v>
+        <v>89.89</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.44</v>
+        <v>0.39</v>
       </c>
       <c r="DM16" t="n">
-        <v>37.88</v>
+        <v>37.27</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.96</v>
+        <v>11.2</v>
       </c>
       <c r="DQ16" t="n">
         <v>10.96</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>52.6</v>
+        <v>52.08</v>
       </c>
       <c r="DW16" t="n">
         <v>0.12</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.4</v>
+        <v>11.38</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.76</v>
+        <v>7.81</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.64</v>
+        <v>3.57</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.2</v>
+        <v>16.04</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="17">
@@ -7420,10 +7420,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
         <v>13</v>
@@ -7432,49 +7432,49 @@
         <v>0.08</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>4.08</v>
       </c>
       <c r="H17" t="n">
-        <v>103.75</v>
+        <v>105.38</v>
       </c>
       <c r="I17" t="n">
         <v>-0.08</v>
       </c>
       <c r="J17" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>5.92</v>
       </c>
       <c r="L17" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="M17" t="n">
-        <v>59.42</v>
+        <v>59.15</v>
       </c>
       <c r="N17" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="P17" t="n">
-        <v>12.75</v>
+        <v>13</v>
       </c>
       <c r="Q17" t="n">
-        <v>13</v>
+        <v>12.54</v>
       </c>
       <c r="R17" t="n">
-        <v>7.08</v>
+        <v>6.92</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="T17" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="U17" t="n">
         <v>0.08</v>
@@ -7486,28 +7486,28 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>52.17</v>
+        <v>52.69</v>
       </c>
       <c r="Y17" t="n">
         <v>0.08</v>
       </c>
       <c r="Z17" t="n">
-        <v>15.83</v>
+        <v>15.54</v>
       </c>
       <c r="AA17" t="n">
-        <v>10.5</v>
+        <v>10.31</v>
       </c>
       <c r="AB17" t="n">
-        <v>5.33</v>
+        <v>5.23</v>
       </c>
       <c r="AC17" t="n">
-        <v>20.42</v>
+        <v>21.15</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AF17" t="n">
         <v>0.15</v>
@@ -7594,67 +7594,67 @@
         <v>3.08</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.28</v>
+        <v>10.15</v>
       </c>
       <c r="BI17" t="n">
         <v>3.08</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.08</v>
+        <v>3.96</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.44</v>
+        <v>5.46</v>
       </c>
       <c r="BR17" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS17" t="n">
-        <v>80</v>
+        <v>80.77</v>
       </c>
       <c r="BT17" t="n">
-        <v>64</v>
+        <v>65.38</v>
       </c>
       <c r="BU17" t="n">
-        <v>56</v>
+        <v>53.85</v>
       </c>
       <c r="BV17" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>52</v>
+        <v>53.85</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.89</v>
+        <v>3.87</v>
       </c>
       <c r="CC17" t="n">
         <v>3.29</v>
@@ -7666,10 +7666,10 @@
         <v>1.31</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CH17" t="n">
         <v>1.52</v>
@@ -7678,7 +7678,7 @@
         <v>2.23</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CK17" t="n">
         <v>1.58</v>
@@ -7696,28 +7696,28 @@
         <v>1.21</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CR17" t="n">
         <v>1.36</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CX17" t="n">
         <v>1.56</v>
@@ -7726,31 +7726,31 @@
         <v>1.93</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DB17" t="n">
         <v>1.28</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="DE17" t="n">
         <v>0.12</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="DH17" t="n">
-        <v>96.8</v>
+        <v>97.88</v>
       </c>
       <c r="DI17" t="n">
         <v>-0.04</v>
@@ -7759,28 +7759,28 @@
         <v>1.96</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.36</v>
+        <v>5.34</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="DM17" t="n">
-        <v>48.8</v>
+        <v>49.08</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.24</v>
+        <v>12.38</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.08</v>
+        <v>11.88</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.24</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DS17" t="n">
         <v>0.08</v>
@@ -7792,28 +7792,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>52.32</v>
+        <v>52.58</v>
       </c>
       <c r="DW17" t="n">
         <v>0.16</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.04</v>
+        <v>13</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.48</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.56</v>
+        <v>4.54</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.32</v>
+        <v>19.73</v>
       </c>
       <c r="EB17" t="n">
         <v>1.5</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="18">
@@ -7823,10 +7823,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -7835,61 +7835,61 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="G18" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="H18" t="n">
-        <v>98.42</v>
+        <v>100</v>
       </c>
       <c r="I18" t="n">
         <v>0.08</v>
       </c>
       <c r="J18" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="K18" t="n">
-        <v>4.5</v>
+        <v>5.08</v>
       </c>
       <c r="L18" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="M18" t="n">
-        <v>42.67</v>
+        <v>44.08</v>
       </c>
       <c r="N18" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="P18" t="n">
-        <v>10.17</v>
+        <v>10.23</v>
       </c>
       <c r="Q18" t="n">
-        <v>11.58</v>
+        <v>12</v>
       </c>
       <c r="R18" t="n">
-        <v>7.25</v>
+        <v>7.15</v>
       </c>
       <c r="S18" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="U18" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V18" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>51.17</v>
+        <v>51.92</v>
       </c>
       <c r="Y18" t="n">
         <v>0.08</v>
@@ -7898,19 +7898,19 @@
         <v>12</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.58</v>
+        <v>6.77</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.42</v>
+        <v>5.23</v>
       </c>
       <c r="AC18" t="n">
-        <v>14.92</v>
+        <v>14.77</v>
       </c>
       <c r="AD18" t="n">
         <v>1.45</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7994,70 +7994,70 @@
         <v>2.23</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.84</v>
+        <v>2.73</v>
       </c>
       <c r="BH18" t="n">
-        <v>8.119999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.84</v>
+        <v>2.73</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.48</v>
+        <v>3.31</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.08</v>
+        <v>3.88</v>
       </c>
       <c r="BR18" t="n">
-        <v>92</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="BS18" t="n">
-        <v>72</v>
+        <v>69.23</v>
       </c>
       <c r="BT18" t="n">
-        <v>60</v>
+        <v>57.69</v>
       </c>
       <c r="BU18" t="n">
-        <v>32</v>
+        <v>30.77</v>
       </c>
       <c r="BV18" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="BW18" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX18" t="n">
-        <v>60</v>
+        <v>57.69</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="CA18" t="n">
         <v>3.75</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="CC18" t="n">
         <v>3.43</v>
@@ -8084,13 +8084,13 @@
         <v>1.69</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CN18" t="n">
         <v>1.72</v>
@@ -8102,7 +8102,7 @@
         <v>1.76</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CR18" t="n">
         <v>1.38</v>
@@ -8126,7 +8126,7 @@
         <v>1.7</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.15</v>
@@ -8147,76 +8147,76 @@
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="DH18" t="n">
-        <v>97.16</v>
+        <v>98</v>
       </c>
       <c r="DI18" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.8</v>
+        <v>4.12</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DM18" t="n">
-        <v>41.32</v>
+        <v>42.08</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="DP18" t="n">
-        <v>11.2</v>
+        <v>11.19</v>
       </c>
       <c r="DQ18" t="n">
-        <v>12.44</v>
+        <v>12.62</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.44</v>
+        <v>7.38</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>52.56</v>
+        <v>52.89</v>
       </c>
       <c r="DW18" t="n">
         <v>0.2</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.2</v>
+        <v>11.23</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.72</v>
+        <v>6.81</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.48</v>
+        <v>4.43</v>
       </c>
       <c r="EA18" t="n">
-        <v>16.28</v>
+        <v>16.15</v>
       </c>
       <c r="EB18" t="n">
         <v>1.33</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="19">
@@ -8226,13 +8226,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" t="n">
         <v>13</v>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E19" t="n">
         <v>0.23</v>
@@ -8316,52 +8316,52 @@
         <v>1.38</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AI19" t="n">
-        <v>93.25</v>
+        <v>91.92</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="AL19" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AN19" t="n">
-        <v>43.58</v>
+        <v>43.08</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>15.08</v>
+        <v>14.92</v>
       </c>
       <c r="AR19" t="n">
-        <v>10.75</v>
+        <v>10.69</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.5</v>
+        <v>7.54</v>
       </c>
       <c r="AT19" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.08</v>
+        <v>1.31</v>
       </c>
       <c r="AV19" t="n">
         <v>0.08</v>
@@ -8373,82 +8373,82 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>42.83</v>
+        <v>43.38</v>
       </c>
       <c r="AZ19" t="n">
         <v>0.08</v>
       </c>
       <c r="BA19" t="n">
-        <v>10.75</v>
+        <v>11.38</v>
       </c>
       <c r="BB19" t="n">
-        <v>7</v>
+        <v>7.46</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="BD19" t="n">
-        <v>15.92</v>
+        <v>15.46</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="BF19" t="n">
         <v>3.08</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.720000000000001</v>
+        <v>9.65</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.48</v>
+        <v>0.54</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.12</v>
+        <v>4.19</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.32</v>
+        <v>5.19</v>
       </c>
       <c r="BR19" t="n">
-        <v>92</v>
+        <v>92.31</v>
       </c>
       <c r="BS19" t="n">
-        <v>60</v>
+        <v>61.54</v>
       </c>
       <c r="BT19" t="n">
-        <v>44</v>
+        <v>46.15</v>
       </c>
       <c r="BU19" t="n">
-        <v>24</v>
+        <v>26.92</v>
       </c>
       <c r="BV19" t="n">
-        <v>8</v>
+        <v>11.54</v>
       </c>
       <c r="BW19" t="n">
-        <v>8</v>
+        <v>11.54</v>
       </c>
       <c r="BX19" t="n">
-        <v>40</v>
+        <v>42.31</v>
       </c>
       <c r="BY19" t="n">
         <v>2.54</v>
@@ -8457,16 +8457,16 @@
         <v>2.62</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CB19" t="n">
         <v>3.58</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.31</v>
+        <v>3.21</v>
       </c>
       <c r="CE19" t="n">
         <v>1.38</v>
@@ -8475,7 +8475,7 @@
         <v>2.84</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CH19" t="n">
         <v>1.4</v>
@@ -8490,7 +8490,7 @@
         <v>1.64</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CM19" t="n">
         <v>2.19</v>
@@ -8505,28 +8505,28 @@
         <v>2.01</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="CR19" t="n">
         <v>1.43</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CU19" t="n">
         <v>1.41</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CY19" t="n">
         <v>2.09</v>
@@ -8541,52 +8541,52 @@
         <v>1.35</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="DH19" t="n">
-        <v>91</v>
+        <v>90.42</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.84</v>
+        <v>4.81</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="DM19" t="n">
-        <v>44.44</v>
+        <v>44.16</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.36</v>
+        <v>14.3</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.6</v>
+        <v>11.53</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.72</v>
+        <v>6.77</v>
       </c>
       <c r="DS19" t="n">
         <v>0.16</v>
@@ -8598,28 +8598,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>43.16</v>
+        <v>43.42</v>
       </c>
       <c r="DW19" t="n">
         <v>0.08</v>
       </c>
       <c r="DX19" t="n">
-        <v>13.04</v>
+        <v>13.26</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.6</v>
+        <v>8.77</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.44</v>
+        <v>4.5</v>
       </c>
       <c r="EA19" t="n">
-        <v>17.4</v>
+        <v>17.12</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="n">
         <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
         <v>0.08</v>
@@ -1472,136 +1472,136 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AH2" t="n">
         <v>2</v>
       </c>
       <c r="AI2" t="n">
-        <v>72.84999999999999</v>
+        <v>72.14</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AN2" t="n">
-        <v>29.15</v>
+        <v>29.79</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.23</v>
+        <v>10.93</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.15</v>
+        <v>9.43</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>39.85</v>
+        <v>40.07</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.92</v>
+        <v>8.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.38</v>
+        <v>5.79</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.54</v>
+        <v>2.71</v>
       </c>
       <c r="BD2" t="n">
-        <v>16.08</v>
+        <v>16.21</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.73</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.38</v>
+        <v>0.48</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.27</v>
+        <v>5.3</v>
       </c>
       <c r="BR2" t="n">
-        <v>96.15000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="BS2" t="n">
-        <v>57.69</v>
+        <v>59.26</v>
       </c>
       <c r="BT2" t="n">
-        <v>23.08</v>
+        <v>25.93</v>
       </c>
       <c r="BU2" t="n">
-        <v>15.38</v>
+        <v>18.52</v>
       </c>
       <c r="BV2" t="n">
-        <v>11.54</v>
+        <v>14.81</v>
       </c>
       <c r="BW2" t="n">
-        <v>3.85</v>
+        <v>7.41</v>
       </c>
       <c r="BX2" t="n">
-        <v>30.77</v>
+        <v>33.33</v>
       </c>
       <c r="BY2" t="n">
         <v>3.54</v>
@@ -1610,28 +1610,28 @@
         <v>3.82</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.98</v>
+        <v>4.07</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="CC2" t="n">
-        <v>7.46</v>
+        <v>7.96</v>
       </c>
       <c r="CD2" t="n">
-        <v>7.88</v>
+        <v>8.32</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CI2" t="n">
         <v>1.82</v>
@@ -1646,19 +1646,19 @@
         <v>2.18</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CO2" t="n">
         <v>1.32</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.56</v>
+        <v>3.51</v>
       </c>
       <c r="CR2" t="n">
         <v>1.45</v>
@@ -1673,13 +1673,13 @@
         <v>1.43</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CW2" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CY2" t="n">
         <v>2.11</v>
@@ -1688,64 +1688,64 @@
         <v>2.19</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DB2" t="n">
         <v>1.38</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.16</v>
+        <v>3.11</v>
       </c>
       <c r="DE2" t="n">
         <v>0.04</v>
       </c>
       <c r="DF2" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DH2" t="n">
-        <v>73</v>
+        <v>72.63</v>
       </c>
       <c r="DI2" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.62</v>
+        <v>3.59</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM2" t="n">
-        <v>31.27</v>
+        <v>31.52</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.27</v>
+        <v>11.04</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.38</v>
+        <v>11.22</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.65</v>
+        <v>8.81</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
@@ -1757,22 +1757,22 @@
         <v>0.04</v>
       </c>
       <c r="DX2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="DY2" t="n">
-        <v>5.96</v>
+        <v>6.15</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="EA2" t="n">
-        <v>17.04</v>
+        <v>17.07</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="3">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
         <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="G6" t="n">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
       <c r="H6" t="n">
-        <v>90.31</v>
+        <v>92</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="K6" t="n">
-        <v>6.15</v>
+        <v>6.21</v>
       </c>
       <c r="L6" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>47.31</v>
+        <v>48.29</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="O6" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="P6" t="n">
-        <v>13.46</v>
+        <v>13</v>
       </c>
       <c r="Q6" t="n">
-        <v>13</v>
+        <v>12.43</v>
       </c>
       <c r="R6" t="n">
-        <v>5.54</v>
+        <v>5.64</v>
       </c>
       <c r="S6" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="U6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="V6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>50.08</v>
+        <v>50.57</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="Z6" t="n">
-        <v>15.69</v>
+        <v>16.43</v>
       </c>
       <c r="AA6" t="n">
-        <v>10.15</v>
+        <v>10.64</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.54</v>
+        <v>5.79</v>
       </c>
       <c r="AC6" t="n">
-        <v>17.15</v>
+        <v>17.14</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AF6" t="n">
         <v>0.08</v>
@@ -3162,70 +3162,70 @@
         <v>2.15</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.69</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="BP6" t="n">
         <v>4.15</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.85</v>
+        <v>4.89</v>
       </c>
       <c r="BR6" t="n">
-        <v>96.15000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="BS6" t="n">
-        <v>80.77</v>
+        <v>81.48</v>
       </c>
       <c r="BT6" t="n">
-        <v>65.38</v>
+        <v>66.67</v>
       </c>
       <c r="BU6" t="n">
-        <v>23.08</v>
+        <v>25.93</v>
       </c>
       <c r="BV6" t="n">
-        <v>11.54</v>
+        <v>14.81</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BX6" t="n">
-        <v>50</v>
+        <v>51.85</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.05</v>
+        <v>4.14</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.06</v>
+        <v>4.17</v>
       </c>
       <c r="CC6" t="n">
         <v>2.7</v>
@@ -3237,25 +3237,25 @@
         <v>1.3</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="CH6" t="n">
         <v>1.54</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CK6" t="n">
         <v>1.57</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CM6" t="n">
         <v>2.26</v>
@@ -3267,10 +3267,10 @@
         <v>1.2</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="CR6" t="n">
         <v>1.35</v>
@@ -3285,10 +3285,10 @@
         <v>1.57</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CX6" t="n">
         <v>1.6</v>
@@ -3306,85 +3306,85 @@
         <v>1.27</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="DH6" t="n">
-        <v>91.73</v>
+        <v>92.55</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.81</v>
+        <v>5.85</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="DM6" t="n">
-        <v>46.92</v>
+        <v>47.45</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.31</v>
+        <v>13.07</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.58</v>
+        <v>12.3</v>
       </c>
       <c r="DR6" t="n">
-        <v>5.93</v>
+        <v>5.96</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>49.77</v>
+        <v>50.04</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX6" t="n">
-        <v>15.12</v>
+        <v>15.52</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.880000000000001</v>
+        <v>10.15</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.23</v>
+        <v>5.37</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.65</v>
+        <v>16.66</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="7">

--- a/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_France_Ligue_1_2025-2026.xlsx
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
         <v>13</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>3.71</v>
       </c>
       <c r="H3" t="n">
-        <v>89.45999999999999</v>
+        <v>88.43000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="K3" t="n">
-        <v>5.38</v>
+        <v>5.43</v>
       </c>
       <c r="L3" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="M3" t="n">
-        <v>44.15</v>
+        <v>42.79</v>
       </c>
       <c r="N3" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.38</v>
+        <v>1.71</v>
       </c>
       <c r="P3" t="n">
-        <v>13.15</v>
+        <v>12.93</v>
       </c>
       <c r="Q3" t="n">
-        <v>14.23</v>
+        <v>14.21</v>
       </c>
       <c r="R3" t="n">
-        <v>5.77</v>
+        <v>6.36</v>
       </c>
       <c r="S3" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="T3" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="U3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="V3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>41.46</v>
+        <v>41.64</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.38</v>
+        <v>11.36</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.08</v>
+        <v>7.79</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.31</v>
+        <v>3.57</v>
       </c>
       <c r="AC3" t="n">
-        <v>17.77</v>
+        <v>17.93</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AF3" t="n">
         <v>0.23</v>
@@ -1953,70 +1953,70 @@
         <v>2.38</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.539999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BO3" t="n">
         <v>1</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.69</v>
+        <v>3.81</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.85</v>
+        <v>5.7</v>
       </c>
       <c r="BR3" t="n">
-        <v>84.62</v>
+        <v>85.19</v>
       </c>
       <c r="BS3" t="n">
-        <v>53.85</v>
+        <v>55.56</v>
       </c>
       <c r="BT3" t="n">
-        <v>38.46</v>
+        <v>40.74</v>
       </c>
       <c r="BU3" t="n">
-        <v>23.08</v>
+        <v>22.22</v>
       </c>
       <c r="BV3" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BW3" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BX3" t="n">
-        <v>34.62</v>
+        <v>33.33</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.69</v>
+        <v>3.59</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.95</v>
+        <v>3.83</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.83</v>
+        <v>3.81</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.82</v>
+        <v>3.79</v>
       </c>
       <c r="CC3" t="n">
         <v>5.04</v>
@@ -2025,13 +2025,13 @@
         <v>5.25</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
     